--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5145CC62-BDC3-1A4C-8EC9-0E89CEF1F61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03E3A58-A324-684D-B93A-B460BCE514DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="514">
   <si>
     <t>User story</t>
   </si>
@@ -1314,9 +1314,6 @@
     <t>RF15e-08: Unit tests: index vacío → build, rebuild sin cambios, rebuild con cambio, search devuelve metadata</t>
   </si>
   <si>
-    <t>RF15e-09: Integrar build_index en pipeline (RF14) y en trigger (RF14c) para reindex automático</t>
-  </si>
-  <si>
     <t>RF15e-10: Docs: docs/rag_kb.md con cómo añadir docs, reconstruir índice y ejemplos de búsqueda</t>
   </si>
   <si>
@@ -1434,9 +1431,6 @@
     <t>RF14c-17: Crear Task Definition Fargate: cpu/mem, env vars, secrets, logConfiguration, ephemeralStorage (si hace falta), command 'python -m ... run'</t>
   </si>
   <si>
-    <t>AG03-01: Crear docs/codex_workflow.md con reglas: qué se permite generar, qué se revisa a mano, checklist de aceptación</t>
-  </si>
-  <si>
     <t>AG03-02: Definir plantilla de prompt para AlphaCodium: objetivo, constraints (allowlist, no inventar columnas), output esperado</t>
   </si>
   <si>
@@ -1449,9 +1443,6 @@
     <t>AG03-05: Integrar en CI: ejecutar pytest + lint + schema validation + (opcional) dry-run del grafo con stubs</t>
   </si>
   <si>
-    <t>AG03-06: Definir cómo registrar evidencias de iteraciones con Codex (ejemplos: prompt→diff→validación)</t>
-  </si>
-  <si>
     <t>AG03-07: Definir 'AlphaCodium Loop' (Plan→Draft→Validate→Repair) como estándar para nodos LLM (hypothesis/test/explain/score)</t>
   </si>
   <si>
@@ -1473,9 +1464,6 @@
     <t>AG03 — Workflow AlphaCodium con aprobación humana (sin autonomía)</t>
   </si>
   <si>
-    <t>AG03 — Workflow AlphaCodium/Codex para construir el grafo y prompts (con aprobación humana)</t>
-  </si>
-  <si>
     <t>[AlphaCodium] Adoptar AlphaCodium como metodología y patrón de orquestación para agentes: cada nodo LLM usa un bucle Plan→Draft→Validate→Repair (con validadores) y se versionan prompts. Se guardan evidencias de iteraciones (prompt→output→errores→fix) para defensa y trazabilidad.</t>
   </si>
   <si>
@@ -1540,13 +1528,61 @@
   </si>
   <si>
     <t>RF18-13: Ejecutar verificación de criterios de aceptación y guardar evidencia (artefactos + enlace de traza LangSmith + logs/reportes)</t>
+  </si>
+  <si>
+    <t>AG03-13: Escribir/actualizar tests unitarios relacionados (pytest) para este requisito</t>
+  </si>
+  <si>
+    <t>AG03-14: Actualizar documentación (README + runbook/docs) describiendo el comportamiento y cómo verificarlo</t>
+  </si>
+  <si>
+    <t>AG03-15: Ejecutar verificación de criterios de aceptación y guardar evidencia (artefactos + enlace de traza LangSmith + logs/reportes)</t>
+  </si>
+  <si>
+    <t>AG03 — Workflow AlphaCodium para construir el grafo y prompts (con aprobación humana)</t>
+  </si>
+  <si>
+    <t>AG03-01: Crear docs/alphacodium_workflow.md con reglas: qué se permite generar, qué se revisa a mano, checklist de aceptación</t>
+  </si>
+  <si>
+    <t>AG03-06: Definir cómo registrar evidencias de iteraciones con Alphacodium (ejemplos: prompt→diff→validación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF15e-09: Integrar build_index en pipeline (RF14) y en trigger (RF14c) para reindex automático </t>
+  </si>
+  <si>
+    <t>RF13-14: Definir catálogo de red flags (`config/red_flags_mapping.yaml`) a partir de `red_flags_final.pdf` con `red_flag_id`,</t>
+  </si>
+  <si>
+    <t>RF13-16: Añadir validación automática de red flags (cada `red_flag_id` debe existir en mapping y ser coherente con `fraud_type`)</t>
+  </si>
+  <si>
+    <t>RF13-15: Extender TestSpec para incluir `red_flag_id` y rellenarlo en todos los tests del catálogo RF13</t>
+  </si>
+  <si>
+    <t>RF13-17: Actualizar reporte para incluir sección `Red Flags activadas` (test_id, red_flag_id, evidencia y explicación mínima)</t>
+  </si>
+  <si>
+    <t>RF13-18: Actualizar pipeline de github</t>
+  </si>
+  <si>
+    <t>RF14-15: Escribir/actualizar tests de integración (pytest) para este requisito</t>
+  </si>
+  <si>
+    <t>RF14-16: Actualizar documentación (README + runbook/docs) describiendo el comportamiento y cómo verificarlo</t>
+  </si>
+  <si>
+    <t>RF14-17: Ejecutar verificación de criterios de aceptación y guardar evidencia (artefactos + enlace de traza LangSmith + logs/reportes)</t>
+  </si>
+  <si>
+    <t>RF14-18:Actualización pipeline Github</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1583,6 +1619,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1706,7 +1749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1759,20 +1802,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1796,27 +1829,57 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2073,19 +2136,19 @@
   <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.1640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.1640625" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="101.5" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="95.1640625" style="8" customWidth="1"/>
     <col min="4" max="4" width="15.5" style="8" customWidth="1"/>
     <col min="5" max="5" width="11.83203125" style="8" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="8" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" style="44" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" style="8" customWidth="1"/>
     <col min="9" max="9" width="3.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2104,7 +2167,7 @@
       <c r="F1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="41" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -2133,6 +2196,7 @@
       <c r="F2" t="s">
         <v>81</v>
       </c>
+      <c r="G2" s="42"/>
     </row>
     <row r="3" spans="1:9" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
@@ -2153,6 +2217,7 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
+      <c r="G3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
@@ -2173,10 +2238,12 @@
       <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="40">
+        <v>46094</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2198,10 +2265,12 @@
       <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="40">
+        <v>46094</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2223,10 +2292,12 @@
       <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="40">
+        <v>46094</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2248,10 +2319,12 @@
       <c r="F7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="40">
+        <v>46094</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2273,10 +2346,12 @@
       <c r="F8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="40">
+        <v>46094</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2298,10 +2373,12 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="40">
+        <v>46094</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2323,10 +2400,12 @@
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="40">
+        <v>46094</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2348,10 +2427,12 @@
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="40">
+        <v>46094</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2373,10 +2454,12 @@
       <c r="F12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="40">
+        <v>46094</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="34" x14ac:dyDescent="0.2">
@@ -2398,7 +2481,7 @@
       <c r="F13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="40"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
@@ -2421,10 +2504,12 @@
       <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="40">
+        <v>46094</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" x14ac:dyDescent="0.2">
@@ -2434,7 +2519,7 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="G15" s="40"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
@@ -2457,7 +2542,7 @@
       <c r="F16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="40"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
@@ -2480,18 +2565,18 @@
       <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="40"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D18" s="5">
@@ -2503,18 +2588,18 @@
       <c r="F18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="23" t="s">
         <v>349</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="23" t="s">
         <v>350</v>
       </c>
       <c r="D19" s="14">
@@ -2526,18 +2611,18 @@
       <c r="F19" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="14"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="22" t="s">
         <v>351</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="23" t="s">
         <v>353</v>
       </c>
       <c r="D20" s="14">
@@ -2549,19 +2634,19 @@
       <c r="F20" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="14"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>446</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>447</v>
       </c>
       <c r="D21" s="14">
         <v>13</v>
@@ -2572,18 +2657,18 @@
       <c r="F21" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="14"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="22" t="s">
         <v>355</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="23" t="s">
         <v>356</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="23" t="s">
         <v>357</v>
       </c>
       <c r="D22" s="14">
@@ -2595,18 +2680,18 @@
       <c r="F22" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="14"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="22" t="s">
         <v>358</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="23" t="s">
         <v>359</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="23" t="s">
         <v>360</v>
       </c>
       <c r="D23" s="14">
@@ -2618,18 +2703,18 @@
       <c r="F23" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="14"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="24" t="s">
         <v>362</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="24" t="s">
         <v>363</v>
       </c>
       <c r="D24" s="14">
@@ -2641,18 +2726,18 @@
       <c r="F24" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="14"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="22" t="s">
         <v>364</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="23" t="s">
         <v>366</v>
       </c>
       <c r="D25" s="14">
@@ -2664,7 +2749,7 @@
       <c r="F25" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="14"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
     </row>
@@ -2687,7 +2772,7 @@
       <c r="F26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="5"/>
+      <c r="G26" s="40"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
@@ -2698,7 +2783,7 @@
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="G27" s="40"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
     </row>
@@ -2721,18 +2806,18 @@
       <c r="F28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="5"/>
+      <c r="G28" s="40"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="22" t="s">
         <v>367</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="23" t="s">
         <v>368</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="23" t="s">
         <v>369</v>
       </c>
       <c r="D29" s="14">
@@ -2744,7 +2829,7 @@
       <c r="F29" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="14"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
     </row>
@@ -2767,7 +2852,7 @@
       <c r="F30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30" s="40"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
@@ -2790,7 +2875,7 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="5"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
     </row>
@@ -2813,7 +2898,7 @@
       <c r="F32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="5"/>
+      <c r="G32" s="40"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
@@ -2836,7 +2921,7 @@
       <c r="F33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="5"/>
+      <c r="G33" s="40"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
     </row>
@@ -2859,7 +2944,7 @@
       <c r="F34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="5"/>
+      <c r="G34" s="40"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
@@ -2882,7 +2967,7 @@
       <c r="F35" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="5"/>
+      <c r="G35" s="40"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
     </row>
@@ -2905,7 +2990,7 @@
       <c r="F36" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="5"/>
+      <c r="G36" s="40"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
@@ -2928,19 +3013,19 @@
       <c r="F37" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="5"/>
+      <c r="G37" s="40"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
     </row>
-    <row r="38" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="16" t="s">
-        <v>479</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>481</v>
+    <row r="38" spans="1:9" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="29" t="s">
+        <v>501</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>476</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>477</v>
       </c>
       <c r="D38" s="14">
         <v>5</v>
@@ -2951,7 +3036,7 @@
       <c r="F38" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="14"/>
+      <c r="G38" s="43"/>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
     </row>
@@ -2974,7 +3059,7 @@
       <c r="F39" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="5"/>
+      <c r="G39" s="40"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
     </row>
@@ -2997,7 +3082,7 @@
       <c r="F40" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G40" s="5"/>
+      <c r="G40" s="40"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
     </row>
@@ -3068,30 +3153,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:E436"/>
+  <dimension ref="A2:E445"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="71.33203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.33203125" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="71.33203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.33203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="35" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3099,7 +3185,7 @@
       <c r="A3" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="31" t="s">
         <v>334</v>
       </c>
       <c r="C3" s="14">
@@ -3110,7 +3196,7 @@
     </row>
     <row r="4" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="31" t="s">
         <v>335</v>
       </c>
       <c r="C4" s="14">
@@ -3121,7 +3207,7 @@
     </row>
     <row r="5" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="31" t="s">
         <v>336</v>
       </c>
       <c r="C5" s="14">
@@ -3132,7 +3218,7 @@
     </row>
     <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="31" t="s">
         <v>337</v>
       </c>
       <c r="C6" s="14">
@@ -3143,7 +3229,7 @@
     </row>
     <row r="7" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="31" t="s">
         <v>338</v>
       </c>
       <c r="C7" s="14">
@@ -3154,7 +3240,7 @@
     </row>
     <row r="8" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="31" t="s">
         <v>339</v>
       </c>
       <c r="C8" s="14">
@@ -3167,7 +3253,7 @@
       <c r="A9" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="31" t="s">
         <v>346</v>
       </c>
       <c r="C9" s="14">
@@ -3178,7 +3264,7 @@
     </row>
     <row r="10" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="16"/>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="31" t="s">
         <v>340</v>
       </c>
       <c r="C10" s="14">
@@ -3189,7 +3275,7 @@
     </row>
     <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="31" t="s">
         <v>341</v>
       </c>
       <c r="C11" s="14">
@@ -3200,7 +3286,7 @@
     </row>
     <row r="12" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="16"/>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="31" t="s">
         <v>342</v>
       </c>
       <c r="C12" s="14">
@@ -3211,7 +3297,7 @@
     </row>
     <row r="13" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="16"/>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="31" t="s">
         <v>343</v>
       </c>
       <c r="C13" s="14">
@@ -3222,7 +3308,7 @@
     </row>
     <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="16"/>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="31" t="s">
         <v>344</v>
       </c>
       <c r="C14" s="14">
@@ -3233,7 +3319,7 @@
     </row>
     <row r="15" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="31" t="s">
         <v>345</v>
       </c>
       <c r="C15" s="14">
@@ -3242,1955 +3328,2029 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="8">
         <v>0.5</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="8">
         <v>0.5</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="8">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="8">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="C22">
-        <v>1.5</v>
-      </c>
-      <c r="D22">
+      <c r="C22" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D22" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="8">
         <v>2</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
+      <c r="C24" s="8">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8">
         <v>0.75</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="8">
         <v>0.7</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="8">
         <v>1.2</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="8">
         <v>0.8</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="C28">
-        <v>1.5</v>
-      </c>
-      <c r="D28">
+      <c r="C28" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B29" s="32" t="s">
+    <row r="29" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C29">
-        <v>1.5</v>
-      </c>
-      <c r="D29">
+      <c r="C29" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D29" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B30" s="32" t="s">
+    <row r="30" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="8">
         <v>1.2</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="8">
         <v>1.2</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="8">
         <v>1.2</v>
       </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B33" s="32" t="s">
+      <c r="D32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B33" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="C33">
-        <v>1.5</v>
-      </c>
-      <c r="D33">
+      <c r="C33" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D33" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+      <c r="D35" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="32"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="22" t="s">
+      <c r="B36" s="28"/>
+    </row>
+    <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="36" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="8">
         <v>0.8</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+      <c r="D39" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+      <c r="D40" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="8">
         <v>0.7</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B43" s="32" t="s">
+      <c r="B43" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="8">
         <v>1.2</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B44" s="32" t="s">
+      <c r="B44" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="8">
         <v>0.8</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="C45">
-        <v>1.5</v>
-      </c>
-      <c r="D45">
+      <c r="C45" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D45" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C46">
-        <v>1.5</v>
-      </c>
-      <c r="D46">
+      <c r="C46" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D46" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+      <c r="D47" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B49" s="32"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="22" t="s">
+      <c r="B49" s="28"/>
+    </row>
+    <row r="50" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A50" s="36" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" s="32" t="s">
+      <c r="B51" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="8">
         <v>0.8</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="8">
         <v>0.8</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="8">
         <v>0.8</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B54" s="32" t="s">
+      <c r="B54" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="8">
         <v>1.2</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B55" s="32" t="s">
+      <c r="B55" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
+      <c r="C55" s="8">
+        <v>1</v>
+      </c>
+      <c r="D55" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="32" t="s">
+      <c r="B56" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56">
+      <c r="C56" s="8">
+        <v>1</v>
+      </c>
+      <c r="D56" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B57" s="32" t="s">
+      <c r="B57" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
+      <c r="C57" s="8">
+        <v>1</v>
+      </c>
+      <c r="D57" s="8">
         <v>0.7</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="8">
         <v>1.2</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="8">
         <v>0.7</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="32" t="s">
+      <c r="B59" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="8">
         <v>0.7</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="8">
         <v>0.7</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B60" s="32" t="s">
+      <c r="B60" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="C60">
-        <v>1.5</v>
-      </c>
-      <c r="D60">
+      <c r="C60" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61">
+      <c r="C61" s="8">
+        <v>1</v>
+      </c>
+      <c r="D61" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B62" s="32" t="s">
+      <c r="B62" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62">
+      <c r="C62" s="8">
+        <v>1</v>
+      </c>
+      <c r="D62" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B63" s="32"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="22" t="s">
+      <c r="B63" s="28"/>
+    </row>
+    <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A64" s="36" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B65" s="32" t="s">
+      <c r="B65" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="C65">
-        <v>1</v>
-      </c>
-      <c r="D65">
+      <c r="C65" s="8">
+        <v>1</v>
+      </c>
+      <c r="D65" s="8">
         <v>0.3</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B66" s="32" t="s">
+      <c r="B66" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="8">
         <v>0.8</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B67" s="32" t="s">
+      <c r="B67" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="8">
         <v>1.2</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="32" t="s">
+      <c r="B68" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
+      <c r="C68" s="8">
+        <v>1</v>
+      </c>
+      <c r="D68" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="32" t="s">
+      <c r="B69" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="8">
         <v>2</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B70" s="32" t="s">
+      <c r="B70" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="8">
         <v>2</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B71" s="32" t="s">
+      <c r="B71" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="8">
         <v>0.8</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B72" s="32" t="s">
+      <c r="B72" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="8">
         <v>0.8</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B73" s="32" t="s">
+      <c r="B73" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="C73">
-        <v>1.5</v>
-      </c>
-      <c r="D73">
+      <c r="C73" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D73" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B74" s="32" t="s">
+      <c r="B74" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74">
+      <c r="C74" s="8">
+        <v>1</v>
+      </c>
+      <c r="D74" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B75" s="32" t="s">
+      <c r="B75" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75">
+      <c r="C75" s="8">
+        <v>1</v>
+      </c>
+      <c r="D75" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A76"/>
-      <c r="B76" s="31" t="s">
-        <v>482</v>
-      </c>
-      <c r="C76">
+      <c r="A76" s="8"/>
+      <c r="B76" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="C76" s="8">
         <v>0.8</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B77" s="32"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="22" t="s">
+      <c r="B77" s="28"/>
+    </row>
+    <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A78" s="36" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B79" s="32" t="s">
+      <c r="B79" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="8">
         <v>1.2</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B80" s="32" t="s">
+      <c r="B80" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="8">
         <v>0.8</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B81" s="32" t="s">
+      <c r="B81" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="8">
         <v>0.8</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B82" s="32" t="s">
+      <c r="B82" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
+      <c r="C82" s="8">
+        <v>1</v>
+      </c>
+      <c r="D82" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B83" s="32" t="s">
+      <c r="B83" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="C83">
-        <v>1.5</v>
-      </c>
-      <c r="D83">
+      <c r="C83" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D83" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B84" s="32" t="s">
+      <c r="B84" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
+      <c r="C84" s="8">
+        <v>1</v>
+      </c>
+      <c r="D84" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B85" s="32" t="s">
+      <c r="B85" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="8">
         <v>0.8</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B86" s="32" t="s">
+      <c r="B86" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="C86">
-        <v>1.5</v>
-      </c>
-      <c r="D86">
+      <c r="C86" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D86" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B87" s="32" t="s">
+      <c r="B87" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87">
+      <c r="C87" s="8">
+        <v>1</v>
+      </c>
+      <c r="D87" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B88" s="32" t="s">
+      <c r="B88" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
+      <c r="C88" s="8">
+        <v>1</v>
+      </c>
+      <c r="D88" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B89" s="32"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="22" t="s">
+      <c r="B89" s="28"/>
+    </row>
+    <row r="90" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A90" s="36" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B91" s="32" t="s">
+      <c r="B91" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="C91">
-        <v>1</v>
-      </c>
-      <c r="D91">
+      <c r="C91" s="8">
+        <v>1</v>
+      </c>
+      <c r="D91" s="8">
         <v>1.2</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B92" s="32" t="s">
+      <c r="B92" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="8">
         <v>1.2</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B93" s="32" t="s">
+      <c r="B93" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="8">
         <v>0.8</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B94" s="32" t="s">
+      <c r="B94" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94">
+      <c r="C94" s="8">
+        <v>1</v>
+      </c>
+      <c r="D94" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B95" s="32" t="s">
+      <c r="B95" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C95">
-        <v>1</v>
-      </c>
-      <c r="D95">
+      <c r="C95" s="8">
+        <v>1</v>
+      </c>
+      <c r="D95" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B96" s="32" t="s">
+      <c r="B96" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="8">
         <v>0.8</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B97" s="32" t="s">
+      <c r="B97" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="C97">
-        <v>1.5</v>
-      </c>
-      <c r="D97">
+      <c r="C97" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D97" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B98" s="32" t="s">
+      <c r="B98" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-      <c r="D98">
+      <c r="C98" s="8">
+        <v>1</v>
+      </c>
+      <c r="D98" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B99" s="32" t="s">
+      <c r="B99" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-      <c r="D99">
+      <c r="C99" s="8">
+        <v>1</v>
+      </c>
+      <c r="D99" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B100" s="32"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="22" t="s">
+      <c r="B100" s="28"/>
+    </row>
+    <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A101" s="36" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B102" s="32" t="s">
+      <c r="B102" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="C102">
-        <v>1</v>
-      </c>
-      <c r="D102">
+      <c r="C102" s="8">
+        <v>1</v>
+      </c>
+      <c r="D102" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B103" s="32" t="s">
+      <c r="B103" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="8">
         <v>1.2</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B104" s="32" t="s">
+      <c r="B104" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="C104">
-        <v>1.5</v>
-      </c>
-      <c r="D104">
+      <c r="C104" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D104" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B105" s="32" t="s">
+      <c r="B105" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="8">
         <v>0.8</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B106" s="32" t="s">
+      <c r="B106" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="8">
         <v>1.2</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B107" s="32" t="s">
+      <c r="B107" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="8">
         <v>0.7</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B108" s="32" t="s">
+      <c r="B108" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="C108">
-        <v>1.5</v>
-      </c>
-      <c r="D108">
+      <c r="C108" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D108" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B109" s="32" t="s">
+      <c r="B109" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="C109">
-        <v>1.5</v>
-      </c>
-      <c r="D109">
+      <c r="C109" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D109" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B110" s="32" t="s">
+      <c r="B110" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-      <c r="D110">
+      <c r="C110" s="8">
+        <v>1</v>
+      </c>
+      <c r="D110" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B111" s="32" t="s">
+      <c r="B111" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="C111">
-        <v>1</v>
-      </c>
-      <c r="D111">
+      <c r="C111" s="8">
+        <v>1</v>
+      </c>
+      <c r="D111" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B112" s="32"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="22" t="s">
+      <c r="B112" s="28"/>
+    </row>
+    <row r="113" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A113" s="36" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B114" s="32" t="s">
+      <c r="B114" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="8">
         <v>0.8</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B115" s="32" t="s">
+      <c r="B115" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="8">
         <v>1.2</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B116" s="32" t="s">
+      <c r="B116" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="8">
         <v>1.2</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B117" s="32" t="s">
+      <c r="B117" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="C117">
-        <v>1</v>
-      </c>
-      <c r="D117">
+      <c r="C117" s="8">
+        <v>1</v>
+      </c>
+      <c r="D117" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B118" s="32" t="s">
+      <c r="B118" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="8">
         <v>0.6</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B119" s="32" t="s">
+      <c r="B119" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="8">
         <v>1.2</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B120" s="32" t="s">
+      <c r="B120" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="C120">
-        <v>1</v>
-      </c>
-      <c r="D120">
+      <c r="C120" s="8">
+        <v>1</v>
+      </c>
+      <c r="D120" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B121" s="32" t="s">
+      <c r="B121" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="C121">
-        <v>1</v>
-      </c>
-      <c r="D121">
+      <c r="C121" s="8">
+        <v>1</v>
+      </c>
+      <c r="D121" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B122" s="32"/>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="22" t="s">
+      <c r="B122" s="28"/>
+    </row>
+    <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A123" s="36" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B124" s="32" t="s">
+      <c r="B124" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="C124">
-        <v>1</v>
-      </c>
-      <c r="D124">
+      <c r="C124" s="8">
+        <v>1</v>
+      </c>
+      <c r="D124" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B125" s="32" t="s">
+      <c r="B125" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="8">
         <v>1.2</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B126" s="32" t="s">
+      <c r="B126" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="8">
         <v>1.2</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B127" s="32" t="s">
+      <c r="B127" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="C127">
-        <v>1</v>
-      </c>
-      <c r="D127">
+      <c r="C127" s="8">
+        <v>1</v>
+      </c>
+      <c r="D127" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B128" s="32" t="s">
+      <c r="B128" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="8">
         <v>0.8</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B129" s="32" t="s">
+      <c r="B129" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="8">
         <v>0.8</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B130" s="32" t="s">
+      <c r="B130" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="8">
         <v>0.8</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B131" s="32" t="s">
+      <c r="B131" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="C131">
-        <v>1.5</v>
-      </c>
-      <c r="D131">
+      <c r="C131" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D131" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B132" s="32" t="s">
+      <c r="B132" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="C132">
-        <v>1</v>
-      </c>
-      <c r="D132">
+      <c r="C132" s="8">
+        <v>1</v>
+      </c>
+      <c r="D132" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B133" s="32" t="s">
+      <c r="B133" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="C133">
-        <v>1</v>
-      </c>
-      <c r="D133">
+      <c r="C133" s="8">
+        <v>1</v>
+      </c>
+      <c r="D133" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B134" s="32"/>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" s="22" t="s">
+      <c r="B134" s="28"/>
+    </row>
+    <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A135" s="36" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B136" s="32" t="s">
+      <c r="B136" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B137" s="32" t="s">
+      <c r="B137" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B138" s="32" t="s">
+      <c r="B138" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B139" s="32" t="s">
+      <c r="B139" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="8">
         <v>1.2</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B140" s="32" t="s">
+      <c r="B140" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B141" s="32" t="s">
+      <c r="B141" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B142" s="32" t="s">
+      <c r="B142" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B143" s="32" t="s">
+      <c r="B143" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B144" s="32" t="s">
+      <c r="B144" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B145" s="32" t="s">
+      <c r="B145" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B146" s="32"/>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A147" s="22" t="s">
+      <c r="B146" s="28"/>
+    </row>
+    <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A147" s="36" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B148" s="32" t="s">
+      <c r="B148" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="8">
         <v>2</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B149" s="32" t="s">
+      <c r="B149" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="8">
         <v>1.2</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B150" s="32" t="s">
+      <c r="B150" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="C150">
-        <v>1</v>
-      </c>
-      <c r="D150">
+      <c r="C150" s="8">
+        <v>1</v>
+      </c>
+      <c r="D150" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B151" s="32" t="s">
+      <c r="B151" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="C151">
-        <v>1.5</v>
-      </c>
-      <c r="D151">
+      <c r="C151" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D151" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B152" s="32" t="s">
+      <c r="B152" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="8">
         <v>0.8</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B153" s="32" t="s">
+      <c r="B153" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="C153">
-        <v>1.5</v>
-      </c>
-      <c r="D153">
+      <c r="C153" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D153" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B154" s="32" t="s">
+      <c r="B154" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="C154">
-        <v>1</v>
-      </c>
-      <c r="D154">
+      <c r="C154" s="8">
+        <v>1</v>
+      </c>
+      <c r="D154" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B155" s="32" t="s">
+      <c r="B155" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="C155">
-        <v>1</v>
-      </c>
-      <c r="D155">
+      <c r="C155" s="8">
+        <v>1</v>
+      </c>
+      <c r="D155" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B156" s="32"/>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A157" s="22" t="s">
+      <c r="B156" s="28"/>
+    </row>
+    <row r="157" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A157" s="36" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B158" s="32" t="s">
+      <c r="B158" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B159" s="32" t="s">
+      <c r="B159" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="8">
         <v>1.2</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B160" s="32" t="s">
+      <c r="B160" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B161" s="32" t="s">
+      <c r="B161" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B162" s="32" t="s">
+      <c r="B162" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B163" s="32" t="s">
+      <c r="B163" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B164" s="32" t="s">
+      <c r="B164" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B165" s="32" t="s">
+      <c r="B165" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B166" s="32" t="s">
+      <c r="B166" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B167" s="32"/>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A168" s="22" t="s">
+      <c r="B167" s="28"/>
+    </row>
+    <row r="168" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A168" s="36" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B169" s="32" t="s">
+      <c r="B169" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="8">
         <v>1.2</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B170" s="32" t="s">
+      <c r="B170" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B171" s="32" t="s">
+      <c r="B171" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B172" s="32" t="s">
+      <c r="B172" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B173" s="32" t="s">
+      <c r="B173" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="8">
         <v>1.2</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B174" s="32" t="s">
+      <c r="B174" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B175" s="32" t="s">
+      <c r="B175" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B176" s="32" t="s">
+      <c r="B176" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B177" s="32"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B177" s="28"/>
+    </row>
+    <row r="178" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="38" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B179" s="32" t="s">
+      <c r="B179" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="C179">
-        <v>1.5</v>
+      <c r="C179" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D179" s="8">
+        <v>0.8</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B180" s="32" t="s">
+      <c r="B180" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="8">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B181" s="32" t="s">
+      <c r="D180" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B181" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="8">
         <v>1.2</v>
       </c>
+      <c r="D181" s="8">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="182" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B182" s="32" t="s">
+      <c r="B182" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="C182">
+      <c r="C182" s="8">
         <v>0.6</v>
       </c>
+      <c r="D182" s="8">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="183" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B183" s="32" t="s">
+      <c r="B183" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="8">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B184" s="32" t="s">
+      <c r="D183" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B184" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="C184">
+      <c r="C184" s="8">
         <v>2</v>
       </c>
+      <c r="D184" s="8">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="185" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B185" s="32" t="s">
+      <c r="B185" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B186" s="32" t="s">
+      <c r="B186" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="C186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B187" s="32" t="s">
+      <c r="C186" s="8">
+        <v>1</v>
+      </c>
+      <c r="D186" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B187" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="C187">
-        <v>1</v>
+      <c r="C187" s="8">
+        <v>1</v>
+      </c>
+      <c r="D187" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A188" s="14"/>
-      <c r="B188" s="32" t="s">
-        <v>483</v>
+      <c r="B188" s="28" t="s">
+        <v>479</v>
       </c>
       <c r="C188" s="14">
         <v>1</v>
       </c>
-      <c r="D188" s="14"/>
+      <c r="D188" s="14">
+        <v>1</v>
+      </c>
       <c r="E188" s="14"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A189" s="14"/>
-      <c r="B189" s="32"/>
-      <c r="C189" s="14"/>
-      <c r="D189" s="14"/>
+      <c r="B189" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="C189" s="14">
+        <v>1</v>
+      </c>
+      <c r="D189" s="14">
+        <v>1</v>
+      </c>
       <c r="E189" s="14"/>
     </row>
     <row r="190" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A190" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="B190" s="32" t="s">
-        <v>370</v>
+      <c r="A190" s="14"/>
+      <c r="B190" s="28" t="s">
+        <v>507</v>
       </c>
       <c r="C190" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D190" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D190" s="14">
+        <v>1.2</v>
+      </c>
       <c r="E190" s="14"/>
     </row>
-    <row r="191" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="16"/>
-      <c r="B191" s="32" t="s">
-        <v>371</v>
+    <row r="191" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A191" s="14"/>
+      <c r="B191" s="28" t="s">
+        <v>506</v>
       </c>
       <c r="C191" s="14">
-        <v>1</v>
-      </c>
-      <c r="D191" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D191" s="14">
+        <v>1.2</v>
+      </c>
       <c r="E191" s="14"/>
     </row>
-    <row r="192" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="16"/>
-      <c r="B192" s="32" t="s">
-        <v>372</v>
+    <row r="192" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A192" s="14"/>
+      <c r="B192" s="28" t="s">
+        <v>508</v>
       </c>
       <c r="C192" s="14">
         <v>1</v>
       </c>
-      <c r="D192" s="14"/>
+      <c r="D192" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E192" s="14"/>
     </row>
-    <row r="193" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="23"/>
-      <c r="B193" s="35" t="s">
-        <v>373</v>
+    <row r="193" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A193" s="14"/>
+      <c r="B193" s="28" t="s">
+        <v>509</v>
       </c>
       <c r="C193" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D193" s="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="D193" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E193" s="14"/>
     </row>
-    <row r="194" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="16"/>
-      <c r="B194" s="32" t="s">
-        <v>374</v>
-      </c>
-      <c r="C194" s="14">
-        <v>2</v>
-      </c>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A194" s="14"/>
+      <c r="B194" s="8"/>
+      <c r="C194" s="14"/>
       <c r="D194" s="14"/>
       <c r="E194" s="14"/>
     </row>
-    <row r="195" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="B195" s="32" t="s">
-        <v>375</v>
+    <row r="195" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A195" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="B195" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="C195" s="14">
         <v>1.5</v>
       </c>
-      <c r="D195" s="14"/>
+      <c r="D195" s="14">
+        <v>1</v>
+      </c>
       <c r="E195" s="14"/>
     </row>
     <row r="196" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="16"/>
-      <c r="B196" s="32" t="s">
-        <v>376</v>
+      <c r="B196" s="28" t="s">
+        <v>371</v>
       </c>
       <c r="C196" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D196" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D196" s="14">
+        <v>1</v>
+      </c>
       <c r="E196" s="14"/>
     </row>
     <row r="197" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="16"/>
-      <c r="B197" s="32" t="s">
-        <v>377</v>
+      <c r="B197" s="28" t="s">
+        <v>372</v>
       </c>
       <c r="C197" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D197" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D197" s="14">
+        <v>1</v>
+      </c>
       <c r="E197" s="14"/>
     </row>
-    <row r="198" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="16"/>
-      <c r="B198" s="32" t="s">
-        <v>378</v>
+    <row r="198" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A198" s="19"/>
+      <c r="B198" s="31" t="s">
+        <v>373</v>
       </c>
       <c r="C198" s="14">
         <v>1.5</v>
       </c>
-      <c r="D198" s="14"/>
+      <c r="D198" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E198" s="14"/>
     </row>
     <row r="199" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="16"/>
-      <c r="B199" s="32" t="s">
-        <v>379</v>
+      <c r="B199" s="28" t="s">
+        <v>374</v>
       </c>
       <c r="C199" s="14">
-        <v>1</v>
-      </c>
-      <c r="D199" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="D199" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E199" s="14"/>
     </row>
     <row r="200" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="16"/>
-      <c r="B200" s="32" t="s">
-        <v>380</v>
+      <c r="A200" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B200" s="28" t="s">
+        <v>375</v>
       </c>
       <c r="C200" s="14">
-        <v>2</v>
-      </c>
-      <c r="D200" s="14"/>
+        <v>1.5</v>
+      </c>
+      <c r="D200" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E200" s="14"/>
     </row>
     <row r="201" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="16"/>
-      <c r="B201" s="32" t="s">
-        <v>381</v>
+      <c r="B201" s="28" t="s">
+        <v>376</v>
       </c>
       <c r="C201" s="14">
-        <v>1</v>
-      </c>
-      <c r="D201" s="14"/>
+        <v>1.5</v>
+      </c>
+      <c r="D201" s="14">
+        <v>3</v>
+      </c>
       <c r="E201" s="14"/>
     </row>
     <row r="202" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="16"/>
-      <c r="B202" s="32" t="s">
-        <v>382</v>
+      <c r="B202" s="28" t="s">
+        <v>377</v>
       </c>
       <c r="C202" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D202" s="14">
+        <v>2</v>
+      </c>
+      <c r="E202" s="14"/>
+    </row>
+    <row r="203" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="16"/>
+      <c r="B203" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="C203" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D203" s="14">
         <v>2.5</v>
       </c>
-      <c r="D202" s="14"/>
-      <c r="E202" s="14"/>
-    </row>
-    <row r="203" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="23"/>
-      <c r="B203" s="35" t="s">
-        <v>383</v>
-      </c>
-      <c r="C203" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D203" s="14"/>
       <c r="E203" s="14"/>
     </row>
     <row r="204" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="16"/>
-      <c r="B204" s="32"/>
-      <c r="C204" s="14"/>
-      <c r="D204" s="14"/>
+      <c r="B204" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="C204" s="14">
+        <v>1</v>
+      </c>
+      <c r="D204" s="14">
+        <v>2</v>
+      </c>
       <c r="E204" s="14"/>
     </row>
-    <row r="205" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A205" s="33" t="s">
-        <v>351</v>
-      </c>
-      <c r="B205" s="32" t="s">
-        <v>384</v>
+    <row r="205" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="16"/>
+      <c r="B205" s="28" t="s">
+        <v>380</v>
       </c>
       <c r="C205" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D205" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="D205" s="14">
+        <v>4</v>
+      </c>
       <c r="E205" s="14"/>
     </row>
     <row r="206" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="16"/>
-      <c r="B206" s="32" t="s">
-        <v>385</v>
+      <c r="B206" s="28" t="s">
+        <v>381</v>
       </c>
       <c r="C206" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D206" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D206" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E206" s="14"/>
     </row>
     <row r="207" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="16"/>
-      <c r="B207" s="32" t="s">
-        <v>386</v>
+      <c r="B207" s="28" t="s">
+        <v>382</v>
       </c>
       <c r="C207" s="14">
-        <v>1</v>
-      </c>
-      <c r="D207" s="14"/>
+        <v>2.5</v>
+      </c>
+      <c r="D207" s="14">
+        <v>3</v>
+      </c>
       <c r="E207" s="14"/>
     </row>
     <row r="208" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="16"/>
-      <c r="B208" s="32" t="s">
-        <v>387</v>
+      <c r="A208" s="19"/>
+      <c r="B208" s="31" t="s">
+        <v>383</v>
       </c>
       <c r="C208" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D208" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D208" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E208" s="14"/>
     </row>
     <row r="209" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="16"/>
-      <c r="B209" s="32" t="s">
-        <v>388</v>
+      <c r="A209" s="19"/>
+      <c r="B209" s="28" t="s">
+        <v>510</v>
       </c>
       <c r="C209" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D209" s="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="D209" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E209" s="14"/>
     </row>
     <row r="210" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="16"/>
-      <c r="B210" s="32" t="s">
-        <v>389</v>
+      <c r="A210" s="19"/>
+      <c r="B210" s="28" t="s">
+        <v>511</v>
       </c>
       <c r="C210" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D210" s="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="D210" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E210" s="14"/>
     </row>
     <row r="211" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="16"/>
-      <c r="B211" s="32" t="s">
-        <v>390</v>
+      <c r="A211" s="19"/>
+      <c r="B211" s="28" t="s">
+        <v>512</v>
       </c>
       <c r="C211" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D211" s="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="D211" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E211" s="14"/>
     </row>
     <row r="212" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="23"/>
-      <c r="B212" s="35" t="s">
-        <v>391</v>
+      <c r="A212" s="19"/>
+      <c r="B212" s="28" t="s">
+        <v>513</v>
       </c>
       <c r="C212" s="14">
-        <v>2</v>
-      </c>
-      <c r="D212" s="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="D212" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E212" s="14"/>
     </row>
     <row r="213" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="16"/>
-      <c r="B213" s="32" t="s">
-        <v>392</v>
-      </c>
-      <c r="C213" s="14">
-        <v>1.2</v>
-      </c>
+      <c r="B213" s="28"/>
+      <c r="C213" s="14"/>
       <c r="D213" s="14"/>
       <c r="E213" s="14"/>
     </row>
-    <row r="214" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="16"/>
-      <c r="B214" s="32" t="s">
-        <v>393</v>
+    <row r="214" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A214" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="B214" s="28" t="s">
+        <v>384</v>
       </c>
       <c r="C214" s="14">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D214" s="14"/>
       <c r="E214" s="14"/>
     </row>
     <row r="215" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="16"/>
-      <c r="B215" s="32"/>
-      <c r="C215" s="14"/>
+      <c r="B215" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="C215" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D215" s="14"/>
       <c r="E215" s="14"/>
     </row>
-    <row r="216" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A216" s="33" t="s">
-        <v>354</v>
-      </c>
-      <c r="B216" s="32" t="s">
-        <v>449</v>
+    <row r="216" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="16"/>
+      <c r="B216" s="28" t="s">
+        <v>386</v>
       </c>
       <c r="C216" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D216" s="14"/>
       <c r="E216" s="14"/>
     </row>
-    <row r="217" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="16"/>
-      <c r="B217" s="32" t="s">
-        <v>450</v>
+      <c r="B217" s="28" t="s">
+        <v>387</v>
       </c>
       <c r="C217" s="14">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D217" s="14"/>
       <c r="E217" s="14"/>
     </row>
-    <row r="218" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="16"/>
-      <c r="B218" s="32" t="s">
-        <v>451</v>
+      <c r="B218" s="28" t="s">
+        <v>388</v>
       </c>
       <c r="C218" s="14">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="D218" s="14"/>
       <c r="E218" s="14"/>
     </row>
-    <row r="219" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="16"/>
-      <c r="B219" s="32" t="s">
-        <v>452</v>
+      <c r="B219" s="28" t="s">
+        <v>389</v>
       </c>
       <c r="C219" s="14">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D219" s="14"/>
       <c r="E219" s="14"/>
     </row>
     <row r="220" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="16"/>
-      <c r="B220" s="32" t="s">
-        <v>453</v>
+      <c r="B220" s="28" t="s">
+        <v>390</v>
       </c>
       <c r="C220" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D220" s="14"/>
       <c r="E220" s="14"/>
     </row>
     <row r="221" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="16"/>
-      <c r="B221" s="32" t="s">
-        <v>454</v>
+      <c r="A221" s="19"/>
+      <c r="B221" s="31" t="s">
+        <v>391</v>
       </c>
       <c r="C221" s="14">
         <v>2</v>
@@ -5199,75 +5359,73 @@
       <c r="E221" s="14"/>
     </row>
     <row r="222" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="23"/>
-      <c r="B222" s="32" t="s">
-        <v>455</v>
+      <c r="A222" s="16"/>
+      <c r="B222" s="28" t="s">
+        <v>392</v>
       </c>
       <c r="C222" s="14">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D222" s="14"/>
       <c r="E222" s="14"/>
     </row>
     <row r="223" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="16"/>
-      <c r="B223" s="35" t="s">
-        <v>456</v>
+      <c r="B223" s="28" t="s">
+        <v>393</v>
       </c>
       <c r="C223" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D223" s="14"/>
       <c r="E223" s="14"/>
     </row>
     <row r="224" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="16"/>
-      <c r="B224" s="32" t="s">
-        <v>457</v>
-      </c>
-      <c r="C224" s="14">
-        <v>1.2</v>
-      </c>
+      <c r="B224" s="28"/>
+      <c r="C224" s="14"/>
       <c r="D224" s="14"/>
       <c r="E224" s="14"/>
     </row>
-    <row r="225" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="16"/>
-      <c r="B225" s="32" t="s">
-        <v>458</v>
+    <row r="225" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A225" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="B225" s="28" t="s">
+        <v>448</v>
       </c>
       <c r="C225" s="14">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="D225" s="14"/>
       <c r="E225" s="14"/>
     </row>
-    <row r="226" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A226" s="16"/>
-      <c r="B226" s="32" t="s">
-        <v>459</v>
+      <c r="B226" s="28" t="s">
+        <v>449</v>
       </c>
       <c r="C226" s="14">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="D226" s="14"/>
       <c r="E226" s="14"/>
     </row>
-    <row r="227" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A227" s="16"/>
-      <c r="B227" s="32" t="s">
-        <v>460</v>
+      <c r="B227" s="28" t="s">
+        <v>450</v>
       </c>
       <c r="C227" s="14">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D227" s="14"/>
       <c r="E227" s="14"/>
     </row>
-    <row r="228" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A228" s="16"/>
-      <c r="B228" s="32" t="s">
-        <v>461</v>
+      <c r="B228" s="28" t="s">
+        <v>451</v>
       </c>
       <c r="C228" s="14">
         <v>0.8</v>
@@ -5277,8 +5435,8 @@
     </row>
     <row r="229" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="16"/>
-      <c r="B229" s="32" t="s">
-        <v>462</v>
+      <c r="B229" s="28" t="s">
+        <v>452</v>
       </c>
       <c r="C229" s="14">
         <v>1.2</v>
@@ -5288,8 +5446,8 @@
     </row>
     <row r="230" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="16"/>
-      <c r="B230" s="32" t="s">
-        <v>463</v>
+      <c r="B230" s="28" t="s">
+        <v>453</v>
       </c>
       <c r="C230" s="14">
         <v>2</v>
@@ -5298,97 +5456,97 @@
       <c r="E230" s="14"/>
     </row>
     <row r="231" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="16"/>
-      <c r="B231" s="32" t="s">
-        <v>464</v>
+      <c r="A231" s="19"/>
+      <c r="B231" s="28" t="s">
+        <v>454</v>
       </c>
       <c r="C231" s="14">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D231" s="14"/>
       <c r="E231" s="14"/>
     </row>
     <row r="232" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="16"/>
-      <c r="B232" s="32" t="s">
-        <v>465</v>
+      <c r="B232" s="31" t="s">
+        <v>455</v>
       </c>
       <c r="C232" s="14">
-        <v>2.2000000000000002</v>
+        <v>1.2</v>
       </c>
       <c r="D232" s="14"/>
       <c r="E232" s="14"/>
     </row>
     <row r="233" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="16"/>
-      <c r="B233" s="32" t="s">
-        <v>487</v>
+      <c r="B233" s="28" t="s">
+        <v>456</v>
       </c>
       <c r="C233" s="14">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D233" s="14"/>
       <c r="E233" s="14"/>
     </row>
-    <row r="234" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="16"/>
-      <c r="B234" s="32" t="s">
-        <v>488</v>
+      <c r="B234" s="28" t="s">
+        <v>457</v>
       </c>
       <c r="C234" s="14">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="D234" s="14"/>
       <c r="E234" s="14"/>
     </row>
-    <row r="235" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A235" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="B235" s="32" t="s">
-        <v>489</v>
+    <row r="235" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="16"/>
+      <c r="B235" s="28" t="s">
+        <v>458</v>
       </c>
       <c r="C235" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D235" s="14"/>
       <c r="E235" s="14"/>
     </row>
     <row r="236" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="16"/>
-      <c r="B236" s="32"/>
-      <c r="C236" s="14"/>
+      <c r="B236" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="C236" s="14">
+        <v>2</v>
+      </c>
       <c r="D236" s="14"/>
       <c r="E236" s="14"/>
     </row>
-    <row r="237" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A237" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="B237" s="35" t="s">
-        <v>428</v>
+    <row r="237" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="16"/>
+      <c r="B237" s="28" t="s">
+        <v>460</v>
       </c>
       <c r="C237" s="14">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D237" s="14"/>
       <c r="E237" s="14"/>
     </row>
-    <row r="238" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="16"/>
-      <c r="B238" s="32" t="s">
-        <v>429</v>
+      <c r="B238" s="28" t="s">
+        <v>461</v>
       </c>
       <c r="C238" s="14">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D238" s="14"/>
       <c r="E238" s="14"/>
     </row>
     <row r="239" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="16"/>
-      <c r="B239" s="32" t="s">
-        <v>430</v>
+      <c r="B239" s="28" t="s">
+        <v>462</v>
       </c>
       <c r="C239" s="14">
         <v>2</v>
@@ -5398,216 +5556,198 @@
     </row>
     <row r="240" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="16"/>
-      <c r="B240" s="32" t="s">
-        <v>431</v>
+      <c r="B240" s="28" t="s">
+        <v>463</v>
       </c>
       <c r="C240" s="14">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D240" s="14"/>
       <c r="E240" s="14"/>
     </row>
     <row r="241" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="16"/>
-      <c r="B241" s="32" t="s">
-        <v>432</v>
+      <c r="B241" s="28" t="s">
+        <v>464</v>
       </c>
       <c r="C241" s="14">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D241" s="14"/>
       <c r="E241" s="14"/>
     </row>
     <row r="242" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="16"/>
-      <c r="B242" s="32" t="s">
-        <v>433</v>
+      <c r="B242" s="28" t="s">
+        <v>483</v>
       </c>
       <c r="C242" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242" s="14"/>
       <c r="E242" s="14"/>
     </row>
-    <row r="243" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A243" s="16"/>
-      <c r="B243" s="32" t="s">
-        <v>434</v>
+      <c r="B243" s="28" t="s">
+        <v>484</v>
       </c>
       <c r="C243" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243" s="14"/>
       <c r="E243" s="14"/>
     </row>
-    <row r="244" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="16"/>
-      <c r="B244" s="32" t="s">
-        <v>490</v>
+    <row r="244" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A244" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B244" s="28" t="s">
+        <v>485</v>
       </c>
       <c r="C244" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D244" s="14"/>
       <c r="E244" s="14"/>
     </row>
     <row r="245" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="B245" s="32" t="s">
-        <v>491</v>
-      </c>
-      <c r="C245" s="14">
-        <v>1</v>
-      </c>
+      <c r="A245" s="16"/>
+      <c r="B245" s="28"/>
+      <c r="C245" s="14"/>
       <c r="D245" s="14"/>
       <c r="E245" s="14"/>
     </row>
-    <row r="246" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="16"/>
-      <c r="B246" s="32" t="s">
-        <v>492</v>
+    <row r="246" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A246" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="B246" s="31" t="s">
+        <v>427</v>
       </c>
       <c r="C246" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D246" s="14"/>
       <c r="E246" s="14"/>
     </row>
-    <row r="247" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A247" s="16"/>
-      <c r="B247" s="32"/>
-      <c r="C247" s="14"/>
+      <c r="B247" s="28" t="s">
+        <v>428</v>
+      </c>
+      <c r="C247" s="14">
+        <v>1.5</v>
+      </c>
       <c r="D247" s="14"/>
       <c r="E247" s="14"/>
     </row>
-    <row r="248" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A248" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="B248" s="32" t="s">
-        <v>394</v>
+    <row r="248" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="16"/>
+      <c r="B248" s="28" t="s">
+        <v>429</v>
       </c>
       <c r="C248" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D248" s="14">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D248" s="14"/>
       <c r="E248" s="14"/>
     </row>
     <row r="249" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="16"/>
-      <c r="B249" s="32" t="s">
-        <v>395</v>
+      <c r="B249" s="28" t="s">
+        <v>430</v>
       </c>
       <c r="C249" s="14">
-        <v>1</v>
-      </c>
-      <c r="D249" s="14">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D249" s="14"/>
       <c r="E249" s="14"/>
     </row>
     <row r="250" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="23"/>
-      <c r="B250" s="35" t="s">
-        <v>396</v>
+      <c r="A250" s="16"/>
+      <c r="B250" s="28" t="s">
+        <v>431</v>
       </c>
       <c r="C250" s="14">
         <v>1.5</v>
       </c>
-      <c r="D250" s="14">
-        <v>1.2</v>
-      </c>
+      <c r="D250" s="14"/>
       <c r="E250" s="14"/>
     </row>
     <row r="251" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="16"/>
-      <c r="B251" s="32" t="s">
-        <v>397</v>
+      <c r="B251" s="28" t="s">
+        <v>432</v>
       </c>
       <c r="C251" s="14">
-        <v>2</v>
-      </c>
-      <c r="D251" s="14">
-        <v>1.8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D251" s="14"/>
       <c r="E251" s="14"/>
     </row>
     <row r="252" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="16"/>
-      <c r="B252" s="32" t="s">
-        <v>398</v>
+      <c r="B252" s="28" t="s">
+        <v>433</v>
       </c>
       <c r="C252" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D252" s="14">
-        <v>1.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D252" s="14"/>
       <c r="E252" s="14"/>
     </row>
     <row r="253" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="16"/>
-      <c r="B253" s="32" t="s">
-        <v>399</v>
+      <c r="B253" s="28" t="s">
+        <v>486</v>
       </c>
       <c r="C253" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D253" s="14">
-        <v>2</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="D253" s="14"/>
       <c r="E253" s="14"/>
     </row>
     <row r="254" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="16"/>
-      <c r="B254" s="32" t="s">
-        <v>400</v>
+      <c r="A254" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B254" s="28" t="s">
+        <v>487</v>
       </c>
       <c r="C254" s="14">
-        <v>2</v>
-      </c>
-      <c r="D254" s="14">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D254" s="14"/>
       <c r="E254" s="14"/>
     </row>
     <row r="255" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="16"/>
-      <c r="B255" s="32" t="s">
-        <v>401</v>
+      <c r="B255" s="28" t="s">
+        <v>488</v>
       </c>
       <c r="C255" s="14">
         <v>1</v>
       </c>
-      <c r="D255" s="14">
-        <v>1</v>
-      </c>
+      <c r="D255" s="14"/>
       <c r="E255" s="14"/>
     </row>
     <row r="256" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="16"/>
-      <c r="B256" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="C256" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D256" s="14">
-        <v>1.2</v>
-      </c>
+      <c r="B256" s="28"/>
+      <c r="C256" s="14"/>
+      <c r="D256" s="14"/>
       <c r="E256" s="14"/>
     </row>
-    <row r="257" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="16"/>
-      <c r="B257" s="32" t="s">
-        <v>484</v>
+    <row r="257" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A257" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="B257" s="28" t="s">
+        <v>394</v>
       </c>
       <c r="C257" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D257" s="14">
         <v>1</v>
@@ -5616,151 +5756,169 @@
     </row>
     <row r="258" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="16"/>
-      <c r="B258" s="32" t="s">
-        <v>485</v>
+      <c r="B258" s="28" t="s">
+        <v>395</v>
       </c>
       <c r="C258" s="14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D258" s="14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E258" s="14"/>
     </row>
     <row r="259" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="16"/>
-      <c r="B259" s="32" t="s">
-        <v>486</v>
+      <c r="A259" s="19"/>
+      <c r="B259" s="31" t="s">
+        <v>396</v>
       </c>
       <c r="C259" s="14">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D259" s="14">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="E259" s="14"/>
     </row>
     <row r="260" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="16"/>
-      <c r="B260" s="32"/>
-      <c r="C260" s="14"/>
-      <c r="D260" s="14"/>
+      <c r="B260" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="C260" s="14">
+        <v>2</v>
+      </c>
+      <c r="D260" s="14">
+        <v>1.8</v>
+      </c>
       <c r="E260" s="14"/>
     </row>
     <row r="261" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="B261" s="32"/>
-      <c r="C261" s="14"/>
-      <c r="D261" s="14"/>
+      <c r="A261" s="16"/>
+      <c r="B261" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="C261" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D261" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E261" s="14"/>
     </row>
     <row r="262" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="33" t="s">
-        <v>361</v>
-      </c>
-      <c r="B262" s="32" t="s">
-        <v>403</v>
+      <c r="A262" s="16"/>
+      <c r="B262" s="28" t="s">
+        <v>399</v>
       </c>
       <c r="C262" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D262" s="14">
         <v>2</v>
       </c>
-      <c r="D262" s="14"/>
       <c r="E262" s="14"/>
     </row>
     <row r="263" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="23"/>
-      <c r="B263" s="35" t="s">
-        <v>404</v>
+      <c r="A263" s="16"/>
+      <c r="B263" s="28" t="s">
+        <v>400</v>
       </c>
       <c r="C263" s="14">
         <v>2</v>
       </c>
-      <c r="D263" s="14"/>
+      <c r="D263" s="14">
+        <v>2</v>
+      </c>
       <c r="E263" s="14"/>
     </row>
     <row r="264" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="16"/>
-      <c r="B264" s="32" t="s">
-        <v>405</v>
+      <c r="B264" s="28" t="s">
+        <v>401</v>
       </c>
       <c r="C264" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D264" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D264" s="14">
+        <v>1</v>
+      </c>
       <c r="E264" s="14"/>
     </row>
     <row r="265" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="16"/>
-      <c r="B265" s="32" t="s">
-        <v>406</v>
+      <c r="B265" s="28" t="s">
+        <v>402</v>
       </c>
       <c r="C265" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D265" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D265" s="14">
+        <v>1.2</v>
+      </c>
       <c r="E265" s="14"/>
     </row>
     <row r="266" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="16"/>
-      <c r="B266" s="32" t="s">
-        <v>407</v>
+      <c r="B266" s="28" t="s">
+        <v>480</v>
       </c>
       <c r="C266" s="14">
-        <v>2</v>
-      </c>
-      <c r="D266" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D266" s="14">
+        <v>1</v>
+      </c>
       <c r="E266" s="14"/>
     </row>
     <row r="267" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="16"/>
-      <c r="B267" s="32" t="s">
-        <v>408</v>
+      <c r="B267" s="28" t="s">
+        <v>481</v>
       </c>
       <c r="C267" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D267" s="14"/>
+        <v>0.8</v>
+      </c>
+      <c r="D267" s="14">
+        <v>0.8</v>
+      </c>
       <c r="E267" s="14"/>
     </row>
     <row r="268" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="16"/>
-      <c r="B268" s="32" t="s">
-        <v>409</v>
+      <c r="B268" s="28" t="s">
+        <v>482</v>
       </c>
       <c r="C268" s="14">
-        <v>2</v>
-      </c>
-      <c r="D268" s="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="D268" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E268" s="14"/>
     </row>
     <row r="269" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="16"/>
-      <c r="B269" s="32" t="s">
-        <v>410</v>
-      </c>
-      <c r="C269" s="14">
-        <v>2</v>
-      </c>
+      <c r="B269" s="28"/>
+      <c r="C269" s="14"/>
       <c r="D269" s="14"/>
       <c r="E269" s="14"/>
     </row>
     <row r="270" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="16"/>
-      <c r="B270" s="32" t="s">
-        <v>411</v>
-      </c>
-      <c r="C270" s="14">
-        <v>2</v>
-      </c>
+      <c r="A270" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B270" s="28"/>
+      <c r="C270" s="14"/>
       <c r="D270" s="14"/>
       <c r="E270" s="14"/>
     </row>
     <row r="271" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="16"/>
-      <c r="B271" s="32" t="s">
-        <v>412</v>
+      <c r="A271" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="B271" s="28" t="s">
+        <v>403</v>
       </c>
       <c r="C271" s="14">
         <v>2</v>
@@ -5769,53 +5927,53 @@
       <c r="E271" s="14"/>
     </row>
     <row r="272" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="23"/>
-      <c r="B272" s="35" t="s">
-        <v>413</v>
+      <c r="A272" s="19"/>
+      <c r="B272" s="31" t="s">
+        <v>404</v>
       </c>
       <c r="C272" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D272" s="14"/>
       <c r="E272" s="14"/>
     </row>
     <row r="273" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="16"/>
-      <c r="B273" s="32" t="s">
-        <v>414</v>
+      <c r="B273" s="28" t="s">
+        <v>405</v>
       </c>
       <c r="C273" s="14">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D273" s="14"/>
       <c r="E273" s="14"/>
     </row>
     <row r="274" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="16"/>
-      <c r="B274" s="32" t="s">
-        <v>415</v>
+      <c r="B274" s="28" t="s">
+        <v>406</v>
       </c>
       <c r="C274" s="14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D274" s="14"/>
       <c r="E274" s="14"/>
     </row>
     <row r="275" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="16"/>
-      <c r="B275" s="32" t="s">
-        <v>416</v>
+      <c r="B275" s="28" t="s">
+        <v>407</v>
       </c>
       <c r="C275" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D275" s="14"/>
       <c r="E275" s="14"/>
     </row>
     <row r="276" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="16"/>
-      <c r="B276" s="32" t="s">
-        <v>417</v>
+      <c r="B276" s="28" t="s">
+        <v>408</v>
       </c>
       <c r="C276" s="14">
         <v>1.5</v>
@@ -5825,10 +5983,10 @@
     </row>
     <row r="277" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="16"/>
-      <c r="B277" s="32" t="s">
-        <v>493</v>
-      </c>
-      <c r="C277">
+      <c r="B277" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="C277" s="14">
         <v>2</v>
       </c>
       <c r="D277" s="14"/>
@@ -5836,74 +5994,74 @@
     </row>
     <row r="278" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="16"/>
-      <c r="B278" s="32" t="s">
-        <v>494</v>
-      </c>
-      <c r="C278">
-        <v>1</v>
+      <c r="B278" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C278" s="14">
+        <v>2</v>
       </c>
       <c r="D278" s="14"/>
       <c r="E278" s="14"/>
     </row>
     <row r="279" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="16"/>
-      <c r="B279" s="32" t="s">
-        <v>495</v>
-      </c>
-      <c r="C279">
-        <v>1</v>
+      <c r="B279" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="C279" s="14">
+        <v>2</v>
       </c>
       <c r="D279" s="14"/>
       <c r="E279" s="14"/>
     </row>
     <row r="280" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="B280" s="32"/>
-      <c r="C280" s="14"/>
+      <c r="A280" s="16"/>
+      <c r="B280" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="C280" s="14">
+        <v>2</v>
+      </c>
       <c r="D280" s="14"/>
       <c r="E280" s="14"/>
     </row>
     <row r="281" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="33" t="s">
-        <v>364</v>
-      </c>
-      <c r="B281" s="32" t="s">
-        <v>418</v>
+      <c r="A281" s="19"/>
+      <c r="B281" s="31" t="s">
+        <v>413</v>
       </c>
       <c r="C281" s="14">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D281" s="14"/>
       <c r="E281" s="14"/>
     </row>
     <row r="282" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="16"/>
-      <c r="B282" s="32" t="s">
-        <v>419</v>
+      <c r="B282" s="28" t="s">
+        <v>414</v>
       </c>
       <c r="C282" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D282" s="14"/>
       <c r="E282" s="14"/>
     </row>
     <row r="283" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="16"/>
-      <c r="B283" s="32" t="s">
-        <v>420</v>
+      <c r="B283" s="28" t="s">
+        <v>415</v>
       </c>
       <c r="C283" s="14">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="D283" s="14"/>
       <c r="E283" s="14"/>
     </row>
     <row r="284" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="23"/>
-      <c r="B284" s="35" t="s">
-        <v>421</v>
+      <c r="A284" s="16"/>
+      <c r="B284" s="28" t="s">
+        <v>416</v>
       </c>
       <c r="C284" s="14">
         <v>1.5</v>
@@ -5913,21 +6071,21 @@
     </row>
     <row r="285" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="16"/>
-      <c r="B285" s="32" t="s">
-        <v>422</v>
+      <c r="B285" s="28" t="s">
+        <v>417</v>
       </c>
       <c r="C285" s="14">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D285" s="14"/>
       <c r="E285" s="14"/>
     </row>
     <row r="286" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="16"/>
-      <c r="B286" s="32" t="s">
-        <v>423</v>
-      </c>
-      <c r="C286" s="14">
+      <c r="B286" s="28" t="s">
+        <v>489</v>
+      </c>
+      <c r="C286" s="8">
         <v>2</v>
       </c>
       <c r="D286" s="14"/>
@@ -5935,329 +6093,357 @@
     </row>
     <row r="287" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="16"/>
-      <c r="B287" s="32" t="s">
-        <v>424</v>
-      </c>
-      <c r="C287" s="14">
-        <v>1.5</v>
+      <c r="B287" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="C287" s="8">
+        <v>1</v>
       </c>
       <c r="D287" s="14"/>
       <c r="E287" s="14"/>
     </row>
     <row r="288" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="16"/>
-      <c r="B288" s="32" t="s">
-        <v>425</v>
-      </c>
-      <c r="C288" s="14">
-        <v>3</v>
+      <c r="B288" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="C288" s="8">
+        <v>1</v>
       </c>
       <c r="D288" s="14"/>
       <c r="E288" s="14"/>
     </row>
     <row r="289" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="16"/>
-      <c r="B289" s="32" t="s">
-        <v>426</v>
-      </c>
-      <c r="C289" s="14">
-        <v>1.2</v>
-      </c>
+      <c r="A289" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B289" s="28"/>
+      <c r="C289" s="14"/>
       <c r="D289" s="14"/>
       <c r="E289" s="14"/>
     </row>
-    <row r="290" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="16"/>
-      <c r="B290" s="32" t="s">
-        <v>427</v>
+    <row r="290" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A290" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="B290" s="18" t="s">
+        <v>418</v>
       </c>
       <c r="C290" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D290" s="14"/>
+        <v>0.8</v>
+      </c>
+      <c r="D290" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E290" s="14"/>
     </row>
     <row r="291" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="16"/>
-      <c r="B291" s="32" t="s">
-        <v>496</v>
+      <c r="B291" s="18" t="s">
+        <v>419</v>
       </c>
       <c r="C291" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D291" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="D291" s="14">
+        <v>1.8</v>
+      </c>
       <c r="E291" s="14"/>
     </row>
-    <row r="292" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="16"/>
-      <c r="B292" s="32" t="s">
-        <v>497</v>
+      <c r="B292" s="18" t="s">
+        <v>420</v>
       </c>
       <c r="C292" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B293" s="32" t="s">
-        <v>498</v>
+        <v>1.2</v>
+      </c>
+      <c r="D292" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E292" s="14"/>
+    </row>
+    <row r="293" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="19"/>
+      <c r="B293" s="14" t="s">
+        <v>421</v>
       </c>
       <c r="C293" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A294" s="22" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="D293" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="E293" s="14"/>
+    </row>
+    <row r="294" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" s="16"/>
+      <c r="B294" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="C294" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D294" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E294" s="14"/>
+    </row>
+    <row r="295" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="16"/>
+      <c r="B295" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="C295" s="14">
+        <v>2</v>
+      </c>
+      <c r="D295" s="14">
+        <v>2</v>
+      </c>
+      <c r="E295" s="14"/>
+    </row>
+    <row r="296" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="16"/>
+      <c r="B296" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="C296" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D296" s="14">
+        <v>1</v>
+      </c>
+      <c r="E296" s="14"/>
+    </row>
+    <row r="297" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="16"/>
+      <c r="B297" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="C297" s="14">
+        <v>3</v>
+      </c>
+      <c r="D297" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="E297" s="14"/>
+    </row>
+    <row r="298" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="16"/>
+      <c r="B298" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="C298" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D298" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E298" s="14"/>
+    </row>
+    <row r="299" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="16"/>
+      <c r="B299" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C299" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D299" s="14">
+        <v>1</v>
+      </c>
+      <c r="E299" s="14"/>
+    </row>
+    <row r="300" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="16"/>
+      <c r="B300" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="C300" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D300" s="14">
+        <v>1</v>
+      </c>
+      <c r="E300" s="14"/>
+    </row>
+    <row r="301" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A301" s="16"/>
+      <c r="B301" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="C301" s="14">
+        <v>1</v>
+      </c>
+      <c r="D301" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B302" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="C302" s="14">
+        <v>1</v>
+      </c>
+      <c r="D302" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A303" s="36" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B295" s="32" t="s">
+    <row r="304" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B304" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="C295">
+      <c r="C304" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B296" s="32" t="s">
+    <row r="305" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B305" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="C296">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B297" s="32" t="s">
+      <c r="C305" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B306" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="C297">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B298" s="32" t="s">
+      <c r="C306" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B307" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="C298">
+      <c r="C307" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B299" s="32" t="s">
+    <row r="308" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B308" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="C299">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B300" s="32" t="s">
+      <c r="C308" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B309" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="C300">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B301" s="32" t="s">
+      <c r="C309" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B310" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="C301">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B302" s="32" t="s">
+      <c r="C310" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B311" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="C302">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B303" s="32"/>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A304" s="22" t="s">
+      <c r="C311" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B312" s="28"/>
+    </row>
+    <row r="313" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A313" s="36" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B305" s="32" t="s">
+    <row r="314" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B314" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="C305">
+      <c r="C314" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B306" s="32" t="s">
+    <row r="315" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B315" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="C306">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B307" s="32" t="s">
+      <c r="C315" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B316" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="C307">
+      <c r="C316" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B308" s="32" t="s">
+    <row r="317" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B317" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="C308">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B309" s="32" t="s">
+      <c r="C317" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B318" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="C309">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B310" s="32" t="s">
+      <c r="C318" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B319" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="C310">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B311" s="32" t="s">
+      <c r="C319" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B320" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="C311">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B312" s="32"/>
-    </row>
-    <row r="313" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B313" s="32" t="s">
-        <v>435</v>
-      </c>
-      <c r="C313" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D313" s="14"/>
-      <c r="E313" s="14"/>
-    </row>
-    <row r="314" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A314" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="B314" s="32" t="s">
-        <v>436</v>
-      </c>
-      <c r="C314" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D314" s="14"/>
-      <c r="E314" s="14"/>
-    </row>
-    <row r="315" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="16"/>
-      <c r="B315" s="32" t="s">
-        <v>437</v>
-      </c>
-      <c r="C315" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D315" s="14"/>
-      <c r="E315" s="14"/>
-    </row>
-    <row r="316" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A316" s="16"/>
-      <c r="B316" s="32" t="s">
-        <v>438</v>
-      </c>
-      <c r="C316" s="14">
-        <v>2</v>
-      </c>
-      <c r="D316" s="14"/>
-      <c r="E316" s="14"/>
-    </row>
-    <row r="317" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A317" s="16"/>
-      <c r="B317" s="32" t="s">
-        <v>439</v>
-      </c>
-      <c r="C317" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D317" s="14"/>
-      <c r="E317" s="14"/>
-    </row>
-    <row r="318" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="16"/>
-      <c r="B318" s="32" t="s">
-        <v>440</v>
-      </c>
-      <c r="C318" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D318" s="14"/>
-      <c r="E318" s="14"/>
-    </row>
-    <row r="319" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A319" s="16"/>
-      <c r="B319" s="32" t="s">
-        <v>441</v>
-      </c>
-      <c r="C319" s="14">
-        <v>1</v>
-      </c>
-      <c r="D319" s="14"/>
-      <c r="E319" s="14"/>
-    </row>
-    <row r="320" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A320" s="16"/>
-      <c r="B320" s="32" t="s">
-        <v>442</v>
-      </c>
-      <c r="C320" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D320" s="14"/>
-      <c r="E320" s="14"/>
-    </row>
-    <row r="321" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A321" s="16"/>
-      <c r="B321" s="32" t="s">
-        <v>443</v>
-      </c>
-      <c r="C321" s="14">
-        <v>2</v>
-      </c>
-      <c r="D321" s="14"/>
-      <c r="E321" s="14"/>
+      <c r="C320" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B321" s="28"/>
     </row>
     <row r="322" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A322" s="16"/>
-      <c r="B322" s="32" t="s">
-        <v>444</v>
+      <c r="B322" s="28" t="s">
+        <v>434</v>
       </c>
       <c r="C322" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D322" s="14"/>
       <c r="E322" s="14"/>
     </row>
     <row r="323" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A323" s="16"/>
-      <c r="B323" s="32" t="s">
-        <v>499</v>
-      </c>
-      <c r="C323">
+      <c r="A323" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="B323" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="C323" s="14">
         <v>1.5</v>
       </c>
       <c r="D323" s="14"/>
@@ -6265,849 +6451,977 @@
     </row>
     <row r="324" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="16"/>
-      <c r="B324" s="32" t="s">
-        <v>500</v>
-      </c>
-      <c r="C324">
-        <v>1</v>
+      <c r="B324" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="C324" s="14">
+        <v>1.5</v>
       </c>
       <c r="D324" s="14"/>
       <c r="E324" s="14"/>
     </row>
     <row r="325" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="16"/>
-      <c r="B325" s="32" t="s">
-        <v>501</v>
-      </c>
-      <c r="C325">
-        <v>1</v>
+      <c r="B325" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="C325" s="14">
+        <v>2</v>
       </c>
       <c r="D325" s="14"/>
       <c r="E325" s="14"/>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="16"/>
-      <c r="B326" s="32"/>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A327" s="22" t="s">
+      <c r="B326" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="C326" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D326" s="14"/>
+      <c r="E326" s="14"/>
+    </row>
+    <row r="327" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="16"/>
+      <c r="B327" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="C327" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D327" s="14"/>
+      <c r="E327" s="14"/>
+    </row>
+    <row r="328" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="16"/>
+      <c r="B328" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="C328" s="14">
+        <v>1</v>
+      </c>
+      <c r="D328" s="14"/>
+      <c r="E328" s="14"/>
+    </row>
+    <row r="329" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="16"/>
+      <c r="B329" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="C329" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D329" s="14"/>
+      <c r="E329" s="14"/>
+    </row>
+    <row r="330" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330" s="16"/>
+      <c r="B330" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="C330" s="14">
+        <v>2</v>
+      </c>
+      <c r="D330" s="14"/>
+      <c r="E330" s="14"/>
+    </row>
+    <row r="331" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331" s="16"/>
+      <c r="B331" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="C331" s="14">
+        <v>1</v>
+      </c>
+      <c r="D331" s="14"/>
+      <c r="E331" s="14"/>
+    </row>
+    <row r="332" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332" s="16"/>
+      <c r="B332" s="28" t="s">
+        <v>495</v>
+      </c>
+      <c r="C332" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D332" s="14"/>
+      <c r="E332" s="14"/>
+    </row>
+    <row r="333" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="16"/>
+      <c r="B333" s="28" t="s">
+        <v>496</v>
+      </c>
+      <c r="C333" s="8">
+        <v>1</v>
+      </c>
+      <c r="D333" s="14"/>
+      <c r="E333" s="14"/>
+    </row>
+    <row r="334" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="16"/>
+      <c r="B334" s="28" t="s">
+        <v>497</v>
+      </c>
+      <c r="C334" s="8">
+        <v>1</v>
+      </c>
+      <c r="D334" s="14"/>
+      <c r="E334" s="14"/>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A335" s="16"/>
+      <c r="B335" s="28"/>
+    </row>
+    <row r="336" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A336" s="36" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B328" s="32" t="s">
+    <row r="337" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B337" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="C328">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B329" s="32" t="s">
+      <c r="C337" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B338" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="C329">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B330" s="32" t="s">
+      <c r="C338" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B339" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="C330">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B331" s="32" t="s">
+      <c r="C339" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B340" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="C331">
+      <c r="C340" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B332" s="32" t="s">
+    <row r="341" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B341" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="C332">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B333" s="32" t="s">
+      <c r="C341" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B342" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="C333">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B334" s="32" t="s">
+      <c r="C342" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B343" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="C334">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B335" s="32" t="s">
+      <c r="C343" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B344" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="C335">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B336" s="32" t="s">
+      <c r="C344" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B345" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="C336">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B337" s="32"/>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A338" s="22" t="s">
+      <c r="C345" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B346" s="28"/>
+    </row>
+    <row r="347" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A347" s="36" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B339" s="32" t="s">
+    <row r="348" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B348" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="C339">
+      <c r="C348" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B340" s="32" t="s">
+    <row r="349" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B349" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="C340">
+      <c r="C349" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B341" s="32" t="s">
+    <row r="350" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B350" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="C341">
+      <c r="C350" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B342" s="32" t="s">
+    <row r="351" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B351" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="C342">
+      <c r="C351" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B343" s="32" t="s">
+    <row r="352" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B352" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="C343">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B344" s="32" t="s">
+      <c r="C352" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B353" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="C344">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B345" s="32" t="s">
+      <c r="C353" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B354" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="C345">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B346" s="32"/>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A347" s="22" t="s">
+      <c r="C354" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B355" s="28"/>
+    </row>
+    <row r="356" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A356" s="36" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B348" s="32" t="s">
+    <row r="357" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B357" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="C348">
+      <c r="C357" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B349" s="32" t="s">
+    <row r="358" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B358" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="C349">
+      <c r="C358" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B350" s="32" t="s">
+    <row r="359" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B359" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B351" s="32" t="s">
+      <c r="C359" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B360" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="C351">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B352" s="32" t="s">
+      <c r="C360" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B361" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="C352">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B353" s="32" t="s">
+      <c r="C361" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B362" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="C353">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B354" s="32" t="s">
+      <c r="C362" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B363" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="C354">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B355" s="32"/>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A356" s="22" t="s">
+      <c r="C363" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B364" s="28"/>
+    </row>
+    <row r="365" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A365" s="36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B357" s="32" t="s">
+    <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B366" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="C357">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B358" s="32" t="s">
+      <c r="C366" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B367" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="C358">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B359" s="32" t="s">
+      <c r="C367" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B368" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="C359">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B360" s="32" t="s">
+      <c r="C368" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B369" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="C360">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B361" s="32" t="s">
+      <c r="C369" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B370" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="C361">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B362" s="32" t="s">
+      <c r="C370" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B371" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="C362">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B363" s="32" t="s">
+      <c r="C371" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B372" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="C363">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B364" s="32"/>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A365" s="22" t="s">
+      <c r="C372" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B373" s="28"/>
+    </row>
+    <row r="374" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A374" s="36" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B366" s="32" t="s">
+    <row r="375" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B375" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="C366">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B367" s="32" t="s">
+      <c r="C375" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B376" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="C367">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B368" s="32" t="s">
+      <c r="C376" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B377" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="C368">
+      <c r="C377" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B369" s="32" t="s">
+    <row r="378" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B378" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="C369">
+      <c r="C378" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B370" s="32" t="s">
+    <row r="379" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B379" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="C370">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B371" s="32" t="s">
+      <c r="C379" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B380" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C371">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B372" s="32"/>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A373" s="22" t="s">
+      <c r="C380" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B381" s="28"/>
+    </row>
+    <row r="382" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A382" s="36" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B374" s="32" t="s">
+    <row r="383" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B383" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="C374">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B375" s="32" t="s">
+      <c r="C383" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B384" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="C375">
+      <c r="C384" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B376" s="32" t="s">
+    <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B385" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="C376">
+      <c r="C385" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B377" s="32" t="s">
+    <row r="386" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B386" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="C377">
+      <c r="C386" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B378" s="32" t="s">
+    <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B387" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="C378">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B379" s="32" t="s">
+      <c r="C387" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B388" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="C379">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B380" s="32" t="s">
+      <c r="C388" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B389" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="C380">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B381" s="32"/>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A382" s="22" t="s">
+      <c r="C389" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B390" s="28"/>
+    </row>
+    <row r="391" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A391" s="36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B383" s="32" t="s">
+    <row r="392" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B392" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="C383">
+      <c r="C392" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B384" s="32" t="s">
+    <row r="393" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B393" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="C384">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B385" s="32" t="s">
+      <c r="C393" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B394" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="C385">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B386" s="32" t="s">
+      <c r="C394" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B395" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="C386">
+      <c r="C395" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B387" s="32" t="s">
+    <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B396" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="C387">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B388" s="32" t="s">
+      <c r="C396" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B397" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="C388">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B389" s="32" t="s">
+      <c r="C397" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B398" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="C389">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B390" s="32"/>
-    </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A391" s="22" t="s">
+      <c r="C398" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B399" s="28"/>
+    </row>
+    <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A400" s="36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B392" s="32" t="s">
+    <row r="401" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B401" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="C392">
+      <c r="C401" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B393" s="32" t="s">
+    <row r="402" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B402" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="C393">
+      <c r="C402" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B394" s="32" t="s">
+    <row r="403" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B403" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="C394">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B395" s="32" t="s">
+      <c r="C403" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B404" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="C395">
+      <c r="C404" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B396" s="32" t="s">
+    <row r="405" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B405" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="C396">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B397" s="32"/>
-      <c r="D397" s="14"/>
-      <c r="E397" s="14"/>
-    </row>
-    <row r="398" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A398" s="33" t="s">
-        <v>478</v>
-      </c>
-      <c r="B398" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="C398" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D398" s="14"/>
-      <c r="E398" s="14"/>
-    </row>
-    <row r="399" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A399" s="16"/>
-      <c r="B399" s="35" t="s">
-        <v>467</v>
-      </c>
-      <c r="C399" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D399" s="14"/>
-      <c r="E399" s="14"/>
-    </row>
-    <row r="400" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A400" s="16"/>
-      <c r="B400" s="35" t="s">
-        <v>468</v>
-      </c>
-      <c r="C400" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D400" s="14"/>
-      <c r="E400" s="14"/>
-    </row>
-    <row r="401" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A401" s="16"/>
-      <c r="B401" s="35" t="s">
-        <v>469</v>
-      </c>
-      <c r="C401" s="14">
-        <v>1</v>
-      </c>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-    </row>
-    <row r="402" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A402" s="16"/>
-      <c r="B402" s="35" t="s">
-        <v>470</v>
-      </c>
-      <c r="C402" s="14">
-        <v>2</v>
-      </c>
-      <c r="D402" s="14"/>
-      <c r="E402" s="14"/>
-    </row>
-    <row r="403" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A403" s="16"/>
-      <c r="B403" s="35" t="s">
-        <v>471</v>
-      </c>
-      <c r="C403" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D403" s="14"/>
-      <c r="E403" s="14"/>
-    </row>
-    <row r="404" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A404" s="16"/>
-      <c r="B404" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="C404" s="14">
-        <v>1</v>
-      </c>
-      <c r="D404" s="14"/>
-      <c r="E404" s="14"/>
-    </row>
-    <row r="405" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A405" s="16"/>
-      <c r="B405" s="35" t="s">
-        <v>473</v>
-      </c>
-      <c r="C405" s="14">
-        <v>2</v>
-      </c>
-      <c r="D405" s="14"/>
-      <c r="E405" s="14"/>
-    </row>
-    <row r="406" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A406" s="16"/>
-      <c r="B406" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="C406" s="14">
-        <v>2</v>
-      </c>
+      <c r="C405" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B406" s="28"/>
       <c r="D406" s="14"/>
       <c r="E406" s="14"/>
     </row>
     <row r="407" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A407" s="16"/>
-      <c r="B407" s="35" t="s">
+      <c r="A407" s="29" t="s">
         <v>475</v>
       </c>
+      <c r="B407" s="31" t="s">
+        <v>502</v>
+      </c>
       <c r="C407" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D407" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D407" s="14">
+        <v>0.8</v>
+      </c>
       <c r="E407" s="14"/>
     </row>
     <row r="408" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A408" s="16"/>
-      <c r="B408" s="35" t="s">
-        <v>476</v>
+      <c r="B408" s="31" t="s">
+        <v>465</v>
       </c>
       <c r="C408" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D408" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="E408" s="14"/>
+    </row>
+    <row r="409" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A409" s="16"/>
+      <c r="B409" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="C409" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="D409" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E409" s="14"/>
+    </row>
+    <row r="410" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A410" s="16"/>
+      <c r="B410" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="C410" s="14">
+        <v>1</v>
+      </c>
+      <c r="D410" s="14">
+        <v>1</v>
+      </c>
+      <c r="E410" s="14"/>
+    </row>
+    <row r="411" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A411" s="16"/>
+      <c r="B411" s="31" t="s">
+        <v>468</v>
+      </c>
+      <c r="C411" s="14">
+        <v>2</v>
+      </c>
+      <c r="D411" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="E411" s="14"/>
+    </row>
+    <row r="412" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A412" s="16"/>
+      <c r="B412" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="C412" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D412" s="14">
+        <v>1</v>
+      </c>
+      <c r="E412" s="14"/>
+    </row>
+    <row r="413" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A413" s="16"/>
+      <c r="B413" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="C413" s="14">
+        <v>1</v>
+      </c>
+      <c r="D413" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E413" s="14"/>
+    </row>
+    <row r="414" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A414" s="16"/>
+      <c r="B414" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="C414" s="14">
+        <v>2</v>
+      </c>
+      <c r="D414" s="14">
+        <v>2</v>
+      </c>
+      <c r="E414" s="14"/>
+    </row>
+    <row r="415" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A415" s="16"/>
+      <c r="B415" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="C415" s="14">
+        <v>2</v>
+      </c>
+      <c r="D415" s="14"/>
+      <c r="E415" s="14"/>
+    </row>
+    <row r="416" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A416" s="16"/>
+      <c r="B416" s="31" t="s">
+        <v>472</v>
+      </c>
+      <c r="C416" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D416" s="14"/>
+      <c r="E416" s="14"/>
+    </row>
+    <row r="417" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A417" s="16"/>
+      <c r="B417" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="C417" s="14">
         <v>2.5</v>
       </c>
-      <c r="D408" s="14"/>
-      <c r="E408" s="14"/>
-    </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A409" s="16"/>
-      <c r="B409" s="36" t="s">
-        <v>477</v>
-      </c>
-      <c r="C409">
-        <v>1.5</v>
-      </c>
-      <c r="D409" s="14"/>
-      <c r="E409" s="14"/>
-    </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A410" s="16"/>
-      <c r="B410" s="35"/>
-      <c r="C410" s="14"/>
-      <c r="D410" s="14"/>
-      <c r="E410" s="14"/>
-    </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A411" s="16"/>
-      <c r="B411" s="35"/>
-      <c r="C411" s="14"/>
-    </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B412" s="32"/>
-    </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A413" s="22" t="s">
+      <c r="D417" s="14"/>
+      <c r="E417" s="14"/>
+    </row>
+    <row r="418" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A418" s="16"/>
+      <c r="B418" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="C418" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D418" s="14"/>
+      <c r="E418" s="14"/>
+    </row>
+    <row r="419" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A419" s="16"/>
+      <c r="B419" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C419" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D419" s="14"/>
+      <c r="E419" s="14"/>
+    </row>
+    <row r="420" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A420" s="16"/>
+      <c r="B420" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C420" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B421" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C421" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A422" s="36" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B414" s="32" t="s">
+    <row r="423" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B423" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="C414">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B415" s="32" t="s">
+      <c r="C423" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B424" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="C415">
+      <c r="C424" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A416" s="21" t="s">
-        <v>448</v>
-      </c>
-      <c r="B416" s="32" t="s">
+    <row r="425" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A425" s="26" t="s">
+        <v>447</v>
+      </c>
+      <c r="B425" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="C416">
+      <c r="C425" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B417" s="32" t="s">
+    <row r="426" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B426" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="C417">
+      <c r="C426" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B418" s="32" t="s">
+    <row r="427" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B427" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="C418">
+      <c r="C427" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B419" s="32" t="s">
+    <row r="428" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B428" s="28" t="s">
         <v>315</v>
       </c>
-      <c r="C419">
+      <c r="C428" s="8">
         <v>1.8</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B420" s="32" t="s">
+    <row r="429" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B429" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="C420">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B421" s="32" t="s">
+      <c r="C429" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B430" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="C421">
+      <c r="C430" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="422" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B422" s="32" t="s">
+    <row r="431" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B431" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="C422">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B423" s="32" t="s">
+      <c r="C431" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B432" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="C423">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B424" s="32"/>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B425" s="32"/>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B426" s="32"/>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A427" s="22" t="s">
+      <c r="C432" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B433" s="28"/>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B434" s="28"/>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B435" s="28"/>
+    </row>
+    <row r="436" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A436" s="36" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="428" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B428" s="32" t="s">
+    <row r="437" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B437" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="C428">
+      <c r="C437" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B429" s="32" t="s">
+    <row r="438" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B438" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="C429">
+      <c r="C438" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="430" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B430" s="32" t="s">
+    <row r="439" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B439" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="C430">
+      <c r="C439" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B431" s="32" t="s">
+    <row r="440" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B440" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="C431">
+      <c r="C440" s="8">
         <v>2.5</v>
       </c>
     </row>
-    <row r="432" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B432" s="32" t="s">
+    <row r="441" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B441" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="C432">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B433" s="32" t="s">
+      <c r="C441" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B442" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="C433">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B434" s="32" t="s">
+      <c r="C442" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B443" s="28" t="s">
         <v>326</v>
       </c>
-      <c r="C434">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B435" s="32"/>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A436" s="21" t="s">
-        <v>448</v>
+      <c r="C443" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B444" s="28"/>
+    </row>
+    <row r="445" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A445" s="26" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03E3A58-A324-684D-B93A-B460BCE514DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81347BAE-E32A-9949-8DF0-F10585CA99EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5913,7 +5913,7 @@
       <c r="D270" s="14"/>
       <c r="E270" s="14"/>
     </row>
-    <row r="271" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A271" s="29" t="s">
         <v>361</v>
       </c>
@@ -5923,10 +5923,12 @@
       <c r="C271" s="14">
         <v>2</v>
       </c>
-      <c r="D271" s="14"/>
+      <c r="D271" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E271" s="14"/>
     </row>
-    <row r="272" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A272" s="19"/>
       <c r="B272" s="31" t="s">
         <v>404</v>
@@ -5934,10 +5936,12 @@
       <c r="C272" s="14">
         <v>2</v>
       </c>
-      <c r="D272" s="14"/>
+      <c r="D272" s="14">
+        <v>3</v>
+      </c>
       <c r="E272" s="14"/>
     </row>
-    <row r="273" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A273" s="16"/>
       <c r="B273" s="28" t="s">
         <v>405</v>
@@ -7194,7 +7198,9 @@
       <c r="C415" s="14">
         <v>2</v>
       </c>
-      <c r="D415" s="14"/>
+      <c r="D415" s="14">
+        <v>2</v>
+      </c>
       <c r="E415" s="14"/>
     </row>
     <row r="416" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -7205,7 +7211,9 @@
       <c r="C416" s="14">
         <v>1.5</v>
       </c>
-      <c r="D416" s="14"/>
+      <c r="D416" s="14">
+        <v>1.8</v>
+      </c>
       <c r="E416" s="14"/>
     </row>
     <row r="417" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -7216,7 +7224,9 @@
       <c r="C417" s="14">
         <v>2.5</v>
       </c>
-      <c r="D417" s="14"/>
+      <c r="D417" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E417" s="14"/>
     </row>
     <row r="418" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -7227,7 +7237,9 @@
       <c r="C418" s="8">
         <v>1.5</v>
       </c>
-      <c r="D418" s="14"/>
+      <c r="D418" s="14">
+        <v>1</v>
+      </c>
       <c r="E418" s="14"/>
     </row>
     <row r="419" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -7238,7 +7250,9 @@
       <c r="C419" s="8">
         <v>1.5</v>
       </c>
-      <c r="D419" s="14"/>
+      <c r="D419" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E419" s="14"/>
     </row>
     <row r="420" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -7249,12 +7263,18 @@
       <c r="C420" s="8">
         <v>1</v>
       </c>
+      <c r="D420" s="8">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="421" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="B421" s="8" t="s">
         <v>500</v>
       </c>
       <c r="C421" s="8">
+        <v>1</v>
+      </c>
+      <c r="D421" s="8">
         <v>1</v>
       </c>
     </row>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81347BAE-E32A-9949-8DF0-F10585CA99EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3CF8DA-D5CB-0E49-9E86-F35202163010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5628,7 +5628,9 @@
       <c r="C246" s="14">
         <v>1.5</v>
       </c>
-      <c r="D246" s="14"/>
+      <c r="D246" s="14">
+        <v>1</v>
+      </c>
       <c r="E246" s="14"/>
     </row>
     <row r="247" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -5639,7 +5641,9 @@
       <c r="C247" s="14">
         <v>1.5</v>
       </c>
-      <c r="D247" s="14"/>
+      <c r="D247" s="14">
+        <v>1</v>
+      </c>
       <c r="E247" s="14"/>
     </row>
     <row r="248" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5650,7 +5654,9 @@
       <c r="C248" s="14">
         <v>2</v>
       </c>
-      <c r="D248" s="14"/>
+      <c r="D248" s="14">
+        <v>2</v>
+      </c>
       <c r="E248" s="14"/>
     </row>
     <row r="249" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5661,7 +5667,9 @@
       <c r="C249" s="14">
         <v>2</v>
       </c>
-      <c r="D249" s="14"/>
+      <c r="D249" s="14">
+        <v>2</v>
+      </c>
       <c r="E249" s="14"/>
     </row>
     <row r="250" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5672,7 +5680,9 @@
       <c r="C250" s="14">
         <v>1.5</v>
       </c>
-      <c r="D250" s="14"/>
+      <c r="D250" s="14">
+        <v>1</v>
+      </c>
       <c r="E250" s="14"/>
     </row>
     <row r="251" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5683,7 +5693,9 @@
       <c r="C251" s="14">
         <v>1</v>
       </c>
-      <c r="D251" s="14"/>
+      <c r="D251" s="14">
+        <v>0.8</v>
+      </c>
       <c r="E251" s="14"/>
     </row>
     <row r="252" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5694,7 +5706,9 @@
       <c r="C252" s="14">
         <v>2</v>
       </c>
-      <c r="D252" s="14"/>
+      <c r="D252" s="14">
+        <v>2</v>
+      </c>
       <c r="E252" s="14"/>
     </row>
     <row r="253" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5705,7 +5719,9 @@
       <c r="C253" s="14">
         <v>1.5</v>
       </c>
-      <c r="D253" s="14"/>
+      <c r="D253" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E253" s="14"/>
     </row>
     <row r="254" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5718,7 +5734,9 @@
       <c r="C254" s="14">
         <v>1</v>
       </c>
-      <c r="D254" s="14"/>
+      <c r="D254" s="14">
+        <v>1</v>
+      </c>
       <c r="E254" s="14"/>
     </row>
     <row r="255" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5729,7 +5747,9 @@
       <c r="C255" s="14">
         <v>1</v>
       </c>
-      <c r="D255" s="14"/>
+      <c r="D255" s="14">
+        <v>1</v>
+      </c>
       <c r="E255" s="14"/>
     </row>
     <row r="256" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5949,10 +5969,12 @@
       <c r="C273" s="14">
         <v>2.5</v>
       </c>
-      <c r="D273" s="14"/>
+      <c r="D273" s="14">
+        <v>3.8</v>
+      </c>
       <c r="E273" s="14"/>
     </row>
-    <row r="274" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A274" s="16"/>
       <c r="B274" s="28" t="s">
         <v>406</v>
@@ -5960,7 +5982,9 @@
       <c r="C274" s="14">
         <v>1.5</v>
       </c>
-      <c r="D274" s="14"/>
+      <c r="D274" s="14">
+        <v>2</v>
+      </c>
       <c r="E274" s="14"/>
     </row>
     <row r="275" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5971,10 +5995,12 @@
       <c r="C275" s="14">
         <v>2</v>
       </c>
-      <c r="D275" s="14"/>
+      <c r="D275" s="14">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="E275" s="14"/>
     </row>
-    <row r="276" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A276" s="16"/>
       <c r="B276" s="28" t="s">
         <v>408</v>
@@ -5982,7 +6008,9 @@
       <c r="C276" s="14">
         <v>1.5</v>
       </c>
-      <c r="D276" s="14"/>
+      <c r="D276" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E276" s="14"/>
     </row>
     <row r="277" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5993,10 +6021,12 @@
       <c r="C277" s="14">
         <v>2</v>
       </c>
-      <c r="D277" s="14"/>
+      <c r="D277" s="14">
+        <v>3.5</v>
+      </c>
       <c r="E277" s="14"/>
     </row>
-    <row r="278" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A278" s="16"/>
       <c r="B278" s="28" t="s">
         <v>410</v>
@@ -6004,7 +6034,9 @@
       <c r="C278" s="14">
         <v>2</v>
       </c>
-      <c r="D278" s="14"/>
+      <c r="D278" s="14">
+        <v>4</v>
+      </c>
       <c r="E278" s="14"/>
     </row>
     <row r="279" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6015,7 +6047,9 @@
       <c r="C279" s="14">
         <v>2</v>
       </c>
-      <c r="D279" s="14"/>
+      <c r="D279" s="14">
+        <v>2.8</v>
+      </c>
       <c r="E279" s="14"/>
     </row>
     <row r="280" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6026,7 +6060,9 @@
       <c r="C280" s="14">
         <v>2</v>
       </c>
-      <c r="D280" s="14"/>
+      <c r="D280" s="14">
+        <v>2</v>
+      </c>
       <c r="E280" s="14"/>
     </row>
     <row r="281" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6037,7 +6073,9 @@
       <c r="C281" s="14">
         <v>1.5</v>
       </c>
-      <c r="D281" s="14"/>
+      <c r="D281" s="14">
+        <v>1.2</v>
+      </c>
       <c r="E281" s="14"/>
     </row>
     <row r="282" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6048,7 +6086,9 @@
       <c r="C282" s="14">
         <v>1</v>
       </c>
-      <c r="D282" s="14"/>
+      <c r="D282" s="14">
+        <v>1</v>
+      </c>
       <c r="E282" s="14"/>
     </row>
     <row r="283" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6059,7 +6099,9 @@
       <c r="C283" s="14">
         <v>3</v>
       </c>
-      <c r="D283" s="14"/>
+      <c r="D283" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E283" s="14"/>
     </row>
     <row r="284" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6070,7 +6112,9 @@
       <c r="C284" s="14">
         <v>1.5</v>
       </c>
-      <c r="D284" s="14"/>
+      <c r="D284" s="14">
+        <v>2.8</v>
+      </c>
       <c r="E284" s="14"/>
     </row>
     <row r="285" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6081,7 +6125,9 @@
       <c r="C285" s="14">
         <v>1.5</v>
       </c>
-      <c r="D285" s="14"/>
+      <c r="D285" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E285" s="14"/>
     </row>
     <row r="286" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6092,7 +6138,9 @@
       <c r="C286" s="8">
         <v>2</v>
       </c>
-      <c r="D286" s="14"/>
+      <c r="D286" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E286" s="14"/>
     </row>
     <row r="287" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6103,7 +6151,9 @@
       <c r="C287" s="8">
         <v>1</v>
       </c>
-      <c r="D287" s="14"/>
+      <c r="D287" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E287" s="14"/>
     </row>
     <row r="288" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6114,7 +6164,9 @@
       <c r="C288" s="8">
         <v>1</v>
       </c>
-      <c r="D288" s="14"/>
+      <c r="D288" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E288" s="14"/>
     </row>
     <row r="289" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6431,26 +6483,30 @@
       <c r="B321" s="28"/>
     </row>
     <row r="322" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="29" t="s">
+        <v>367</v>
+      </c>
       <c r="B322" s="28" t="s">
         <v>434</v>
       </c>
       <c r="C322" s="14">
         <v>1.5</v>
       </c>
-      <c r="D322" s="14"/>
+      <c r="D322" s="14">
+        <v>1.2</v>
+      </c>
       <c r="E322" s="14"/>
     </row>
     <row r="323" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A323" s="29" t="s">
-        <v>367</v>
-      </c>
       <c r="B323" s="28" t="s">
         <v>435</v>
       </c>
       <c r="C323" s="14">
         <v>1.5</v>
       </c>
-      <c r="D323" s="14"/>
+      <c r="D323" s="14">
+        <v>2</v>
+      </c>
       <c r="E323" s="14"/>
     </row>
     <row r="324" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6461,7 +6517,9 @@
       <c r="C324" s="14">
         <v>1.5</v>
       </c>
-      <c r="D324" s="14"/>
+      <c r="D324" s="14">
+        <v>2</v>
+      </c>
       <c r="E324" s="14"/>
     </row>
     <row r="325" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6472,7 +6530,9 @@
       <c r="C325" s="14">
         <v>2</v>
       </c>
-      <c r="D325" s="14"/>
+      <c r="D325" s="14">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="E325" s="14"/>
     </row>
     <row r="326" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6483,7 +6543,9 @@
       <c r="C326" s="14">
         <v>1.5</v>
       </c>
-      <c r="D326" s="14"/>
+      <c r="D326" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E326" s="14"/>
     </row>
     <row r="327" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6494,7 +6556,9 @@
       <c r="C327" s="14">
         <v>1.2</v>
       </c>
-      <c r="D327" s="14"/>
+      <c r="D327" s="14">
+        <v>1</v>
+      </c>
       <c r="E327" s="14"/>
     </row>
     <row r="328" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6505,10 +6569,12 @@
       <c r="C328" s="14">
         <v>1</v>
       </c>
-      <c r="D328" s="14"/>
+      <c r="D328" s="14">
+        <v>0.8</v>
+      </c>
       <c r="E328" s="14"/>
     </row>
-    <row r="329" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A329" s="16"/>
       <c r="B329" s="28" t="s">
         <v>441</v>
@@ -6516,7 +6582,9 @@
       <c r="C329" s="14">
         <v>1.5</v>
       </c>
-      <c r="D329" s="14"/>
+      <c r="D329" s="14">
+        <v>1.8</v>
+      </c>
       <c r="E329" s="14"/>
     </row>
     <row r="330" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6527,7 +6595,9 @@
       <c r="C330" s="14">
         <v>2</v>
       </c>
-      <c r="D330" s="14"/>
+      <c r="D330" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E330" s="14"/>
     </row>
     <row r="331" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6538,7 +6608,9 @@
       <c r="C331" s="14">
         <v>1</v>
       </c>
-      <c r="D331" s="14"/>
+      <c r="D331" s="14">
+        <v>1</v>
+      </c>
       <c r="E331" s="14"/>
     </row>
     <row r="332" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6549,7 +6621,9 @@
       <c r="C332" s="8">
         <v>1.5</v>
       </c>
-      <c r="D332" s="14"/>
+      <c r="D332" s="14">
+        <v>1</v>
+      </c>
       <c r="E332" s="14"/>
     </row>
     <row r="333" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6560,7 +6634,9 @@
       <c r="C333" s="8">
         <v>1</v>
       </c>
-      <c r="D333" s="14"/>
+      <c r="D333" s="14">
+        <v>0.8</v>
+      </c>
       <c r="E333" s="14"/>
     </row>
     <row r="334" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6571,7 +6647,9 @@
       <c r="C334" s="8">
         <v>1</v>
       </c>
-      <c r="D334" s="14"/>
+      <c r="D334" s="8">
+        <v>0.5</v>
+      </c>
       <c r="E334" s="14"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3CF8DA-D5CB-0E49-9E86-F35202163010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A86670-290B-E641-9D85-D77CFCAD4344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="524">
   <si>
     <t>User story</t>
   </si>
@@ -1576,6 +1576,36 @@
   </si>
   <si>
     <t>RF14-18:Actualización pipeline Github</t>
+  </si>
+  <si>
+    <t>PREREQUISITOS:</t>
+  </si>
+  <si>
+    <t>RF14B-P01:Congelar contratos de salida (GraphState/Explanation/Score/Report) y añadir test de compatibilidad retro</t>
+  </si>
+  <si>
+    <t>RF14B-P02:  Centralizar carga de configuración y eliminar defaults duplicados entre CLI y nodos</t>
+  </si>
+  <si>
+    <t>RF14B-P03: Normalizar observabilidad local (logs + métricas + taxonomy de errores) antes de tracing externo</t>
+  </si>
+  <si>
+    <t>RF14B-P04: Definir y ejecutar release gate de regresión pre-LangSmith (subset RF14/RF15/RF15c/RF18)</t>
+  </si>
+  <si>
+    <t>RF14B-P05: Preparar baseline de secretos (`env.example`) y validación de variables obligatorias</t>
+  </si>
+  <si>
+    <t>RF14B-P06: Cerrar checklist pre-LangSmith y adjuntar evidencia en docs/pre_langsmith_checklist.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RF14b-11: Escribir/actualizar tests de integración (pytest) para este requisito</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RF14b-11: Actualizar documentación (README + runbook/docs) describiendo el comportamiento y cómo verificarlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RF14b-11: Ejecutar verificación de criterios de aceptación y guardar evidencia (artefactos + enlace de traza LangSmith +</t>
   </si>
 </sst>
 </file>
@@ -3153,7 +3183,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:E445"/>
+  <dimension ref="A2:E456"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.33203125" style="26" bestFit="1" customWidth="1"/>
@@ -5262,294 +5292,316 @@
       <c r="E212" s="14"/>
     </row>
     <row r="213" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="16"/>
+      <c r="A213" s="19"/>
       <c r="B213" s="28"/>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
       <c r="E213" s="14"/>
     </row>
-    <row r="214" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="29" t="s">
         <v>351</v>
       </c>
-      <c r="B214" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="C214" s="14">
-        <v>0.8</v>
-      </c>
+      <c r="B214" s="28"/>
+      <c r="C214" s="14"/>
       <c r="D214" s="14"/>
       <c r="E214" s="14"/>
     </row>
     <row r="215" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="16"/>
       <c r="B215" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="C215" s="14">
-        <v>1.2</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="C215" s="14"/>
       <c r="D215" s="14"/>
       <c r="E215" s="14"/>
     </row>
     <row r="216" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="16"/>
       <c r="B216" s="28" t="s">
-        <v>386</v>
+        <v>515</v>
       </c>
       <c r="C216" s="14">
-        <v>1</v>
-      </c>
-      <c r="D216" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D216" s="14">
+        <v>1.8</v>
+      </c>
       <c r="E216" s="14"/>
     </row>
     <row r="217" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="16"/>
       <c r="B217" s="28" t="s">
-        <v>387</v>
+        <v>516</v>
       </c>
       <c r="C217" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D217" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D217" s="14">
+        <v>2</v>
+      </c>
       <c r="E217" s="14"/>
     </row>
     <row r="218" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="16"/>
       <c r="B218" s="28" t="s">
-        <v>388</v>
+        <v>517</v>
       </c>
       <c r="C218" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D218" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D218" s="14">
+        <v>1.8</v>
+      </c>
       <c r="E218" s="14"/>
     </row>
     <row r="219" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="16"/>
       <c r="B219" s="28" t="s">
-        <v>389</v>
+        <v>518</v>
       </c>
       <c r="C219" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D219" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D219" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E219" s="14"/>
     </row>
     <row r="220" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="16"/>
       <c r="B220" s="28" t="s">
-        <v>390</v>
+        <v>519</v>
       </c>
       <c r="C220" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D220" s="14"/>
+        <v>0.8</v>
+      </c>
+      <c r="D220" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E220" s="14"/>
     </row>
     <row r="221" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="19"/>
-      <c r="B221" s="31" t="s">
-        <v>391</v>
+      <c r="A221" s="16"/>
+      <c r="B221" s="28" t="s">
+        <v>520</v>
       </c>
       <c r="C221" s="14">
-        <v>2</v>
-      </c>
-      <c r="D221" s="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="D221" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E221" s="14"/>
     </row>
-    <row r="222" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="16"/>
+    <row r="222" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A222" s="8"/>
       <c r="B222" s="28" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C222" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D222" s="14"/>
+        <v>0.8</v>
+      </c>
+      <c r="D222" s="14">
+        <v>1</v>
+      </c>
       <c r="E222" s="14"/>
     </row>
     <row r="223" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="16"/>
       <c r="B223" s="28" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C223" s="14">
-        <v>1</v>
-      </c>
-      <c r="D223" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D223" s="14">
+        <v>2</v>
+      </c>
       <c r="E223" s="14"/>
     </row>
     <row r="224" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="16"/>
-      <c r="B224" s="28"/>
-      <c r="C224" s="14"/>
-      <c r="D224" s="14"/>
+      <c r="B224" s="28" t="s">
+        <v>386</v>
+      </c>
+      <c r="C224" s="14">
+        <v>1</v>
+      </c>
+      <c r="D224" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E224" s="14"/>
     </row>
-    <row r="225" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A225" s="29" t="s">
-        <v>354</v>
-      </c>
+    <row r="225" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="16"/>
       <c r="B225" s="28" t="s">
-        <v>448</v>
+        <v>387</v>
       </c>
       <c r="C225" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D225" s="14"/>
+        <v>0.8</v>
+      </c>
+      <c r="D225" s="14">
+        <v>1</v>
+      </c>
       <c r="E225" s="14"/>
     </row>
-    <row r="226" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="16"/>
       <c r="B226" s="28" t="s">
-        <v>449</v>
+        <v>388</v>
       </c>
       <c r="C226" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="D226" s="14"/>
+        <v>2.5</v>
+      </c>
+      <c r="D226" s="14">
+        <v>0</v>
+      </c>
       <c r="E226" s="14"/>
     </row>
-    <row r="227" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="16"/>
       <c r="B227" s="28" t="s">
-        <v>450</v>
+        <v>389</v>
       </c>
       <c r="C227" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="D227" s="14"/>
+        <v>1.5</v>
+      </c>
+      <c r="D227" s="14">
+        <v>0</v>
+      </c>
       <c r="E227" s="14"/>
     </row>
-    <row r="228" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="16"/>
       <c r="B228" s="28" t="s">
-        <v>451</v>
+        <v>390</v>
       </c>
       <c r="C228" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D228" s="14"/>
+        <v>1.5</v>
+      </c>
+      <c r="D228" s="14">
+        <v>1.8</v>
+      </c>
       <c r="E228" s="14"/>
     </row>
     <row r="229" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="16"/>
-      <c r="B229" s="28" t="s">
-        <v>452</v>
+      <c r="A229" s="19"/>
+      <c r="B229" s="31" t="s">
+        <v>391</v>
       </c>
       <c r="C229" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D229" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="D229" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E229" s="14"/>
     </row>
     <row r="230" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="16"/>
       <c r="B230" s="28" t="s">
-        <v>453</v>
+        <v>392</v>
       </c>
       <c r="C230" s="14">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D230" s="14"/>
       <c r="E230" s="14"/>
     </row>
     <row r="231" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="19"/>
+      <c r="A231" s="16"/>
       <c r="B231" s="28" t="s">
-        <v>454</v>
+        <v>393</v>
       </c>
       <c r="C231" s="14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D231" s="14"/>
       <c r="E231" s="14"/>
     </row>
-    <row r="232" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A232" s="16"/>
-      <c r="B232" s="31" t="s">
-        <v>455</v>
+      <c r="B232" s="8" t="s">
+        <v>521</v>
       </c>
       <c r="C232" s="14">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D232" s="14"/>
       <c r="E232" s="14"/>
     </row>
-    <row r="233" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A233" s="16"/>
-      <c r="B233" s="28" t="s">
-        <v>456</v>
+      <c r="B233" s="8" t="s">
+        <v>522</v>
       </c>
       <c r="C233" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D233" s="14"/>
       <c r="E233" s="14"/>
     </row>
-    <row r="234" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A234" s="16"/>
-      <c r="B234" s="28" t="s">
-        <v>457</v>
+      <c r="B234" s="8" t="s">
+        <v>523</v>
       </c>
       <c r="C234" s="14">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="D234" s="14"/>
       <c r="E234" s="14"/>
     </row>
     <row r="235" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="16"/>
-      <c r="B235" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="C235" s="14">
-        <v>1.5</v>
-      </c>
+      <c r="B235" s="28"/>
+      <c r="C235" s="14"/>
       <c r="D235" s="14"/>
       <c r="E235" s="14"/>
     </row>
-    <row r="236" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="16"/>
+    <row r="236" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A236" s="29" t="s">
+        <v>354</v>
+      </c>
       <c r="B236" s="28" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C236" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D236" s="14"/>
       <c r="E236" s="14"/>
     </row>
-    <row r="237" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A237" s="16"/>
       <c r="B237" s="28" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C237" s="14">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D237" s="14"/>
       <c r="E237" s="14"/>
     </row>
-    <row r="238" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A238" s="16"/>
       <c r="B238" s="28" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="C238" s="14">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="D238" s="14"/>
       <c r="E238" s="14"/>
     </row>
-    <row r="239" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A239" s="16"/>
       <c r="B239" s="28" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C239" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="D239" s="14"/>
       <c r="E239" s="14"/>
@@ -5557,7 +5609,7 @@
     <row r="240" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="16"/>
       <c r="B240" s="28" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="C240" s="14">
         <v>1.2</v>
@@ -5568,188 +5620,168 @@
     <row r="241" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="16"/>
       <c r="B241" s="28" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C241" s="14">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="D241" s="14"/>
       <c r="E241" s="14"/>
     </row>
     <row r="242" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="16"/>
+      <c r="A242" s="19"/>
       <c r="B242" s="28" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
       <c r="C242" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="D242" s="14"/>
       <c r="E242" s="14"/>
     </row>
-    <row r="243" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="16"/>
-      <c r="B243" s="28" t="s">
-        <v>484</v>
+      <c r="B243" s="31" t="s">
+        <v>455</v>
       </c>
       <c r="C243" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D243" s="14"/>
       <c r="E243" s="14"/>
     </row>
-    <row r="244" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A244" s="16" t="s">
-        <v>447</v>
-      </c>
+    <row r="244" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="16"/>
       <c r="B244" s="28" t="s">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="C244" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D244" s="14"/>
       <c r="E244" s="14"/>
     </row>
     <row r="245" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="16"/>
-      <c r="B245" s="28"/>
-      <c r="C245" s="14"/>
+      <c r="B245" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="C245" s="14">
+        <v>1.8</v>
+      </c>
       <c r="D245" s="14"/>
       <c r="E245" s="14"/>
     </row>
-    <row r="246" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A246" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="B246" s="31" t="s">
-        <v>427</v>
+    <row r="246" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="16"/>
+      <c r="B246" s="28" t="s">
+        <v>458</v>
       </c>
       <c r="C246" s="14">
         <v>1.5</v>
       </c>
-      <c r="D246" s="14">
-        <v>1</v>
-      </c>
+      <c r="D246" s="14"/>
       <c r="E246" s="14"/>
     </row>
-    <row r="247" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="16"/>
       <c r="B247" s="28" t="s">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="C247" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D247" s="14">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D247" s="14"/>
       <c r="E247" s="14"/>
     </row>
     <row r="248" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="16"/>
       <c r="B248" s="28" t="s">
-        <v>429</v>
+        <v>460</v>
       </c>
       <c r="C248" s="14">
-        <v>2</v>
-      </c>
-      <c r="D248" s="14">
-        <v>2</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="D248" s="14"/>
       <c r="E248" s="14"/>
     </row>
     <row r="249" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="16"/>
       <c r="B249" s="28" t="s">
-        <v>430</v>
+        <v>461</v>
       </c>
       <c r="C249" s="14">
-        <v>2</v>
-      </c>
-      <c r="D249" s="14">
-        <v>2</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="D249" s="14"/>
       <c r="E249" s="14"/>
     </row>
     <row r="250" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="16"/>
       <c r="B250" s="28" t="s">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="C250" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D250" s="14">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D250" s="14"/>
       <c r="E250" s="14"/>
     </row>
     <row r="251" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="16"/>
       <c r="B251" s="28" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="C251" s="14">
-        <v>1</v>
-      </c>
-      <c r="D251" s="14">
-        <v>0.8</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="D251" s="14"/>
       <c r="E251" s="14"/>
     </row>
     <row r="252" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="16"/>
       <c r="B252" s="28" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="C252" s="14">
-        <v>2</v>
-      </c>
-      <c r="D252" s="14">
-        <v>2</v>
-      </c>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D252" s="14"/>
       <c r="E252" s="14"/>
     </row>
     <row r="253" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="16"/>
       <c r="B253" s="28" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C253" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D253" s="14">
-        <v>1.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D253" s="14"/>
       <c r="E253" s="14"/>
     </row>
-    <row r="254" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="16" t="s">
+    <row r="254" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A254" s="16"/>
+      <c r="B254" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="C254" s="14">
+        <v>1</v>
+      </c>
+      <c r="D254" s="14"/>
+      <c r="E254" s="14"/>
+    </row>
+    <row r="255" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A255" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="B254" s="28" t="s">
-        <v>487</v>
-      </c>
-      <c r="C254" s="14">
-        <v>1</v>
-      </c>
-      <c r="D254" s="14">
-        <v>1</v>
-      </c>
-      <c r="E254" s="14"/>
-    </row>
-    <row r="255" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="16"/>
       <c r="B255" s="28" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C255" s="14">
         <v>1</v>
       </c>
-      <c r="D255" s="14">
-        <v>1</v>
-      </c>
+      <c r="D255" s="14"/>
       <c r="E255" s="14"/>
     </row>
     <row r="256" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5760,11 +5792,11 @@
       <c r="E256" s="14"/>
     </row>
     <row r="257" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A257" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="B257" s="28" t="s">
-        <v>394</v>
+      <c r="A257" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="B257" s="31" t="s">
+        <v>427</v>
       </c>
       <c r="C257" s="14">
         <v>1.5</v>
@@ -5774,13 +5806,13 @@
       </c>
       <c r="E257" s="14"/>
     </row>
-    <row r="258" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A258" s="16"/>
       <c r="B258" s="28" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="C258" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D258" s="14">
         <v>1</v>
@@ -5788,61 +5820,61 @@
       <c r="E258" s="14"/>
     </row>
     <row r="259" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="19"/>
-      <c r="B259" s="31" t="s">
-        <v>396</v>
+      <c r="A259" s="16"/>
+      <c r="B259" s="28" t="s">
+        <v>429</v>
       </c>
       <c r="C259" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D259" s="14">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E259" s="14"/>
     </row>
     <row r="260" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="16"/>
       <c r="B260" s="28" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="C260" s="14">
         <v>2</v>
       </c>
       <c r="D260" s="14">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E260" s="14"/>
     </row>
     <row r="261" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="16"/>
       <c r="B261" s="28" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="C261" s="14">
         <v>1.5</v>
       </c>
       <c r="D261" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E261" s="14"/>
     </row>
     <row r="262" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="16"/>
       <c r="B262" s="28" t="s">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="C262" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D262" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="E262" s="14"/>
     </row>
     <row r="263" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="16"/>
       <c r="B263" s="28" t="s">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="C263" s="14">
         <v>2</v>
@@ -5855,33 +5887,35 @@
     <row r="264" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="16"/>
       <c r="B264" s="28" t="s">
-        <v>401</v>
+        <v>486</v>
       </c>
       <c r="C264" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D264" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E264" s="14"/>
     </row>
     <row r="265" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="16"/>
+      <c r="A265" s="16" t="s">
+        <v>447</v>
+      </c>
       <c r="B265" s="28" t="s">
-        <v>402</v>
+        <v>487</v>
       </c>
       <c r="C265" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D265" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E265" s="14"/>
     </row>
     <row r="266" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="16"/>
       <c r="B266" s="28" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C266" s="14">
         <v>1</v>
@@ -5893,94 +5927,98 @@
     </row>
     <row r="267" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="16"/>
-      <c r="B267" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="C267" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D267" s="14">
-        <v>0.8</v>
-      </c>
+      <c r="B267" s="28"/>
+      <c r="C267" s="14"/>
+      <c r="D267" s="14"/>
       <c r="E267" s="14"/>
     </row>
-    <row r="268" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="16"/>
+    <row r="268" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A268" s="29" t="s">
+        <v>358</v>
+      </c>
       <c r="B268" s="28" t="s">
-        <v>482</v>
+        <v>394</v>
       </c>
       <c r="C268" s="14">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D268" s="14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E268" s="14"/>
     </row>
     <row r="269" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="16"/>
-      <c r="B269" s="28"/>
-      <c r="C269" s="14"/>
-      <c r="D269" s="14"/>
+      <c r="B269" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="C269" s="14">
+        <v>1</v>
+      </c>
+      <c r="D269" s="14">
+        <v>1</v>
+      </c>
       <c r="E269" s="14"/>
     </row>
     <row r="270" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="B270" s="28"/>
-      <c r="C270" s="14"/>
-      <c r="D270" s="14"/>
+      <c r="A270" s="19"/>
+      <c r="B270" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="C270" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D270" s="14">
+        <v>1.2</v>
+      </c>
       <c r="E270" s="14"/>
     </row>
-    <row r="271" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A271" s="29" t="s">
-        <v>361</v>
-      </c>
+    <row r="271" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="16"/>
       <c r="B271" s="28" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C271" s="14">
         <v>2</v>
       </c>
       <c r="D271" s="14">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E271" s="14"/>
     </row>
-    <row r="272" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A272" s="19"/>
-      <c r="B272" s="31" t="s">
-        <v>404</v>
+    <row r="272" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="16"/>
+      <c r="B272" s="28" t="s">
+        <v>398</v>
       </c>
       <c r="C272" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D272" s="14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E272" s="14"/>
     </row>
-    <row r="273" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="16"/>
       <c r="B273" s="28" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C273" s="14">
         <v>2.5</v>
       </c>
       <c r="D273" s="14">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="E273" s="14"/>
     </row>
-    <row r="274" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="16"/>
       <c r="B274" s="28" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C274" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D274" s="14">
         <v>2</v>
@@ -5990,255 +6028,249 @@
     <row r="275" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="16"/>
       <c r="B275" s="28" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C275" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D275" s="14">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="E275" s="14"/>
     </row>
-    <row r="276" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="16"/>
       <c r="B276" s="28" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C276" s="14">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D276" s="14">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E276" s="14"/>
     </row>
     <row r="277" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="16"/>
       <c r="B277" s="28" t="s">
-        <v>409</v>
+        <v>480</v>
       </c>
       <c r="C277" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D277" s="14">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="E277" s="14"/>
     </row>
-    <row r="278" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="16"/>
       <c r="B278" s="28" t="s">
-        <v>410</v>
+        <v>481</v>
       </c>
       <c r="C278" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="D278" s="14">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="E278" s="14"/>
     </row>
     <row r="279" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="16"/>
       <c r="B279" s="28" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
       <c r="C279" s="14">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D279" s="14">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="E279" s="14"/>
     </row>
     <row r="280" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="16"/>
-      <c r="B280" s="28" t="s">
-        <v>412</v>
-      </c>
-      <c r="C280" s="14">
+      <c r="B280" s="28"/>
+      <c r="C280" s="14"/>
+      <c r="D280" s="14"/>
+      <c r="E280" s="14"/>
+    </row>
+    <row r="281" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B281" s="28"/>
+      <c r="C281" s="14"/>
+      <c r="D281" s="14"/>
+      <c r="E281" s="14"/>
+    </row>
+    <row r="282" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A282" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="B282" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="C282" s="14">
         <v>2</v>
       </c>
-      <c r="D280" s="14">
+      <c r="D282" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E282" s="14"/>
+    </row>
+    <row r="283" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A283" s="19"/>
+      <c r="B283" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="C283" s="14">
         <v>2</v>
       </c>
-      <c r="E280" s="14"/>
-    </row>
-    <row r="281" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="19"/>
-      <c r="B281" s="31" t="s">
-        <v>413</v>
-      </c>
-      <c r="C281" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D281" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="E281" s="14"/>
-    </row>
-    <row r="282" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="16"/>
-      <c r="B282" s="28" t="s">
-        <v>414</v>
-      </c>
-      <c r="C282" s="14">
-        <v>1</v>
-      </c>
-      <c r="D282" s="14">
-        <v>1</v>
-      </c>
-      <c r="E282" s="14"/>
-    </row>
-    <row r="283" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="16"/>
-      <c r="B283" s="28" t="s">
-        <v>415</v>
-      </c>
-      <c r="C283" s="14">
+      <c r="D283" s="14">
         <v>3</v>
       </c>
-      <c r="D283" s="14">
-        <v>2.5</v>
-      </c>
       <c r="E283" s="14"/>
     </row>
-    <row r="284" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A284" s="16"/>
       <c r="B284" s="28" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="C284" s="14">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D284" s="14">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="E284" s="14"/>
     </row>
-    <row r="285" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A285" s="16"/>
       <c r="B285" s="28" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C285" s="14">
         <v>1.5</v>
       </c>
       <c r="D285" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E285" s="14"/>
     </row>
     <row r="286" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="16"/>
       <c r="B286" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="C286" s="8">
+        <v>407</v>
+      </c>
+      <c r="C286" s="14">
         <v>2</v>
       </c>
       <c r="D286" s="14">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E286" s="14"/>
     </row>
-    <row r="287" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A287" s="16"/>
       <c r="B287" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="C287" s="8">
-        <v>1</v>
+        <v>408</v>
+      </c>
+      <c r="C287" s="14">
+        <v>1.5</v>
       </c>
       <c r="D287" s="14">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E287" s="14"/>
     </row>
     <row r="288" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="16"/>
       <c r="B288" s="28" t="s">
-        <v>491</v>
-      </c>
-      <c r="C288" s="8">
-        <v>1</v>
+        <v>409</v>
+      </c>
+      <c r="C288" s="14">
+        <v>2</v>
       </c>
       <c r="D288" s="14">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="E288" s="14"/>
     </row>
-    <row r="289" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="B289" s="28"/>
-      <c r="C289" s="14"/>
-      <c r="D289" s="14"/>
+    <row r="289" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A289" s="16"/>
+      <c r="B289" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C289" s="14">
+        <v>2</v>
+      </c>
+      <c r="D289" s="14">
+        <v>4</v>
+      </c>
       <c r="E289" s="14"/>
     </row>
-    <row r="290" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A290" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="B290" s="18" t="s">
-        <v>418</v>
+    <row r="290" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="16"/>
+      <c r="B290" s="28" t="s">
+        <v>411</v>
       </c>
       <c r="C290" s="14">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="D290" s="14">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="E290" s="14"/>
     </row>
     <row r="291" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="16"/>
-      <c r="B291" s="18" t="s">
-        <v>419</v>
+      <c r="B291" s="28" t="s">
+        <v>412</v>
       </c>
       <c r="C291" s="14">
         <v>2</v>
       </c>
       <c r="D291" s="14">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E291" s="14"/>
     </row>
     <row r="292" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="16"/>
-      <c r="B292" s="18" t="s">
-        <v>420</v>
+      <c r="A292" s="19"/>
+      <c r="B292" s="31" t="s">
+        <v>413</v>
       </c>
       <c r="C292" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D292" s="14">
         <v>1.2</v>
       </c>
-      <c r="D292" s="14">
-        <v>1.5</v>
-      </c>
       <c r="E292" s="14"/>
     </row>
     <row r="293" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="19"/>
-      <c r="B293" s="14" t="s">
-        <v>421</v>
+      <c r="A293" s="16"/>
+      <c r="B293" s="28" t="s">
+        <v>414</v>
       </c>
       <c r="C293" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D293" s="14">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E293" s="14"/>
     </row>
     <row r="294" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="16"/>
-      <c r="B294" s="18" t="s">
-        <v>422</v>
+      <c r="B294" s="28" t="s">
+        <v>415</v>
       </c>
       <c r="C294" s="14">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D294" s="14">
         <v>2.5</v>
@@ -6247,543 +6279,604 @@
     </row>
     <row r="295" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="16"/>
-      <c r="B295" s="18" t="s">
-        <v>423</v>
+      <c r="B295" s="28" t="s">
+        <v>416</v>
       </c>
       <c r="C295" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D295" s="14">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E295" s="14"/>
     </row>
     <row r="296" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="16"/>
-      <c r="B296" s="18" t="s">
-        <v>424</v>
+      <c r="B296" s="28" t="s">
+        <v>417</v>
       </c>
       <c r="C296" s="14">
         <v>1.5</v>
       </c>
       <c r="D296" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E296" s="14"/>
     </row>
     <row r="297" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="16"/>
-      <c r="B297" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="C297" s="14">
-        <v>3</v>
+      <c r="B297" s="28" t="s">
+        <v>489</v>
+      </c>
+      <c r="C297" s="8">
+        <v>2</v>
       </c>
       <c r="D297" s="14">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="E297" s="14"/>
     </row>
     <row r="298" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="16"/>
-      <c r="B298" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="C298" s="14">
-        <v>1.2</v>
+      <c r="B298" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="C298" s="8">
+        <v>1</v>
       </c>
       <c r="D298" s="14">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E298" s="14"/>
     </row>
     <row r="299" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="16"/>
-      <c r="B299" s="18" t="s">
+      <c r="B299" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="C299" s="8">
+        <v>1</v>
+      </c>
+      <c r="D299" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E299" s="14"/>
+    </row>
+    <row r="300" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B300" s="28"/>
+      <c r="C300" s="14"/>
+      <c r="D300" s="14"/>
+      <c r="E300" s="14"/>
+    </row>
+    <row r="301" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A301" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="B301" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="C301" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="D301" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E301" s="14"/>
+    </row>
+    <row r="302" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="16"/>
+      <c r="B302" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="C302" s="14">
+        <v>2</v>
+      </c>
+      <c r="D302" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="E302" s="14"/>
+    </row>
+    <row r="303" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="16"/>
+      <c r="B303" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="C303" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D303" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E303" s="14"/>
+    </row>
+    <row r="304" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" s="19"/>
+      <c r="B304" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="C304" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D304" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="E304" s="14"/>
+    </row>
+    <row r="305" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="16"/>
+      <c r="B305" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="C305" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D305" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E305" s="14"/>
+    </row>
+    <row r="306" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="16"/>
+      <c r="B306" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="C306" s="14">
+        <v>2</v>
+      </c>
+      <c r="D306" s="14">
+        <v>2</v>
+      </c>
+      <c r="E306" s="14"/>
+    </row>
+    <row r="307" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="16"/>
+      <c r="B307" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="C307" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D307" s="14">
+        <v>1</v>
+      </c>
+      <c r="E307" s="14"/>
+    </row>
+    <row r="308" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="16"/>
+      <c r="B308" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="C308" s="14">
+        <v>3</v>
+      </c>
+      <c r="D308" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="E308" s="14"/>
+    </row>
+    <row r="309" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309" s="16"/>
+      <c r="B309" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="C309" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D309" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E309" s="14"/>
+    </row>
+    <row r="310" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="16"/>
+      <c r="B310" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="C299" s="14">
+      <c r="C310" s="14">
         <v>1.2</v>
       </c>
-      <c r="D299" s="14">
-        <v>1</v>
-      </c>
-      <c r="E299" s="14"/>
-    </row>
-    <row r="300" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="16"/>
-      <c r="B300" s="18" t="s">
+      <c r="D310" s="14">
+        <v>1</v>
+      </c>
+      <c r="E310" s="14"/>
+    </row>
+    <row r="311" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311" s="16"/>
+      <c r="B311" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="C300" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D300" s="14">
-        <v>1</v>
-      </c>
-      <c r="E300" s="14"/>
-    </row>
-    <row r="301" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A301" s="16"/>
-      <c r="B301" s="18" t="s">
+      <c r="C311" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D311" s="14">
+        <v>1</v>
+      </c>
+      <c r="E311" s="14"/>
+    </row>
+    <row r="312" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A312" s="16"/>
+      <c r="B312" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="C301" s="14">
-        <v>1</v>
-      </c>
-      <c r="D301" s="8">
+      <c r="C312" s="14">
+        <v>1</v>
+      </c>
+      <c r="D312" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B302" s="18" t="s">
+    <row r="313" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B313" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="C302" s="14">
-        <v>1</v>
-      </c>
-      <c r="D302" s="8">
+      <c r="C313" s="14">
+        <v>1</v>
+      </c>
+      <c r="D313" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A303" s="36" t="s">
+    <row r="314" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A314" s="36" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B304" s="28" t="s">
+    <row r="315" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B315" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="C304" s="8">
+      <c r="C315" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B305" s="28" t="s">
+    <row r="316" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B316" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="C305" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B306" s="28" t="s">
+      <c r="C316" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B317" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="C306" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B307" s="28" t="s">
+      <c r="C317" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B318" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="C307" s="8">
+      <c r="C318" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B308" s="28" t="s">
+    <row r="319" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B319" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="C308" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B309" s="28" t="s">
+      <c r="C319" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B320" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="C309" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B310" s="28" t="s">
+      <c r="C320" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B321" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="C310" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B311" s="28" t="s">
+      <c r="C321" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B322" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="C311" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B312" s="28"/>
-    </row>
-    <row r="313" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A313" s="36" t="s">
+      <c r="C322" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B323" s="28"/>
+    </row>
+    <row r="324" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A324" s="36" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B314" s="28" t="s">
+    <row r="325" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B325" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="C314" s="8">
+      <c r="C325" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B315" s="28" t="s">
+    <row r="326" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B326" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="C315" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B316" s="28" t="s">
+      <c r="C326" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B327" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="C316" s="8">
+      <c r="C327" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B317" s="28" t="s">
+    <row r="328" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B328" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="C317" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B318" s="28" t="s">
+      <c r="C328" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B329" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="C318" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B319" s="28" t="s">
+      <c r="C329" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B330" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="C319" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B320" s="28" t="s">
+      <c r="C330" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B331" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="C320" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B321" s="28"/>
-    </row>
-    <row r="322" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A322" s="29" t="s">
+      <c r="C331" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B332" s="28"/>
+    </row>
+    <row r="333" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="29" t="s">
         <v>367</v>
       </c>
-      <c r="B322" s="28" t="s">
+      <c r="B333" s="28" t="s">
         <v>434</v>
       </c>
-      <c r="C322" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D322" s="14">
+      <c r="C333" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D333" s="14">
         <v>1.2</v>
       </c>
-      <c r="E322" s="14"/>
-    </row>
-    <row r="323" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B323" s="28" t="s">
+      <c r="E333" s="14"/>
+    </row>
+    <row r="334" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B334" s="28" t="s">
         <v>435</v>
       </c>
-      <c r="C323" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D323" s="14">
+      <c r="C334" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D334" s="14">
         <v>2</v>
       </c>
-      <c r="E323" s="14"/>
-    </row>
-    <row r="324" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A324" s="16"/>
-      <c r="B324" s="28" t="s">
+      <c r="E334" s="14"/>
+    </row>
+    <row r="335" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A335" s="16"/>
+      <c r="B335" s="28" t="s">
         <v>436</v>
       </c>
-      <c r="C324" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D324" s="14">
+      <c r="C335" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D335" s="14">
         <v>2</v>
       </c>
-      <c r="E324" s="14"/>
-    </row>
-    <row r="325" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A325" s="16"/>
-      <c r="B325" s="28" t="s">
+      <c r="E335" s="14"/>
+    </row>
+    <row r="336" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A336" s="16"/>
+      <c r="B336" s="28" t="s">
         <v>437</v>
       </c>
-      <c r="C325" s="14">
+      <c r="C336" s="14">
         <v>2</v>
       </c>
-      <c r="D325" s="14">
+      <c r="D336" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E325" s="14"/>
-    </row>
-    <row r="326" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A326" s="16"/>
-      <c r="B326" s="28" t="s">
+      <c r="E336" s="14"/>
+    </row>
+    <row r="337" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A337" s="16"/>
+      <c r="B337" s="28" t="s">
         <v>438</v>
       </c>
-      <c r="C326" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D326" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E326" s="14"/>
-    </row>
-    <row r="327" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A327" s="16"/>
-      <c r="B327" s="28" t="s">
+      <c r="C337" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D337" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E337" s="14"/>
+    </row>
+    <row r="338" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338" s="16"/>
+      <c r="B338" s="28" t="s">
         <v>439</v>
       </c>
-      <c r="C327" s="14">
+      <c r="C338" s="14">
         <v>1.2</v>
       </c>
-      <c r="D327" s="14">
-        <v>1</v>
-      </c>
-      <c r="E327" s="14"/>
-    </row>
-    <row r="328" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A328" s="16"/>
-      <c r="B328" s="28" t="s">
+      <c r="D338" s="14">
+        <v>1</v>
+      </c>
+      <c r="E338" s="14"/>
+    </row>
+    <row r="339" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A339" s="16"/>
+      <c r="B339" s="28" t="s">
         <v>440</v>
       </c>
-      <c r="C328" s="14">
-        <v>1</v>
-      </c>
-      <c r="D328" s="14">
+      <c r="C339" s="14">
+        <v>1</v>
+      </c>
+      <c r="D339" s="14">
         <v>0.8</v>
       </c>
-      <c r="E328" s="14"/>
-    </row>
-    <row r="329" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A329" s="16"/>
-      <c r="B329" s="28" t="s">
+      <c r="E339" s="14"/>
+    </row>
+    <row r="340" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A340" s="16"/>
+      <c r="B340" s="28" t="s">
         <v>441</v>
       </c>
-      <c r="C329" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D329" s="14">
+      <c r="C340" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D340" s="14">
         <v>1.8</v>
       </c>
-      <c r="E329" s="14"/>
-    </row>
-    <row r="330" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A330" s="16"/>
-      <c r="B330" s="28" t="s">
+      <c r="E340" s="14"/>
+    </row>
+    <row r="341" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="16"/>
+      <c r="B341" s="28" t="s">
         <v>442</v>
       </c>
-      <c r="C330" s="14">
+      <c r="C341" s="14">
         <v>2</v>
       </c>
-      <c r="D330" s="14">
+      <c r="D341" s="14">
         <v>2.5</v>
       </c>
-      <c r="E330" s="14"/>
-    </row>
-    <row r="331" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A331" s="16"/>
-      <c r="B331" s="28" t="s">
+      <c r="E341" s="14"/>
+    </row>
+    <row r="342" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A342" s="16"/>
+      <c r="B342" s="28" t="s">
         <v>443</v>
       </c>
-      <c r="C331" s="14">
-        <v>1</v>
-      </c>
-      <c r="D331" s="14">
-        <v>1</v>
-      </c>
-      <c r="E331" s="14"/>
-    </row>
-    <row r="332" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A332" s="16"/>
-      <c r="B332" s="28" t="s">
+      <c r="C342" s="14">
+        <v>1</v>
+      </c>
+      <c r="D342" s="14">
+        <v>1</v>
+      </c>
+      <c r="E342" s="14"/>
+    </row>
+    <row r="343" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="16"/>
+      <c r="B343" s="28" t="s">
         <v>495</v>
       </c>
-      <c r="C332" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D332" s="14">
-        <v>1</v>
-      </c>
-      <c r="E332" s="14"/>
-    </row>
-    <row r="333" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A333" s="16"/>
-      <c r="B333" s="28" t="s">
+      <c r="C343" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D343" s="14">
+        <v>1</v>
+      </c>
+      <c r="E343" s="14"/>
+    </row>
+    <row r="344" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="16"/>
+      <c r="B344" s="28" t="s">
         <v>496</v>
       </c>
-      <c r="C333" s="8">
-        <v>1</v>
-      </c>
-      <c r="D333" s="14">
+      <c r="C344" s="8">
+        <v>1</v>
+      </c>
+      <c r="D344" s="14">
         <v>0.8</v>
       </c>
-      <c r="E333" s="14"/>
-    </row>
-    <row r="334" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A334" s="16"/>
-      <c r="B334" s="28" t="s">
+      <c r="E344" s="14"/>
+    </row>
+    <row r="345" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A345" s="16"/>
+      <c r="B345" s="28" t="s">
         <v>497</v>
       </c>
-      <c r="C334" s="8">
-        <v>1</v>
-      </c>
-      <c r="D334" s="8">
+      <c r="C345" s="8">
+        <v>1</v>
+      </c>
+      <c r="D345" s="8">
         <v>0.5</v>
       </c>
-      <c r="E334" s="14"/>
-    </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A335" s="16"/>
-      <c r="B335" s="28"/>
-    </row>
-    <row r="336" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A336" s="36" t="s">
+      <c r="E345" s="14"/>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A346" s="16"/>
+      <c r="B346" s="28"/>
+    </row>
+    <row r="347" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A347" s="36" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B337" s="28" t="s">
+    <row r="348" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B348" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="C337" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B338" s="28" t="s">
+      <c r="C348" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B349" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="C338" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B339" s="28" t="s">
+      <c r="C349" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B350" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="C339" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B340" s="28" t="s">
+      <c r="C350" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B351" s="28" t="s">
         <v>258</v>
-      </c>
-      <c r="C340" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B341" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="C341" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B342" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="C342" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B343" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="C343" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B344" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="C344" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B345" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C345" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B346" s="28"/>
-    </row>
-    <row r="347" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A347" s="36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B348" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="C348" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B349" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="C349" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B350" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="C350" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B351" s="28" t="s">
-        <v>267</v>
       </c>
       <c r="C351" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B352" s="28" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C352" s="8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B353" s="28" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C353" s="8">
         <v>1</v>
@@ -6791,183 +6884,183 @@
     </row>
     <row r="354" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B354" s="28" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C354" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B355" s="28"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B355" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="C355" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="356" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A356" s="36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B357" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="C357" s="8">
-        <v>0.8</v>
-      </c>
+      <c r="B356" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C356" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B357" s="28"/>
     </row>
     <row r="358" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B358" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="C358" s="8">
-        <v>0.8</v>
+      <c r="A358" s="36" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B359" s="28" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C359" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B360" s="28" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C360" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B361" s="28" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C361" s="8">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B362" s="28" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C362" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B363" s="28" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C363" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B364" s="28"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B364" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="C364" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="365" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A365" s="36" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B366" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="C366" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B367" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="C367" s="8">
-        <v>1.5</v>
+      <c r="B365" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="C365" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B366" s="28"/>
+    </row>
+    <row r="367" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A367" s="36" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B368" s="28" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C368" s="8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B369" s="28" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C369" s="8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B370" s="28" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C370" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B371" s="28" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C371" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B372" s="28" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C372" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B373" s="28"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B373" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="C373" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="374" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A374" s="36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B375" s="28" t="s">
-        <v>285</v>
-      </c>
-      <c r="C375" s="8">
-        <v>1.5</v>
-      </c>
+      <c r="B374" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="C374" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B375" s="28"/>
     </row>
     <row r="376" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B376" s="28" t="s">
-        <v>286</v>
-      </c>
-      <c r="C376" s="8">
-        <v>1.5</v>
+      <c r="A376" s="36" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B377" s="28" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C377" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B378" s="28" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C378" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B379" s="28" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C379" s="8">
         <v>1</v>
@@ -6975,111 +7068,111 @@
     </row>
     <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B380" s="28" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="C380" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B381" s="28"/>
-    </row>
-    <row r="382" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A382" s="36" t="s">
-        <v>75</v>
+    <row r="381" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B381" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="C381" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B382" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="C382" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B383" s="28" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C383" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B384" s="28" t="s">
-        <v>292</v>
-      </c>
-      <c r="C384" s="8">
-        <v>1.2</v>
-      </c>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B384" s="28"/>
     </row>
     <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B385" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="C385" s="8">
-        <v>0.8</v>
+      <c r="A385" s="36" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B386" s="28" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C386" s="8">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B387" s="28" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C387" s="8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B388" s="28" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C388" s="8">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B389" s="28" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C389" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B390" s="28"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B390" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="C390" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="391" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A391" s="36" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B392" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="C392" s="8">
-        <v>1.2</v>
-      </c>
+      <c r="B391" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="C391" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B392" s="28"/>
     </row>
     <row r="393" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B393" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="C393" s="8">
-        <v>1</v>
+      <c r="A393" s="36" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B394" s="28" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C394" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B395" s="28" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C395" s="8">
         <v>1.2</v>
@@ -7087,380 +7180,390 @@
     </row>
     <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B396" s="28" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C396" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B397" s="28" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C397" s="8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B398" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="C398" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B399" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="C399" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B400" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C400" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B401" s="28"/>
+    </row>
+    <row r="402" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A402" s="36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B403" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="C403" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B404" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="C404" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B405" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="C405" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B406" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="C406" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B407" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="C407" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B408" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="C408" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B409" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="C398" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B399" s="28"/>
-    </row>
-    <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A400" s="36" t="s">
+      <c r="C409" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B410" s="28"/>
+    </row>
+    <row r="411" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A411" s="36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B401" s="28" t="s">
+    <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B412" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="C401" s="8">
+      <c r="C412" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B402" s="28" t="s">
+    <row r="413" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B413" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="C402" s="8">
+      <c r="C413" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B403" s="28" t="s">
+    <row r="414" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B414" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="C403" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B404" s="28" t="s">
+      <c r="C414" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B415" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="C404" s="8">
+      <c r="C415" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B405" s="28" t="s">
+    <row r="416" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B416" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="C405" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B406" s="28"/>
-      <c r="D406" s="14"/>
-      <c r="E406" s="14"/>
-    </row>
-    <row r="407" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A407" s="29" t="s">
+      <c r="C416" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B417" s="28"/>
+      <c r="D417" s="14"/>
+      <c r="E417" s="14"/>
+    </row>
+    <row r="418" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A418" s="29" t="s">
         <v>475</v>
       </c>
-      <c r="B407" s="31" t="s">
+      <c r="B418" s="31" t="s">
         <v>502</v>
       </c>
-      <c r="C407" s="14">
+      <c r="C418" s="14">
         <v>1.2</v>
       </c>
-      <c r="D407" s="14">
+      <c r="D418" s="14">
         <v>0.8</v>
       </c>
-      <c r="E407" s="14"/>
-    </row>
-    <row r="408" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A408" s="16"/>
-      <c r="B408" s="31" t="s">
+      <c r="E418" s="14"/>
+    </row>
+    <row r="419" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A419" s="16"/>
+      <c r="B419" s="31" t="s">
         <v>465</v>
       </c>
-      <c r="C408" s="14">
+      <c r="C419" s="14">
         <v>1.2</v>
       </c>
-      <c r="D408" s="14">
+      <c r="D419" s="14">
         <v>0.8</v>
       </c>
-      <c r="E408" s="14"/>
-    </row>
-    <row r="409" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A409" s="16"/>
-      <c r="B409" s="31" t="s">
+      <c r="E419" s="14"/>
+    </row>
+    <row r="420" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A420" s="16"/>
+      <c r="B420" s="31" t="s">
         <v>466</v>
       </c>
-      <c r="C409" s="14">
+      <c r="C420" s="14">
         <v>0.8</v>
       </c>
-      <c r="D409" s="14">
+      <c r="D420" s="14">
         <v>0.5</v>
       </c>
-      <c r="E409" s="14"/>
-    </row>
-    <row r="410" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A410" s="16"/>
-      <c r="B410" s="31" t="s">
+      <c r="E420" s="14"/>
+    </row>
+    <row r="421" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A421" s="16"/>
+      <c r="B421" s="31" t="s">
         <v>467</v>
       </c>
-      <c r="C410" s="14">
-        <v>1</v>
-      </c>
-      <c r="D410" s="14">
-        <v>1</v>
-      </c>
-      <c r="E410" s="14"/>
-    </row>
-    <row r="411" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A411" s="16"/>
-      <c r="B411" s="31" t="s">
+      <c r="C421" s="14">
+        <v>1</v>
+      </c>
+      <c r="D421" s="14">
+        <v>1</v>
+      </c>
+      <c r="E421" s="14"/>
+    </row>
+    <row r="422" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A422" s="16"/>
+      <c r="B422" s="31" t="s">
         <v>468</v>
       </c>
-      <c r="C411" s="14">
+      <c r="C422" s="14">
         <v>2</v>
       </c>
-      <c r="D411" s="14">
+      <c r="D422" s="14">
         <v>1.8</v>
       </c>
-      <c r="E411" s="14"/>
-    </row>
-    <row r="412" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A412" s="16"/>
-      <c r="B412" s="31" t="s">
+      <c r="E422" s="14"/>
+    </row>
+    <row r="423" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A423" s="16"/>
+      <c r="B423" s="31" t="s">
         <v>503</v>
       </c>
-      <c r="C412" s="14">
+      <c r="C423" s="14">
         <v>1.2</v>
       </c>
-      <c r="D412" s="14">
-        <v>1</v>
-      </c>
-      <c r="E412" s="14"/>
-    </row>
-    <row r="413" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A413" s="16"/>
-      <c r="B413" s="31" t="s">
+      <c r="D423" s="14">
+        <v>1</v>
+      </c>
+      <c r="E423" s="14"/>
+    </row>
+    <row r="424" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A424" s="16"/>
+      <c r="B424" s="31" t="s">
         <v>469</v>
       </c>
-      <c r="C413" s="14">
-        <v>1</v>
-      </c>
-      <c r="D413" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E413" s="14"/>
-    </row>
-    <row r="414" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A414" s="16"/>
-      <c r="B414" s="31" t="s">
+      <c r="C424" s="14">
+        <v>1</v>
+      </c>
+      <c r="D424" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E424" s="14"/>
+    </row>
+    <row r="425" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A425" s="16"/>
+      <c r="B425" s="31" t="s">
         <v>470</v>
       </c>
-      <c r="C414" s="14">
+      <c r="C425" s="14">
         <v>2</v>
       </c>
-      <c r="D414" s="14">
+      <c r="D425" s="14">
         <v>2</v>
       </c>
-      <c r="E414" s="14"/>
-    </row>
-    <row r="415" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A415" s="16"/>
-      <c r="B415" s="31" t="s">
+      <c r="E425" s="14"/>
+    </row>
+    <row r="426" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A426" s="16"/>
+      <c r="B426" s="31" t="s">
         <v>471</v>
       </c>
-      <c r="C415" s="14">
+      <c r="C426" s="14">
         <v>2</v>
       </c>
-      <c r="D415" s="14">
+      <c r="D426" s="14">
         <v>2</v>
       </c>
-      <c r="E415" s="14"/>
-    </row>
-    <row r="416" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A416" s="16"/>
-      <c r="B416" s="31" t="s">
+      <c r="E426" s="14"/>
+    </row>
+    <row r="427" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A427" s="16"/>
+      <c r="B427" s="31" t="s">
         <v>472</v>
       </c>
-      <c r="C416" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D416" s="14">
+      <c r="C427" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D427" s="14">
         <v>1.8</v>
       </c>
-      <c r="E416" s="14"/>
-    </row>
-    <row r="417" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A417" s="16"/>
-      <c r="B417" s="31" t="s">
+      <c r="E427" s="14"/>
+    </row>
+    <row r="428" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A428" s="16"/>
+      <c r="B428" s="31" t="s">
         <v>473</v>
       </c>
-      <c r="C417" s="14">
+      <c r="C428" s="14">
         <v>2.5</v>
       </c>
-      <c r="D417" s="14">
+      <c r="D428" s="14">
         <v>2.5</v>
       </c>
-      <c r="E417" s="14"/>
-    </row>
-    <row r="418" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A418" s="16"/>
-      <c r="B418" s="37" t="s">
+      <c r="E428" s="14"/>
+    </row>
+    <row r="429" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A429" s="16"/>
+      <c r="B429" s="37" t="s">
         <v>474</v>
       </c>
-      <c r="C418" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D418" s="14">
-        <v>1</v>
-      </c>
-      <c r="E418" s="14"/>
-    </row>
-    <row r="419" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A419" s="16"/>
-      <c r="B419" s="8" t="s">
+      <c r="C429" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D429" s="14">
+        <v>1</v>
+      </c>
+      <c r="E429" s="14"/>
+    </row>
+    <row r="430" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A430" s="16"/>
+      <c r="B430" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="C419" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D419" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E419" s="14"/>
-    </row>
-    <row r="420" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A420" s="16"/>
-      <c r="B420" s="8" t="s">
+      <c r="C430" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D430" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E430" s="14"/>
+    </row>
+    <row r="431" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A431" s="16"/>
+      <c r="B431" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="C420" s="8">
-        <v>1</v>
-      </c>
-      <c r="D420" s="8">
+      <c r="C431" s="8">
+        <v>1</v>
+      </c>
+      <c r="D431" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B421" s="8" t="s">
+    <row r="432" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B432" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="C421" s="8">
-        <v>1</v>
-      </c>
-      <c r="D421" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="422" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A422" s="36" t="s">
+      <c r="C432" s="8">
+        <v>1</v>
+      </c>
+      <c r="D432" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A433" s="36" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B423" s="28" t="s">
+    <row r="434" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B434" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="C423" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B424" s="28" t="s">
+      <c r="C434" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B435" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="C424" s="8">
+      <c r="C435" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A425" s="26" t="s">
+    <row r="436" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A436" s="26" t="s">
         <v>447</v>
       </c>
-      <c r="B425" s="28" t="s">
+      <c r="B436" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="C425" s="8">
+      <c r="C436" s="8">
         <v>1.2</v>
-      </c>
-    </row>
-    <row r="426" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B426" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="C426" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="427" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B427" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="C427" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="428" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B428" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="C428" s="8">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="429" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B429" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="C429" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="430" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B430" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="C430" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="431" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B431" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="C431" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="432" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B432" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="C432" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B433" s="28"/>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B434" s="28"/>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B435" s="28"/>
-    </row>
-    <row r="436" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A436" s="36" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B437" s="28" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C437" s="8">
         <v>2</v>
@@ -7468,39 +7571,39 @@
     </row>
     <row r="438" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B438" s="28" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C438" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B439" s="28" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C439" s="8">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B440" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C440" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B441" s="28" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C441" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B442" s="28" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C442" s="8">
         <v>1</v>
@@ -7508,7 +7611,7 @@
     </row>
     <row r="443" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B443" s="28" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C443" s="8">
         <v>1</v>
@@ -7517,8 +7620,78 @@
     <row r="444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B444" s="28"/>
     </row>
-    <row r="445" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A445" s="26" t="s">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B445" s="28"/>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B446" s="28"/>
+    </row>
+    <row r="447" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A447" s="36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B448" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="C448" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B449" s="28" t="s">
+        <v>321</v>
+      </c>
+      <c r="C449" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B450" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="C450" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B451" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="C451" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B452" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="C452" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B453" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="C453" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B454" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="C454" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B455" s="28"/>
+    </row>
+    <row r="456" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A456" s="26" t="s">
         <v>447</v>
       </c>
     </row>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A86670-290B-E641-9D85-D77CFCAD4344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BC9D80-3BDB-6345-A51B-E7804F2BCBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5506,7 +5506,9 @@
       <c r="C230" s="14">
         <v>1.2</v>
       </c>
-      <c r="D230" s="14"/>
+      <c r="D230" s="14">
+        <v>1</v>
+      </c>
       <c r="E230" s="14"/>
     </row>
     <row r="231" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5517,10 +5519,12 @@
       <c r="C231" s="14">
         <v>1</v>
       </c>
-      <c r="D231" s="14"/>
+      <c r="D231" s="14">
+        <v>1</v>
+      </c>
       <c r="E231" s="14"/>
     </row>
-    <row r="232" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A232" s="16"/>
       <c r="B232" s="8" t="s">
         <v>521</v>
@@ -5528,7 +5532,9 @@
       <c r="C232" s="14">
         <v>2</v>
       </c>
-      <c r="D232" s="14"/>
+      <c r="D232" s="14">
+        <v>1</v>
+      </c>
       <c r="E232" s="14"/>
     </row>
     <row r="233" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -5539,7 +5545,9 @@
       <c r="C233" s="14">
         <v>1</v>
       </c>
-      <c r="D233" s="14"/>
+      <c r="D233" s="14">
+        <v>1.2</v>
+      </c>
       <c r="E233" s="14"/>
     </row>
     <row r="234" spans="1:5" ht="34" x14ac:dyDescent="0.2">
@@ -5550,7 +5558,9 @@
       <c r="C234" s="14">
         <v>1</v>
       </c>
-      <c r="D234" s="14"/>
+      <c r="D234" s="14">
+        <v>1</v>
+      </c>
       <c r="E234" s="14"/>
     </row>
     <row r="235" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BC9D80-3BDB-6345-A51B-E7804F2BCBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6170307C-5A4C-2E4C-911A-2126ED0E1B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REQUISITOS" sheetId="1" r:id="rId1"/>
@@ -1685,7 +1685,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1738,6 +1738,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1779,7 +1785,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1909,6 +1915,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2576,28 +2597,28 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:9" s="49" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="47">
         <v>8</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="E17" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="48"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
     </row>
     <row r="18" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
@@ -3194,7 +3215,7 @@
     <col min="6" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>93</v>
       </c>
@@ -4894,7 +4915,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B181" s="28" t="s">
         <v>233</v>
       </c>
@@ -4927,7 +4948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B184" s="28" t="s">
         <v>236</v>
       </c>
@@ -4957,7 +4978,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B187" s="28" t="s">
         <v>239</v>
       </c>
@@ -4994,7 +5015,7 @@
       </c>
       <c r="E189" s="14"/>
     </row>
-    <row r="190" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A190" s="14"/>
       <c r="B190" s="28" t="s">
         <v>507</v>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6170307C-5A4C-2E4C-911A-2126ED0E1B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6188DC8E-0774-D94B-8F89-CE31232806A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REQUISITOS" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="525">
   <si>
     <t>User story</t>
   </si>
@@ -1606,6 +1606,9 @@
   </si>
   <si>
     <t xml:space="preserve"> RF14b-11: Ejecutar verificación de criterios de aceptación y guardar evidencia (artefactos + enlace de traza LangSmith +</t>
+  </si>
+  <si>
+    <t>RF15-11: Actualizar proyecto para que fraud type proceda de documentación oficial</t>
   </si>
 </sst>
 </file>
@@ -3204,7 +3207,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:E456"/>
+  <dimension ref="A2:E457"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.33203125" style="26" bestFit="1" customWidth="1"/>
@@ -5958,98 +5961,98 @@
     </row>
     <row r="267" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="16"/>
-      <c r="B267" s="28"/>
-      <c r="C267" s="14"/>
-      <c r="D267" s="14"/>
+      <c r="B267" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="C267" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D267" s="14">
+        <v>1.5</v>
+      </c>
       <c r="E267" s="14"/>
     </row>
-    <row r="268" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A268" s="29" t="s">
+    <row r="268" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="16"/>
+      <c r="B268" s="28"/>
+      <c r="C268" s="14"/>
+      <c r="D268" s="14"/>
+      <c r="E268" s="14"/>
+    </row>
+    <row r="269" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A269" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="B268" s="28" t="s">
+      <c r="B269" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="C268" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D268" s="14">
-        <v>1</v>
-      </c>
-      <c r="E268" s="14"/>
-    </row>
-    <row r="269" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="16"/>
-      <c r="B269" s="28" t="s">
+      <c r="C269" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D269" s="14">
+        <v>1</v>
+      </c>
+      <c r="E269" s="14"/>
+    </row>
+    <row r="270" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" s="16"/>
+      <c r="B270" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="C269" s="14">
-        <v>1</v>
-      </c>
-      <c r="D269" s="14">
-        <v>1</v>
-      </c>
-      <c r="E269" s="14"/>
-    </row>
-    <row r="270" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="19"/>
-      <c r="B270" s="31" t="s">
+      <c r="C270" s="14">
+        <v>1</v>
+      </c>
+      <c r="D270" s="14">
+        <v>1</v>
+      </c>
+      <c r="E270" s="14"/>
+    </row>
+    <row r="271" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="19"/>
+      <c r="B271" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="C270" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D270" s="14">
+      <c r="C271" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D271" s="14">
         <v>1.2</v>
-      </c>
-      <c r="E270" s="14"/>
-    </row>
-    <row r="271" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="16"/>
-      <c r="B271" s="28" t="s">
-        <v>397</v>
-      </c>
-      <c r="C271" s="14">
-        <v>2</v>
-      </c>
-      <c r="D271" s="14">
-        <v>1.8</v>
       </c>
       <c r="E271" s="14"/>
     </row>
     <row r="272" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="16"/>
       <c r="B272" s="28" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C272" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D272" s="14">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="E272" s="14"/>
     </row>
     <row r="273" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="16"/>
       <c r="B273" s="28" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C273" s="14">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D273" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E273" s="14"/>
     </row>
     <row r="274" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="16"/>
       <c r="B274" s="28" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C274" s="14">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D274" s="14">
         <v>2</v>
@@ -6059,288 +6062,288 @@
     <row r="275" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="16"/>
       <c r="B275" s="28" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C275" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D275" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E275" s="14"/>
     </row>
     <row r="276" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="16"/>
       <c r="B276" s="28" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C276" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D276" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E276" s="14"/>
     </row>
     <row r="277" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="16"/>
       <c r="B277" s="28" t="s">
-        <v>480</v>
+        <v>402</v>
       </c>
       <c r="C277" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D277" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E277" s="14"/>
     </row>
     <row r="278" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="16"/>
       <c r="B278" s="28" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C278" s="14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D278" s="14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E278" s="14"/>
     </row>
     <row r="279" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="16"/>
       <c r="B279" s="28" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C279" s="14">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D279" s="14">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E279" s="14"/>
     </row>
     <row r="280" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="16"/>
-      <c r="B280" s="28"/>
-      <c r="C280" s="14"/>
-      <c r="D280" s="14"/>
+      <c r="B280" s="28" t="s">
+        <v>482</v>
+      </c>
+      <c r="C280" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="D280" s="14">
+        <v>0.5</v>
+      </c>
       <c r="E280" s="14"/>
     </row>
     <row r="281" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="16" t="s">
-        <v>447</v>
-      </c>
+      <c r="A281" s="16"/>
       <c r="B281" s="28"/>
       <c r="C281" s="14"/>
       <c r="D281" s="14"/>
       <c r="E281" s="14"/>
     </row>
-    <row r="282" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A282" s="29" t="s">
+    <row r="282" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B282" s="28"/>
+      <c r="C282" s="14"/>
+      <c r="D282" s="14"/>
+      <c r="E282" s="14"/>
+    </row>
+    <row r="283" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A283" s="29" t="s">
         <v>361</v>
       </c>
-      <c r="B282" s="28" t="s">
+      <c r="B283" s="28" t="s">
         <v>403</v>
-      </c>
-      <c r="C282" s="14">
-        <v>2</v>
-      </c>
-      <c r="D282" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="E282" s="14"/>
-    </row>
-    <row r="283" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A283" s="19"/>
-      <c r="B283" s="31" t="s">
-        <v>404</v>
       </c>
       <c r="C283" s="14">
         <v>2</v>
       </c>
       <c r="D283" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E283" s="14"/>
+    </row>
+    <row r="284" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A284" s="19"/>
+      <c r="B284" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="C284" s="14">
+        <v>2</v>
+      </c>
+      <c r="D284" s="14">
         <v>3</v>
-      </c>
-      <c r="E283" s="14"/>
-    </row>
-    <row r="284" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A284" s="16"/>
-      <c r="B284" s="28" t="s">
-        <v>405</v>
-      </c>
-      <c r="C284" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D284" s="14">
-        <v>3.8</v>
       </c>
       <c r="E284" s="14"/>
     </row>
     <row r="285" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A285" s="16"/>
       <c r="B285" s="28" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C285" s="14">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D285" s="14">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="E285" s="14"/>
     </row>
-    <row r="286" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A286" s="16"/>
       <c r="B286" s="28" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C286" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D286" s="14">
         <v>2</v>
       </c>
-      <c r="D286" s="14">
-        <v>2.2000000000000002</v>
-      </c>
       <c r="E286" s="14"/>
     </row>
-    <row r="287" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="16"/>
       <c r="B287" s="28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C287" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D287" s="14">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E287" s="14"/>
     </row>
-    <row r="288" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A288" s="16"/>
       <c r="B288" s="28" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C288" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D288" s="14">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="E288" s="14"/>
     </row>
-    <row r="289" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="16"/>
       <c r="B289" s="28" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C289" s="14">
         <v>2</v>
       </c>
       <c r="D289" s="14">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E289" s="14"/>
     </row>
-    <row r="290" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A290" s="16"/>
       <c r="B290" s="28" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C290" s="14">
         <v>2</v>
       </c>
       <c r="D290" s="14">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="E290" s="14"/>
     </row>
     <row r="291" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="16"/>
       <c r="B291" s="28" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C291" s="14">
         <v>2</v>
       </c>
       <c r="D291" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="E291" s="14"/>
+    </row>
+    <row r="292" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" s="16"/>
+      <c r="B292" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="C292" s="14">
         <v>2</v>
       </c>
-      <c r="E291" s="14"/>
-    </row>
-    <row r="292" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="19"/>
-      <c r="B292" s="31" t="s">
+      <c r="D292" s="14">
+        <v>2</v>
+      </c>
+      <c r="E292" s="14"/>
+    </row>
+    <row r="293" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="19"/>
+      <c r="B293" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="C292" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D292" s="14">
+      <c r="C293" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D293" s="14">
         <v>1.2</v>
-      </c>
-      <c r="E292" s="14"/>
-    </row>
-    <row r="293" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="16"/>
-      <c r="B293" s="28" t="s">
-        <v>414</v>
-      </c>
-      <c r="C293" s="14">
-        <v>1</v>
-      </c>
-      <c r="D293" s="14">
-        <v>1</v>
       </c>
       <c r="E293" s="14"/>
     </row>
     <row r="294" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="16"/>
       <c r="B294" s="28" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C294" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D294" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E294" s="14"/>
     </row>
     <row r="295" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="16"/>
       <c r="B295" s="28" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C295" s="14">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D295" s="14">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="E295" s="14"/>
     </row>
     <row r="296" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="16"/>
       <c r="B296" s="28" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C296" s="14">
         <v>1.5</v>
       </c>
       <c r="D296" s="14">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="E296" s="14"/>
     </row>
     <row r="297" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="16"/>
       <c r="B297" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="C297" s="8">
-        <v>2</v>
+        <v>417</v>
+      </c>
+      <c r="C297" s="14">
+        <v>1.5</v>
       </c>
       <c r="D297" s="14">
         <v>1.5</v>
@@ -6350,20 +6353,20 @@
     <row r="298" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="16"/>
       <c r="B298" s="28" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C298" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D298" s="14">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E298" s="14"/>
     </row>
     <row r="299" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="16"/>
       <c r="B299" s="28" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C299" s="8">
         <v>1</v>
@@ -6374,174 +6377,176 @@
       <c r="E299" s="14"/>
     </row>
     <row r="300" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="16" t="s">
+      <c r="A300" s="16"/>
+      <c r="B300" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="C300" s="8">
+        <v>1</v>
+      </c>
+      <c r="D300" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E300" s="14"/>
+    </row>
+    <row r="301" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="B300" s="28"/>
-      <c r="C300" s="14"/>
-      <c r="D300" s="14"/>
-      <c r="E300" s="14"/>
-    </row>
-    <row r="301" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A301" s="29" t="s">
+      <c r="B301" s="28"/>
+      <c r="C301" s="14"/>
+      <c r="D301" s="14"/>
+      <c r="E301" s="14"/>
+    </row>
+    <row r="302" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A302" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="B301" s="18" t="s">
+      <c r="B302" s="18" t="s">
         <v>418</v>
       </c>
-      <c r="C301" s="14">
+      <c r="C302" s="14">
         <v>0.8</v>
       </c>
-      <c r="D301" s="14">
+      <c r="D302" s="14">
         <v>0.5</v>
-      </c>
-      <c r="E301" s="14"/>
-    </row>
-    <row r="302" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="16"/>
-      <c r="B302" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="C302" s="14">
-        <v>2</v>
-      </c>
-      <c r="D302" s="14">
-        <v>1.8</v>
       </c>
       <c r="E302" s="14"/>
     </row>
     <row r="303" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="16"/>
       <c r="B303" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="C303" s="14">
+        <v>2</v>
+      </c>
+      <c r="D303" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="E303" s="14"/>
+    </row>
+    <row r="304" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" s="16"/>
+      <c r="B304" s="18" t="s">
         <v>420</v>
       </c>
-      <c r="C303" s="14">
+      <c r="C304" s="14">
         <v>1.2</v>
       </c>
-      <c r="D303" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E303" s="14"/>
-    </row>
-    <row r="304" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A304" s="19"/>
-      <c r="B304" s="14" t="s">
+      <c r="D304" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E304" s="14"/>
+    </row>
+    <row r="305" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="19"/>
+      <c r="B305" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="C304" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D304" s="14">
+      <c r="C305" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D305" s="14">
         <v>1.8</v>
-      </c>
-      <c r="E304" s="14"/>
-    </row>
-    <row r="305" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="16"/>
-      <c r="B305" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="C305" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D305" s="14">
-        <v>2.5</v>
       </c>
       <c r="E305" s="14"/>
     </row>
     <row r="306" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="16"/>
       <c r="B306" s="18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C306" s="14">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D306" s="14">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E306" s="14"/>
     </row>
     <row r="307" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="16"/>
       <c r="B307" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C307" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D307" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E307" s="14"/>
     </row>
     <row r="308" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="16"/>
       <c r="B308" s="18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C308" s="14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D308" s="14">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="E308" s="14"/>
     </row>
     <row r="309" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="16"/>
       <c r="B309" s="18" t="s">
-        <v>504</v>
+        <v>425</v>
       </c>
       <c r="C309" s="14">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="D309" s="14">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="E309" s="14"/>
     </row>
     <row r="310" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="16"/>
       <c r="B310" s="18" t="s">
-        <v>426</v>
+        <v>504</v>
       </c>
       <c r="C310" s="14">
         <v>1.2</v>
       </c>
       <c r="D310" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E310" s="14"/>
     </row>
     <row r="311" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="16"/>
       <c r="B311" s="18" t="s">
-        <v>492</v>
+        <v>426</v>
       </c>
       <c r="C311" s="14">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="D311" s="14">
         <v>1</v>
       </c>
       <c r="E311" s="14"/>
     </row>
-    <row r="312" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="16"/>
       <c r="B312" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="C312" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D312" s="14">
+        <v>1</v>
+      </c>
+      <c r="E312" s="14"/>
+    </row>
+    <row r="313" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A313" s="16"/>
+      <c r="B313" s="18" t="s">
         <v>493</v>
-      </c>
-      <c r="C312" s="14">
-        <v>1</v>
-      </c>
-      <c r="D312" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B313" s="18" t="s">
-        <v>494</v>
       </c>
       <c r="C313" s="14">
         <v>1</v>
@@ -6550,173 +6555,171 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A314" s="36" t="s">
+    <row r="314" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B314" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="C314" s="14">
+        <v>1</v>
+      </c>
+      <c r="D314" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A315" s="36" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B315" s="28" t="s">
+    <row r="316" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B316" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="C315" s="8">
+      <c r="C316" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B316" s="28" t="s">
+    <row r="317" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B317" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="C316" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B317" s="28" t="s">
-        <v>242</v>
-      </c>
       <c r="C317" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="318" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B318" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C318" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B319" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C319" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B320" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="C320" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B321" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="C320" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B321" s="28" t="s">
+      <c r="C321" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B322" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="C321" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B322" s="28" t="s">
+      <c r="C322" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B323" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="C322" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B323" s="28"/>
-    </row>
-    <row r="324" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A324" s="36" t="s">
+      <c r="C323" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B324" s="28"/>
+    </row>
+    <row r="325" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A325" s="36" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B325" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="C325" s="8">
-        <v>1.2</v>
       </c>
     </row>
     <row r="326" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B326" s="28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C326" s="8">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="327" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B327" s="28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C327" s="8">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B328" s="28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C328" s="8">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="329" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B329" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C329" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B330" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="C329" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B330" s="28" t="s">
+      <c r="C330" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B331" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="C330" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B331" s="28" t="s">
+      <c r="C331" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B332" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="C331" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B332" s="28"/>
-    </row>
-    <row r="333" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A333" s="29" t="s">
+      <c r="C332" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B333" s="28"/>
+    </row>
+    <row r="334" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="29" t="s">
         <v>367</v>
       </c>
-      <c r="B333" s="28" t="s">
+      <c r="B334" s="28" t="s">
         <v>434</v>
       </c>
-      <c r="C333" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D333" s="14">
+      <c r="C334" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D334" s="14">
         <v>1.2</v>
       </c>
-      <c r="E333" s="14"/>
-    </row>
-    <row r="334" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B334" s="28" t="s">
+      <c r="E334" s="14"/>
+    </row>
+    <row r="335" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B335" s="28" t="s">
         <v>435</v>
-      </c>
-      <c r="C334" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D334" s="14">
-        <v>2</v>
-      </c>
-      <c r="E334" s="14"/>
-    </row>
-    <row r="335" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A335" s="16"/>
-      <c r="B335" s="28" t="s">
-        <v>436</v>
       </c>
       <c r="C335" s="14">
         <v>1.5</v>
@@ -6729,101 +6732,101 @@
     <row r="336" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="16"/>
       <c r="B336" s="28" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C336" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D336" s="14">
         <v>2</v>
-      </c>
-      <c r="D336" s="14">
-        <v>2.2000000000000002</v>
       </c>
       <c r="E336" s="14"/>
     </row>
     <row r="337" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="16"/>
       <c r="B337" s="28" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C337" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D337" s="14">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E337" s="14"/>
     </row>
     <row r="338" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="16"/>
       <c r="B338" s="28" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C338" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D338" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E338" s="14"/>
     </row>
     <row r="339" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="16"/>
       <c r="B339" s="28" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C339" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D339" s="14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E339" s="14"/>
     </row>
-    <row r="340" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="16"/>
       <c r="B340" s="28" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C340" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D340" s="14">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="E340" s="14"/>
     </row>
-    <row r="341" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A341" s="16"/>
       <c r="B341" s="28" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C341" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D341" s="14">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E341" s="14"/>
     </row>
     <row r="342" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="16"/>
       <c r="B342" s="28" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C342" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D342" s="14">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E342" s="14"/>
     </row>
     <row r="343" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="16"/>
       <c r="B343" s="28" t="s">
-        <v>495</v>
-      </c>
-      <c r="C343" s="8">
-        <v>1.5</v>
+        <v>443</v>
+      </c>
+      <c r="C343" s="14">
+        <v>1</v>
       </c>
       <c r="D343" s="14">
         <v>1</v>
@@ -6833,57 +6836,62 @@
     <row r="344" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="16"/>
       <c r="B344" s="28" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C344" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D344" s="14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E344" s="14"/>
     </row>
     <row r="345" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="16"/>
       <c r="B345" s="28" t="s">
+        <v>496</v>
+      </c>
+      <c r="C345" s="8">
+        <v>1</v>
+      </c>
+      <c r="D345" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="E345" s="14"/>
+    </row>
+    <row r="346" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A346" s="16"/>
+      <c r="B346" s="28" t="s">
         <v>497</v>
       </c>
-      <c r="C345" s="8">
-        <v>1</v>
-      </c>
-      <c r="D345" s="8">
+      <c r="C346" s="8">
+        <v>1</v>
+      </c>
+      <c r="D346" s="8">
         <v>0.5</v>
       </c>
-      <c r="E345" s="14"/>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A346" s="16"/>
-      <c r="B346" s="28"/>
-    </row>
-    <row r="347" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A347" s="36" t="s">
+      <c r="E346" s="14"/>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A347" s="16"/>
+      <c r="B347" s="28"/>
+    </row>
+    <row r="348" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A348" s="36" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B348" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="C348" s="8">
-        <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B349" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C349" s="8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B350" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C350" s="8">
         <v>1.5</v>
@@ -6891,71 +6899,71 @@
     </row>
     <row r="351" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B351" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C351" s="8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="352" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B352" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C352" s="8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B353" s="28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C353" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B354" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="C354" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B355" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="C354" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B355" s="28" t="s">
+      <c r="C355" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B356" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="C355" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B356" s="28" t="s">
+      <c r="C356" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B357" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="C356" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B357" s="28"/>
-    </row>
-    <row r="358" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A358" s="36" t="s">
+      <c r="C357" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B358" s="28"/>
+    </row>
+    <row r="359" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A359" s="36" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B359" s="28" t="s">
+    <row r="360" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B360" s="28" t="s">
         <v>264</v>
-      </c>
-      <c r="C359" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B360" s="28" t="s">
-        <v>265</v>
       </c>
       <c r="C360" s="8">
         <v>1.2</v>
@@ -6963,7 +6971,7 @@
     </row>
     <row r="361" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B361" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C361" s="8">
         <v>1.2</v>
@@ -6971,55 +6979,55 @@
     </row>
     <row r="362" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B362" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C362" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B363" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="C362" s="8">
+      <c r="C363" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B363" s="28" t="s">
+    <row r="364" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B364" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="C363" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B364" s="28" t="s">
+      <c r="C364" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B365" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="C364" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B365" s="28" t="s">
+      <c r="C365" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B366" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="C365" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B366" s="28"/>
-    </row>
-    <row r="367" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A367" s="36" t="s">
+      <c r="C366" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B367" s="28"/>
+    </row>
+    <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A368" s="36" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B368" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="C368" s="8">
-        <v>0.8</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B369" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C369" s="8">
         <v>0.8</v>
@@ -7027,79 +7035,79 @@
     </row>
     <row r="370" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B370" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C370" s="8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B371" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C371" s="8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B372" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C372" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B373" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="C372" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B373" s="28" t="s">
+      <c r="C373" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B374" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="C373" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B374" s="28" t="s">
+      <c r="C374" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B375" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="C374" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B375" s="28"/>
-    </row>
-    <row r="376" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A376" s="36" t="s">
+      <c r="C375" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B376" s="28"/>
+    </row>
+    <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A377" s="36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B377" s="28" t="s">
+    <row r="378" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B378" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="C377" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B378" s="28" t="s">
+      <c r="C378" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B379" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="C378" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B379" s="28" t="s">
-        <v>280</v>
-      </c>
       <c r="C379" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B380" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C380" s="8">
         <v>1</v>
@@ -7107,47 +7115,47 @@
     </row>
     <row r="381" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B381" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="C381" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B382" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="C381" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B382" s="28" t="s">
+      <c r="C382" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B383" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="C382" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B383" s="28" t="s">
+      <c r="C383" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B384" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="C383" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B384" s="28"/>
-    </row>
-    <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A385" s="36" t="s">
+      <c r="C384" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B385" s="28"/>
+    </row>
+    <row r="386" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A386" s="36" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B386" s="28" t="s">
-        <v>285</v>
-      </c>
-      <c r="C386" s="8">
-        <v>1.5</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B387" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C387" s="8">
         <v>1.5</v>
@@ -7155,71 +7163,71 @@
     </row>
     <row r="388" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B388" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C388" s="8">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B389" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="C389" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B390" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="C389" s="8">
+      <c r="C390" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B390" s="28" t="s">
+    <row r="391" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B391" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="C390" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B391" s="28" t="s">
+      <c r="C391" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B392" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="C391" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B392" s="28"/>
-    </row>
-    <row r="393" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A393" s="36" t="s">
+      <c r="C392" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B393" s="28"/>
+    </row>
+    <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A394" s="36" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B394" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="C394" s="8">
-        <v>1</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B395" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C395" s="8">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B396" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C396" s="8">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B397" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C397" s="8">
         <v>0.8</v>
@@ -7227,111 +7235,111 @@
     </row>
     <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B398" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="C398" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B399" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="C398" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B399" s="28" t="s">
+      <c r="C399" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B400" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="C399" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B400" s="28" t="s">
+      <c r="C400" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B401" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="C400" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B401" s="28"/>
-    </row>
-    <row r="402" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A402" s="36" t="s">
+      <c r="C401" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B402" s="28"/>
+    </row>
+    <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A403" s="36" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B403" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="C403" s="8">
-        <v>1.2</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B404" s="28" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C404" s="8">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B405" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="C405" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B406" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="C405" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B406" s="28" t="s">
+      <c r="C406" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B407" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="C406" s="8">
+      <c r="C407" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B407" s="28" t="s">
+    <row r="408" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B408" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="C407" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B408" s="28" t="s">
+      <c r="C408" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B409" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="C408" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B409" s="28" t="s">
+      <c r="C409" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B410" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="C409" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B410" s="28"/>
-    </row>
-    <row r="411" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A411" s="36" t="s">
+      <c r="C410" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B411" s="28"/>
+    </row>
+    <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A412" s="36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B412" s="28" t="s">
+    <row r="413" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B413" s="28" t="s">
         <v>305</v>
-      </c>
-      <c r="C412" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B413" s="28" t="s">
-        <v>306</v>
       </c>
       <c r="C413" s="8">
         <v>1.2</v>
@@ -7339,52 +7347,47 @@
     </row>
     <row r="414" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B414" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="C414" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B415" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="C414" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B415" s="28" t="s">
-        <v>308</v>
-      </c>
       <c r="C415" s="8">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B416" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="C416" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B417" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="C416" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B417" s="28"/>
-      <c r="D417" s="14"/>
-      <c r="E417" s="14"/>
-    </row>
-    <row r="418" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A418" s="29" t="s">
+      <c r="C417" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B418" s="28"/>
+      <c r="D418" s="14"/>
+      <c r="E418" s="14"/>
+    </row>
+    <row r="419" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A419" s="29" t="s">
         <v>475</v>
       </c>
-      <c r="B418" s="31" t="s">
+      <c r="B419" s="31" t="s">
         <v>502</v>
-      </c>
-      <c r="C418" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D418" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E418" s="14"/>
-    </row>
-    <row r="419" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A419" s="16"/>
-      <c r="B419" s="31" t="s">
-        <v>465</v>
       </c>
       <c r="C419" s="14">
         <v>1.2</v>
@@ -7394,88 +7397,88 @@
       </c>
       <c r="E419" s="14"/>
     </row>
-    <row r="420" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A420" s="16"/>
       <c r="B420" s="31" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C420" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D420" s="14">
         <v>0.8</v>
       </c>
-      <c r="D420" s="14">
-        <v>0.5</v>
-      </c>
       <c r="E420" s="14"/>
     </row>
-    <row r="421" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A421" s="16"/>
       <c r="B421" s="31" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C421" s="14">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D421" s="14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E421" s="14"/>
     </row>
     <row r="422" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A422" s="16"/>
       <c r="B422" s="31" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C422" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D422" s="14">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E422" s="14"/>
     </row>
     <row r="423" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A423" s="16"/>
       <c r="B423" s="31" t="s">
-        <v>503</v>
+        <v>468</v>
       </c>
       <c r="C423" s="14">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D423" s="14">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E423" s="14"/>
     </row>
     <row r="424" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A424" s="16"/>
       <c r="B424" s="31" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="C424" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D424" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E424" s="14"/>
     </row>
     <row r="425" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A425" s="16"/>
       <c r="B425" s="31" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C425" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D425" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E425" s="14"/>
     </row>
     <row r="426" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A426" s="16"/>
       <c r="B426" s="31" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C426" s="14">
         <v>2</v>
@@ -7488,241 +7491,254 @@
     <row r="427" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A427" s="16"/>
       <c r="B427" s="31" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C427" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D427" s="14">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E427" s="14"/>
     </row>
     <row r="428" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A428" s="16"/>
       <c r="B428" s="31" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C428" s="14">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D428" s="14">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E428" s="14"/>
     </row>
     <row r="429" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A429" s="16"/>
-      <c r="B429" s="37" t="s">
+      <c r="B429" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="C429" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D429" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E429" s="14"/>
+    </row>
+    <row r="430" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A430" s="16"/>
+      <c r="B430" s="37" t="s">
         <v>474</v>
       </c>
-      <c r="C429" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D429" s="14">
-        <v>1</v>
-      </c>
-      <c r="E429" s="14"/>
-    </row>
-    <row r="430" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A430" s="16"/>
-      <c r="B430" s="8" t="s">
-        <v>498</v>
-      </c>
       <c r="C430" s="8">
         <v>1.5</v>
       </c>
       <c r="D430" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E430" s="14"/>
     </row>
-    <row r="431" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A431" s="16"/>
       <c r="B431" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C431" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D431" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E431" s="14"/>
+    </row>
+    <row r="432" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A432" s="16"/>
+      <c r="B432" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="C431" s="8">
-        <v>1</v>
-      </c>
-      <c r="D431" s="8">
+      <c r="C432" s="8">
+        <v>1</v>
+      </c>
+      <c r="D432" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B432" s="8" t="s">
+    <row r="433" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B433" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="C432" s="8">
-        <v>1</v>
-      </c>
-      <c r="D432" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A433" s="36" t="s">
+      <c r="C433" s="8">
+        <v>1</v>
+      </c>
+      <c r="D433" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A434" s="36" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="434" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B434" s="28" t="s">
+    <row r="435" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B435" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="C434" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B435" s="28" t="s">
+      <c r="C435" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B436" s="28" t="s">
         <v>311</v>
-      </c>
-      <c r="C435" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A436" s="26" t="s">
-        <v>447</v>
-      </c>
-      <c r="B436" s="28" t="s">
-        <v>312</v>
       </c>
       <c r="C436" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="437" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A437" s="26" t="s">
+        <v>447</v>
+      </c>
       <c r="B437" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="C437" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B438" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="C437" s="8">
+      <c r="C438" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="438" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B438" s="28" t="s">
+    <row r="439" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B439" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="C438" s="8">
+      <c r="C439" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B439" s="28" t="s">
+    <row r="440" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B440" s="28" t="s">
         <v>315</v>
       </c>
-      <c r="C439" s="8">
+      <c r="C440" s="8">
         <v>1.8</v>
       </c>
     </row>
-    <row r="440" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B440" s="28" t="s">
+    <row r="441" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B441" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="C440" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B441" s="28" t="s">
+      <c r="C441" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B442" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="C441" s="8">
+      <c r="C442" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="442" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B442" s="28" t="s">
+    <row r="443" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B443" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="C442" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B443" s="28" t="s">
+      <c r="C443" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B444" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="C443" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B444" s="28"/>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C444" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B445" s="28"/>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B446" s="28"/>
     </row>
-    <row r="447" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A447" s="36" t="s">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B447" s="28"/>
+    </row>
+    <row r="448" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A448" s="36" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="448" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B448" s="28" t="s">
+    <row r="449" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B449" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="C448" s="8">
+      <c r="C449" s="8">
         <v>2</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B449" s="28" t="s">
-        <v>321</v>
-      </c>
-      <c r="C449" s="8">
-        <v>1.2</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B450" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C450" s="8">
-        <v>3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B451" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="C451" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B452" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="C451" s="8">
+      <c r="C452" s="8">
         <v>2.5</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B452" s="28" t="s">
+    <row r="453" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B453" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="C452" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B453" s="28" t="s">
-        <v>325</v>
-      </c>
       <c r="C453" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B454" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="C454" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B455" s="28" t="s">
         <v>326</v>
       </c>
-      <c r="C454" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B455" s="28"/>
-    </row>
-    <row r="456" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A456" s="26" t="s">
+      <c r="C455" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B456" s="28"/>
+    </row>
+    <row r="457" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A457" s="26" t="s">
         <v>447</v>
       </c>
     </row>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6188DC8E-0774-D94B-8F89-CE31232806A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2977F47-C4C4-5F45-8337-5F1F8D52E785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REQUISITOS" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="539">
   <si>
     <t>User story</t>
   </si>
@@ -171,12 +171,6 @@
     <t>RF11 — Modelo canónico mínimo P2P/O2C</t>
   </si>
   <si>
-    <t>[Fase 2] Define modelo canónico y entidades mínimas para P2P/O2C con campos y claves.</t>
-  </si>
-  <si>
-    <t>Existe canonical_schema.(yaml|json) y documento explicativo. Un mapper convierte el dataset P2P a tablas canónicas y pasa validación.</t>
-  </si>
-  <si>
     <t>Should</t>
   </si>
   <si>
@@ -186,18 +180,12 @@
     <t>[Fase 2] Permite ajustar nombres de columnas/tablas y castings por empresa sin tocar código.</t>
   </si>
   <si>
-    <t>Con mapping.yaml alternativo, el pipeline carga y ejecuta tests siempre que se satisfagan campos obligatorios; el validador informa faltantes.</t>
-  </si>
-  <si>
     <t>RF13 — Catálogo ampliado (10–20 tests) con referencias ACFE</t>
   </si>
   <si>
     <t>[Fase 2] Ampliación del catálogo con tests ACFE y documentación mínima por test.</t>
   </si>
   <si>
-    <t>Hay 10–20 tests implementados, cada uno con acfe_reference, fraud_type, data_requirements y versión; todos ejecutables y con salida estándar.</t>
-  </si>
-  <si>
     <t>RF16 — Persistencia y comparación de runs</t>
   </si>
   <si>
@@ -678,33 +666,6 @@
     <t>RF10-08: Ejecutar verificación de criterios de aceptación y guardar evidencia (logs/reportes)</t>
   </si>
   <si>
-    <t>RF11-01: Definir entidades canónicas (P2P/O2C): invoice, payment, vendor, employee, customer (mínimas)</t>
-  </si>
-  <si>
-    <t>RF11-02: Definir claves primarias y foráneas canónicas y reglas de integridad (documentar)</t>
-  </si>
-  <si>
-    <t>RF11-03: Crear canonical_schema.yaml con campos, tipos y obligatoriedad</t>
-  </si>
-  <si>
-    <t>RF11-04: Implementar conversión del dataset a tablas canónicas en DuckDB (views o tablas)</t>
-  </si>
-  <si>
-    <t>RF11-05: Validar canónico: checks de campos obligatorios, tipos, y cardinalidades básicas</t>
-  </si>
-  <si>
-    <t>RF11-06: Actualizar tests existentes para leer del modelo canónico (cuando aplique)</t>
-  </si>
-  <si>
-    <t>RF11-07: Escribir/actualizar tests unitarios relacionados (pytest) para este requisito</t>
-  </si>
-  <si>
-    <t>RF11-08: Actualizar documentación (README/docs) describiendo el comportamiento y cómo verificarlo</t>
-  </si>
-  <si>
-    <t>RF11-09: Ejecutar verificación de criterios de aceptación y guardar evidencia (logs/reportes)</t>
-  </si>
-  <si>
     <t>RF12-01: Definir formato mapping.yaml (tabla_origen→tabla_canónica, columna_origen→columna_canónica, casts)</t>
   </si>
   <si>
@@ -1609,13 +1570,97 @@
   </si>
   <si>
     <t>RF15-11: Actualizar proyecto para que fraud type proceda de documentación oficial</t>
+  </si>
+  <si>
+    <t>RF-11 — Implementación O2C desde raw_data (modelo, mapping y ejecución)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    O2C en DuckDB con validación de calidad mínima, y al menos un run O2C completo produce artefactos estándar (findings/ranking/report)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    sin romper el flujo P2P existente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Fase 2] Extiende el pipeline de P2P a O2C usando fuentes raw_data del dataset ERP Fraud Data. Define modelo
+    canónico O2C, transforma raw a entidades O2C, habilita ejecución/validación sobre O2C y deja trazabilidad separada por proceso.
+  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Existe documentación funcional/técnica de O2C y su mapping desde raw_data. Se generan tablas canónicas O2C en DuckDB con validación de calidad mínima, y al menos un run O2C completo produce artefactos estándar (findings/ranking/report)
+    sin romper el flujo P2P existente.</t>
+  </si>
+  <si>
+    <t>Leyenda</t>
+  </si>
+  <si>
+    <t>1a Entrega</t>
+  </si>
+  <si>
+    <t>2a Entrega</t>
+  </si>
+  <si>
+    <t>3a Entrega</t>
+  </si>
+  <si>
+    <t>No se realiza</t>
+  </si>
+  <si>
+    <t>RF11-01: Definir alcance O2C exacto (Order, Delivery, Invoice, Collection/Cash Application) y límites de fase</t>
+  </si>
+  <si>
+    <t>RF11-02: Inventariar tablas/columnas en raw_data relevantes para O2C y documentar correspondencias preliminares</t>
+  </si>
+  <si>
+    <t>RF11-03: Definir modelo canónico O2C (entidades, claves, relaciones, tipos, campos obligatorios) en canonical_schema_o2c.yaml</t>
+  </si>
+  <si>
+    <t>RF11-04: Definir business keys O2C y estrategia de deduplicación/normalización por entidad</t>
+  </si>
+  <si>
+    <t>RF11-05: Implementar transformaciones raw-&gt;canónico O2C en DuckDB (staging + tablas/vistas finales)</t>
+  </si>
+  <si>
+    <t>RF11-06: Implementar validaciones técnicas O2C (missing required, parseos críticos, null ratios, cardinalidades básicas)</t>
+  </si>
+  <si>
+    <t>RF11-07: Integrar selector de proceso (`process_family`: p2p|o2c) en metadata/config para no mezclar ejecuciones</t>
+  </si>
+  <si>
+    <t>RF11-08: Adaptar ingest/orquestación para soportar run O2C sin romper backward compatibility de P2P</t>
+  </si>
+  <si>
+    <t>RF11-09: Crear mapping explícito raw_data-&gt;O2C canónico (column_mapping_o2c.yaml) con casts y defaults controlados</t>
+  </si>
+  <si>
+    <t>RF11-10: Añadir data dictionary O2C mínimo (campos críticos por entidad O2C y fuente raw)</t>
+  </si>
+  <si>
+    <t>RF11-11: Definir matriz O2C hipótesis→tests→evidencias (base para planner/explainer en proceso O2C)</t>
+  </si>
+  <si>
+    <t>RF11-12: Incorporar taxonomía de fraude O2C y alinearla con Fraud Tree oficial y fraud_type internos</t>
+  </si>
+  <si>
+    <t>RF11-13: Escribir tests de integración O2C (run O2C end-to-end + persistencia + reporte) con fixtures raw</t>
+  </si>
+  <si>
+    <t>RF11-14: Ejecutar prueba de regresión cruzada P2P vs O2C para asegurar no regresión funcional en P2P</t>
+  </si>
+  <si>
+    <t>RF11-15: Actualizar documentación operativa (README + how_to_run + rf11.md) con comandos y evidencias O2C</t>
+  </si>
+  <si>
+    <t>RF11-16:  Ejecutar verificación final y guardar evidencias (run_results O2C + reporte de validación + lista de riesgos abiertos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">posibilidad de cambiarlo </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1687,8 +1732,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1743,7 +1794,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1788,7 +1845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1862,9 +1919,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1926,20 +1980,120 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2187,22 +2341,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.1640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.1640625" style="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="101.5" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="95.1640625" style="8" customWidth="1"/>
     <col min="4" max="4" width="15.5" style="8" customWidth="1"/>
     <col min="5" max="5" width="11.83203125" style="8" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="8" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" style="43" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" style="8" customWidth="1"/>
     <col min="9" max="9" width="3.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2219,9 +2373,9 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G1" s="41" t="s">
+        <v>314</v>
+      </c>
+      <c r="G1" s="40" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -2231,15 +2385,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -2248,19 +2402,22 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="42"/>
-    </row>
-    <row r="3" spans="1:9" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="G2" s="41"/>
+      <c r="L2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -2271,9 +2428,12 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="42"/>
-    </row>
-    <row r="4" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="G3" s="41"/>
+      <c r="L3" s="54" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>8</v>
       </c>
@@ -2292,15 +2452,18 @@
       <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="39">
         <v>46094</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+      <c r="L4" s="55" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
@@ -2319,15 +2482,18 @@
       <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="39">
         <v>46094</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+      <c r="L5" s="56" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>17</v>
       </c>
@@ -2346,15 +2512,18 @@
       <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="39">
         <v>46094</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+      <c r="L6" s="57" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>20</v>
       </c>
@@ -2373,15 +2542,15 @@
       <c r="F7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="39">
         <v>46094</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>23</v>
       </c>
@@ -2400,15 +2569,15 @@
       <c r="F8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="39">
         <v>46094</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -2427,15 +2596,15 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="39">
         <v>46094</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2454,15 +2623,15 @@
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="39">
         <v>46094</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>32</v>
       </c>
@@ -2481,15 +2650,15 @@
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="39">
         <v>46094</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>35</v>
       </c>
@@ -2508,22 +2677,22 @@
       <c r="F12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="39">
         <v>46094</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="45" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="5">
@@ -2535,11 +2704,11 @@
       <c r="F13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="40"/>
+      <c r="G13" s="39"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:9" ht="38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="38" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>41</v>
       </c>
@@ -2558,103 +2727,105 @@
       <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="39">
         <v>46094</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="40"/>
+      <c r="G15" s="39"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    <row r="16" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A16" s="44" t="s">
+        <v>512</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>516</v>
+      </c>
+      <c r="D16" s="5">
+        <v>21</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="5">
-        <v>8</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="F16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="40"/>
+        <v>12</v>
+      </c>
+      <c r="G16" s="39"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="49" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="45" t="s">
+    <row r="17" spans="1:9" s="51" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>513</v>
+      </c>
+      <c r="D17" s="49">
+        <v>8</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="50"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+    </row>
+    <row r="18" spans="1:9" ht="19" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B18" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="47">
-        <v>8</v>
-      </c>
-      <c r="E17" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="48"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-    </row>
-    <row r="18" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>52</v>
-      </c>
       <c r="C18" s="21" t="s">
-        <v>53</v>
+        <v>514</v>
       </c>
       <c r="D18" s="5">
         <v>13</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="40"/>
-      <c r="H18" s="5"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
@@ -2665,19 +2836,21 @@
       <c r="F19" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="43"/>
-      <c r="H19" s="14"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I19" s="14"/>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="22" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D20" s="14">
         <v>8</v>
@@ -2688,42 +2861,44 @@
       <c r="F20" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="14"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I20" s="14"/>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>446</v>
+      <c r="A21" s="46" t="s">
+        <v>341</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>432</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>433</v>
       </c>
       <c r="D21" s="14">
         <v>13</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="43"/>
+      <c r="G21" s="42"/>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D22" s="14">
         <v>8</v>
@@ -2734,19 +2909,21 @@
       <c r="F22" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="43"/>
-      <c r="H22" s="14"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="22" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
@@ -2757,19 +2934,21 @@
       <c r="F23" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="43"/>
-      <c r="H23" s="14"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="D24" s="14">
         <v>13</v>
@@ -2780,19 +2959,21 @@
       <c r="F24" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="43"/>
-      <c r="H24" s="14"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="22" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="D25" s="14">
         <v>10</v>
@@ -2803,30 +2984,32 @@
       <c r="F25" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="43"/>
-      <c r="H25" s="14"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D26" s="5">
         <v>8</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="40"/>
+      <c r="G26" s="39"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
@@ -2837,42 +3020,42 @@
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="40"/>
+      <c r="G27" s="39"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D28" s="5">
         <v>5</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="40"/>
+      <c r="G28" s="39"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="22" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D29" s="14">
         <v>13</v>
@@ -2883,42 +3066,44 @@
       <c r="F29" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="43"/>
-      <c r="H29" s="14"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I29" s="14"/>
     </row>
     <row r="30" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D30" s="5">
         <v>8</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="40"/>
+      <c r="G30" s="39"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D31" s="5">
         <v>5</v>
@@ -2929,19 +3114,19 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="40"/>
+      <c r="G31" s="39"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D32" s="5">
         <v>5</v>
@@ -2952,19 +3137,19 @@
       <c r="F32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="40"/>
+      <c r="G32" s="39"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D33" s="5">
         <v>5</v>
@@ -2975,19 +3160,19 @@
       <c r="F33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="40"/>
+      <c r="G33" s="39"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D34" s="5">
         <v>3</v>
@@ -2998,19 +3183,19 @@
       <c r="F34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="40"/>
+      <c r="G34" s="39"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D35" s="5">
         <v>3</v>
@@ -3021,19 +3206,19 @@
       <c r="F35" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="40"/>
+      <c r="G35" s="39"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
     </row>
     <row r="36" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D36" s="5">
         <v>3</v>
@@ -3042,44 +3227,44 @@
         <v>11</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G36" s="40"/>
+        <v>77</v>
+      </c>
+      <c r="G36" s="39"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D37" s="5">
         <v>3</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="40"/>
+      <c r="G37" s="39"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29" t="s">
-        <v>501</v>
+      <c r="A38" s="28" t="s">
+        <v>488</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="D38" s="14">
         <v>5</v>
@@ -3090,53 +3275,55 @@
       <c r="F38" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="43"/>
-      <c r="H38" s="14"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="I38" s="14"/>
     </row>
     <row r="39" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D39" s="5">
         <v>8</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="40"/>
+      <c r="G39" s="39"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D40" s="5">
         <v>5</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G40" s="40"/>
+        <v>77</v>
+      </c>
+      <c r="G40" s="39"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
     </row>
@@ -3172,33 +3359,63 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Won't">
+    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="Won't">
       <formula>NOT(ISERROR(SEARCH("Won't",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Could">
+    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="Could">
       <formula>NOT(ISERROR(SEARCH("Could",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Should">
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="Should">
       <formula>NOT(ISERROR(SEARCH("Should",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Must">
+    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="Must">
       <formula>NOT(ISERROR(SEARCH("Must",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Bajo">
+    <cfRule type="containsText" dxfId="9" priority="12" operator="containsText" text="Bajo">
       <formula>NOT(ISERROR(SEARCH("Bajo",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="Medio">
+    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="Medio">
       <formula>NOT(ISERROR(SEARCH("Medio",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="8" operator="containsText" text="Alto">
+    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="Alto">
       <formula>NOT(ISERROR(SEARCH("Alto",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",H18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",H19)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",H20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:H25">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",H22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",H29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Sí">
-      <formula>NOT(ISERROR(SEARCH("Sí",I1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Sí",H38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3207,11 +3424,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:E457"/>
+  <dimension ref="A2:E464"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="71.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.33203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="71.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.33203125" style="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -3220,27 +3437,27 @@
   <sheetData>
     <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="34" t="s">
         <v>93</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>334</v>
+        <v>315</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>321</v>
       </c>
       <c r="C3" s="14">
         <v>0.6</v>
@@ -3250,8 +3467,8 @@
     </row>
     <row r="4" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
-      <c r="B4" s="31" t="s">
-        <v>335</v>
+      <c r="B4" s="30" t="s">
+        <v>322</v>
       </c>
       <c r="C4" s="14">
         <v>0.8</v>
@@ -3261,8 +3478,8 @@
     </row>
     <row r="5" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
-      <c r="B5" s="31" t="s">
-        <v>336</v>
+      <c r="B5" s="30" t="s">
+        <v>323</v>
       </c>
       <c r="C5" s="14">
         <v>0.8</v>
@@ -3272,8 +3489,8 @@
     </row>
     <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
-      <c r="B6" s="31" t="s">
-        <v>337</v>
+      <c r="B6" s="30" t="s">
+        <v>324</v>
       </c>
       <c r="C6" s="14">
         <v>0.8</v>
@@ -3283,8 +3500,8 @@
     </row>
     <row r="7" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
-      <c r="B7" s="31" t="s">
-        <v>338</v>
+      <c r="B7" s="30" t="s">
+        <v>325</v>
       </c>
       <c r="C7" s="14">
         <v>0.5</v>
@@ -3294,8 +3511,8 @@
     </row>
     <row r="8" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
-      <c r="B8" s="31" t="s">
-        <v>339</v>
+      <c r="B8" s="30" t="s">
+        <v>326</v>
       </c>
       <c r="C8" s="14">
         <v>0.5</v>
@@ -3305,10 +3522,10 @@
     </row>
     <row r="9" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>346</v>
+        <v>318</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>333</v>
       </c>
       <c r="C9" s="14">
         <v>1</v>
@@ -3318,8 +3535,8 @@
     </row>
     <row r="10" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="16"/>
-      <c r="B10" s="31" t="s">
-        <v>340</v>
+      <c r="B10" s="30" t="s">
+        <v>327</v>
       </c>
       <c r="C10" s="14">
         <v>1</v>
@@ -3329,8 +3546,8 @@
     </row>
     <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
-      <c r="B11" s="31" t="s">
-        <v>341</v>
+      <c r="B11" s="30" t="s">
+        <v>328</v>
       </c>
       <c r="C11" s="14">
         <v>1</v>
@@ -3340,8 +3557,8 @@
     </row>
     <row r="12" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="16"/>
-      <c r="B12" s="31" t="s">
-        <v>342</v>
+      <c r="B12" s="30" t="s">
+        <v>329</v>
       </c>
       <c r="C12" s="14">
         <v>1</v>
@@ -3351,8 +3568,8 @@
     </row>
     <row r="13" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="16"/>
-      <c r="B13" s="31" t="s">
-        <v>343</v>
+      <c r="B13" s="30" t="s">
+        <v>330</v>
       </c>
       <c r="C13" s="14">
         <v>1</v>
@@ -3362,8 +3579,8 @@
     </row>
     <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="16"/>
-      <c r="B14" s="31" t="s">
-        <v>344</v>
+      <c r="B14" s="30" t="s">
+        <v>331</v>
       </c>
       <c r="C14" s="14">
         <v>1.2</v>
@@ -3373,8 +3590,8 @@
     </row>
     <row r="15" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
-      <c r="B15" s="31" t="s">
-        <v>345</v>
+      <c r="B15" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="C15" s="14">
         <v>0.6</v>
@@ -3383,13 +3600,13 @@
       <c r="E15" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="61" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B18" s="28" t="s">
-        <v>98</v>
+      <c r="B18" s="27" t="s">
+        <v>94</v>
       </c>
       <c r="C18" s="8">
         <v>0.5</v>
@@ -3399,8 +3616,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="28" t="s">
-        <v>99</v>
+      <c r="B19" s="27" t="s">
+        <v>95</v>
       </c>
       <c r="C19" s="8">
         <v>0.5</v>
@@ -3410,8 +3627,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B20" s="28" t="s">
-        <v>100</v>
+      <c r="B20" s="27" t="s">
+        <v>96</v>
       </c>
       <c r="C20" s="8">
         <v>1</v>
@@ -3421,8 +3638,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B21" s="28" t="s">
-        <v>101</v>
+      <c r="B21" s="27" t="s">
+        <v>97</v>
       </c>
       <c r="C21" s="8">
         <v>1</v>
@@ -3432,8 +3649,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B22" s="28" t="s">
-        <v>102</v>
+      <c r="B22" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="C22" s="8">
         <v>1.5</v>
@@ -3443,8 +3660,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B23" s="28" t="s">
-        <v>103</v>
+      <c r="B23" s="27" t="s">
+        <v>99</v>
       </c>
       <c r="C23" s="8">
         <v>2</v>
@@ -3454,8 +3671,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="28" t="s">
-        <v>104</v>
+      <c r="B24" s="27" t="s">
+        <v>100</v>
       </c>
       <c r="C24" s="8">
         <v>1</v>
@@ -3465,8 +3682,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B25" s="28" t="s">
-        <v>105</v>
+      <c r="B25" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="C25" s="8">
         <v>0.7</v>
@@ -3476,8 +3693,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B26" s="28" t="s">
-        <v>106</v>
+      <c r="B26" s="27" t="s">
+        <v>102</v>
       </c>
       <c r="C26" s="8">
         <v>1.2</v>
@@ -3487,8 +3704,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B27" s="28" t="s">
-        <v>107</v>
+      <c r="B27" s="27" t="s">
+        <v>103</v>
       </c>
       <c r="C27" s="8">
         <v>0.8</v>
@@ -3498,8 +3715,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B28" s="28" t="s">
-        <v>108</v>
+      <c r="B28" s="27" t="s">
+        <v>104</v>
       </c>
       <c r="C28" s="8">
         <v>1.5</v>
@@ -3509,8 +3726,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="28" t="s">
-        <v>109</v>
+      <c r="B29" s="27" t="s">
+        <v>105</v>
       </c>
       <c r="C29" s="8">
         <v>1.5</v>
@@ -3520,8 +3737,8 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="28" t="s">
-        <v>110</v>
+      <c r="B30" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="C30" s="8">
         <v>1.2</v>
@@ -3531,8 +3748,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B31" s="28" t="s">
-        <v>111</v>
+      <c r="B31" s="27" t="s">
+        <v>107</v>
       </c>
       <c r="C31" s="8">
         <v>1.2</v>
@@ -3542,8 +3759,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B32" s="28" t="s">
-        <v>112</v>
+      <c r="B32" s="27" t="s">
+        <v>108</v>
       </c>
       <c r="C32" s="8">
         <v>1.2</v>
@@ -3553,8 +3770,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="39" t="s">
-        <v>113</v>
+      <c r="B33" s="38" t="s">
+        <v>109</v>
       </c>
       <c r="C33" s="8">
         <v>1.5</v>
@@ -3564,8 +3781,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B34" s="28" t="s">
-        <v>114</v>
+      <c r="B34" s="27" t="s">
+        <v>110</v>
       </c>
       <c r="C34" s="8">
         <v>1</v>
@@ -3575,8 +3792,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B35" s="28" t="s">
-        <v>115</v>
+      <c r="B35" s="27" t="s">
+        <v>111</v>
       </c>
       <c r="C35" s="8">
         <v>1</v>
@@ -3586,16 +3803,16 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="28"/>
+      <c r="B36" s="27"/>
     </row>
     <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="61" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B38" s="28" t="s">
-        <v>116</v>
+      <c r="B38" s="27" t="s">
+        <v>112</v>
       </c>
       <c r="C38" s="8">
         <v>0.8</v>
@@ -3605,8 +3822,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B39" s="28" t="s">
-        <v>117</v>
+      <c r="B39" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="C39" s="8">
         <v>1</v>
@@ -3616,8 +3833,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B40" s="28" t="s">
-        <v>118</v>
+      <c r="B40" s="27" t="s">
+        <v>114</v>
       </c>
       <c r="C40" s="8">
         <v>1</v>
@@ -3627,8 +3844,8 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B41" s="28" t="s">
-        <v>119</v>
+      <c r="B41" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="C41" s="8">
         <v>0.7</v>
@@ -3638,8 +3855,8 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B42" s="28" t="s">
-        <v>120</v>
+      <c r="B42" s="27" t="s">
+        <v>116</v>
       </c>
       <c r="C42" s="8">
         <v>1</v>
@@ -3649,8 +3866,8 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B43" s="28" t="s">
-        <v>121</v>
+      <c r="B43" s="27" t="s">
+        <v>117</v>
       </c>
       <c r="C43" s="8">
         <v>1.2</v>
@@ -3660,8 +3877,8 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B44" s="28" t="s">
-        <v>122</v>
+      <c r="B44" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="C44" s="8">
         <v>0.8</v>
@@ -3671,8 +3888,8 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B45" s="28" t="s">
-        <v>123</v>
+      <c r="B45" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="C45" s="8">
         <v>1.5</v>
@@ -3682,8 +3899,8 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B46" s="28" t="s">
-        <v>124</v>
+      <c r="B46" s="27" t="s">
+        <v>120</v>
       </c>
       <c r="C46" s="8">
         <v>1.5</v>
@@ -3693,8 +3910,8 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B47" s="28" t="s">
-        <v>125</v>
+      <c r="B47" s="27" t="s">
+        <v>121</v>
       </c>
       <c r="C47" s="8">
         <v>1</v>
@@ -3704,8 +3921,8 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B48" s="28" t="s">
-        <v>126</v>
+      <c r="B48" s="27" t="s">
+        <v>122</v>
       </c>
       <c r="C48" s="8">
         <v>1</v>
@@ -3715,16 +3932,16 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B49" s="28"/>
+      <c r="B49" s="27"/>
     </row>
     <row r="50" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="61" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" s="28" t="s">
-        <v>127</v>
+      <c r="B51" s="27" t="s">
+        <v>123</v>
       </c>
       <c r="C51" s="8">
         <v>0.8</v>
@@ -3734,8 +3951,8 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B52" s="28" t="s">
-        <v>128</v>
+      <c r="B52" s="27" t="s">
+        <v>124</v>
       </c>
       <c r="C52" s="8">
         <v>0.8</v>
@@ -3745,8 +3962,8 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B53" s="28" t="s">
-        <v>129</v>
+      <c r="B53" s="27" t="s">
+        <v>125</v>
       </c>
       <c r="C53" s="8">
         <v>0.8</v>
@@ -3756,8 +3973,8 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B54" s="28" t="s">
-        <v>130</v>
+      <c r="B54" s="27" t="s">
+        <v>126</v>
       </c>
       <c r="C54" s="8">
         <v>1.2</v>
@@ -3767,8 +3984,8 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B55" s="28" t="s">
-        <v>131</v>
+      <c r="B55" s="27" t="s">
+        <v>127</v>
       </c>
       <c r="C55" s="8">
         <v>1</v>
@@ -3778,8 +3995,8 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="28" t="s">
-        <v>132</v>
+      <c r="B56" s="27" t="s">
+        <v>128</v>
       </c>
       <c r="C56" s="8">
         <v>1</v>
@@ -3789,8 +4006,8 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B57" s="28" t="s">
-        <v>133</v>
+      <c r="B57" s="27" t="s">
+        <v>129</v>
       </c>
       <c r="C57" s="8">
         <v>1</v>
@@ -3800,8 +4017,8 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B58" s="28" t="s">
-        <v>134</v>
+      <c r="B58" s="27" t="s">
+        <v>130</v>
       </c>
       <c r="C58" s="8">
         <v>1.2</v>
@@ -3811,8 +4028,8 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="28" t="s">
-        <v>135</v>
+      <c r="B59" s="27" t="s">
+        <v>131</v>
       </c>
       <c r="C59" s="8">
         <v>0.7</v>
@@ -3822,8 +4039,8 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B60" s="28" t="s">
-        <v>136</v>
+      <c r="B60" s="27" t="s">
+        <v>132</v>
       </c>
       <c r="C60" s="8">
         <v>1.5</v>
@@ -3833,8 +4050,8 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B61" s="28" t="s">
-        <v>137</v>
+      <c r="B61" s="27" t="s">
+        <v>133</v>
       </c>
       <c r="C61" s="8">
         <v>1</v>
@@ -3844,8 +4061,8 @@
       </c>
     </row>
     <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B62" s="28" t="s">
-        <v>138</v>
+      <c r="B62" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="C62" s="8">
         <v>1</v>
@@ -3855,16 +4072,16 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B63" s="28"/>
+      <c r="B63" s="27"/>
     </row>
     <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="36" t="s">
+      <c r="A64" s="61" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B65" s="28" t="s">
-        <v>139</v>
+      <c r="B65" s="27" t="s">
+        <v>135</v>
       </c>
       <c r="C65" s="8">
         <v>1</v>
@@ -3874,8 +4091,8 @@
       </c>
     </row>
     <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B66" s="28" t="s">
-        <v>140</v>
+      <c r="B66" s="27" t="s">
+        <v>136</v>
       </c>
       <c r="C66" s="8">
         <v>0.8</v>
@@ -3885,8 +4102,8 @@
       </c>
     </row>
     <row r="67" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B67" s="28" t="s">
-        <v>141</v>
+      <c r="B67" s="27" t="s">
+        <v>137</v>
       </c>
       <c r="C67" s="8">
         <v>1.2</v>
@@ -3896,8 +4113,8 @@
       </c>
     </row>
     <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="28" t="s">
-        <v>142</v>
+      <c r="B68" s="27" t="s">
+        <v>138</v>
       </c>
       <c r="C68" s="8">
         <v>1</v>
@@ -3907,8 +4124,8 @@
       </c>
     </row>
     <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="28" t="s">
-        <v>143</v>
+      <c r="B69" s="27" t="s">
+        <v>139</v>
       </c>
       <c r="C69" s="8">
         <v>2</v>
@@ -3918,8 +4135,8 @@
       </c>
     </row>
     <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B70" s="28" t="s">
-        <v>144</v>
+      <c r="B70" s="27" t="s">
+        <v>140</v>
       </c>
       <c r="C70" s="8">
         <v>2</v>
@@ -3929,8 +4146,8 @@
       </c>
     </row>
     <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B71" s="28" t="s">
-        <v>145</v>
+      <c r="B71" s="27" t="s">
+        <v>141</v>
       </c>
       <c r="C71" s="8">
         <v>0.8</v>
@@ -3940,8 +4157,8 @@
       </c>
     </row>
     <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B72" s="28" t="s">
-        <v>146</v>
+      <c r="B72" s="27" t="s">
+        <v>142</v>
       </c>
       <c r="C72" s="8">
         <v>0.8</v>
@@ -3951,8 +4168,8 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B73" s="28" t="s">
-        <v>147</v>
+      <c r="B73" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C73" s="8">
         <v>1.5</v>
@@ -3962,8 +4179,8 @@
       </c>
     </row>
     <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B74" s="28" t="s">
-        <v>148</v>
+      <c r="B74" s="27" t="s">
+        <v>144</v>
       </c>
       <c r="C74" s="8">
         <v>1</v>
@@ -3973,8 +4190,8 @@
       </c>
     </row>
     <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B75" s="28" t="s">
-        <v>149</v>
+      <c r="B75" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="C75" s="8">
         <v>1</v>
@@ -3985,8 +4202,8 @@
     </row>
     <row r="76" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A76" s="8"/>
-      <c r="B76" s="27" t="s">
-        <v>478</v>
+      <c r="B76" s="26" t="s">
+        <v>465</v>
       </c>
       <c r="C76" s="8">
         <v>0.8</v>
@@ -3996,16 +4213,16 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B77" s="28"/>
+      <c r="B77" s="27"/>
     </row>
     <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A78" s="36" t="s">
+      <c r="A78" s="61" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B79" s="28" t="s">
-        <v>150</v>
+      <c r="B79" s="27" t="s">
+        <v>146</v>
       </c>
       <c r="C79" s="8">
         <v>1.2</v>
@@ -4015,8 +4232,8 @@
       </c>
     </row>
     <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B80" s="28" t="s">
-        <v>151</v>
+      <c r="B80" s="27" t="s">
+        <v>147</v>
       </c>
       <c r="C80" s="8">
         <v>0.8</v>
@@ -4026,8 +4243,8 @@
       </c>
     </row>
     <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B81" s="28" t="s">
-        <v>152</v>
+      <c r="B81" s="27" t="s">
+        <v>148</v>
       </c>
       <c r="C81" s="8">
         <v>0.8</v>
@@ -4037,8 +4254,8 @@
       </c>
     </row>
     <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B82" s="28" t="s">
-        <v>153</v>
+      <c r="B82" s="27" t="s">
+        <v>149</v>
       </c>
       <c r="C82" s="8">
         <v>1</v>
@@ -4048,8 +4265,8 @@
       </c>
     </row>
     <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B83" s="28" t="s">
-        <v>154</v>
+      <c r="B83" s="27" t="s">
+        <v>150</v>
       </c>
       <c r="C83" s="8">
         <v>1.5</v>
@@ -4059,8 +4276,8 @@
       </c>
     </row>
     <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B84" s="28" t="s">
-        <v>155</v>
+      <c r="B84" s="27" t="s">
+        <v>151</v>
       </c>
       <c r="C84" s="8">
         <v>1</v>
@@ -4070,8 +4287,8 @@
       </c>
     </row>
     <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B85" s="28" t="s">
-        <v>156</v>
+      <c r="B85" s="27" t="s">
+        <v>152</v>
       </c>
       <c r="C85" s="8">
         <v>0.8</v>
@@ -4081,8 +4298,8 @@
       </c>
     </row>
     <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B86" s="28" t="s">
-        <v>157</v>
+      <c r="B86" s="27" t="s">
+        <v>153</v>
       </c>
       <c r="C86" s="8">
         <v>1.5</v>
@@ -4092,8 +4309,8 @@
       </c>
     </row>
     <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B87" s="28" t="s">
-        <v>158</v>
+      <c r="B87" s="27" t="s">
+        <v>154</v>
       </c>
       <c r="C87" s="8">
         <v>1</v>
@@ -4103,8 +4320,8 @@
       </c>
     </row>
     <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B88" s="28" t="s">
-        <v>159</v>
+      <c r="B88" s="27" t="s">
+        <v>155</v>
       </c>
       <c r="C88" s="8">
         <v>1</v>
@@ -4114,16 +4331,16 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B89" s="28"/>
+      <c r="B89" s="27"/>
     </row>
     <row r="90" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="36" t="s">
+      <c r="A90" s="61" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B91" s="28" t="s">
-        <v>160</v>
+      <c r="B91" s="27" t="s">
+        <v>156</v>
       </c>
       <c r="C91" s="8">
         <v>1</v>
@@ -4133,8 +4350,8 @@
       </c>
     </row>
     <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B92" s="28" t="s">
-        <v>161</v>
+      <c r="B92" s="27" t="s">
+        <v>157</v>
       </c>
       <c r="C92" s="8">
         <v>1.2</v>
@@ -4144,8 +4361,8 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B93" s="28" t="s">
-        <v>162</v>
+      <c r="B93" s="27" t="s">
+        <v>158</v>
       </c>
       <c r="C93" s="8">
         <v>0.8</v>
@@ -4155,8 +4372,8 @@
       </c>
     </row>
     <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B94" s="28" t="s">
-        <v>163</v>
+      <c r="B94" s="27" t="s">
+        <v>159</v>
       </c>
       <c r="C94" s="8">
         <v>1</v>
@@ -4166,8 +4383,8 @@
       </c>
     </row>
     <row r="95" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B95" s="28" t="s">
-        <v>164</v>
+      <c r="B95" s="27" t="s">
+        <v>160</v>
       </c>
       <c r="C95" s="8">
         <v>1</v>
@@ -4177,8 +4394,8 @@
       </c>
     </row>
     <row r="96" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B96" s="28" t="s">
-        <v>165</v>
+      <c r="B96" s="27" t="s">
+        <v>161</v>
       </c>
       <c r="C96" s="8">
         <v>0.8</v>
@@ -4188,8 +4405,8 @@
       </c>
     </row>
     <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B97" s="28" t="s">
-        <v>166</v>
+      <c r="B97" s="27" t="s">
+        <v>162</v>
       </c>
       <c r="C97" s="8">
         <v>1.5</v>
@@ -4199,8 +4416,8 @@
       </c>
     </row>
     <row r="98" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B98" s="28" t="s">
-        <v>167</v>
+      <c r="B98" s="27" t="s">
+        <v>163</v>
       </c>
       <c r="C98" s="8">
         <v>1</v>
@@ -4210,8 +4427,8 @@
       </c>
     </row>
     <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B99" s="28" t="s">
-        <v>168</v>
+      <c r="B99" s="27" t="s">
+        <v>164</v>
       </c>
       <c r="C99" s="8">
         <v>1</v>
@@ -4221,16 +4438,16 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B100" s="28"/>
+      <c r="B100" s="27"/>
     </row>
     <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="36" t="s">
+      <c r="A101" s="61" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B102" s="28" t="s">
-        <v>169</v>
+      <c r="B102" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="C102" s="8">
         <v>1</v>
@@ -4240,8 +4457,8 @@
       </c>
     </row>
     <row r="103" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B103" s="28" t="s">
-        <v>170</v>
+      <c r="B103" s="27" t="s">
+        <v>166</v>
       </c>
       <c r="C103" s="8">
         <v>1.2</v>
@@ -4251,8 +4468,8 @@
       </c>
     </row>
     <row r="104" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B104" s="28" t="s">
-        <v>171</v>
+      <c r="B104" s="27" t="s">
+        <v>167</v>
       </c>
       <c r="C104" s="8">
         <v>1.5</v>
@@ -4262,8 +4479,8 @@
       </c>
     </row>
     <row r="105" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B105" s="28" t="s">
-        <v>172</v>
+      <c r="B105" s="27" t="s">
+        <v>168</v>
       </c>
       <c r="C105" s="8">
         <v>0.8</v>
@@ -4273,8 +4490,8 @@
       </c>
     </row>
     <row r="106" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B106" s="28" t="s">
-        <v>173</v>
+      <c r="B106" s="27" t="s">
+        <v>169</v>
       </c>
       <c r="C106" s="8">
         <v>1.2</v>
@@ -4284,8 +4501,8 @@
       </c>
     </row>
     <row r="107" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B107" s="28" t="s">
-        <v>174</v>
+      <c r="B107" s="27" t="s">
+        <v>170</v>
       </c>
       <c r="C107" s="8">
         <v>0.7</v>
@@ -4295,8 +4512,8 @@
       </c>
     </row>
     <row r="108" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B108" s="28" t="s">
-        <v>175</v>
+      <c r="B108" s="27" t="s">
+        <v>171</v>
       </c>
       <c r="C108" s="8">
         <v>1.5</v>
@@ -4306,8 +4523,8 @@
       </c>
     </row>
     <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B109" s="28" t="s">
-        <v>176</v>
+      <c r="B109" s="27" t="s">
+        <v>172</v>
       </c>
       <c r="C109" s="8">
         <v>1.5</v>
@@ -4317,8 +4534,8 @@
       </c>
     </row>
     <row r="110" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B110" s="28" t="s">
-        <v>177</v>
+      <c r="B110" s="27" t="s">
+        <v>173</v>
       </c>
       <c r="C110" s="8">
         <v>1</v>
@@ -4328,8 +4545,8 @@
       </c>
     </row>
     <row r="111" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B111" s="28" t="s">
-        <v>178</v>
+      <c r="B111" s="27" t="s">
+        <v>174</v>
       </c>
       <c r="C111" s="8">
         <v>1</v>
@@ -4339,16 +4556,16 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B112" s="28"/>
+      <c r="B112" s="27"/>
     </row>
     <row r="113" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A113" s="36" t="s">
+      <c r="A113" s="61" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B114" s="28" t="s">
-        <v>179</v>
+      <c r="B114" s="27" t="s">
+        <v>175</v>
       </c>
       <c r="C114" s="8">
         <v>0.8</v>
@@ -4358,8 +4575,8 @@
       </c>
     </row>
     <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B115" s="28" t="s">
-        <v>180</v>
+      <c r="B115" s="27" t="s">
+        <v>176</v>
       </c>
       <c r="C115" s="8">
         <v>1.2</v>
@@ -4369,8 +4586,8 @@
       </c>
     </row>
     <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B116" s="28" t="s">
-        <v>181</v>
+      <c r="B116" s="27" t="s">
+        <v>177</v>
       </c>
       <c r="C116" s="8">
         <v>1.2</v>
@@ -4380,8 +4597,8 @@
       </c>
     </row>
     <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B117" s="28" t="s">
-        <v>182</v>
+      <c r="B117" s="27" t="s">
+        <v>178</v>
       </c>
       <c r="C117" s="8">
         <v>1</v>
@@ -4391,8 +4608,8 @@
       </c>
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B118" s="28" t="s">
-        <v>183</v>
+      <c r="B118" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="C118" s="8">
         <v>0.6</v>
@@ -4402,8 +4619,8 @@
       </c>
     </row>
     <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B119" s="28" t="s">
-        <v>184</v>
+      <c r="B119" s="27" t="s">
+        <v>180</v>
       </c>
       <c r="C119" s="8">
         <v>1.2</v>
@@ -4413,8 +4630,8 @@
       </c>
     </row>
     <row r="120" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B120" s="28" t="s">
-        <v>185</v>
+      <c r="B120" s="27" t="s">
+        <v>181</v>
       </c>
       <c r="C120" s="8">
         <v>1</v>
@@ -4424,8 +4641,8 @@
       </c>
     </row>
     <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B121" s="28" t="s">
-        <v>186</v>
+      <c r="B121" s="27" t="s">
+        <v>182</v>
       </c>
       <c r="C121" s="8">
         <v>1</v>
@@ -4435,16 +4652,16 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B122" s="28"/>
+      <c r="B122" s="27"/>
     </row>
     <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A123" s="36" t="s">
+      <c r="A123" s="61" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B124" s="28" t="s">
-        <v>187</v>
+      <c r="B124" s="27" t="s">
+        <v>183</v>
       </c>
       <c r="C124" s="8">
         <v>1</v>
@@ -4454,8 +4671,8 @@
       </c>
     </row>
     <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B125" s="28" t="s">
-        <v>188</v>
+      <c r="B125" s="27" t="s">
+        <v>184</v>
       </c>
       <c r="C125" s="8">
         <v>1.2</v>
@@ -4465,8 +4682,8 @@
       </c>
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B126" s="28" t="s">
-        <v>189</v>
+      <c r="B126" s="27" t="s">
+        <v>185</v>
       </c>
       <c r="C126" s="8">
         <v>1.2</v>
@@ -4476,8 +4693,8 @@
       </c>
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B127" s="28" t="s">
-        <v>347</v>
+      <c r="B127" s="27" t="s">
+        <v>334</v>
       </c>
       <c r="C127" s="8">
         <v>1</v>
@@ -4487,8 +4704,8 @@
       </c>
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B128" s="28" t="s">
-        <v>190</v>
+      <c r="B128" s="27" t="s">
+        <v>186</v>
       </c>
       <c r="C128" s="8">
         <v>0.8</v>
@@ -4498,8 +4715,8 @@
       </c>
     </row>
     <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B129" s="28" t="s">
-        <v>191</v>
+      <c r="B129" s="27" t="s">
+        <v>187</v>
       </c>
       <c r="C129" s="8">
         <v>0.8</v>
@@ -4509,8 +4726,8 @@
       </c>
     </row>
     <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B130" s="28" t="s">
-        <v>192</v>
+      <c r="B130" s="27" t="s">
+        <v>188</v>
       </c>
       <c r="C130" s="8">
         <v>0.8</v>
@@ -4520,8 +4737,8 @@
       </c>
     </row>
     <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B131" s="28" t="s">
-        <v>193</v>
+      <c r="B131" s="27" t="s">
+        <v>189</v>
       </c>
       <c r="C131" s="8">
         <v>1.5</v>
@@ -4531,8 +4748,8 @@
       </c>
     </row>
     <row r="132" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B132" s="28" t="s">
-        <v>194</v>
+      <c r="B132" s="27" t="s">
+        <v>190</v>
       </c>
       <c r="C132" s="8">
         <v>1</v>
@@ -4542,8 +4759,8 @@
       </c>
     </row>
     <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B133" s="28" t="s">
-        <v>195</v>
+      <c r="B133" s="27" t="s">
+        <v>191</v>
       </c>
       <c r="C133" s="8">
         <v>1</v>
@@ -4553,104 +4770,104 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B134" s="28"/>
+      <c r="B134" s="27"/>
     </row>
     <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A135" s="36" t="s">
+      <c r="A135" s="58" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B136" s="28" t="s">
-        <v>196</v>
+      <c r="B136" s="27" t="s">
+        <v>192</v>
       </c>
       <c r="C136" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B137" s="28" t="s">
-        <v>197</v>
+      <c r="B137" s="27" t="s">
+        <v>193</v>
       </c>
       <c r="C137" s="8">
         <v>0.8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B138" s="28" t="s">
-        <v>198</v>
+      <c r="B138" s="27" t="s">
+        <v>194</v>
       </c>
       <c r="C138" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B139" s="28" t="s">
-        <v>199</v>
+      <c r="B139" s="27" t="s">
+        <v>195</v>
       </c>
       <c r="C139" s="8">
         <v>1.2</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B140" s="28" t="s">
-        <v>200</v>
+      <c r="B140" s="27" t="s">
+        <v>196</v>
       </c>
       <c r="C140" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B141" s="28" t="s">
+      <c r="B141" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C141" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B142" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C142" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B143" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C143" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B144" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C144" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B145" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="C141" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B142" s="28" t="s">
+      <c r="C145" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B146" s="27"/>
+    </row>
+    <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A147" s="61" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B148" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C142" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B143" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="C143" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B144" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="C144" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B145" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="C145" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B146" s="28"/>
-    </row>
-    <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A147" s="36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B148" s="28" t="s">
-        <v>206</v>
       </c>
       <c r="C148" s="8">
         <v>2</v>
@@ -4660,8 +4877,8 @@
       </c>
     </row>
     <row r="149" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B149" s="28" t="s">
-        <v>207</v>
+      <c r="B149" s="27" t="s">
+        <v>203</v>
       </c>
       <c r="C149" s="8">
         <v>1.2</v>
@@ -4671,8 +4888,8 @@
       </c>
     </row>
     <row r="150" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B150" s="28" t="s">
-        <v>208</v>
+      <c r="B150" s="27" t="s">
+        <v>204</v>
       </c>
       <c r="C150" s="8">
         <v>1</v>
@@ -4682,8 +4899,8 @@
       </c>
     </row>
     <row r="151" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B151" s="28" t="s">
-        <v>209</v>
+      <c r="B151" s="27" t="s">
+        <v>205</v>
       </c>
       <c r="C151" s="8">
         <v>1.5</v>
@@ -4693,8 +4910,8 @@
       </c>
     </row>
     <row r="152" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B152" s="28" t="s">
-        <v>210</v>
+      <c r="B152" s="27" t="s">
+        <v>206</v>
       </c>
       <c r="C152" s="8">
         <v>0.8</v>
@@ -4704,8 +4921,8 @@
       </c>
     </row>
     <row r="153" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B153" s="28" t="s">
-        <v>211</v>
+      <c r="B153" s="27" t="s">
+        <v>207</v>
       </c>
       <c r="C153" s="8">
         <v>1.5</v>
@@ -4715,8 +4932,8 @@
       </c>
     </row>
     <row r="154" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B154" s="28" t="s">
-        <v>212</v>
+      <c r="B154" s="27" t="s">
+        <v>208</v>
       </c>
       <c r="C154" s="8">
         <v>1</v>
@@ -4726,8 +4943,8 @@
       </c>
     </row>
     <row r="155" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B155" s="28" t="s">
-        <v>213</v>
+      <c r="B155" s="27" t="s">
+        <v>209</v>
       </c>
       <c r="C155" s="8">
         <v>1</v>
@@ -4737,1034 +4954,1040 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B156" s="28"/>
+      <c r="B156" s="27"/>
     </row>
     <row r="157" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A157" s="36" t="s">
+      <c r="A157" s="58" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B158" s="28" t="s">
+      <c r="B158" s="27" t="s">
+        <v>522</v>
+      </c>
+      <c r="C158" s="8">
+        <v>1</v>
+      </c>
+      <c r="D158" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B159" s="27" t="s">
+        <v>523</v>
+      </c>
+      <c r="C159" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D159" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B160" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="C160" s="8">
+        <v>2</v>
+      </c>
+      <c r="D160" s="8">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B161" s="27" t="s">
+        <v>525</v>
+      </c>
+      <c r="C161" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D161" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B162" s="27" t="s">
+        <v>526</v>
+      </c>
+      <c r="C162" s="8">
+        <v>3</v>
+      </c>
+      <c r="D162" s="8">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B163" s="27" t="s">
+        <v>527</v>
+      </c>
+      <c r="C163" s="8">
+        <v>2</v>
+      </c>
+      <c r="D163" s="8">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B164" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="C164" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D164" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B165" s="27" t="s">
+        <v>529</v>
+      </c>
+      <c r="C165" s="8">
+        <v>2</v>
+      </c>
+      <c r="D165" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B166" s="27" t="s">
+        <v>530</v>
+      </c>
+      <c r="C166" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="D166" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B167" s="27" t="s">
+        <v>531</v>
+      </c>
+      <c r="C167" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D167" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B168" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="C168" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D168" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B169" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="C169" s="8">
+        <v>1</v>
+      </c>
+      <c r="D169" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B170" s="27" t="s">
+        <v>534</v>
+      </c>
+      <c r="C170" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D170" s="8">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B171" s="27" t="s">
+        <v>535</v>
+      </c>
+      <c r="C171" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D171" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B172" s="27" t="s">
+        <v>536</v>
+      </c>
+      <c r="C172" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D172" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B173" s="36" t="s">
+        <v>537</v>
+      </c>
+      <c r="C173" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D173" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B174" s="27"/>
+    </row>
+    <row r="175" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A175" s="60" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B176" s="59" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B177" s="59" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B178" s="59" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B179" s="59" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B180" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="C158" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B159" s="28" t="s">
+    </row>
+    <row r="181" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B181" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="C159" s="8">
+    </row>
+    <row r="182" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B182" s="59" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B183" s="59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B184" s="27"/>
+    </row>
+    <row r="185" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A185" s="37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B186" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="C186" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D186" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B187" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="C187" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="D187" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B188" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C188" s="8">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B160" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C160" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B161" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="C161" s="8">
+      <c r="D188" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B189" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="C189" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="D189" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B190" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C190" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D190" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B191" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="C191" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B162" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="C162" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B163" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="C163" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B164" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="C164" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B165" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="C165" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B166" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="C166" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B167" s="28"/>
-    </row>
-    <row r="168" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A168" s="36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B169" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="C169" s="8">
+      <c r="D191" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B192" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C192" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B193" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="C193" s="8">
+        <v>1</v>
+      </c>
+      <c r="D193" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B194" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C194" s="8">
+        <v>1</v>
+      </c>
+      <c r="D194" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A195" s="14"/>
+      <c r="B195" s="27" t="s">
+        <v>466</v>
+      </c>
+      <c r="C195" s="14">
+        <v>1</v>
+      </c>
+      <c r="D195" s="14">
+        <v>1</v>
+      </c>
+      <c r="E195" s="14"/>
+    </row>
+    <row r="196" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A196" s="14"/>
+      <c r="B196" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="C196" s="14">
+        <v>1</v>
+      </c>
+      <c r="D196" s="14">
+        <v>1</v>
+      </c>
+      <c r="E196" s="14"/>
+    </row>
+    <row r="197" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A197" s="14"/>
+      <c r="B197" s="27" t="s">
+        <v>494</v>
+      </c>
+      <c r="C197" s="14">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B170" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="C170" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B171" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="C171" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B172" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="C172" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B173" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="C173" s="8">
+      <c r="D197" s="14">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B174" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="C174" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B175" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="C175" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B176" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="C176" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B177" s="28"/>
-    </row>
-    <row r="178" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A178" s="38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B179" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="C179" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D179" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B180" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="C180" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="D180" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B181" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="C181" s="8">
+      <c r="E197" s="14"/>
+    </row>
+    <row r="198" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A198" s="14"/>
+      <c r="B198" s="27" t="s">
+        <v>493</v>
+      </c>
+      <c r="C198" s="14">
         <v>1.2</v>
       </c>
-      <c r="D181" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B182" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="C182" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="D182" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B183" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="C183" s="8">
+      <c r="D198" s="14">
         <v>1.2</v>
       </c>
-      <c r="D183" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B184" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="C184" s="8">
-        <v>2</v>
-      </c>
-      <c r="D184" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B185" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="C185" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B186" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="C186" s="8">
-        <v>1</v>
-      </c>
-      <c r="D186" s="8">
+      <c r="E198" s="14"/>
+    </row>
+    <row r="199" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A199" s="14"/>
+      <c r="B199" s="27" t="s">
+        <v>495</v>
+      </c>
+      <c r="C199" s="14">
+        <v>1</v>
+      </c>
+      <c r="D199" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B187" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="C187" s="8">
-        <v>1</v>
-      </c>
-      <c r="D187" s="8">
+      <c r="E199" s="14"/>
+    </row>
+    <row r="200" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A200" s="14"/>
+      <c r="B200" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="C200" s="14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A188" s="14"/>
-      <c r="B188" s="28" t="s">
-        <v>479</v>
-      </c>
-      <c r="C188" s="14">
-        <v>1</v>
-      </c>
-      <c r="D188" s="14">
-        <v>1</v>
-      </c>
-      <c r="E188" s="14"/>
-    </row>
-    <row r="189" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A189" s="14"/>
-      <c r="B189" s="28" t="s">
-        <v>505</v>
-      </c>
-      <c r="C189" s="14">
-        <v>1</v>
-      </c>
-      <c r="D189" s="14">
-        <v>1</v>
-      </c>
-      <c r="E189" s="14"/>
-    </row>
-    <row r="190" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A190" s="14"/>
-      <c r="B190" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="C190" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D190" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="E190" s="14"/>
-    </row>
-    <row r="191" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A191" s="14"/>
-      <c r="B191" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="C191" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D191" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="E191" s="14"/>
-    </row>
-    <row r="192" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A192" s="14"/>
-      <c r="B192" s="28" t="s">
-        <v>508</v>
-      </c>
-      <c r="C192" s="14">
-        <v>1</v>
-      </c>
-      <c r="D192" s="14">
+      <c r="D200" s="14">
         <v>0.5</v>
       </c>
-      <c r="E192" s="14"/>
-    </row>
-    <row r="193" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A193" s="14"/>
-      <c r="B193" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="C193" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="D193" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E193" s="14"/>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194" s="14"/>
-      <c r="B194" s="8"/>
-      <c r="C194" s="14"/>
-      <c r="D194" s="14"/>
-      <c r="E194" s="14"/>
-    </row>
-    <row r="195" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A195" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="B195" s="28" t="s">
-        <v>370</v>
-      </c>
-      <c r="C195" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D195" s="14">
-        <v>1</v>
-      </c>
-      <c r="E195" s="14"/>
-    </row>
-    <row r="196" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="16"/>
-      <c r="B196" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="C196" s="14">
-        <v>1</v>
-      </c>
-      <c r="D196" s="14">
-        <v>1</v>
-      </c>
-      <c r="E196" s="14"/>
-    </row>
-    <row r="197" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="16"/>
-      <c r="B197" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="C197" s="14">
-        <v>1</v>
-      </c>
-      <c r="D197" s="14">
-        <v>1</v>
-      </c>
-      <c r="E197" s="14"/>
-    </row>
-    <row r="198" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A198" s="19"/>
-      <c r="B198" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="C198" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D198" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E198" s="14"/>
-    </row>
-    <row r="199" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="16"/>
-      <c r="B199" s="28" t="s">
-        <v>374</v>
-      </c>
-      <c r="C199" s="14">
-        <v>2</v>
-      </c>
-      <c r="D199" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="E199" s="14"/>
-    </row>
-    <row r="200" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="B200" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="C200" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D200" s="14">
-        <v>2.5</v>
-      </c>
       <c r="E200" s="14"/>
     </row>
-    <row r="201" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="16"/>
-      <c r="B201" s="28" t="s">
-        <v>376</v>
-      </c>
-      <c r="C201" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D201" s="14">
-        <v>3</v>
-      </c>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A201" s="14"/>
+      <c r="B201" s="8"/>
+      <c r="C201" s="14"/>
+      <c r="D201" s="14"/>
       <c r="E201" s="14"/>
     </row>
-    <row r="202" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="16"/>
-      <c r="B202" s="28" t="s">
-        <v>377</v>
+    <row r="202" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A202" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="B202" s="27" t="s">
+        <v>357</v>
       </c>
       <c r="C202" s="14">
         <v>1.5</v>
       </c>
       <c r="D202" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E202" s="14"/>
     </row>
     <row r="203" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="16"/>
-      <c r="B203" s="28" t="s">
-        <v>378</v>
+      <c r="B203" s="27" t="s">
+        <v>358</v>
       </c>
       <c r="C203" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D203" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E203" s="14"/>
     </row>
     <row r="204" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="16"/>
-      <c r="B204" s="28" t="s">
-        <v>379</v>
+      <c r="B204" s="27" t="s">
+        <v>359</v>
       </c>
       <c r="C204" s="14">
         <v>1</v>
       </c>
       <c r="D204" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E204" s="14"/>
     </row>
-    <row r="205" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="16"/>
-      <c r="B205" s="28" t="s">
-        <v>380</v>
+    <row r="205" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A205" s="19"/>
+      <c r="B205" s="30" t="s">
+        <v>360</v>
       </c>
       <c r="C205" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D205" s="14">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="E205" s="14"/>
     </row>
     <row r="206" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="16"/>
-      <c r="B206" s="28" t="s">
-        <v>381</v>
+      <c r="B206" s="27" t="s">
+        <v>361</v>
       </c>
       <c r="C206" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D206" s="14">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E206" s="14"/>
     </row>
     <row r="207" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="16"/>
-      <c r="B207" s="28" t="s">
-        <v>382</v>
+      <c r="A207" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B207" s="27" t="s">
+        <v>362</v>
       </c>
       <c r="C207" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D207" s="14">
         <v>2.5</v>
       </c>
-      <c r="D207" s="14">
+      <c r="E207" s="14"/>
+    </row>
+    <row r="208" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="16"/>
+      <c r="B208" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="C208" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D208" s="14">
         <v>3</v>
       </c>
-      <c r="E207" s="14"/>
-    </row>
-    <row r="208" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="19"/>
-      <c r="B208" s="31" t="s">
-        <v>383</v>
-      </c>
-      <c r="C208" s="14">
+      <c r="E208" s="14"/>
+    </row>
+    <row r="209" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="16"/>
+      <c r="B209" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="C209" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D209" s="14">
+        <v>2</v>
+      </c>
+      <c r="E209" s="14"/>
+    </row>
+    <row r="210" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="16"/>
+      <c r="B210" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="C210" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D210" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E210" s="14"/>
+    </row>
+    <row r="211" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="16"/>
+      <c r="B211" s="27" t="s">
+        <v>366</v>
+      </c>
+      <c r="C211" s="14">
+        <v>1</v>
+      </c>
+      <c r="D211" s="14">
+        <v>2</v>
+      </c>
+      <c r="E211" s="14"/>
+    </row>
+    <row r="212" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="16"/>
+      <c r="B212" s="27" t="s">
+        <v>367</v>
+      </c>
+      <c r="C212" s="14">
+        <v>2</v>
+      </c>
+      <c r="D212" s="14">
+        <v>4</v>
+      </c>
+      <c r="E212" s="14"/>
+    </row>
+    <row r="213" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="16"/>
+      <c r="B213" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="C213" s="14">
+        <v>1</v>
+      </c>
+      <c r="D213" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E213" s="14"/>
+    </row>
+    <row r="214" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="16"/>
+      <c r="B214" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="C214" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D214" s="14">
+        <v>3</v>
+      </c>
+      <c r="E214" s="14"/>
+    </row>
+    <row r="215" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="19"/>
+      <c r="B215" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="C215" s="14">
         <v>1.2</v>
       </c>
-      <c r="D208" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E208" s="14"/>
-    </row>
-    <row r="209" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="19"/>
-      <c r="B209" s="28" t="s">
-        <v>510</v>
-      </c>
-      <c r="C209" s="14">
+      <c r="D215" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E215" s="14"/>
+    </row>
+    <row r="216" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="19"/>
+      <c r="B216" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="C216" s="14">
         <v>0.5</v>
       </c>
-      <c r="D209" s="14">
+      <c r="D216" s="14">
         <v>0.5</v>
       </c>
-      <c r="E209" s="14"/>
-    </row>
-    <row r="210" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="19"/>
-      <c r="B210" s="28" t="s">
-        <v>511</v>
-      </c>
-      <c r="C210" s="14">
+      <c r="E216" s="14"/>
+    </row>
+    <row r="217" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="19"/>
+      <c r="B217" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="C217" s="14">
         <v>0.5</v>
       </c>
-      <c r="D210" s="14">
+      <c r="D217" s="14">
         <v>0.5</v>
       </c>
-      <c r="E210" s="14"/>
-    </row>
-    <row r="211" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="19"/>
-      <c r="B211" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="C211" s="14">
+      <c r="E217" s="14"/>
+    </row>
+    <row r="218" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="19"/>
+      <c r="B218" s="27" t="s">
+        <v>499</v>
+      </c>
+      <c r="C218" s="14">
         <v>0.5</v>
       </c>
-      <c r="D211" s="14">
+      <c r="D218" s="14">
         <v>0.5</v>
       </c>
-      <c r="E211" s="14"/>
-    </row>
-    <row r="212" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="19"/>
-      <c r="B212" s="28" t="s">
-        <v>513</v>
-      </c>
-      <c r="C212" s="14">
+      <c r="E218" s="14"/>
+    </row>
+    <row r="219" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="19"/>
+      <c r="B219" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="C219" s="14">
         <v>0.5</v>
       </c>
-      <c r="D212" s="14">
+      <c r="D219" s="14">
         <v>0.5</v>
       </c>
-      <c r="E212" s="14"/>
-    </row>
-    <row r="213" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="19"/>
-      <c r="B213" s="28"/>
-      <c r="C213" s="14"/>
-      <c r="D213" s="14"/>
-      <c r="E213" s="14"/>
-    </row>
-    <row r="214" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="B214" s="28"/>
-      <c r="C214" s="14"/>
-      <c r="D214" s="14"/>
-      <c r="E214" s="14"/>
-    </row>
-    <row r="215" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="16"/>
-      <c r="B215" s="28" t="s">
-        <v>514</v>
-      </c>
-      <c r="C215" s="14"/>
-      <c r="D215" s="14"/>
-      <c r="E215" s="14"/>
-    </row>
-    <row r="216" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="16"/>
-      <c r="B216" s="28" t="s">
-        <v>515</v>
-      </c>
-      <c r="C216" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D216" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E216" s="14"/>
-    </row>
-    <row r="217" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="16"/>
-      <c r="B217" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="C217" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D217" s="14">
-        <v>2</v>
-      </c>
-      <c r="E217" s="14"/>
-    </row>
-    <row r="218" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="16"/>
-      <c r="B218" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="C218" s="14">
-        <v>1</v>
-      </c>
-      <c r="D218" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E218" s="14"/>
-    </row>
-    <row r="219" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="16"/>
-      <c r="B219" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="C219" s="14">
-        <v>1</v>
-      </c>
-      <c r="D219" s="14">
-        <v>1.5</v>
-      </c>
       <c r="E219" s="14"/>
     </row>
     <row r="220" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="16"/>
-      <c r="B220" s="28" t="s">
-        <v>519</v>
-      </c>
-      <c r="C220" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D220" s="14">
-        <v>1.5</v>
-      </c>
+      <c r="A220" s="19"/>
+      <c r="B220" s="27"/>
+      <c r="C220" s="14"/>
+      <c r="D220" s="14"/>
       <c r="E220" s="14"/>
     </row>
     <row r="221" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="16"/>
-      <c r="B221" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="C221" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="D221" s="14">
-        <v>0.5</v>
-      </c>
+      <c r="A221" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="B221" s="27"/>
+      <c r="C221" s="14"/>
+      <c r="D221" s="14"/>
       <c r="E221" s="14"/>
     </row>
-    <row r="222" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A222" s="8"/>
-      <c r="B222" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="C222" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D222" s="14">
-        <v>1</v>
-      </c>
+    <row r="222" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="16"/>
+      <c r="B222" s="27" t="s">
+        <v>501</v>
+      </c>
+      <c r="C222" s="14"/>
+      <c r="D222" s="14"/>
       <c r="E222" s="14"/>
     </row>
     <row r="223" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="16"/>
-      <c r="B223" s="28" t="s">
-        <v>385</v>
+      <c r="B223" s="27" t="s">
+        <v>502</v>
       </c>
       <c r="C223" s="14">
         <v>1.2</v>
       </c>
       <c r="D223" s="14">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E223" s="14"/>
     </row>
     <row r="224" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="16"/>
-      <c r="B224" s="28" t="s">
-        <v>386</v>
+      <c r="B224" s="27" t="s">
+        <v>503</v>
       </c>
       <c r="C224" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D224" s="14">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E224" s="14"/>
     </row>
     <row r="225" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="16"/>
-      <c r="B225" s="28" t="s">
-        <v>387</v>
+      <c r="B225" s="27" t="s">
+        <v>504</v>
       </c>
       <c r="C225" s="14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D225" s="14">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E225" s="14"/>
     </row>
     <row r="226" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="16"/>
-      <c r="B226" s="28" t="s">
-        <v>388</v>
+      <c r="B226" s="27" t="s">
+        <v>505</v>
       </c>
       <c r="C226" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D226" s="14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E226" s="14"/>
     </row>
     <row r="227" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="16"/>
-      <c r="B227" s="28" t="s">
-        <v>389</v>
+      <c r="B227" s="27" t="s">
+        <v>506</v>
       </c>
       <c r="C227" s="14">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D227" s="14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E227" s="14"/>
     </row>
     <row r="228" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="16"/>
-      <c r="B228" s="28" t="s">
-        <v>390</v>
+      <c r="B228" s="27" t="s">
+        <v>507</v>
       </c>
       <c r="C228" s="14">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D228" s="14">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="E228" s="14"/>
     </row>
-    <row r="229" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="19"/>
-      <c r="B229" s="31" t="s">
-        <v>391</v>
+    <row r="229" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A229" s="8"/>
+      <c r="B229" s="27" t="s">
+        <v>371</v>
       </c>
       <c r="C229" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="D229" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E229" s="14"/>
     </row>
     <row r="230" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="16"/>
-      <c r="B230" s="28" t="s">
-        <v>392</v>
+      <c r="B230" s="27" t="s">
+        <v>372</v>
       </c>
       <c r="C230" s="14">
         <v>1.2</v>
       </c>
       <c r="D230" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E230" s="14"/>
     </row>
     <row r="231" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="16"/>
-      <c r="B231" s="28" t="s">
-        <v>393</v>
+      <c r="B231" s="27" t="s">
+        <v>373</v>
       </c>
       <c r="C231" s="14">
         <v>1</v>
       </c>
       <c r="D231" s="14">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E231" s="14"/>
     </row>
-    <row r="232" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="16"/>
-      <c r="B232" s="8" t="s">
-        <v>521</v>
+      <c r="B232" s="27" t="s">
+        <v>374</v>
       </c>
       <c r="C232" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="D232" s="14">
         <v>1</v>
       </c>
       <c r="E232" s="14"/>
     </row>
-    <row r="233" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="16"/>
-      <c r="B233" s="8" t="s">
-        <v>522</v>
+      <c r="B233" s="27" t="s">
+        <v>375</v>
       </c>
       <c r="C233" s="14">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D233" s="14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E233" s="14"/>
     </row>
-    <row r="234" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="16"/>
-      <c r="B234" s="8" t="s">
-        <v>523</v>
+      <c r="B234" s="27" t="s">
+        <v>376</v>
       </c>
       <c r="C234" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D234" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" s="14"/>
     </row>
     <row r="235" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="16"/>
-      <c r="B235" s="28"/>
-      <c r="C235" s="14"/>
-      <c r="D235" s="14"/>
+      <c r="B235" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C235" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D235" s="14">
+        <v>1.8</v>
+      </c>
       <c r="E235" s="14"/>
     </row>
-    <row r="236" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A236" s="29" t="s">
-        <v>354</v>
-      </c>
-      <c r="B236" s="28" t="s">
-        <v>448</v>
+    <row r="236" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="19"/>
+      <c r="B236" s="30" t="s">
+        <v>378</v>
       </c>
       <c r="C236" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D236" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="D236" s="14">
+        <v>2.5</v>
+      </c>
       <c r="E236" s="14"/>
     </row>
-    <row r="237" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="16"/>
-      <c r="B237" s="28" t="s">
-        <v>449</v>
+      <c r="B237" s="27" t="s">
+        <v>379</v>
       </c>
       <c r="C237" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="D237" s="14"/>
+        <v>1.2</v>
+      </c>
+      <c r="D237" s="14">
+        <v>1</v>
+      </c>
       <c r="E237" s="14"/>
     </row>
-    <row r="238" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="16"/>
-      <c r="B238" s="28" t="s">
-        <v>450</v>
+      <c r="B238" s="27" t="s">
+        <v>380</v>
       </c>
       <c r="C238" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="D238" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D238" s="14">
+        <v>1</v>
+      </c>
       <c r="E238" s="14"/>
     </row>
-    <row r="239" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A239" s="16"/>
-      <c r="B239" s="28" t="s">
-        <v>451</v>
+      <c r="B239" s="8" t="s">
+        <v>508</v>
       </c>
       <c r="C239" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D239" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="D239" s="14">
+        <v>1</v>
+      </c>
       <c r="E239" s="14"/>
     </row>
-    <row r="240" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A240" s="16"/>
-      <c r="B240" s="28" t="s">
-        <v>452</v>
+      <c r="B240" s="8" t="s">
+        <v>509</v>
       </c>
       <c r="C240" s="14">
+        <v>1</v>
+      </c>
+      <c r="D240" s="14">
         <v>1.2</v>
       </c>
-      <c r="D240" s="14"/>
       <c r="E240" s="14"/>
     </row>
-    <row r="241" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A241" s="16"/>
-      <c r="B241" s="28" t="s">
-        <v>453</v>
+      <c r="B241" s="8" t="s">
+        <v>510</v>
       </c>
       <c r="C241" s="14">
-        <v>2</v>
-      </c>
-      <c r="D241" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="D241" s="14">
+        <v>1</v>
+      </c>
       <c r="E241" s="14"/>
     </row>
     <row r="242" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="19"/>
-      <c r="B242" s="28" t="s">
-        <v>454</v>
-      </c>
-      <c r="C242" s="14">
-        <v>0.8</v>
-      </c>
+      <c r="A242" s="16"/>
+      <c r="B242" s="27"/>
+      <c r="C242" s="14"/>
       <c r="D242" s="14"/>
       <c r="E242" s="14"/>
     </row>
-    <row r="243" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="16"/>
-      <c r="B243" s="31" t="s">
-        <v>455</v>
+    <row r="243" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A243" s="62" t="s">
+        <v>341</v>
+      </c>
+      <c r="B243" s="27" t="s">
+        <v>435</v>
       </c>
       <c r="C243" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D243" s="14"/>
       <c r="E243" s="14"/>
     </row>
-    <row r="244" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A244" s="16"/>
-      <c r="B244" s="28" t="s">
-        <v>456</v>
+      <c r="B244" s="27" t="s">
+        <v>436</v>
       </c>
       <c r="C244" s="14">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="D244" s="14"/>
       <c r="E244" s="14"/>
     </row>
-    <row r="245" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A245" s="16"/>
-      <c r="B245" s="28" t="s">
-        <v>457</v>
+      <c r="B245" s="27" t="s">
+        <v>437</v>
       </c>
       <c r="C245" s="14">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="D245" s="14"/>
       <c r="E245" s="14"/>
     </row>
-    <row r="246" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A246" s="16"/>
-      <c r="B246" s="28" t="s">
-        <v>458</v>
+      <c r="B246" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="C246" s="14">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D246" s="14"/>
       <c r="E246" s="14"/>
     </row>
     <row r="247" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="16"/>
-      <c r="B247" s="28" t="s">
-        <v>459</v>
+      <c r="B247" s="27" t="s">
+        <v>439</v>
       </c>
       <c r="C247" s="14">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D247" s="14"/>
       <c r="E247" s="14"/>
     </row>
     <row r="248" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="16"/>
-      <c r="B248" s="28" t="s">
-        <v>460</v>
+      <c r="B248" s="27" t="s">
+        <v>440</v>
       </c>
       <c r="C248" s="14">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="D248" s="14"/>
       <c r="E248" s="14"/>
     </row>
     <row r="249" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A249" s="16"/>
-      <c r="B249" s="28" t="s">
-        <v>461</v>
+      <c r="A249" s="19"/>
+      <c r="B249" s="27" t="s">
+        <v>441</v>
       </c>
       <c r="C249" s="14">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D249" s="14"/>
       <c r="E249" s="14"/>
     </row>
     <row r="250" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="16"/>
-      <c r="B250" s="28" t="s">
-        <v>462</v>
+      <c r="B250" s="30" t="s">
+        <v>442</v>
       </c>
       <c r="C250" s="14">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D250" s="14"/>
       <c r="E250" s="14"/>
     </row>
     <row r="251" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="16"/>
-      <c r="B251" s="28" t="s">
-        <v>463</v>
+      <c r="B251" s="27" t="s">
+        <v>443</v>
       </c>
       <c r="C251" s="14">
         <v>1.2</v>
@@ -5774,172 +5997,156 @@
     </row>
     <row r="252" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="16"/>
-      <c r="B252" s="28" t="s">
-        <v>464</v>
+      <c r="B252" s="27" t="s">
+        <v>444</v>
       </c>
       <c r="C252" s="14">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="D252" s="14"/>
       <c r="E252" s="14"/>
     </row>
     <row r="253" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="16"/>
-      <c r="B253" s="28" t="s">
-        <v>483</v>
+      <c r="B253" s="27" t="s">
+        <v>445</v>
       </c>
       <c r="C253" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D253" s="14"/>
       <c r="E253" s="14"/>
     </row>
-    <row r="254" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="16"/>
-      <c r="B254" s="28" t="s">
-        <v>484</v>
+      <c r="B254" s="27" t="s">
+        <v>446</v>
       </c>
       <c r="C254" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D254" s="14"/>
       <c r="E254" s="14"/>
     </row>
-    <row r="255" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A255" s="16" t="s">
+    <row r="255" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="16"/>
+      <c r="B255" s="27" t="s">
         <v>447</v>
       </c>
-      <c r="B255" s="28" t="s">
-        <v>485</v>
-      </c>
       <c r="C255" s="14">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D255" s="14"/>
       <c r="E255" s="14"/>
     </row>
     <row r="256" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="16"/>
-      <c r="B256" s="28"/>
-      <c r="C256" s="14"/>
+      <c r="B256" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="C256" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D256" s="14"/>
       <c r="E256" s="14"/>
     </row>
-    <row r="257" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A257" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="B257" s="31" t="s">
-        <v>427</v>
+    <row r="257" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="16"/>
+      <c r="B257" s="27" t="s">
+        <v>449</v>
       </c>
       <c r="C257" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D257" s="14">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D257" s="14"/>
       <c r="E257" s="14"/>
     </row>
-    <row r="258" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="16"/>
-      <c r="B258" s="28" t="s">
-        <v>428</v>
+      <c r="B258" s="27" t="s">
+        <v>450</v>
       </c>
       <c r="C258" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D258" s="14">
-        <v>1</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="D258" s="14"/>
       <c r="E258" s="14"/>
     </row>
     <row r="259" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="16"/>
-      <c r="B259" s="28" t="s">
-        <v>429</v>
+      <c r="B259" s="27" t="s">
+        <v>451</v>
       </c>
       <c r="C259" s="14">
-        <v>2</v>
-      </c>
-      <c r="D259" s="14">
-        <v>2</v>
-      </c>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D259" s="14"/>
       <c r="E259" s="14"/>
     </row>
     <row r="260" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="16"/>
-      <c r="B260" s="28" t="s">
-        <v>430</v>
+      <c r="B260" s="27" t="s">
+        <v>470</v>
       </c>
       <c r="C260" s="14">
         <v>2</v>
       </c>
-      <c r="D260" s="14">
-        <v>2</v>
-      </c>
+      <c r="D260" s="14"/>
       <c r="E260" s="14"/>
     </row>
-    <row r="261" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A261" s="16"/>
-      <c r="B261" s="28" t="s">
-        <v>431</v>
+      <c r="B261" s="27" t="s">
+        <v>471</v>
       </c>
       <c r="C261" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D261" s="14">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D261" s="14"/>
       <c r="E261" s="14"/>
     </row>
-    <row r="262" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="16"/>
-      <c r="B262" s="28" t="s">
-        <v>432</v>
+    <row r="262" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A262" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B262" s="27" t="s">
+        <v>472</v>
       </c>
       <c r="C262" s="14">
         <v>1</v>
       </c>
-      <c r="D262" s="14">
-        <v>0.8</v>
-      </c>
+      <c r="D262" s="14"/>
       <c r="E262" s="14"/>
     </row>
     <row r="263" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="16"/>
-      <c r="B263" s="28" t="s">
-        <v>433</v>
-      </c>
-      <c r="C263" s="14">
-        <v>2</v>
-      </c>
-      <c r="D263" s="14">
-        <v>2</v>
-      </c>
+      <c r="B263" s="27"/>
+      <c r="C263" s="14"/>
+      <c r="D263" s="14"/>
       <c r="E263" s="14"/>
     </row>
-    <row r="264" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="16"/>
-      <c r="B264" s="28" t="s">
-        <v>486</v>
+    <row r="264" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A264" s="31" t="s">
+        <v>342</v>
+      </c>
+      <c r="B264" s="30" t="s">
+        <v>414</v>
       </c>
       <c r="C264" s="14">
         <v>1.5</v>
       </c>
       <c r="D264" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E264" s="14"/>
     </row>
-    <row r="265" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="B265" s="28" t="s">
-        <v>487</v>
+    <row r="265" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A265" s="16"/>
+      <c r="B265" s="27" t="s">
+        <v>415</v>
       </c>
       <c r="C265" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D265" s="14">
         <v>1</v>
@@ -5948,137 +6155,139 @@
     </row>
     <row r="266" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="16"/>
-      <c r="B266" s="28" t="s">
-        <v>488</v>
+      <c r="B266" s="27" t="s">
+        <v>416</v>
       </c>
       <c r="C266" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D266" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E266" s="14"/>
     </row>
     <row r="267" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="16"/>
-      <c r="B267" s="28" t="s">
-        <v>524</v>
+      <c r="B267" s="27" t="s">
+        <v>417</v>
       </c>
       <c r="C267" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D267" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E267" s="14"/>
     </row>
     <row r="268" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="16"/>
-      <c r="B268" s="28"/>
-      <c r="C268" s="14"/>
-      <c r="D268" s="14"/>
+      <c r="B268" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="C268" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D268" s="14">
+        <v>1</v>
+      </c>
       <c r="E268" s="14"/>
     </row>
-    <row r="269" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A269" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="B269" s="28" t="s">
-        <v>394</v>
+    <row r="269" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="16"/>
+      <c r="B269" s="27" t="s">
+        <v>419</v>
       </c>
       <c r="C269" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D269" s="14">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E269" s="14"/>
     </row>
     <row r="270" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="16"/>
-      <c r="B270" s="28" t="s">
-        <v>395</v>
+      <c r="B270" s="27" t="s">
+        <v>420</v>
       </c>
       <c r="C270" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D270" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E270" s="14"/>
     </row>
     <row r="271" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="19"/>
-      <c r="B271" s="31" t="s">
-        <v>396</v>
+      <c r="A271" s="16"/>
+      <c r="B271" s="27" t="s">
+        <v>473</v>
       </c>
       <c r="C271" s="14">
         <v>1.5</v>
       </c>
       <c r="D271" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E271" s="14"/>
     </row>
     <row r="272" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="16"/>
-      <c r="B272" s="28" t="s">
-        <v>397</v>
+      <c r="A272" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B272" s="27" t="s">
+        <v>474</v>
       </c>
       <c r="C272" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D272" s="14">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E272" s="14"/>
     </row>
     <row r="273" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="16"/>
-      <c r="B273" s="28" t="s">
-        <v>398</v>
+      <c r="B273" s="27" t="s">
+        <v>475</v>
       </c>
       <c r="C273" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D273" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E273" s="14"/>
     </row>
     <row r="274" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="16"/>
-      <c r="B274" s="28" t="s">
-        <v>399</v>
+      <c r="B274" s="27" t="s">
+        <v>511</v>
       </c>
       <c r="C274" s="14">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D274" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E274" s="14"/>
     </row>
     <row r="275" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="16"/>
-      <c r="B275" s="28" t="s">
-        <v>400</v>
-      </c>
-      <c r="C275" s="14">
-        <v>2</v>
-      </c>
-      <c r="D275" s="14">
-        <v>2</v>
-      </c>
+      <c r="B275" s="27"/>
+      <c r="C275" s="14"/>
+      <c r="D275" s="14"/>
       <c r="E275" s="14"/>
     </row>
-    <row r="276" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="16"/>
-      <c r="B276" s="28" t="s">
-        <v>401</v>
+    <row r="276" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A276" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="B276" s="27" t="s">
+        <v>381</v>
       </c>
       <c r="C276" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D276" s="14">
         <v>1</v>
@@ -6087,352 +6296,354 @@
     </row>
     <row r="277" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="16"/>
-      <c r="B277" s="28" t="s">
-        <v>402</v>
+      <c r="B277" s="27" t="s">
+        <v>382</v>
       </c>
       <c r="C277" s="14">
+        <v>1</v>
+      </c>
+      <c r="D277" s="14">
+        <v>1</v>
+      </c>
+      <c r="E277" s="14"/>
+    </row>
+    <row r="278" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="19"/>
+      <c r="B278" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="C278" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D278" s="14">
         <v>1.2</v>
-      </c>
-      <c r="D277" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="E277" s="14"/>
-    </row>
-    <row r="278" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="16"/>
-      <c r="B278" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="C278" s="14">
-        <v>1</v>
-      </c>
-      <c r="D278" s="14">
-        <v>1</v>
       </c>
       <c r="E278" s="14"/>
     </row>
     <row r="279" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="16"/>
-      <c r="B279" s="28" t="s">
-        <v>481</v>
+      <c r="B279" s="27" t="s">
+        <v>384</v>
       </c>
       <c r="C279" s="14">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="D279" s="14">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="E279" s="14"/>
     </row>
     <row r="280" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="16"/>
-      <c r="B280" s="28" t="s">
-        <v>482</v>
+      <c r="B280" s="27" t="s">
+        <v>385</v>
       </c>
       <c r="C280" s="14">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D280" s="14">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E280" s="14"/>
     </row>
     <row r="281" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="16"/>
-      <c r="B281" s="28"/>
-      <c r="C281" s="14"/>
-      <c r="D281" s="14"/>
+      <c r="B281" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="C281" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D281" s="14">
+        <v>2</v>
+      </c>
       <c r="E281" s="14"/>
     </row>
     <row r="282" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="B282" s="28"/>
-      <c r="C282" s="14"/>
-      <c r="D282" s="14"/>
+      <c r="A282" s="16"/>
+      <c r="B282" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="C282" s="14">
+        <v>2</v>
+      </c>
+      <c r="D282" s="14">
+        <v>2</v>
+      </c>
       <c r="E282" s="14"/>
     </row>
-    <row r="283" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A283" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="B283" s="28" t="s">
-        <v>403</v>
+    <row r="283" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" s="16"/>
+      <c r="B283" s="27" t="s">
+        <v>388</v>
       </c>
       <c r="C283" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D283" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E283" s="14"/>
     </row>
-    <row r="284" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A284" s="19"/>
-      <c r="B284" s="31" t="s">
-        <v>404</v>
+    <row r="284" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="16"/>
+      <c r="B284" s="27" t="s">
+        <v>389</v>
       </c>
       <c r="C284" s="14">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D284" s="14">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="E284" s="14"/>
     </row>
-    <row r="285" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="16"/>
-      <c r="B285" s="28" t="s">
-        <v>405</v>
+      <c r="B285" s="27" t="s">
+        <v>467</v>
       </c>
       <c r="C285" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D285" s="14">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="E285" s="14"/>
     </row>
-    <row r="286" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="16"/>
-      <c r="B286" s="28" t="s">
-        <v>406</v>
+      <c r="B286" s="27" t="s">
+        <v>468</v>
       </c>
       <c r="C286" s="14">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D286" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="E286" s="14"/>
     </row>
     <row r="287" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="16"/>
-      <c r="B287" s="28" t="s">
-        <v>407</v>
+      <c r="B287" s="27" t="s">
+        <v>469</v>
       </c>
       <c r="C287" s="14">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D287" s="14">
-        <v>2.2000000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="E287" s="14"/>
     </row>
-    <row r="288" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="16"/>
-      <c r="B288" s="28" t="s">
-        <v>408</v>
-      </c>
-      <c r="C288" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D288" s="14">
-        <v>1.5</v>
-      </c>
+      <c r="B288" s="27"/>
+      <c r="C288" s="14"/>
+      <c r="D288" s="14"/>
       <c r="E288" s="14"/>
     </row>
     <row r="289" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="16"/>
-      <c r="B289" s="28" t="s">
-        <v>409</v>
-      </c>
-      <c r="C289" s="14">
-        <v>2</v>
-      </c>
-      <c r="D289" s="14">
-        <v>3.5</v>
-      </c>
+      <c r="A289" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B289" s="27"/>
+      <c r="C289" s="14"/>
+      <c r="D289" s="14"/>
       <c r="E289" s="14"/>
     </row>
     <row r="290" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A290" s="16"/>
-      <c r="B290" s="28" t="s">
-        <v>410</v>
+      <c r="A290" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="B290" s="27" t="s">
+        <v>390</v>
       </c>
       <c r="C290" s="14">
         <v>2</v>
       </c>
       <c r="D290" s="14">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="E290" s="14"/>
     </row>
-    <row r="291" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="16"/>
-      <c r="B291" s="28" t="s">
-        <v>411</v>
+    <row r="291" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A291" s="19"/>
+      <c r="B291" s="30" t="s">
+        <v>391</v>
       </c>
       <c r="C291" s="14">
         <v>2</v>
       </c>
       <c r="D291" s="14">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E291" s="14"/>
     </row>
-    <row r="292" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A292" s="16"/>
-      <c r="B292" s="28" t="s">
-        <v>412</v>
+      <c r="B292" s="27" t="s">
+        <v>392</v>
       </c>
       <c r="C292" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D292" s="14">
+        <v>3.8</v>
+      </c>
+      <c r="E292" s="14"/>
+    </row>
+    <row r="293" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A293" s="16"/>
+      <c r="B293" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="C293" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D293" s="14">
         <v>2</v>
-      </c>
-      <c r="D292" s="14">
-        <v>2</v>
-      </c>
-      <c r="E292" s="14"/>
-    </row>
-    <row r="293" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="19"/>
-      <c r="B293" s="31" t="s">
-        <v>413</v>
-      </c>
-      <c r="C293" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D293" s="14">
-        <v>1.2</v>
       </c>
       <c r="E293" s="14"/>
     </row>
     <row r="294" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="16"/>
-      <c r="B294" s="28" t="s">
-        <v>414</v>
+      <c r="B294" s="27" t="s">
+        <v>394</v>
       </c>
       <c r="C294" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D294" s="14">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E294" s="14"/>
     </row>
-    <row r="295" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A295" s="16"/>
-      <c r="B295" s="28" t="s">
-        <v>415</v>
+      <c r="B295" s="27" t="s">
+        <v>395</v>
       </c>
       <c r="C295" s="14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D295" s="14">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E295" s="14"/>
     </row>
     <row r="296" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="16"/>
-      <c r="B296" s="28" t="s">
-        <v>416</v>
+      <c r="B296" s="27" t="s">
+        <v>396</v>
       </c>
       <c r="C296" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D296" s="14">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="E296" s="14"/>
     </row>
-    <row r="297" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A297" s="16"/>
-      <c r="B297" s="28" t="s">
-        <v>417</v>
+      <c r="B297" s="27" t="s">
+        <v>397</v>
       </c>
       <c r="C297" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D297" s="14">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E297" s="14"/>
     </row>
     <row r="298" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="16"/>
-      <c r="B298" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="C298" s="8">
+      <c r="B298" s="27" t="s">
+        <v>398</v>
+      </c>
+      <c r="C298" s="14">
         <v>2</v>
       </c>
       <c r="D298" s="14">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="E298" s="14"/>
     </row>
     <row r="299" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="16"/>
-      <c r="B299" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="C299" s="8">
-        <v>1</v>
+      <c r="B299" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="C299" s="14">
+        <v>2</v>
       </c>
       <c r="D299" s="14">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E299" s="14"/>
     </row>
     <row r="300" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="16"/>
-      <c r="B300" s="28" t="s">
-        <v>491</v>
-      </c>
-      <c r="C300" s="8">
-        <v>1</v>
+      <c r="A300" s="19"/>
+      <c r="B300" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="C300" s="14">
+        <v>1.5</v>
       </c>
       <c r="D300" s="14">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="E300" s="14"/>
     </row>
     <row r="301" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="B301" s="28"/>
-      <c r="C301" s="14"/>
-      <c r="D301" s="14"/>
+      <c r="A301" s="16"/>
+      <c r="B301" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="C301" s="14">
+        <v>1</v>
+      </c>
+      <c r="D301" s="14">
+        <v>1</v>
+      </c>
       <c r="E301" s="14"/>
     </row>
-    <row r="302" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A302" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="B302" s="18" t="s">
-        <v>418</v>
+    <row r="302" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="16"/>
+      <c r="B302" s="27" t="s">
+        <v>402</v>
       </c>
       <c r="C302" s="14">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="D302" s="14">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="E302" s="14"/>
     </row>
     <row r="303" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="16"/>
-      <c r="B303" s="18" t="s">
-        <v>419</v>
+      <c r="B303" s="27" t="s">
+        <v>403</v>
       </c>
       <c r="C303" s="14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D303" s="14">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="E303" s="14"/>
     </row>
     <row r="304" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="16"/>
-      <c r="B304" s="18" t="s">
-        <v>420</v>
+      <c r="B304" s="27" t="s">
+        <v>404</v>
       </c>
       <c r="C304" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D304" s="14">
         <v>1.5</v>
@@ -6440,1309 +6651,1399 @@
       <c r="E304" s="14"/>
     </row>
     <row r="305" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="19"/>
-      <c r="B305" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="C305" s="14">
-        <v>1.5</v>
+      <c r="A305" s="16"/>
+      <c r="B305" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="C305" s="8">
+        <v>2</v>
       </c>
       <c r="D305" s="14">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="E305" s="14"/>
     </row>
     <row r="306" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="16"/>
-      <c r="B306" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="C306" s="14">
-        <v>2.5</v>
+      <c r="B306" s="27" t="s">
+        <v>477</v>
+      </c>
+      <c r="C306" s="8">
+        <v>1</v>
       </c>
       <c r="D306" s="14">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="E306" s="14"/>
     </row>
     <row r="307" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="16"/>
-      <c r="B307" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="C307" s="14">
-        <v>2</v>
+      <c r="B307" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="C307" s="8">
+        <v>1</v>
       </c>
       <c r="D307" s="14">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E307" s="14"/>
     </row>
     <row r="308" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="16"/>
-      <c r="B308" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="C308" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D308" s="14">
-        <v>1</v>
-      </c>
+      <c r="A308" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="B308" s="27"/>
+      <c r="C308" s="14"/>
+      <c r="D308" s="14"/>
       <c r="E308" s="14"/>
     </row>
-    <row r="309" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A309" s="16"/>
+    <row r="309" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A309" s="28" t="s">
+        <v>351</v>
+      </c>
       <c r="B309" s="18" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C309" s="14">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="D309" s="14">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="E309" s="14"/>
     </row>
     <row r="310" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="16"/>
       <c r="B310" s="18" t="s">
-        <v>504</v>
+        <v>406</v>
       </c>
       <c r="C310" s="14">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D310" s="14">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="E310" s="14"/>
     </row>
     <row r="311" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="16"/>
       <c r="B311" s="18" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="C311" s="14">
         <v>1.2</v>
       </c>
       <c r="D311" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E311" s="14"/>
     </row>
     <row r="312" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A312" s="16"/>
-      <c r="B312" s="18" t="s">
-        <v>492</v>
+      <c r="A312" s="19"/>
+      <c r="B312" s="14" t="s">
+        <v>408</v>
       </c>
       <c r="C312" s="14">
         <v>1.5</v>
       </c>
       <c r="D312" s="14">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E312" s="14"/>
     </row>
-    <row r="313" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="16"/>
       <c r="B313" s="18" t="s">
-        <v>493</v>
+        <v>409</v>
       </c>
       <c r="C313" s="14">
-        <v>1</v>
-      </c>
-      <c r="D313" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D313" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E313" s="14"/>
+    </row>
+    <row r="314" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="16"/>
+      <c r="B314" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="C314" s="14">
+        <v>2</v>
+      </c>
+      <c r="D314" s="14">
+        <v>2</v>
+      </c>
+      <c r="E314" s="14"/>
+    </row>
+    <row r="315" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="16"/>
+      <c r="B315" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="C315" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D315" s="14">
+        <v>1</v>
+      </c>
+      <c r="E315" s="14"/>
+    </row>
+    <row r="316" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="16"/>
+      <c r="B316" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="C316" s="14">
+        <v>3</v>
+      </c>
+      <c r="D316" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="E316" s="14"/>
+    </row>
+    <row r="317" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="16"/>
+      <c r="B317" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C317" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D317" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E317" s="14"/>
+    </row>
+    <row r="318" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318" s="16"/>
+      <c r="B318" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="C318" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D318" s="14">
+        <v>1</v>
+      </c>
+      <c r="E318" s="14"/>
+    </row>
+    <row r="319" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="16"/>
+      <c r="B319" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="C319" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D319" s="14">
+        <v>1</v>
+      </c>
+      <c r="E319" s="14"/>
+    </row>
+    <row r="320" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A320" s="16"/>
+      <c r="B320" s="18" t="s">
+        <v>480</v>
+      </c>
+      <c r="C320" s="14">
+        <v>1</v>
+      </c>
+      <c r="D320" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B314" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="C314" s="14">
-        <v>1</v>
-      </c>
-      <c r="D314" s="8">
+    <row r="321" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B321" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="C321" s="14">
+        <v>1</v>
+      </c>
+      <c r="D321" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A315" s="36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B316" s="28" t="s">
+    <row r="322" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A322" s="35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B323" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C323" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B324" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C324" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B325" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C325" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B326" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C326" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B327" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C327" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B328" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C328" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B329" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C329" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B330" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C330" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B331" s="27"/>
+    </row>
+    <row r="332" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A332" s="35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B333" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C333" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B334" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C334" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B335" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="C335" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B336" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C336" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B337" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="C337" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B338" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="C316" s="8">
+      <c r="C338" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B339" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="C339" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B340" s="27"/>
+    </row>
+    <row r="341" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="B341" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="C341" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D341" s="14">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="317" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B317" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C317" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B318" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="C318" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B319" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="C319" s="8">
+      <c r="E341" s="14"/>
+    </row>
+    <row r="342" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B342" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="C342" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D342" s="14">
         <v>2</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B320" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="C320" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B321" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="C321" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B322" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="C322" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B323" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="C323" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B324" s="28"/>
-    </row>
-    <row r="325" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A325" s="36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B326" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="C326" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B327" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="C327" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B328" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="C328" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B329" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="C329" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B330" s="28" t="s">
-        <v>252</v>
-      </c>
-      <c r="C330" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B331" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="C331" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B332" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="C332" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B333" s="28"/>
-    </row>
-    <row r="334" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A334" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="B334" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="C334" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D334" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="E334" s="14"/>
-    </row>
-    <row r="335" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B335" s="28" t="s">
-        <v>435</v>
-      </c>
-      <c r="C335" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D335" s="14">
-        <v>2</v>
-      </c>
-      <c r="E335" s="14"/>
-    </row>
-    <row r="336" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A336" s="16"/>
-      <c r="B336" s="28" t="s">
-        <v>436</v>
-      </c>
-      <c r="C336" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D336" s="14">
-        <v>2</v>
-      </c>
-      <c r="E336" s="14"/>
-    </row>
-    <row r="337" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A337" s="16"/>
-      <c r="B337" s="28" t="s">
-        <v>437</v>
-      </c>
-      <c r="C337" s="14">
-        <v>2</v>
-      </c>
-      <c r="D337" s="14">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E337" s="14"/>
-    </row>
-    <row r="338" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A338" s="16"/>
-      <c r="B338" s="28" t="s">
-        <v>438</v>
-      </c>
-      <c r="C338" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D338" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E338" s="14"/>
-    </row>
-    <row r="339" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A339" s="16"/>
-      <c r="B339" s="28" t="s">
-        <v>439</v>
-      </c>
-      <c r="C339" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D339" s="14">
-        <v>1</v>
-      </c>
-      <c r="E339" s="14"/>
-    </row>
-    <row r="340" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A340" s="16"/>
-      <c r="B340" s="28" t="s">
-        <v>440</v>
-      </c>
-      <c r="C340" s="14">
-        <v>1</v>
-      </c>
-      <c r="D340" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E340" s="14"/>
-    </row>
-    <row r="341" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A341" s="16"/>
-      <c r="B341" s="28" t="s">
-        <v>441</v>
-      </c>
-      <c r="C341" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D341" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E341" s="14"/>
-    </row>
-    <row r="342" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A342" s="16"/>
-      <c r="B342" s="28" t="s">
-        <v>442</v>
-      </c>
-      <c r="C342" s="14">
-        <v>2</v>
-      </c>
-      <c r="D342" s="14">
-        <v>2.5</v>
       </c>
       <c r="E342" s="14"/>
     </row>
     <row r="343" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="16"/>
-      <c r="B343" s="28" t="s">
-        <v>443</v>
+      <c r="B343" s="27" t="s">
+        <v>423</v>
       </c>
       <c r="C343" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D343" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E343" s="14"/>
     </row>
     <row r="344" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="16"/>
-      <c r="B344" s="28" t="s">
-        <v>495</v>
-      </c>
-      <c r="C344" s="8">
-        <v>1.5</v>
+      <c r="B344" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="C344" s="14">
+        <v>2</v>
       </c>
       <c r="D344" s="14">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E344" s="14"/>
     </row>
     <row r="345" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="16"/>
-      <c r="B345" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="C345" s="8">
-        <v>1</v>
+      <c r="B345" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="C345" s="14">
+        <v>1.5</v>
       </c>
       <c r="D345" s="14">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="E345" s="14"/>
     </row>
     <row r="346" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="16"/>
-      <c r="B346" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="C346" s="8">
-        <v>1</v>
-      </c>
-      <c r="D346" s="8">
+      <c r="B346" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="C346" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D346" s="14">
+        <v>1</v>
+      </c>
+      <c r="E346" s="14"/>
+    </row>
+    <row r="347" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A347" s="16"/>
+      <c r="B347" s="27" t="s">
+        <v>427</v>
+      </c>
+      <c r="C347" s="14">
+        <v>1</v>
+      </c>
+      <c r="D347" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="E347" s="14"/>
+    </row>
+    <row r="348" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A348" s="16"/>
+      <c r="B348" s="27" t="s">
+        <v>428</v>
+      </c>
+      <c r="C348" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D348" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="E348" s="14"/>
+    </row>
+    <row r="349" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A349" s="16"/>
+      <c r="B349" s="27" t="s">
+        <v>429</v>
+      </c>
+      <c r="C349" s="14">
+        <v>2</v>
+      </c>
+      <c r="D349" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E349" s="14"/>
+    </row>
+    <row r="350" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A350" s="16"/>
+      <c r="B350" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="C350" s="14">
+        <v>1</v>
+      </c>
+      <c r="D350" s="14">
+        <v>1</v>
+      </c>
+      <c r="E350" s="14"/>
+    </row>
+    <row r="351" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A351" s="16"/>
+      <c r="B351" s="27" t="s">
+        <v>482</v>
+      </c>
+      <c r="C351" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D351" s="14">
+        <v>1</v>
+      </c>
+      <c r="E351" s="14"/>
+    </row>
+    <row r="352" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A352" s="16"/>
+      <c r="B352" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="C352" s="8">
+        <v>1</v>
+      </c>
+      <c r="D352" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="E352" s="14"/>
+    </row>
+    <row r="353" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A353" s="16"/>
+      <c r="B353" s="27" t="s">
+        <v>484</v>
+      </c>
+      <c r="C353" s="8">
+        <v>1</v>
+      </c>
+      <c r="D353" s="8">
         <v>0.5</v>
       </c>
-      <c r="E346" s="14"/>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A347" s="16"/>
-      <c r="B347" s="28"/>
-    </row>
-    <row r="348" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A348" s="36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B349" s="28" t="s">
+      <c r="E353" s="14"/>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A354" s="16"/>
+      <c r="B354" s="27"/>
+    </row>
+    <row r="355" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A355" s="35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B356" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C356" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B357" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C357" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B358" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C358" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B359" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="C359" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B360" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C360" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B361" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C361" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B362" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="C362" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B363" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C363" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B364" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C364" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B365" s="27"/>
+    </row>
+    <row r="366" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A366" s="35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B367" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C367" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B368" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C368" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B369" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C369" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B370" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C370" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B371" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="C349" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B350" s="28" t="s">
+      <c r="C371" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B372" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="C350" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B351" s="28" t="s">
+      <c r="C372" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B373" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="C351" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B352" s="28" t="s">
+      <c r="C373" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B374" s="27"/>
+    </row>
+    <row r="375" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A375" s="35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B376" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="C352" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B353" s="28" t="s">
+      <c r="C376" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B377" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="C353" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B354" s="28" t="s">
+      <c r="C377" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B378" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="C354" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B355" s="28" t="s">
+      <c r="C378" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B379" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="C355" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B356" s="28" t="s">
+      <c r="C379" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B380" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="C356" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B357" s="28" t="s">
+      <c r="C380" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B381" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="C357" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B358" s="28"/>
-    </row>
-    <row r="359" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A359" s="36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B360" s="28" t="s">
+      <c r="C381" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B382" s="27" t="s">
         <v>264</v>
       </c>
-      <c r="C360" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B361" s="28" t="s">
+      <c r="C382" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B383" s="27"/>
+    </row>
+    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A384" s="35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B385" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="C361" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B362" s="28" t="s">
+      <c r="C385" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B386" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="C362" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B363" s="28" t="s">
+      <c r="C386" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B387" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="C363" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B364" s="28" t="s">
+      <c r="C387" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B388" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="C364" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B365" s="28" t="s">
+      <c r="C388" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B389" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="C365" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B366" s="28" t="s">
+      <c r="C389" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B390" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="C366" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B367" s="28"/>
-    </row>
-    <row r="368" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A368" s="36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B369" s="28" t="s">
+      <c r="C390" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B391" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="C369" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B370" s="28" t="s">
+      <c r="C391" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B392" s="27"/>
+    </row>
+    <row r="393" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A393" s="35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B394" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="C370" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B371" s="28" t="s">
+      <c r="C394" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B395" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="C371" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B372" s="28" t="s">
+      <c r="C395" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B396" s="27" t="s">
         <v>274</v>
-      </c>
-      <c r="C372" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B373" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="C373" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B374" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="C374" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B375" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="C375" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B376" s="28"/>
-    </row>
-    <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A377" s="36" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B378" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="C378" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B379" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="C379" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B380" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="C380" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B381" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="C381" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B382" s="28" t="s">
-        <v>282</v>
-      </c>
-      <c r="C382" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B383" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="C383" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B384" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="C384" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B385" s="28"/>
-    </row>
-    <row r="386" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A386" s="36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B387" s="28" t="s">
-        <v>285</v>
-      </c>
-      <c r="C387" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B388" s="28" t="s">
-        <v>286</v>
-      </c>
-      <c r="C388" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B389" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="C389" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B390" s="28" t="s">
-        <v>288</v>
-      </c>
-      <c r="C390" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B391" s="28" t="s">
-        <v>289</v>
-      </c>
-      <c r="C391" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B392" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="C392" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B393" s="28"/>
-    </row>
-    <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A394" s="36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B395" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="C395" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B396" s="28" t="s">
-        <v>292</v>
       </c>
       <c r="C396" s="8">
         <v>1.2</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B397" s="28" t="s">
-        <v>293</v>
+      <c r="B397" s="27" t="s">
+        <v>275</v>
       </c>
       <c r="C397" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B398" s="28" t="s">
-        <v>294</v>
+    <row r="398" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B398" s="27" t="s">
+        <v>276</v>
       </c>
       <c r="C398" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B399" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="C399" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B400" s="27"/>
+    </row>
+    <row r="401" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A401" s="35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B402" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="C402" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B403" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C403" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B404" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C404" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B399" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="C399" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B400" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="C400" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B401" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="C401" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B402" s="28"/>
-    </row>
-    <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A403" s="36" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B404" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="C404" s="8">
+    <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B405" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C405" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B406" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C406" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B407" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C407" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B408" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="C408" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B409" s="27"/>
+    </row>
+    <row r="410" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A410" s="35" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B411" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C411" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B405" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="C405" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B406" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="C406" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B407" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="C407" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B408" s="28" t="s">
-        <v>302</v>
-      </c>
-      <c r="C408" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B409" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="C409" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B410" s="28" t="s">
-        <v>304</v>
-      </c>
-      <c r="C410" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B411" s="28"/>
-    </row>
     <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A412" s="36" t="s">
-        <v>82</v>
+      <c r="B412" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C412" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B413" s="28" t="s">
-        <v>305</v>
+      <c r="B413" s="27" t="s">
+        <v>287</v>
       </c>
       <c r="C413" s="8">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B414" s="28" t="s">
-        <v>306</v>
+      <c r="B414" s="27" t="s">
+        <v>288</v>
       </c>
       <c r="C414" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B415" s="28" t="s">
-        <v>307</v>
+    <row r="415" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B415" s="27" t="s">
+        <v>289</v>
       </c>
       <c r="C415" s="8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B416" s="28" t="s">
-        <v>308</v>
+    <row r="416" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B416" s="27" t="s">
+        <v>290</v>
       </c>
       <c r="C416" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B417" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="C417" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B418" s="27"/>
+    </row>
+    <row r="419" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A419" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B420" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C420" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B421" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C421" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B422" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C422" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B423" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C423" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B417" s="28" t="s">
-        <v>309</v>
-      </c>
-      <c r="C417" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B418" s="28"/>
-      <c r="D418" s="14"/>
-      <c r="E418" s="14"/>
-    </row>
-    <row r="419" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A419" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="B419" s="31" t="s">
-        <v>502</v>
-      </c>
-      <c r="C419" s="14">
+    <row r="424" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B424" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C424" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B425" s="27"/>
+      <c r="D425" s="14"/>
+      <c r="E425" s="14"/>
+    </row>
+    <row r="426" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A426" s="28" t="s">
+        <v>462</v>
+      </c>
+      <c r="B426" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="C426" s="14">
         <v>1.2</v>
       </c>
-      <c r="D419" s="14">
+      <c r="D426" s="14">
         <v>0.8</v>
-      </c>
-      <c r="E419" s="14"/>
-    </row>
-    <row r="420" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A420" s="16"/>
-      <c r="B420" s="31" t="s">
-        <v>465</v>
-      </c>
-      <c r="C420" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D420" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E420" s="14"/>
-    </row>
-    <row r="421" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A421" s="16"/>
-      <c r="B421" s="31" t="s">
-        <v>466</v>
-      </c>
-      <c r="C421" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D421" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E421" s="14"/>
-    </row>
-    <row r="422" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A422" s="16"/>
-      <c r="B422" s="31" t="s">
-        <v>467</v>
-      </c>
-      <c r="C422" s="14">
-        <v>1</v>
-      </c>
-      <c r="D422" s="14">
-        <v>1</v>
-      </c>
-      <c r="E422" s="14"/>
-    </row>
-    <row r="423" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A423" s="16"/>
-      <c r="B423" s="31" t="s">
-        <v>468</v>
-      </c>
-      <c r="C423" s="14">
-        <v>2</v>
-      </c>
-      <c r="D423" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E423" s="14"/>
-    </row>
-    <row r="424" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A424" s="16"/>
-      <c r="B424" s="31" t="s">
-        <v>503</v>
-      </c>
-      <c r="C424" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D424" s="14">
-        <v>1</v>
-      </c>
-      <c r="E424" s="14"/>
-    </row>
-    <row r="425" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A425" s="16"/>
-      <c r="B425" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="C425" s="14">
-        <v>1</v>
-      </c>
-      <c r="D425" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E425" s="14"/>
-    </row>
-    <row r="426" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A426" s="16"/>
-      <c r="B426" s="31" t="s">
-        <v>470</v>
-      </c>
-      <c r="C426" s="14">
-        <v>2</v>
-      </c>
-      <c r="D426" s="14">
-        <v>2</v>
       </c>
       <c r="E426" s="14"/>
     </row>
     <row r="427" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A427" s="16"/>
-      <c r="B427" s="31" t="s">
-        <v>471</v>
+      <c r="B427" s="30" t="s">
+        <v>452</v>
       </c>
       <c r="C427" s="14">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D427" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="E427" s="14"/>
     </row>
-    <row r="428" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A428" s="16"/>
-      <c r="B428" s="31" t="s">
-        <v>472</v>
+      <c r="B428" s="30" t="s">
+        <v>453</v>
       </c>
       <c r="C428" s="14">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D428" s="14">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="E428" s="14"/>
     </row>
     <row r="429" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A429" s="16"/>
-      <c r="B429" s="31" t="s">
-        <v>473</v>
+      <c r="B429" s="30" t="s">
+        <v>454</v>
       </c>
       <c r="C429" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D429" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E429" s="14"/>
     </row>
     <row r="430" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A430" s="16"/>
-      <c r="B430" s="37" t="s">
-        <v>474</v>
-      </c>
-      <c r="C430" s="8">
-        <v>1.5</v>
+      <c r="B430" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="C430" s="14">
+        <v>2</v>
       </c>
       <c r="D430" s="14">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E430" s="14"/>
     </row>
-    <row r="431" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A431" s="16"/>
-      <c r="B431" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="C431" s="8">
-        <v>1.5</v>
+      <c r="B431" s="30" t="s">
+        <v>490</v>
+      </c>
+      <c r="C431" s="14">
+        <v>1.2</v>
       </c>
       <c r="D431" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E431" s="14"/>
     </row>
     <row r="432" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A432" s="16"/>
-      <c r="B432" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="C432" s="8">
-        <v>1</v>
-      </c>
-      <c r="D432" s="8">
+      <c r="B432" s="30" t="s">
+        <v>456</v>
+      </c>
+      <c r="C432" s="14">
+        <v>1</v>
+      </c>
+      <c r="D432" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E432" s="14"/>
+    </row>
+    <row r="433" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A433" s="16"/>
+      <c r="B433" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="C433" s="14">
+        <v>2</v>
+      </c>
+      <c r="D433" s="14">
+        <v>2</v>
+      </c>
+      <c r="E433" s="14"/>
+    </row>
+    <row r="434" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A434" s="16"/>
+      <c r="B434" s="30" t="s">
+        <v>458</v>
+      </c>
+      <c r="C434" s="14">
+        <v>2</v>
+      </c>
+      <c r="D434" s="14">
+        <v>2</v>
+      </c>
+      <c r="E434" s="14"/>
+    </row>
+    <row r="435" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A435" s="16"/>
+      <c r="B435" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="C435" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D435" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="E435" s="14"/>
+    </row>
+    <row r="436" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A436" s="16"/>
+      <c r="B436" s="30" t="s">
+        <v>460</v>
+      </c>
+      <c r="C436" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D436" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="E436" s="14"/>
+    </row>
+    <row r="437" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A437" s="16"/>
+      <c r="B437" s="36" t="s">
+        <v>461</v>
+      </c>
+      <c r="C437" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D437" s="14">
+        <v>1</v>
+      </c>
+      <c r="E437" s="14"/>
+    </row>
+    <row r="438" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A438" s="16"/>
+      <c r="B438" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="C438" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D438" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E438" s="14"/>
+    </row>
+    <row r="439" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A439" s="16"/>
+      <c r="B439" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C439" s="8">
+        <v>1</v>
+      </c>
+      <c r="D439" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B433" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="C433" s="8">
-        <v>1</v>
-      </c>
-      <c r="D433" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="434" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A434" s="36" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="435" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B435" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="C435" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="436" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B436" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="C436" s="8">
+    <row r="440" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B440" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="C440" s="8">
+        <v>1</v>
+      </c>
+      <c r="D440" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A441" s="35" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B442" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C442" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B443" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C443" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A437" s="26" t="s">
-        <v>447</v>
-      </c>
-      <c r="B437" s="28" t="s">
-        <v>312</v>
-      </c>
-      <c r="C437" s="8">
+    <row r="444" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A444" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="B444" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C444" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B438" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="C438" s="8">
+    <row r="445" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B445" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C445" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B439" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="C439" s="8">
+    <row r="446" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B446" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C446" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B440" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="C440" s="8">
+    <row r="447" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="B447" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C447" s="8">
         <v>1.8</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B441" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="C441" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="442" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B442" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="C442" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="443" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B443" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="C443" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="444" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B444" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="C444" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B445" s="28"/>
-    </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B446" s="28"/>
-    </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B447" s="28"/>
-    </row>
-    <row r="448" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A448" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B449" s="28" t="s">
-        <v>320</v>
+    <row r="448" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="B448" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="C448" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B449" s="27" t="s">
+        <v>304</v>
       </c>
       <c r="C449" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B450" s="28" t="s">
-        <v>321</v>
+      <c r="B450" s="27" t="s">
+        <v>305</v>
       </c>
       <c r="C450" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B451" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="C451" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B452" s="27"/>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B453" s="27"/>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B454" s="27"/>
+    </row>
+    <row r="455" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A455" s="35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B456" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="C456" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B457" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="C457" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="451" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B451" s="28" t="s">
-        <v>322</v>
-      </c>
-      <c r="C451" s="8">
+    <row r="458" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B458" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="C458" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B452" s="28" t="s">
-        <v>323</v>
-      </c>
-      <c r="C452" s="8">
+    <row r="459" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B459" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="C459" s="8">
         <v>2.5</v>
       </c>
     </row>
-    <row r="453" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B453" s="28" t="s">
-        <v>324</v>
-      </c>
-      <c r="C453" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B454" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="C454" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B455" s="28" t="s">
-        <v>326</v>
-      </c>
-      <c r="C455" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B456" s="28"/>
-    </row>
-    <row r="457" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A457" s="26" t="s">
-        <v>447</v>
+    <row r="460" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B460" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="C460" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B461" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C461" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B462" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C462" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B463" s="27"/>
+    </row>
+    <row r="464" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A464" s="25" t="s">
+        <v>434</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2977F47-C4C4-5F45-8337-5F1F8D52E785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0422E04-F5C0-8F43-9F81-18EFF0447C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REQUISITOS" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="562">
   <si>
     <t>User story</t>
   </si>
@@ -189,12 +189,6 @@
     <t>RF16 — Persistencia y comparación de runs</t>
   </si>
   <si>
-    <t>[Fase 2] Guarda histórico de ejecuciones y permite comparar resultados entre runs.</t>
-  </si>
-  <si>
-    <t>Existe storage de runs (tabla o carpeta) con run_id, dataset_hash y versiones. Comandos list-runs y compare-runs producen diffs de ranking/tests.</t>
-  </si>
-  <si>
     <t>RF17 — Taxonomía de fraude (fraud_type) y mapping</t>
   </si>
   <si>
@@ -315,9 +309,6 @@
     <t>TIEMPO REAL (h)</t>
   </si>
   <si>
-    <t>FECHA DE ENTREGA</t>
-  </si>
-  <si>
     <t>RF01-01: Crear estructura de proyecto: src/erp_fraud/ingest, src/erp_fraud/storage, src/erp_fraud/cli</t>
   </si>
   <si>
@@ -717,30 +708,6 @@
     <t>RF13-09: Ejecutar verificación de criterios de aceptación y guardar evidencia (logs/reportes)</t>
   </si>
   <si>
-    <t>RF16-01: Definir almacenamiento de runs: carpeta persistente o tabla DuckDB 'runs' + 'test_results'</t>
-  </si>
-  <si>
-    <t>RF16-02: Implementar escritura: registrar run_id, dataset_hash, config_hash, tests_versions, timestamps</t>
-  </si>
-  <si>
-    <t>RF16-03: Implementar comando 'list-runs' (tabla resumen) y filtros por fecha/dataset_hash</t>
-  </si>
-  <si>
-    <t>RF16-04: Implementar comando 'compare-runs A B' (diff ranking, tests fallidos, métricas)</t>
-  </si>
-  <si>
-    <t>RF16-05: Añadir export compare a MD/JSON y enlazarlo desde reportes</t>
-  </si>
-  <si>
-    <t>RF16-06: Escribir/actualizar tests unitarios relacionados (pytest) para este requisito</t>
-  </si>
-  <si>
-    <t>RF16-07: Actualizar documentación (README/docs) describiendo el comportamiento y cómo verificarlo</t>
-  </si>
-  <si>
-    <t>RF16-08: Ejecutar verificación de criterios de aceptación y guardar evidencia (logs/reportes)</t>
-  </si>
-  <si>
     <t>RF17-01: Diseñar taxonomía mínima (yaml) y documentar definiciones</t>
   </si>
   <si>
@@ -1332,66 +1299,12 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>[Productivización AWS] Ejecutar el pipeline multiagente como un job en cloud: imagen Docker en ECR, ejecución en ECS Fargate (run-task), inputs/outputs en S3 (runs/&lt;run_id&gt;/), logs en CloudWatch, secretos en Secrets Manager y permisos IAM. Re-ejecutar automáticamente cuando cambien artefactos (catálogos/prompts/KB) usando artifact_hash + trigger (S3/EventBridge/Lambda). Persistir/reutilizar índice Chroma (kb_index en S3) para RAG.</t>
-  </si>
-  <si>
-    <t>Existe un despliegue mínimo en AWS: se puede lanzar un run con 'ecs run-task' y genera outputs en S3 + logs en CloudWatch + trazas en LangSmith. Un trigger (S3/EventBridge+Lambda) relanza el pipeline solo si artifact_hash cambia (actualiza last_hash en S3). El índice Chroma se restaura/persiste desde S3. Documentación paso a paso (docs/cloud_aws.md) + runbook de troubleshooting.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>RF14c-01: Definir arquitectura AWS mínima 'job': ECR (imagen), ECS Fargate (run-task), S3 (inputs/outputs/state), CloudWatch Logs, Secrets Manager, IAM roles</t>
-  </si>
-  <si>
-    <t>RF14c-02: Elegir región AWS y naming estándar (prefijo proyecto) para recursos; crear documento docs/aws_naming.md</t>
-  </si>
-  <si>
     <t>RF14c-03: Preparar credenciales locales: instalar AWS CLI, configurar perfil, validar con 'aws sts get-caller-identity'</t>
   </si>
   <si>
-    <t>RF14c-04: Definir estructura S3 (carpetas): inputs/datasets/, inputs/docs/, artifacts/prompts/, artifacts/catalogs/, state/, runs/&lt;run_id&gt;/</t>
-  </si>
-  <si>
-    <t>RF14c-05: Crear buckets S3 (o uno con prefijos) y aplicar versioning + lifecycle (retención runs) + cifrado (SSE-S3)</t>
-  </si>
-  <si>
-    <t>RF14c-06: Implementar en código 'S3 IO layer': descargar inputs al inicio (dataset zip + docs) y subir outputs (run_results) al final</t>
-  </si>
-  <si>
-    <t>RF14c-07: Añadir configuración por ENV: S3_INPUT_URI, S3_OUTPUT_URI, S3_STATE_URI, AWS_REGION, RUN_MODE=cloud/local</t>
-  </si>
-  <si>
-    <t>RF14c-08: Implementar cálculo de artifact_hash (catálogo tests/datos, prompts, KB docs, mapping) y guardarlo en run_metadata.json</t>
-  </si>
-  <si>
-    <t>RF14c-09: Implementar 'state store' en S3: escribir/leer last_artifact_hash.json en s3://.../state/ (idempotente)</t>
-  </si>
-  <si>
-    <t>RF14c-10: Containerizar pipeline (Dockerfile): base slim + dependencias + entrypoint; build local; smoke test con RUN_MODE=local</t>
-  </si>
-  <si>
-    <t>RF14c-11: Crear repositorio ECR y script de build+push con tag por git_sha; documentar en docs/aws_ecr.md</t>
-  </si>
-  <si>
-    <t>RF14c-12: (Opcional recomendado) GitHub Action: on push main → build/push a ECR y publicar imagen; guardar outputs del build</t>
-  </si>
-  <si>
-    <t>RF14c-13: Crear CloudWatch Log Group para el job y definir formato de logs estructurados; probar que aparecen logs</t>
-  </si>
-  <si>
-    <t>RF14c-14: Crear Secrets Manager secrets (OPENAI_API_KEY, LANGSMITH_API_KEY, etc.) y documentar cómo rotarlos</t>
-  </si>
-  <si>
-    <t>RF14c-15: Crear IAM: (a) ECS execution role (pull ECR + logs), (b) task role (S3 read/write + SecretsManager read)</t>
-  </si>
-  <si>
-    <t>RF14c-16: Crear ECS Cluster (Fargate) y elegir red (usar VPC default + subnets) + security group (egress only)</t>
-  </si>
-  <si>
-    <t>RF14c-17: Crear Task Definition Fargate: cpu/mem, env vars, secrets, logConfiguration, ephemeralStorage (si hace falta), command 'python -m ... run'</t>
-  </si>
-  <si>
     <t>AG03-02: Definir plantilla de prompt para AlphaCodium: objetivo, constraints (allowlist, no inventar columnas), output esperado</t>
   </si>
   <si>
@@ -1444,15 +1357,6 @@
   </si>
   <si>
     <t>RF15b-12:Ejecutar verificación de criterios de aceptación y guardar evidencia (logs/reportes)</t>
-  </si>
-  <si>
-    <t>RF14c-18: Escribir/actualizar tests de integración (pytest) para este requisito</t>
-  </si>
-  <si>
-    <t>RF14c-19: Actualizar documentación (README + runbook/docs) describiendo el comportamiento y cómo verificarlo</t>
-  </si>
-  <si>
-    <t>RF14c-20: Ejecutar verificación de criterios de aceptación y guardar evidencia (artefactos + enlace de traza LangSmith + logs/reportes)</t>
   </si>
   <si>
     <t>RF15-08: Escribir/actualizar tests unitarios relacionados (pytest) para este requisito</t>
@@ -1653,7 +1557,185 @@
     <t>RF11-16:  Ejecutar verificación final y guardar evidencias (run_results O2C + reporte de validación + lista de riesgos abiertos)</t>
   </si>
   <si>
-    <t xml:space="preserve">posibilidad de cambiarlo </t>
+    <t>RF16 — Agente explicador de 2º nivel (comparación de runs y recomendaciones)</t>
+  </si>
+  <si>
+    <t>[Fase 3] Implementa un explicador de segundo nivel que compara runs (P2P/O2C o single-run), identifica similitudes/concurrencias
+    de fraude y propone recomendaciones de auditoría accionables.</t>
+  </si>
+  <si>
+    <t>Existe lógica RF16 para cargar snapshots de runs, comparar selected_tests/findings/fraud_types, generar recomendaciones
+    (incluyendo caso single-run) y persistir artefactos JSON/MD. CLI incluye list-runs y compare-runs, y compare-runs soporta auto-selección
+    del último run P2P + O2C.</t>
+  </si>
+  <si>
+    <t>RF16-01: Diseñar contrato de snapshot de run (campos mínimos para comparación) y definir parser robusto desde artefactos de run_results</t>
+  </si>
+  <si>
+    <t>RF16-02: Implementar módulo storage RF16 para comparación (carga snapshots, similitud, resumen, recomendaciones, export JSON/MD)</t>
+  </si>
+  <si>
+    <t>RF16-03: Implementar comando CLI list-runs con salida humana y JSON</t>
+  </si>
+  <si>
+    <t>RF16-04: Implementar comando CLI compare-runs (N runs) con persistencia de rf16_second_level_analysis.json/md</t>
+  </si>
+  <si>
+    <t>RF16-05: Soportar modo comparativo P2P+O2C automático (auto latest por process_family) y modo single-run con recomendaciones válidas</t>
+  </si>
+  <si>
+    <t>RF16-07: Escribir/actualizar tests de integración RF16 (storage + CLI)</t>
+  </si>
+  <si>
+    <t>RF 16-09: Actualizar runbook general y registro de tests de integración con RF16</t>
+  </si>
+  <si>
+    <t>RF16-10: Ejecutar verificación de criterios de aceptación y guardar evidencia (artefactos + outputs de compare-runs)</t>
+  </si>
+  <si>
+    <t>RF16-08: Documentar RF16 (objetivo, arquitectura, comandos, outputs, interpretación de recomendaciones)</t>
+  </si>
+  <si>
+    <t>RF16-06: Añadir script operativo scripts/run_rf16_second_level_explainer.py para uso directo en demos/operación</t>
+  </si>
+  <si>
+    <t>RF16b — Nodo/agente LLM final en grafo (second_level_explainer)</t>
+  </si>
+  <si>
+    <t>[Fase 3] Implementa el agente LLM de 2º nivel como último nodo del flujo (`second_level_explainer`) para consumir el run actual
+    + runs de referencia, emitir conclusiones cross-process/single-run y recomendar procedimientos de auditoría/tests adicionales.</t>
+  </si>
+  <si>
+    <t>DEFAULT_GRAPH_SEQUENCE_FULL incluye second_level_explainer tras persist. El nodo genera `graph/second_level_analysis.json|md`,
+    registra runtime LLM por nodo (`llm_runtime_by_node.second_level_explainer`), persiste artefactos en manifest, y funciona con fallback
+    determinista en stub/errores.</t>
+  </si>
+  <si>
+    <t>RF16b-01: Definir contrato de salida del agente (executive_summary, conclusiones, procedimientos, tests recomendados, next_actions)</t>
+  </si>
+  <si>
+    <t>RF16b-02: Implementar nodo `src/erp_fraud/graph/nodes/second_level_explainer.py` con comparación base determinista + capa LLM</t>
+  </si>
+  <si>
+    <t>RF16b-03: Integrar nodo en dispatcher (`registry.py`) y exports de nodos (`nodes/__init__.py`, `graph/__init__.py`)</t>
+  </si>
+  <si>
+    <t>RF16b-04:Añadir nodo al final de `DEFAULT_GRAPH_SEQUENCE_FULL` y validar routing/abort sin romper persistencia</t>
+  </si>
+  <si>
+    <t>RF16b-05: Persistir artefactos `second_level_analysis.json` y `second_level_analysis.md` en `run_results/&lt;run_id&gt;/graph/`</t>
+  </si>
+  <si>
+    <t>RF16b-06: Actualizar manifest/artifact_paths para incluir salidas RF16b y exponerlas en `run_metadata`/`export_paths`</t>
+  </si>
+  <si>
+    <t>RF16b-07: Exponer configuración RF16b en `run_rf15c_e2e_manual.py` (auto latest, run_ids explícitos, include current run)</t>
+  </si>
+  <si>
+    <t>RF16b-08: Ampliar `scripts/show_run_summary.py` para mostrar conclusiones del agente de 2º nivel</t>
+  </si>
+  <si>
+    <t>RF16b-09: Escribir tests de integración RF16b (`tests/test_rf16_second_level_agent_node.py`) y ajustar suites RF14/RF16</t>
+  </si>
+  <si>
+    <t>RF16b-10: Corregir selección auto latest P2P+O2C priorizando runs con artefactos de grafo y fallback a metadata/report</t>
+  </si>
+  <si>
+    <t>RF16b-11: Actualizar documentación (`docs/rf16.md`, `docs/langgraph_architecture.md`, `docs/how_to_run.md`, `docs/integration_tests_registry.md`)</t>
+  </si>
+  <si>
+    <t>RF16b-12: Ejecutar verificación final (pytest completo + smoke compare-runs + smoke run real) y guardar evidencia</t>
+  </si>
+  <si>
+    <t>RF14c-01:Definir arquitectura AWS mínima 'job': ECR (imagen), ECS Fargate (run-task), S3 (inputs/outputs/state), CloudWatch Logs, Secrets Manager, IAM roles y networking mínimo (VPC default, subnets públicas, public IP, SG egress-only).</t>
+  </si>
+  <si>
+    <t>RF14c-02: Elegir región AWS, naming estándar y convención de tags para recursos; crear documento docs/aws_naming.md.</t>
+  </si>
+  <si>
+    <t>RF14c-04: Definir estrategia multi-dominio P2P/O2C y parametrización de ejecución (PROCESS_SCOPE=p2p|o2c|both); documentarlo.</t>
+  </si>
+  <si>
+    <t>RF14c-05: Definir estructura S3 lógica: inputs/datasets/, inputs/docs/, artifacts/prompts/, artifacts/catalogs/, artifacts/mappings/, state/, runs/&lt;run_id&gt;/; decidir si se separa por dominio.</t>
+  </si>
+  <si>
+    <t>RF14c-06: Crear bucket S3 (o uno con prefijos) y aplicar versioning + lifecycle + cifrado; crear prefijos iniciales y subir estructura base.</t>
+  </si>
+  <si>
+    <t>RF14c-07: Añadir configuración por ENV: S3_INPUT_URI, S3_OUTPUT_URI, S3_STATE_URI, AWS_REGION, RUN_MODE=cloud/local, PROCESS_SCOPE, LANGSMITH_TRACING, LANGSMITH_PROJECT.</t>
+  </si>
+  <si>
+    <t>RF14c-08: Implementar en código la capa S3 IO: descargar inputs/artefactos al inicio y subir outputs al final.</t>
+  </si>
+  <si>
+    <t>RF14c-09: Implementar cálculo de artifact_hash (prompts, catálogos, KB docs, mappings y otros artefactos relevantes) y guardarlo en run_metadata.json.</t>
+  </si>
+  <si>
+    <t>RF14c-10: Implementar state store en S3: leer/escribir last_artifact_hash.json (idempotente) con last_run_id y updated_at.</t>
+  </si>
+  <si>
+    <t>RF14c-11: Adaptar el runner para modo cloud no interactivo: crear run_id, workspace temporal, resolver PROCESS_SCOPE, descargar inputs, ejecutar pipeline, subir outputs y devolver exit code correcto.</t>
+  </si>
+  <si>
+    <t>RF14c-12: Definir outputs mínimos obligatorios por run en runs/&lt;run_id&gt;/ y validar que siempre se generen (run_metadata, report, ranking, schema_summary, graph artifacts, etc.).</t>
+  </si>
+  <si>
+    <t>RF14c-13: Containerizar pipeline (Dockerfile + .dockerignore + entrypoint): build local y smoke test con RUN_MODE=local y/o cloud simulado.</t>
+  </si>
+  <si>
+    <t>RF14c-14: Crear repositorio ECR y script de build+push con tag por git_sha; documentar en docs/aws_ecr.md.</t>
+  </si>
+  <si>
+    <t>RF14c-15: Crear CloudWatch Log Group para el job y definir formato de logs estructurados; probar que aparecen logs del contenedor.</t>
+  </si>
+  <si>
+    <t>RF14c-16: Crear Secrets Manager secrets (OPENAI_API_KEY, LANGSMITH_API_KEY, etc.) y documentar cómo rotarlos/inyectarlos.</t>
+  </si>
+  <si>
+    <t>RF14c-17: Crear IAM: (a) ECS task execution role (ECR + CloudWatch Logs + lectura de secretos inyectados), (b) task role (S3 read/write y permisos runtime mínimos).</t>
+  </si>
+  <si>
+    <t>RF14c-18: Crear ECS Cluster (Fargate) y configurar red mínima: VPC default, subnets públicas, assign public IP habilitado y security group sin inbound.</t>
+  </si>
+  <si>
+    <t>RF14c-19: Crear Task Definition Fargate: cpu/mem, imagen ECR, env vars, secrets, logConfiguration y command; distinguir configuración fija vs overrides por run.</t>
+  </si>
+  <si>
+    <t>RF14c-20: Lanzar primera ejecución manual con 'ecs run-task' para PROCESS_SCOPE=p2p y verificar estado, exit code y outputs.</t>
+  </si>
+  <si>
+    <t>RF14c-21: Lanzar ejecución manual para PROCESS_SCOPE=o2c y, si aplica, PROCESS_SCOPE=both; verificar outputs separados por run_id y dominio.</t>
+  </si>
+  <si>
+    <t>RF14c-22: Configurar EventBridge Scheduler para re-ejecuciones programadas (solo después de estabilizar el run manual).</t>
+  </si>
+  <si>
+    <t>RF14c-23: Implementar trigger automático por cambio de artefactos con S3 Event + Lambda + comparación de artifact_hash antes de llamar a ecs run-task.</t>
+  </si>
+  <si>
+    <t>RF14c-24: Escribir/actualizar tests de integración (pytest) para runner cloud, S3 IO, artifact_hash, state store y configuración multi-dominio.</t>
+  </si>
+  <si>
+    <t>RF14c-25: Actualizar documentación (README + runbook/docs/cloud_aws.md + troubleshooting) describiendo comportamiento, despliegue y verificación.</t>
+  </si>
+  <si>
+    <t>RF14c-26: Ejecutar verificación final de criterios de aceptación y guardar evidencia (artefactos S3 + enlace LangSmith + logs/reportes + capturas/consola AWS).</t>
+  </si>
+  <si>
+    <t>RF14c-27: (Opcional recomendado) Añadir GitHub Action: on push main → build/push a ECR y publicar imagen; guardar outputs del build.</t>
+  </si>
+  <si>
+    <t>[Productivización AWS] Ejecutar el pipeline multiagente como un job en cloud: imagen Docker en ECR, ejecución
+    en ECS Fargate (run-task), inputs/outputs/state en S3, logs en CloudWatch, secretos en Secrets Manager y permisos IAM.
+    Preparar ejecución multi-dominio (P2P/O2C) mediante parametrización por scope y re-ejecutar automáticamente cuando cambien
+    artefactos (catálogos/prompts/KB/mappings) usando artifact_hash + trigger (S3/EventBridge/Lambda). La primera versión
+    prioriza ejecución manual reproducible; el trigger automático se activa después.'</t>
+  </si>
+  <si>
+    <t>Existe un despliegue mínimo en AWS: se puede lanzar un run con ''ecs run-task'' y genera outputs en
+    S3 + logs en CloudWatch + trazas en LangSmith. El mismo despliegue soporta PROCESS_SCOPE=p2p, o2c y both sin duplicar
+    infraestructura. Un trigger (S3/EventBridge+Lambda) relanza el pipeline solo si artifact_hash cambia (actualiza last_hash
+    en S3). Documentación paso a paso (docs/cloud_aws.md) + runbook de troubleshooting.</t>
   </si>
 </sst>
 </file>
@@ -1739,7 +1821,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1765,12 +1847,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -1845,7 +1921,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1877,13 +1953,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1904,31 +1980,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1937,7 +2013,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1946,16 +2022,13 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1974,86 +2047,63 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2350,7 +2400,7 @@
     <col min="4" max="4" width="15.5" style="8" customWidth="1"/>
     <col min="5" max="5" width="11.83203125" style="8" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="8" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="43" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" style="42" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" style="8" customWidth="1"/>
     <col min="9" max="9" width="3.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="8"/>
@@ -2373,9 +2423,9 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G1" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1" s="39" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -2387,13 +2437,13 @@
     </row>
     <row r="2" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -2402,22 +2452,20 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="41"/>
-      <c r="L2" t="s">
-        <v>517</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="G2" s="40"/>
+      <c r="L2" s="8"/>
     </row>
     <row r="3" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -2428,10 +2476,8 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="L3" s="54" t="s">
-        <v>518</v>
-      </c>
+      <c r="G3" s="40"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
@@ -2452,15 +2498,12 @@
       <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="39">
+      <c r="G4" s="38">
         <v>46094</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="L4" s="55" t="s">
-        <v>519</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2482,15 +2525,12 @@
       <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="38">
         <v>46094</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="L5" s="56" t="s">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2512,15 +2552,12 @@
       <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="38">
         <v>46094</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="L6" s="57" t="s">
-        <v>521</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2542,12 +2579,12 @@
       <c r="F7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="38">
         <v>46094</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2569,12 +2606,12 @@
       <c r="F8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="38">
         <v>46094</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2596,12 +2633,12 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="38">
         <v>46094</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2623,12 +2660,12 @@
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="38">
         <v>46094</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2650,12 +2687,12 @@
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="38">
         <v>46094</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2677,22 +2714,22 @@
       <c r="F12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="38">
         <v>46094</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="44" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="5">
@@ -2704,7 +2741,7 @@
       <c r="F13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="39"/>
+      <c r="G13" s="38"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
@@ -2727,12 +2764,12 @@
       <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="38">
         <v>46094</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.2">
@@ -2742,19 +2779,19 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="39"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:12" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="44" t="s">
-        <v>512</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>515</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>516</v>
+      <c r="A16" s="43" t="s">
+        <v>480</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>483</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>484</v>
       </c>
       <c r="D16" s="5">
         <v>21</v>
@@ -2765,32 +2802,32 @@
       <c r="F16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="39"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="51" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="52" t="s">
+    <row r="17" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="53" t="s">
-        <v>513</v>
-      </c>
-      <c r="D17" s="49">
+      <c r="C17" s="49" t="s">
+        <v>481</v>
+      </c>
+      <c r="D17" s="5">
         <v>8</v>
       </c>
-      <c r="E17" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="50"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
+      <c r="E17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="38"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
@@ -2800,7 +2837,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="D18" s="5">
         <v>13</v>
@@ -2811,21 +2848,23 @@
       <c r="F18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="39"/>
-      <c r="H18" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I18" s="5"/>
+      <c r="G18" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
@@ -2836,21 +2875,23 @@
       <c r="F19" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="42"/>
-      <c r="H19" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I19" s="14"/>
+      <c r="G19" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="22" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="D20" s="14">
         <v>8</v>
@@ -2861,24 +2902,26 @@
       <c r="F20" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="42"/>
-      <c r="H20" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I20" s="14"/>
+      <c r="G20" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="46" t="s">
-        <v>341</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>432</v>
-      </c>
-      <c r="C21" s="48" t="s">
-        <v>433</v>
+      <c r="A21" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>560</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>561</v>
       </c>
       <c r="D21" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>45</v>
@@ -2886,19 +2929,19 @@
       <c r="F21" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="42"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="D22" s="14">
         <v>8</v>
@@ -2909,21 +2952,23 @@
       <c r="F22" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="42"/>
-      <c r="H22" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I22" s="14"/>
+      <c r="G22" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="22" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
@@ -2934,21 +2979,23 @@
       <c r="F23" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="42"/>
-      <c r="H23" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I23" s="14"/>
+      <c r="G23" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="D24" s="14">
         <v>13</v>
@@ -2959,21 +3006,23 @@
       <c r="F24" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="42"/>
-      <c r="H24" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I24" s="14"/>
+      <c r="G24" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="22" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D25" s="14">
         <v>10</v>
@@ -2984,24 +3033,26 @@
       <c r="F25" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="42"/>
-      <c r="H25" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>52</v>
+      <c r="G25" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+      <c r="A26" s="43" t="s">
+        <v>506</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>507</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>508</v>
       </c>
       <c r="D26" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>45</v>
@@ -3009,30 +3060,42 @@
       <c r="F26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="39"/>
+      <c r="G26" s="38"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" spans="1:9" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="39"/>
+    <row r="27" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+      <c r="A27" s="43" t="s">
+        <v>519</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>520</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>521</v>
+      </c>
+      <c r="D27" s="5">
+        <v>12</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="38"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="D28" s="5">
         <v>5</v>
@@ -3043,19 +3106,19 @@
       <c r="F28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="39"/>
+      <c r="G28" s="38"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="22" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="D29" s="14">
         <v>13</v>
@@ -3066,21 +3129,23 @@
       <c r="F29" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="42"/>
-      <c r="H29" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I29" s="14"/>
+      <c r="G29" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="D30" s="5">
         <v>8</v>
@@ -3091,19 +3156,19 @@
       <c r="F30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="39"/>
+      <c r="G30" s="38"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="D31" s="5">
         <v>5</v>
@@ -3114,19 +3179,19 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="39"/>
+      <c r="G31" s="38"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="D32" s="5">
         <v>5</v>
@@ -3137,19 +3202,19 @@
       <c r="F32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="39"/>
+      <c r="G32" s="38"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="D33" s="5">
         <v>5</v>
@@ -3160,19 +3225,19 @@
       <c r="F33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="39"/>
+      <c r="G33" s="38"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="D34" s="5">
         <v>3</v>
@@ -3183,19 +3248,19 @@
       <c r="F34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="39"/>
+      <c r="G34" s="38"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="D35" s="5">
         <v>3</v>
@@ -3206,19 +3271,19 @@
       <c r="F35" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="39"/>
+      <c r="G35" s="38"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
     </row>
     <row r="36" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="D36" s="5">
         <v>3</v>
@@ -3227,21 +3292,21 @@
         <v>11</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G36" s="39"/>
+        <v>75</v>
+      </c>
+      <c r="G36" s="38"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="D37" s="5">
         <v>3</v>
@@ -3252,19 +3317,19 @@
       <c r="F37" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="38"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="28" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="D38" s="14">
         <v>5</v>
@@ -3275,55 +3340,57 @@
       <c r="F38" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="42"/>
-      <c r="H38" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I38" s="14"/>
+      <c r="G38" s="38">
+        <v>46121</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="39" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="D39" s="5">
         <v>8</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="39"/>
+      <c r="G39" s="38"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="D40" s="5">
         <v>5</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="39"/>
+        <v>75</v>
+      </c>
+      <c r="G40" s="38"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
     </row>
@@ -3334,15 +3401,32 @@
       <c r="B42" s="2"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>485</v>
+      </c>
       <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" s="50" t="s">
+        <v>486</v>
+      </c>
       <c r="B44" s="9"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A45" s="51" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A46" s="52" t="s">
+        <v>488</v>
+      </c>
       <c r="B46" s="2"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="53" t="s">
+        <v>489</v>
+      </c>
       <c r="B47" s="2"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
@@ -3359,63 +3443,53 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="Won't">
+    <cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="Won't">
       <formula>NOT(ISERROR(SEARCH("Won't",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="Could">
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Could">
       <formula>NOT(ISERROR(SEARCH("Could",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="Should">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="Should">
       <formula>NOT(ISERROR(SEARCH("Should",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="Must">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="Must">
       <formula>NOT(ISERROR(SEARCH("Must",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="containsText" dxfId="9" priority="12" operator="containsText" text="Bajo">
+    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="Bajo">
       <formula>NOT(ISERROR(SEARCH("Bajo",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="Medio">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="Medio">
       <formula>NOT(ISERROR(SEARCH("Medio",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="Alto">
+    <cfRule type="containsText" dxfId="5" priority="14" operator="containsText" text="Alto">
       <formula>NOT(ISERROR(SEARCH("Alto",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Sí">
-      <formula>NOT(ISERROR(SEARCH("Sí",I1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Sí">
+  <conditionalFormatting sqref="H18:I20">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H18)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Sí">
-      <formula>NOT(ISERROR(SEARCH("Sí",H19)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Sí">
-      <formula>NOT(ISERROR(SEARCH("Sí",H20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H25">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Sí">
+  <conditionalFormatting sqref="H22:I25">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H22)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Sí">
+  <conditionalFormatting sqref="H29:I29">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H29)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Sí">
+  <conditionalFormatting sqref="H38:I38">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H38)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I17 I39:I1048576">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3424,189 +3498,172 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:E464"/>
+  <dimension ref="A2:D487"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.33203125" style="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.33203125" style="35" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="8"/>
+    <col min="5" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="D2" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C3" s="14">
         <v>0.6</v>
       </c>
       <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-    </row>
-    <row r="4" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="30" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C4" s="14">
         <v>0.8</v>
       </c>
       <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="5" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
       <c r="B5" s="30" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C5" s="14">
         <v>0.8</v>
       </c>
       <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
       <c r="B6" s="30" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C6" s="14">
         <v>0.8</v>
       </c>
       <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-    </row>
-    <row r="7" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
       <c r="B7" s="30" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="C7" s="14">
         <v>0.5</v>
       </c>
       <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
       <c r="B8" s="30" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="C8" s="14">
         <v>0.5</v>
       </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-    </row>
-    <row r="9" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="C9" s="14">
         <v>1</v>
       </c>
       <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-    </row>
-    <row r="10" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="16"/>
       <c r="B10" s="30" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="C10" s="14">
         <v>1</v>
       </c>
       <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-    </row>
-    <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="30" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="C11" s="14">
         <v>1</v>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-    </row>
-    <row r="12" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="16"/>
       <c r="B12" s="30" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="C12" s="14">
         <v>1</v>
       </c>
       <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-    </row>
-    <row r="13" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="16"/>
       <c r="B13" s="30" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="C13" s="14">
         <v>1</v>
       </c>
       <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-    </row>
-    <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="16"/>
       <c r="B14" s="30" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="C14" s="14">
         <v>1.2</v>
       </c>
       <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="30" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="C15" s="14">
         <v>0.6</v>
       </c>
       <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="56" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B18" s="27" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C18" s="8">
         <v>0.5</v>
@@ -3617,7 +3674,7 @@
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B19" s="27" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C19" s="8">
         <v>0.5</v>
@@ -3628,7 +3685,7 @@
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B20" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C20" s="8">
         <v>1</v>
@@ -3639,7 +3696,7 @@
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C21" s="8">
         <v>1</v>
@@ -3650,7 +3707,7 @@
     </row>
     <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B22" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C22" s="8">
         <v>1.5</v>
@@ -3661,7 +3718,7 @@
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B23" s="27" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C23" s="8">
         <v>2</v>
@@ -3672,7 +3729,7 @@
     </row>
     <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B24" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C24" s="8">
         <v>1</v>
@@ -3683,7 +3740,7 @@
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C25" s="8">
         <v>0.7</v>
@@ -3694,7 +3751,7 @@
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B26" s="27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C26" s="8">
         <v>1.2</v>
@@ -3705,7 +3762,7 @@
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B27" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C27" s="8">
         <v>0.8</v>
@@ -3716,7 +3773,7 @@
     </row>
     <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B28" s="27" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C28" s="8">
         <v>1.5</v>
@@ -3727,7 +3784,7 @@
     </row>
     <row r="29" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="27" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C29" s="8">
         <v>1.5</v>
@@ -3738,7 +3795,7 @@
     </row>
     <row r="30" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C30" s="8">
         <v>1.2</v>
@@ -3749,7 +3806,7 @@
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B31" s="27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C31" s="8">
         <v>1.2</v>
@@ -3760,7 +3817,7 @@
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B32" s="27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C32" s="8">
         <v>1.2</v>
@@ -3770,8 +3827,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="38" t="s">
-        <v>109</v>
+      <c r="B33" s="37" t="s">
+        <v>106</v>
       </c>
       <c r="C33" s="8">
         <v>1.5</v>
@@ -3782,7 +3839,7 @@
     </row>
     <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B34" s="27" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C34" s="8">
         <v>1</v>
@@ -3793,7 +3850,7 @@
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B35" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C35" s="8">
         <v>1</v>
@@ -3806,13 +3863,13 @@
       <c r="B36" s="27"/>
     </row>
     <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="61" t="s">
+      <c r="A37" s="56" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B38" s="27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C38" s="8">
         <v>0.8</v>
@@ -3823,7 +3880,7 @@
     </row>
     <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B39" s="27" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C39" s="8">
         <v>1</v>
@@ -3834,7 +3891,7 @@
     </row>
     <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B40" s="27" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C40" s="8">
         <v>1</v>
@@ -3845,7 +3902,7 @@
     </row>
     <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B41" s="27" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C41" s="8">
         <v>0.7</v>
@@ -3856,7 +3913,7 @@
     </row>
     <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B42" s="27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C42" s="8">
         <v>1</v>
@@ -3867,7 +3924,7 @@
     </row>
     <row r="43" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B43" s="27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C43" s="8">
         <v>1.2</v>
@@ -3878,7 +3935,7 @@
     </row>
     <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C44" s="8">
         <v>0.8</v>
@@ -3889,7 +3946,7 @@
     </row>
     <row r="45" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B45" s="27" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C45" s="8">
         <v>1.5</v>
@@ -3900,7 +3957,7 @@
     </row>
     <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B46" s="27" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C46" s="8">
         <v>1.5</v>
@@ -3911,7 +3968,7 @@
     </row>
     <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B47" s="27" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C47" s="8">
         <v>1</v>
@@ -3922,7 +3979,7 @@
     </row>
     <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B48" s="27" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C48" s="8">
         <v>1</v>
@@ -3935,13 +3992,13 @@
       <c r="B49" s="27"/>
     </row>
     <row r="50" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="61" t="s">
+      <c r="A50" s="56" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B51" s="27" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C51" s="8">
         <v>0.8</v>
@@ -3952,7 +4009,7 @@
     </row>
     <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B52" s="27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C52" s="8">
         <v>0.8</v>
@@ -3963,7 +4020,7 @@
     </row>
     <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B53" s="27" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C53" s="8">
         <v>0.8</v>
@@ -3974,7 +4031,7 @@
     </row>
     <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B54" s="27" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C54" s="8">
         <v>1.2</v>
@@ -3985,7 +4042,7 @@
     </row>
     <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C55" s="8">
         <v>1</v>
@@ -3996,7 +4053,7 @@
     </row>
     <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="27" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C56" s="8">
         <v>1</v>
@@ -4007,7 +4064,7 @@
     </row>
     <row r="57" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B57" s="27" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C57" s="8">
         <v>1</v>
@@ -4018,7 +4075,7 @@
     </row>
     <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B58" s="27" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C58" s="8">
         <v>1.2</v>
@@ -4029,7 +4086,7 @@
     </row>
     <row r="59" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B59" s="27" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C59" s="8">
         <v>0.7</v>
@@ -4040,7 +4097,7 @@
     </row>
     <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B60" s="27" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C60" s="8">
         <v>1.5</v>
@@ -4051,7 +4108,7 @@
     </row>
     <row r="61" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B61" s="27" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C61" s="8">
         <v>1</v>
@@ -4062,7 +4119,7 @@
     </row>
     <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B62" s="27" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C62" s="8">
         <v>1</v>
@@ -4075,13 +4132,13 @@
       <c r="B63" s="27"/>
     </row>
     <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="61" t="s">
+      <c r="A64" s="56" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B65" s="27" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C65" s="8">
         <v>1</v>
@@ -4092,7 +4149,7 @@
     </row>
     <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B66" s="27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C66" s="8">
         <v>0.8</v>
@@ -4103,7 +4160,7 @@
     </row>
     <row r="67" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B67" s="27" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C67" s="8">
         <v>1.2</v>
@@ -4114,7 +4171,7 @@
     </row>
     <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B68" s="27" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C68" s="8">
         <v>1</v>
@@ -4125,7 +4182,7 @@
     </row>
     <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B69" s="27" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C69" s="8">
         <v>2</v>
@@ -4136,7 +4193,7 @@
     </row>
     <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B70" s="27" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C70" s="8">
         <v>2</v>
@@ -4147,7 +4204,7 @@
     </row>
     <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B71" s="27" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C71" s="8">
         <v>0.8</v>
@@ -4158,7 +4215,7 @@
     </row>
     <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B72" s="27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C72" s="8">
         <v>0.8</v>
@@ -4169,7 +4226,7 @@
     </row>
     <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B73" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C73" s="8">
         <v>1.5</v>
@@ -4180,7 +4237,7 @@
     </row>
     <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B74" s="27" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C74" s="8">
         <v>1</v>
@@ -4191,7 +4248,7 @@
     </row>
     <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B75" s="27" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C75" s="8">
         <v>1</v>
@@ -4203,7 +4260,7 @@
     <row r="76" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A76" s="8"/>
       <c r="B76" s="26" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="C76" s="8">
         <v>0.8</v>
@@ -4216,13 +4273,13 @@
       <c r="B77" s="27"/>
     </row>
     <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A78" s="61" t="s">
+      <c r="A78" s="56" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B79" s="27" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C79" s="8">
         <v>1.2</v>
@@ -4233,7 +4290,7 @@
     </row>
     <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B80" s="27" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C80" s="8">
         <v>0.8</v>
@@ -4244,7 +4301,7 @@
     </row>
     <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B81" s="27" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C81" s="8">
         <v>0.8</v>
@@ -4255,7 +4312,7 @@
     </row>
     <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B82" s="27" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C82" s="8">
         <v>1</v>
@@ -4266,7 +4323,7 @@
     </row>
     <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B83" s="27" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C83" s="8">
         <v>1.5</v>
@@ -4277,7 +4334,7 @@
     </row>
     <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B84" s="27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C84" s="8">
         <v>1</v>
@@ -4288,7 +4345,7 @@
     </row>
     <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B85" s="27" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C85" s="8">
         <v>0.8</v>
@@ -4299,7 +4356,7 @@
     </row>
     <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B86" s="27" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C86" s="8">
         <v>1.5</v>
@@ -4310,7 +4367,7 @@
     </row>
     <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B87" s="27" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C87" s="8">
         <v>1</v>
@@ -4321,7 +4378,7 @@
     </row>
     <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B88" s="27" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C88" s="8">
         <v>1</v>
@@ -4334,13 +4391,13 @@
       <c r="B89" s="27"/>
     </row>
     <row r="90" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="61" t="s">
+      <c r="A90" s="56" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B91" s="27" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C91" s="8">
         <v>1</v>
@@ -4351,7 +4408,7 @@
     </row>
     <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B92" s="27" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C92" s="8">
         <v>1.2</v>
@@ -4362,7 +4419,7 @@
     </row>
     <row r="93" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B93" s="27" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C93" s="8">
         <v>0.8</v>
@@ -4373,7 +4430,7 @@
     </row>
     <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B94" s="27" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C94" s="8">
         <v>1</v>
@@ -4384,7 +4441,7 @@
     </row>
     <row r="95" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B95" s="27" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C95" s="8">
         <v>1</v>
@@ -4395,7 +4452,7 @@
     </row>
     <row r="96" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B96" s="27" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C96" s="8">
         <v>0.8</v>
@@ -4406,7 +4463,7 @@
     </row>
     <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B97" s="27" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C97" s="8">
         <v>1.5</v>
@@ -4417,7 +4474,7 @@
     </row>
     <row r="98" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B98" s="27" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="8">
         <v>1</v>
@@ -4428,7 +4485,7 @@
     </row>
     <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B99" s="27" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C99" s="8">
         <v>1</v>
@@ -4441,13 +4498,13 @@
       <c r="B100" s="27"/>
     </row>
     <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="61" t="s">
+      <c r="A101" s="56" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B102" s="27" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C102" s="8">
         <v>1</v>
@@ -4458,7 +4515,7 @@
     </row>
     <row r="103" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B103" s="27" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C103" s="8">
         <v>1.2</v>
@@ -4469,7 +4526,7 @@
     </row>
     <row r="104" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B104" s="27" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C104" s="8">
         <v>1.5</v>
@@ -4480,7 +4537,7 @@
     </row>
     <row r="105" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B105" s="27" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C105" s="8">
         <v>0.8</v>
@@ -4491,7 +4548,7 @@
     </row>
     <row r="106" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B106" s="27" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C106" s="8">
         <v>1.2</v>
@@ -4502,7 +4559,7 @@
     </row>
     <row r="107" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B107" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C107" s="8">
         <v>0.7</v>
@@ -4513,7 +4570,7 @@
     </row>
     <row r="108" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B108" s="27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C108" s="8">
         <v>1.5</v>
@@ -4524,7 +4581,7 @@
     </row>
     <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B109" s="27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C109" s="8">
         <v>1.5</v>
@@ -4535,7 +4592,7 @@
     </row>
     <row r="110" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B110" s="27" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C110" s="8">
         <v>1</v>
@@ -4546,7 +4603,7 @@
     </row>
     <row r="111" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B111" s="27" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C111" s="8">
         <v>1</v>
@@ -4559,13 +4616,13 @@
       <c r="B112" s="27"/>
     </row>
     <row r="113" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A113" s="61" t="s">
+      <c r="A113" s="56" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B114" s="27" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C114" s="8">
         <v>0.8</v>
@@ -4576,7 +4633,7 @@
     </row>
     <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B115" s="27" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C115" s="8">
         <v>1.2</v>
@@ -4587,7 +4644,7 @@
     </row>
     <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B116" s="27" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C116" s="8">
         <v>1.2</v>
@@ -4598,7 +4655,7 @@
     </row>
     <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B117" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C117" s="8">
         <v>1</v>
@@ -4609,7 +4666,7 @@
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B118" s="27" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C118" s="8">
         <v>0.6</v>
@@ -4620,7 +4677,7 @@
     </row>
     <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B119" s="27" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C119" s="8">
         <v>1.2</v>
@@ -4631,7 +4688,7 @@
     </row>
     <row r="120" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B120" s="27" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C120" s="8">
         <v>1</v>
@@ -4642,7 +4699,7 @@
     </row>
     <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B121" s="27" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C121" s="8">
         <v>1</v>
@@ -4655,13 +4712,13 @@
       <c r="B122" s="27"/>
     </row>
     <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A123" s="61" t="s">
+      <c r="A123" s="56" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B124" s="27" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C124" s="8">
         <v>1</v>
@@ -4672,7 +4729,7 @@
     </row>
     <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B125" s="27" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C125" s="8">
         <v>1.2</v>
@@ -4683,7 +4740,7 @@
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B126" s="27" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C126" s="8">
         <v>1.2</v>
@@ -4694,7 +4751,7 @@
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B127" s="27" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C127" s="8">
         <v>1</v>
@@ -4705,7 +4762,7 @@
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B128" s="27" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C128" s="8">
         <v>0.8</v>
@@ -4716,7 +4773,7 @@
     </row>
     <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B129" s="27" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C129" s="8">
         <v>0.8</v>
@@ -4727,7 +4784,7 @@
     </row>
     <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B130" s="27" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C130" s="8">
         <v>0.8</v>
@@ -4738,7 +4795,7 @@
     </row>
     <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B131" s="27" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C131" s="8">
         <v>1.5</v>
@@ -4749,7 +4806,7 @@
     </row>
     <row r="132" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B132" s="27" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C132" s="8">
         <v>1</v>
@@ -4760,7 +4817,7 @@
     </row>
     <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B133" s="27" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C133" s="8">
         <v>1</v>
@@ -4773,13 +4830,13 @@
       <c r="B134" s="27"/>
     </row>
     <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A135" s="58" t="s">
+      <c r="A135" s="54" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B136" s="27" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C136" s="8">
         <v>1.5</v>
@@ -4787,7 +4844,7 @@
     </row>
     <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B137" s="27" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C137" s="8">
         <v>0.8</v>
@@ -4795,7 +4852,7 @@
     </row>
     <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B138" s="27" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C138" s="8">
         <v>1.5</v>
@@ -4803,7 +4860,7 @@
     </row>
     <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B139" s="27" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C139" s="8">
         <v>1.2</v>
@@ -4811,7 +4868,7 @@
     </row>
     <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B140" s="27" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C140" s="8">
         <v>2</v>
@@ -4819,7 +4876,7 @@
     </row>
     <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B141" s="27" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C141" s="8">
         <v>1.5</v>
@@ -4827,7 +4884,7 @@
     </row>
     <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B142" s="27" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C142" s="8">
         <v>1</v>
@@ -4835,7 +4892,7 @@
     </row>
     <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B143" s="27" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C143" s="8">
         <v>1</v>
@@ -4843,7 +4900,7 @@
     </row>
     <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="27" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C144" s="8">
         <v>1.5</v>
@@ -4851,7 +4908,7 @@
     </row>
     <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B145" s="27" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C145" s="8">
         <v>1</v>
@@ -4861,13 +4918,13 @@
       <c r="B146" s="27"/>
     </row>
     <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A147" s="61" t="s">
+      <c r="A147" s="56" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B148" s="27" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C148" s="8">
         <v>2</v>
@@ -4878,7 +4935,7 @@
     </row>
     <row r="149" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B149" s="27" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C149" s="8">
         <v>1.2</v>
@@ -4889,7 +4946,7 @@
     </row>
     <row r="150" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B150" s="27" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C150" s="8">
         <v>1</v>
@@ -4900,7 +4957,7 @@
     </row>
     <row r="151" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B151" s="27" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C151" s="8">
         <v>1.5</v>
@@ -4911,7 +4968,7 @@
     </row>
     <row r="152" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B152" s="27" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C152" s="8">
         <v>0.8</v>
@@ -4922,7 +4979,7 @@
     </row>
     <row r="153" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B153" s="27" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C153" s="8">
         <v>1.5</v>
@@ -4933,7 +4990,7 @@
     </row>
     <row r="154" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B154" s="27" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C154" s="8">
         <v>1</v>
@@ -4944,7 +5001,7 @@
     </row>
     <row r="155" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B155" s="27" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C155" s="8">
         <v>1</v>
@@ -4957,13 +5014,13 @@
       <c r="B156" s="27"/>
     </row>
     <row r="157" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A157" s="58" t="s">
+      <c r="A157" s="54" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B158" s="27" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="C158" s="8">
         <v>1</v>
@@ -4974,7 +5031,7 @@
     </row>
     <row r="159" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B159" s="27" t="s">
-        <v>523</v>
+        <v>491</v>
       </c>
       <c r="C159" s="8">
         <v>1.5</v>
@@ -4985,7 +5042,7 @@
     </row>
     <row r="160" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B160" s="27" t="s">
-        <v>524</v>
+        <v>492</v>
       </c>
       <c r="C160" s="8">
         <v>2</v>
@@ -4994,9 +5051,9 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B161" s="27" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="C161" s="8">
         <v>1.2</v>
@@ -5005,9 +5062,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B162" s="27" t="s">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="C162" s="8">
         <v>3</v>
@@ -5016,9 +5073,9 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B163" s="27" t="s">
-        <v>527</v>
+        <v>495</v>
       </c>
       <c r="C163" s="8">
         <v>2</v>
@@ -5027,9 +5084,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B164" s="27" t="s">
-        <v>528</v>
+        <v>496</v>
       </c>
       <c r="C164" s="8">
         <v>1.2</v>
@@ -5037,13 +5094,10 @@
       <c r="D164" s="8">
         <v>1.2</v>
       </c>
-      <c r="E164" s="8" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B165" s="27" t="s">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="C165" s="8">
         <v>2</v>
@@ -5052,9 +5106,9 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B166" s="27" t="s">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="C166" s="8">
         <v>1.8</v>
@@ -5063,9 +5117,9 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B167" s="27" t="s">
-        <v>531</v>
+        <v>499</v>
       </c>
       <c r="C167" s="8">
         <v>1.5</v>
@@ -5074,9 +5128,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B168" s="27" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="C168" s="8">
         <v>1.5</v>
@@ -5085,9 +5139,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B169" s="27" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
       <c r="C169" s="8">
         <v>1</v>
@@ -5096,9 +5150,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B170" s="27" t="s">
-        <v>534</v>
+        <v>502</v>
       </c>
       <c r="C170" s="8">
         <v>2.5</v>
@@ -5107,9 +5161,9 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B171" s="27" t="s">
-        <v>535</v>
+        <v>503</v>
       </c>
       <c r="C171" s="8">
         <v>1.5</v>
@@ -5118,9 +5172,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B172" s="27" t="s">
-        <v>536</v>
+        <v>504</v>
       </c>
       <c r="C172" s="8">
         <v>1.5</v>
@@ -5129,9 +5183,9 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B173" s="36" t="s">
-        <v>537</v>
+    <row r="173" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B173" s="35" t="s">
+        <v>505</v>
       </c>
       <c r="C173" s="8">
         <v>1.5</v>
@@ -5140,65 +5194,65 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B174" s="27"/>
     </row>
-    <row r="175" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A175" s="60" t="s">
+    <row r="175" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A175" s="55" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B176" s="59" t="s">
+    <row r="176" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B176" s="27" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B177" s="27" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B178" s="27" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B179" s="27" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B177" s="59" t="s">
+    <row r="180" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B180" s="27" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B178" s="59" t="s">
+    <row r="181" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B181" s="27" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B179" s="59" t="s">
+    <row r="182" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B182" s="27" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B180" s="59" t="s">
+    <row r="183" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B183" s="27" t="s">
         <v>214</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B181" s="59" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B182" s="59" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B183" s="59" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B184" s="27"/>
     </row>
     <row r="185" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A185" s="37" t="s">
+      <c r="A185" s="36" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B186" s="27" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C186" s="8">
         <v>1.5</v>
@@ -5209,7 +5263,7 @@
     </row>
     <row r="187" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B187" s="27" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C187" s="8">
         <v>0.6</v>
@@ -5220,7 +5274,7 @@
     </row>
     <row r="188" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B188" s="27" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C188" s="8">
         <v>1.2</v>
@@ -5231,7 +5285,7 @@
     </row>
     <row r="189" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B189" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C189" s="8">
         <v>0.6</v>
@@ -5242,7 +5296,7 @@
     </row>
     <row r="190" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B190" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C190" s="8">
         <v>1.2</v>
@@ -5253,7 +5307,7 @@
     </row>
     <row r="191" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B191" s="27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C191" s="8">
         <v>2</v>
@@ -5264,15 +5318,15 @@
     </row>
     <row r="192" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B192" s="27" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C192" s="8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B193" s="27" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C193" s="8">
         <v>1</v>
@@ -5281,9 +5335,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B194" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C194" s="8">
         <v>1</v>
@@ -5292,10 +5346,10 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A195" s="14"/>
       <c r="B195" s="27" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="C195" s="14">
         <v>1</v>
@@ -5303,12 +5357,11 @@
       <c r="D195" s="14">
         <v>1</v>
       </c>
-      <c r="E195" s="14"/>
-    </row>
-    <row r="196" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="196" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A196" s="14"/>
       <c r="B196" s="27" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="C196" s="14">
         <v>1</v>
@@ -5316,12 +5369,11 @@
       <c r="D196" s="14">
         <v>1</v>
       </c>
-      <c r="E196" s="14"/>
-    </row>
-    <row r="197" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A197" s="14"/>
       <c r="B197" s="27" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="C197" s="14">
         <v>1.2</v>
@@ -5329,12 +5381,11 @@
       <c r="D197" s="14">
         <v>1.2</v>
       </c>
-      <c r="E197" s="14"/>
-    </row>
-    <row r="198" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A198" s="14"/>
       <c r="B198" s="27" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="C198" s="14">
         <v>1.2</v>
@@ -5342,12 +5393,11 @@
       <c r="D198" s="14">
         <v>1.2</v>
       </c>
-      <c r="E198" s="14"/>
-    </row>
-    <row r="199" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="199" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A199" s="14"/>
       <c r="B199" s="27" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
       <c r="C199" s="14">
         <v>1</v>
@@ -5355,12 +5405,11 @@
       <c r="D199" s="14">
         <v>0.5</v>
       </c>
-      <c r="E199" s="14"/>
-    </row>
-    <row r="200" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="200" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A200" s="14"/>
       <c r="B200" s="27" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="C200" s="14">
         <v>0.5</v>
@@ -5368,21 +5417,19 @@
       <c r="D200" s="14">
         <v>0.5</v>
       </c>
-      <c r="E200" s="14"/>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" s="14"/>
       <c r="B201" s="8"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
-      <c r="E201" s="14"/>
-    </row>
-    <row r="202" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="202" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A202" s="28" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="B202" s="27" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="C202" s="14">
         <v>1.5</v>
@@ -5390,12 +5437,11 @@
       <c r="D202" s="14">
         <v>1</v>
       </c>
-      <c r="E202" s="14"/>
-    </row>
-    <row r="203" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="203" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="16"/>
       <c r="B203" s="27" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="C203" s="14">
         <v>1</v>
@@ -5403,12 +5449,11 @@
       <c r="D203" s="14">
         <v>1</v>
       </c>
-      <c r="E203" s="14"/>
-    </row>
-    <row r="204" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="204" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="16"/>
       <c r="B204" s="27" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C204" s="14">
         <v>1</v>
@@ -5416,12 +5461,11 @@
       <c r="D204" s="14">
         <v>1</v>
       </c>
-      <c r="E204" s="14"/>
-    </row>
-    <row r="205" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="205" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A205" s="19"/>
       <c r="B205" s="30" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="C205" s="14">
         <v>1.5</v>
@@ -5429,12 +5473,11 @@
       <c r="D205" s="14">
         <v>1.5</v>
       </c>
-      <c r="E205" s="14"/>
-    </row>
-    <row r="206" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="206" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="16"/>
       <c r="B206" s="27" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="C206" s="14">
         <v>2</v>
@@ -5442,14 +5485,13 @@
       <c r="D206" s="14">
         <v>2.5</v>
       </c>
-      <c r="E206" s="14"/>
-    </row>
-    <row r="207" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="207" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="16" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="B207" s="27" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C207" s="14">
         <v>1.5</v>
@@ -5457,12 +5499,11 @@
       <c r="D207" s="14">
         <v>2.5</v>
       </c>
-      <c r="E207" s="14"/>
-    </row>
-    <row r="208" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="208" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="16"/>
       <c r="B208" s="27" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="C208" s="14">
         <v>1.5</v>
@@ -5470,12 +5511,11 @@
       <c r="D208" s="14">
         <v>3</v>
       </c>
-      <c r="E208" s="14"/>
-    </row>
-    <row r="209" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="209" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="16"/>
       <c r="B209" s="27" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C209" s="14">
         <v>1.5</v>
@@ -5483,12 +5523,11 @@
       <c r="D209" s="14">
         <v>2</v>
       </c>
-      <c r="E209" s="14"/>
-    </row>
-    <row r="210" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="210" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="16"/>
       <c r="B210" s="27" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="C210" s="14">
         <v>1.5</v>
@@ -5496,12 +5535,11 @@
       <c r="D210" s="14">
         <v>2.5</v>
       </c>
-      <c r="E210" s="14"/>
-    </row>
-    <row r="211" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="211" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="16"/>
       <c r="B211" s="27" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="C211" s="14">
         <v>1</v>
@@ -5509,12 +5547,11 @@
       <c r="D211" s="14">
         <v>2</v>
       </c>
-      <c r="E211" s="14"/>
-    </row>
-    <row r="212" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="212" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="16"/>
       <c r="B212" s="27" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="C212" s="14">
         <v>2</v>
@@ -5522,12 +5559,11 @@
       <c r="D212" s="14">
         <v>4</v>
       </c>
-      <c r="E212" s="14"/>
-    </row>
-    <row r="213" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="213" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="16"/>
       <c r="B213" s="27" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="C213" s="14">
         <v>1</v>
@@ -5535,12 +5571,11 @@
       <c r="D213" s="14">
         <v>1.5</v>
       </c>
-      <c r="E213" s="14"/>
-    </row>
-    <row r="214" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="214" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="16"/>
       <c r="B214" s="27" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C214" s="14">
         <v>2.5</v>
@@ -5548,12 +5583,11 @@
       <c r="D214" s="14">
         <v>3</v>
       </c>
-      <c r="E214" s="14"/>
-    </row>
-    <row r="215" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="215" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="19"/>
       <c r="B215" s="30" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C215" s="14">
         <v>1.2</v>
@@ -5561,12 +5595,11 @@
       <c r="D215" s="14">
         <v>1.5</v>
       </c>
-      <c r="E215" s="14"/>
-    </row>
-    <row r="216" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="216" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="19"/>
       <c r="B216" s="27" t="s">
-        <v>497</v>
+        <v>465</v>
       </c>
       <c r="C216" s="14">
         <v>0.5</v>
@@ -5574,12 +5607,11 @@
       <c r="D216" s="14">
         <v>0.5</v>
       </c>
-      <c r="E216" s="14"/>
-    </row>
-    <row r="217" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="217" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="19"/>
       <c r="B217" s="27" t="s">
-        <v>498</v>
+        <v>466</v>
       </c>
       <c r="C217" s="14">
         <v>0.5</v>
@@ -5587,12 +5619,11 @@
       <c r="D217" s="14">
         <v>0.5</v>
       </c>
-      <c r="E217" s="14"/>
-    </row>
-    <row r="218" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="218" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="19"/>
       <c r="B218" s="27" t="s">
-        <v>499</v>
+        <v>467</v>
       </c>
       <c r="C218" s="14">
         <v>0.5</v>
@@ -5600,12 +5631,11 @@
       <c r="D218" s="14">
         <v>0.5</v>
       </c>
-      <c r="E218" s="14"/>
-    </row>
-    <row r="219" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="219" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="19"/>
       <c r="B219" s="27" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="C219" s="14">
         <v>0.5</v>
@@ -5613,37 +5643,33 @@
       <c r="D219" s="14">
         <v>0.5</v>
       </c>
-      <c r="E219" s="14"/>
-    </row>
-    <row r="220" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="220" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="19"/>
       <c r="B220" s="27"/>
       <c r="C220" s="14"/>
       <c r="D220" s="14"/>
-      <c r="E220" s="14"/>
-    </row>
-    <row r="221" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="221" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="28" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B221" s="27"/>
       <c r="C221" s="14"/>
       <c r="D221" s="14"/>
-      <c r="E221" s="14"/>
-    </row>
-    <row r="222" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="222" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="16"/>
       <c r="B222" s="27" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
-      <c r="E222" s="14"/>
-    </row>
-    <row r="223" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="223" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="16"/>
       <c r="B223" s="27" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="C223" s="14">
         <v>1.2</v>
@@ -5651,12 +5677,11 @@
       <c r="D223" s="14">
         <v>1.8</v>
       </c>
-      <c r="E223" s="14"/>
-    </row>
-    <row r="224" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="224" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="16"/>
       <c r="B224" s="27" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
       <c r="C224" s="14">
         <v>1.2</v>
@@ -5664,12 +5689,11 @@
       <c r="D224" s="14">
         <v>2</v>
       </c>
-      <c r="E224" s="14"/>
-    </row>
-    <row r="225" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="225" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="16"/>
       <c r="B225" s="27" t="s">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="C225" s="14">
         <v>1</v>
@@ -5677,12 +5701,11 @@
       <c r="D225" s="14">
         <v>1.8</v>
       </c>
-      <c r="E225" s="14"/>
-    </row>
-    <row r="226" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="226" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="16"/>
       <c r="B226" s="27" t="s">
-        <v>505</v>
+        <v>473</v>
       </c>
       <c r="C226" s="14">
         <v>1</v>
@@ -5690,12 +5713,11 @@
       <c r="D226" s="14">
         <v>1.5</v>
       </c>
-      <c r="E226" s="14"/>
-    </row>
-    <row r="227" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="227" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="16"/>
       <c r="B227" s="27" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="C227" s="14">
         <v>0.8</v>
@@ -5703,12 +5725,11 @@
       <c r="D227" s="14">
         <v>1.5</v>
       </c>
-      <c r="E227" s="14"/>
-    </row>
-    <row r="228" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="228" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="16"/>
       <c r="B228" s="27" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
       <c r="C228" s="14">
         <v>0.5</v>
@@ -5716,12 +5737,11 @@
       <c r="D228" s="14">
         <v>0.5</v>
       </c>
-      <c r="E228" s="14"/>
-    </row>
-    <row r="229" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="229" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A229" s="8"/>
       <c r="B229" s="27" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C229" s="14">
         <v>0.8</v>
@@ -5729,12 +5749,11 @@
       <c r="D229" s="14">
         <v>1</v>
       </c>
-      <c r="E229" s="14"/>
-    </row>
-    <row r="230" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="230" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="16"/>
       <c r="B230" s="27" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C230" s="14">
         <v>1.2</v>
@@ -5742,12 +5761,11 @@
       <c r="D230" s="14">
         <v>2</v>
       </c>
-      <c r="E230" s="14"/>
-    </row>
-    <row r="231" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="231" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="16"/>
       <c r="B231" s="27" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C231" s="14">
         <v>1</v>
@@ -5755,12 +5773,11 @@
       <c r="D231" s="14">
         <v>2.5</v>
       </c>
-      <c r="E231" s="14"/>
-    </row>
-    <row r="232" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="232" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="16"/>
       <c r="B232" s="27" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C232" s="14">
         <v>0.8</v>
@@ -5768,12 +5785,11 @@
       <c r="D232" s="14">
         <v>1</v>
       </c>
-      <c r="E232" s="14"/>
-    </row>
-    <row r="233" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="233" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="16"/>
       <c r="B233" s="27" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C233" s="14">
         <v>2.5</v>
@@ -5781,12 +5797,11 @@
       <c r="D233" s="14">
         <v>0</v>
       </c>
-      <c r="E233" s="14"/>
-    </row>
-    <row r="234" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="234" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="16"/>
       <c r="B234" s="27" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C234" s="14">
         <v>1.5</v>
@@ -5794,12 +5809,11 @@
       <c r="D234" s="14">
         <v>0</v>
       </c>
-      <c r="E234" s="14"/>
-    </row>
-    <row r="235" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="235" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="16"/>
       <c r="B235" s="27" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C235" s="14">
         <v>1.5</v>
@@ -5807,12 +5821,11 @@
       <c r="D235" s="14">
         <v>1.8</v>
       </c>
-      <c r="E235" s="14"/>
-    </row>
-    <row r="236" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="236" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="19"/>
       <c r="B236" s="30" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C236" s="14">
         <v>2</v>
@@ -5820,12 +5833,11 @@
       <c r="D236" s="14">
         <v>2.5</v>
       </c>
-      <c r="E236" s="14"/>
-    </row>
-    <row r="237" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="237" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="16"/>
       <c r="B237" s="27" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="C237" s="14">
         <v>1.2</v>
@@ -5833,12 +5845,11 @@
       <c r="D237" s="14">
         <v>1</v>
       </c>
-      <c r="E237" s="14"/>
-    </row>
-    <row r="238" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="238" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="16"/>
       <c r="B238" s="27" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="C238" s="14">
         <v>1</v>
@@ -5846,12 +5857,11 @@
       <c r="D238" s="14">
         <v>1</v>
       </c>
-      <c r="E238" s="14"/>
-    </row>
-    <row r="239" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="239" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A239" s="16"/>
       <c r="B239" s="8" t="s">
-        <v>508</v>
+        <v>476</v>
       </c>
       <c r="C239" s="14">
         <v>2</v>
@@ -5859,12 +5869,11 @@
       <c r="D239" s="14">
         <v>1</v>
       </c>
-      <c r="E239" s="14"/>
-    </row>
-    <row r="240" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="240" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A240" s="16"/>
       <c r="B240" s="8" t="s">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="C240" s="14">
         <v>1</v>
@@ -5872,12 +5881,11 @@
       <c r="D240" s="14">
         <v>1.2</v>
       </c>
-      <c r="E240" s="14"/>
-    </row>
-    <row r="241" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="241" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A241" s="16"/>
       <c r="B241" s="8" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="C241" s="14">
         <v>1</v>
@@ -5885,2161 +5893,2343 @@
       <c r="D241" s="14">
         <v>1</v>
       </c>
-      <c r="E241" s="14"/>
-    </row>
-    <row r="242" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="242" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="16"/>
       <c r="B242" s="27"/>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
-      <c r="E242" s="14"/>
-    </row>
-    <row r="243" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A243" s="62" t="s">
-        <v>341</v>
+    </row>
+    <row r="243" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A243" s="57" t="s">
+        <v>330</v>
       </c>
       <c r="B243" s="27" t="s">
-        <v>435</v>
+        <v>534</v>
       </c>
       <c r="C243" s="14">
         <v>1.5</v>
       </c>
-      <c r="D243" s="14"/>
-      <c r="E243" s="14"/>
-    </row>
-    <row r="244" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="D243" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A244" s="16"/>
       <c r="B244" s="27" t="s">
-        <v>436</v>
+        <v>535</v>
       </c>
       <c r="C244" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="D244" s="14"/>
-      <c r="E244" s="14"/>
-    </row>
-    <row r="245" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+      <c r="D244" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A245" s="16"/>
       <c r="B245" s="27" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="C245" s="14">
         <v>0.6</v>
       </c>
-      <c r="D245" s="14"/>
-      <c r="E245" s="14"/>
-    </row>
-    <row r="246" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="D245" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A246" s="16"/>
       <c r="B246" s="27" t="s">
-        <v>438</v>
+        <v>536</v>
       </c>
       <c r="C246" s="14">
         <v>0.8</v>
       </c>
-      <c r="D246" s="14"/>
-      <c r="E246" s="14"/>
-    </row>
-    <row r="247" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D246" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A247" s="16"/>
       <c r="B247" s="27" t="s">
-        <v>439</v>
+        <v>537</v>
       </c>
       <c r="C247" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D247" s="14"/>
-      <c r="E247" s="14"/>
-    </row>
-    <row r="248" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+      <c r="D247" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A248" s="16"/>
       <c r="B248" s="27" t="s">
-        <v>440</v>
+        <v>538</v>
       </c>
       <c r="C248" s="14">
-        <v>2</v>
-      </c>
-      <c r="D248" s="14"/>
-      <c r="E248" s="14"/>
-    </row>
-    <row r="249" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.3</v>
+      </c>
+      <c r="D248" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A249" s="19"/>
       <c r="B249" s="27" t="s">
-        <v>441</v>
+        <v>539</v>
       </c>
       <c r="C249" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D249" s="14"/>
-      <c r="E249" s="14"/>
-    </row>
-    <row r="250" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D249" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="16"/>
       <c r="B250" s="30" t="s">
-        <v>442</v>
+        <v>540</v>
       </c>
       <c r="C250" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D250" s="14"/>
-      <c r="E250" s="14"/>
-    </row>
-    <row r="251" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D250" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A251" s="16"/>
       <c r="B251" s="27" t="s">
-        <v>443</v>
+        <v>541</v>
       </c>
       <c r="C251" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D251" s="14"/>
-      <c r="E251" s="14"/>
-    </row>
-    <row r="252" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.4</v>
+      </c>
+      <c r="D251" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="16"/>
       <c r="B252" s="27" t="s">
-        <v>444</v>
+        <v>542</v>
       </c>
       <c r="C252" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="D252" s="14"/>
-      <c r="E252" s="14"/>
-    </row>
-    <row r="253" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+      <c r="D252" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="16"/>
       <c r="B253" s="27" t="s">
-        <v>445</v>
+        <v>543</v>
       </c>
       <c r="C253" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D253" s="14"/>
-      <c r="E253" s="14"/>
-    </row>
-    <row r="254" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D253" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="16"/>
       <c r="B254" s="27" t="s">
-        <v>446</v>
+        <v>544</v>
       </c>
       <c r="C254" s="14">
-        <v>2</v>
-      </c>
-      <c r="D254" s="14"/>
-      <c r="E254" s="14"/>
-    </row>
-    <row r="255" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.9</v>
+      </c>
+      <c r="D254" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A255" s="16"/>
       <c r="B255" s="27" t="s">
-        <v>447</v>
+        <v>545</v>
       </c>
       <c r="C255" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D255" s="14"/>
-      <c r="E255" s="14"/>
-    </row>
-    <row r="256" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.8</v>
+      </c>
+      <c r="D255" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="16"/>
       <c r="B256" s="27" t="s">
-        <v>448</v>
+        <v>546</v>
       </c>
       <c r="C256" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D256" s="14"/>
-      <c r="E256" s="14"/>
-    </row>
-    <row r="257" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+      <c r="D256" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="16"/>
       <c r="B257" s="27" t="s">
-        <v>449</v>
+        <v>547</v>
       </c>
       <c r="C257" s="14">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="D257" s="14"/>
-      <c r="E257" s="14"/>
-    </row>
-    <row r="258" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="258" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="16"/>
       <c r="B258" s="27" t="s">
-        <v>450</v>
+        <v>548</v>
       </c>
       <c r="C258" s="14">
         <v>1.2</v>
       </c>
       <c r="D258" s="14"/>
-      <c r="E258" s="14"/>
-    </row>
-    <row r="259" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="259" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="16"/>
       <c r="B259" s="27" t="s">
-        <v>451</v>
+        <v>549</v>
       </c>
       <c r="C259" s="14">
         <v>2.2000000000000002</v>
       </c>
       <c r="D259" s="14"/>
-      <c r="E259" s="14"/>
-    </row>
-    <row r="260" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="260" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="16"/>
       <c r="B260" s="27" t="s">
-        <v>470</v>
+        <v>550</v>
       </c>
       <c r="C260" s="14">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="D260" s="14"/>
-      <c r="E260" s="14"/>
-    </row>
-    <row r="261" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="261" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A261" s="16"/>
       <c r="B261" s="27" t="s">
-        <v>471</v>
+        <v>551</v>
       </c>
       <c r="C261" s="14">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D261" s="14"/>
-      <c r="E261" s="14"/>
-    </row>
-    <row r="262" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="262" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A262" s="16" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="B262" s="27" t="s">
-        <v>472</v>
+        <v>552</v>
       </c>
       <c r="C262" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D262" s="14"/>
-      <c r="E262" s="14"/>
-    </row>
-    <row r="263" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="263" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A263" s="16"/>
-      <c r="B263" s="27"/>
-      <c r="C263" s="14"/>
+      <c r="B263" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="C263" s="14">
+        <v>1</v>
+      </c>
       <c r="D263" s="14"/>
-      <c r="E263" s="14"/>
-    </row>
-    <row r="264" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A264" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="B264" s="30" t="s">
-        <v>414</v>
+    </row>
+    <row r="264" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="16"/>
+      <c r="B264" s="27" t="s">
+        <v>554</v>
       </c>
       <c r="C264" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D264" s="14">
-        <v>1</v>
-      </c>
-      <c r="E264" s="14"/>
-    </row>
-    <row r="265" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+      <c r="D264" s="14"/>
+    </row>
+    <row r="265" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="16"/>
       <c r="B265" s="27" t="s">
-        <v>415</v>
+        <v>555</v>
       </c>
       <c r="C265" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D265" s="14">
-        <v>1</v>
-      </c>
-      <c r="E265" s="14"/>
-    </row>
-    <row r="266" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D265" s="14"/>
+    </row>
+    <row r="266" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="16"/>
       <c r="B266" s="27" t="s">
-        <v>416</v>
+        <v>556</v>
       </c>
       <c r="C266" s="14">
-        <v>2</v>
-      </c>
-      <c r="D266" s="14">
-        <v>2</v>
-      </c>
-      <c r="E266" s="14"/>
-    </row>
-    <row r="267" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D266" s="14"/>
+    </row>
+    <row r="267" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="16"/>
       <c r="B267" s="27" t="s">
-        <v>417</v>
+        <v>557</v>
       </c>
       <c r="C267" s="14">
-        <v>2</v>
-      </c>
-      <c r="D267" s="14">
-        <v>2</v>
-      </c>
-      <c r="E267" s="14"/>
-    </row>
-    <row r="268" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+      <c r="D267" s="14"/>
+    </row>
+    <row r="268" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A268" s="16"/>
       <c r="B268" s="27" t="s">
-        <v>418</v>
+        <v>558</v>
       </c>
       <c r="C268" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D268" s="14">
-        <v>1</v>
-      </c>
-      <c r="E268" s="14"/>
-    </row>
-    <row r="269" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D268" s="14"/>
+    </row>
+    <row r="269" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="16"/>
       <c r="B269" s="27" t="s">
-        <v>419</v>
+        <v>559</v>
       </c>
       <c r="C269" s="14">
-        <v>1</v>
-      </c>
-      <c r="D269" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E269" s="14"/>
-    </row>
-    <row r="270" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D269" s="14"/>
+    </row>
+    <row r="270" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="16"/>
-      <c r="B270" s="27" t="s">
-        <v>420</v>
-      </c>
-      <c r="C270" s="14">
-        <v>2</v>
-      </c>
-      <c r="D270" s="14">
-        <v>2</v>
-      </c>
-      <c r="E270" s="14"/>
-    </row>
-    <row r="271" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="16"/>
-      <c r="B271" s="27" t="s">
-        <v>473</v>
-      </c>
-      <c r="C271" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D271" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E271" s="14"/>
-    </row>
-    <row r="272" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="16" t="s">
-        <v>434</v>
-      </c>
+      <c r="B270" s="27"/>
+      <c r="C270" s="14"/>
+      <c r="D270" s="14"/>
+    </row>
+    <row r="271" spans="1:4" s="60" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A271" s="31" t="s">
+        <v>331</v>
+      </c>
+      <c r="B271" s="30" t="s">
+        <v>403</v>
+      </c>
+      <c r="C271" s="59">
+        <v>1.5</v>
+      </c>
+      <c r="D271" s="59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A272" s="16"/>
       <c r="B272" s="27" t="s">
-        <v>474</v>
+        <v>404</v>
       </c>
       <c r="C272" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D272" s="14">
         <v>1</v>
       </c>
-      <c r="E272" s="14"/>
-    </row>
-    <row r="273" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="273" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="16"/>
       <c r="B273" s="27" t="s">
-        <v>475</v>
+        <v>405</v>
       </c>
       <c r="C273" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D273" s="14">
-        <v>1</v>
-      </c>
-      <c r="E273" s="14"/>
-    </row>
-    <row r="274" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="16"/>
       <c r="B274" s="27" t="s">
-        <v>511</v>
+        <v>406</v>
       </c>
       <c r="C274" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D274" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E274" s="14"/>
-    </row>
-    <row r="275" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="16"/>
-      <c r="B275" s="27"/>
-      <c r="C275" s="14"/>
-      <c r="D275" s="14"/>
-      <c r="E275" s="14"/>
-    </row>
-    <row r="276" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A276" s="28" t="s">
-        <v>345</v>
-      </c>
+      <c r="B275" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="C275" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D275" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" s="16"/>
       <c r="B276" s="27" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="C276" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D276" s="14">
-        <v>1</v>
-      </c>
-      <c r="E276" s="14"/>
-    </row>
-    <row r="277" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="16"/>
       <c r="B277" s="27" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C277" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D277" s="14">
-        <v>1</v>
-      </c>
-      <c r="E277" s="14"/>
-    </row>
-    <row r="278" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="19"/>
-      <c r="B278" s="30" t="s">
-        <v>383</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="16"/>
+      <c r="B278" s="27" t="s">
+        <v>441</v>
       </c>
       <c r="C278" s="14">
         <v>1.5</v>
       </c>
       <c r="D278" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="E278" s="14"/>
-    </row>
-    <row r="279" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="16"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="16" t="s">
+        <v>421</v>
+      </c>
       <c r="B279" s="27" t="s">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="C279" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D279" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E279" s="14"/>
-    </row>
-    <row r="280" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="16"/>
       <c r="B280" s="27" t="s">
-        <v>385</v>
+        <v>443</v>
       </c>
       <c r="C280" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D280" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E280" s="14"/>
-    </row>
-    <row r="281" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="16"/>
       <c r="B281" s="27" t="s">
-        <v>386</v>
+        <v>479</v>
       </c>
       <c r="C281" s="14">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D281" s="14">
-        <v>2</v>
-      </c>
-      <c r="E281" s="14"/>
-    </row>
-    <row r="282" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="16"/>
-      <c r="B282" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="C282" s="14">
-        <v>2</v>
-      </c>
-      <c r="D282" s="14">
-        <v>2</v>
-      </c>
-      <c r="E282" s="14"/>
-    </row>
-    <row r="283" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="16"/>
+      <c r="B282" s="27"/>
+      <c r="C282" s="14"/>
+      <c r="D282" s="14"/>
+    </row>
+    <row r="283" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A283" s="28" t="s">
+        <v>334</v>
+      </c>
       <c r="B283" s="27" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C283" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D283" s="14">
         <v>1</v>
       </c>
-      <c r="E283" s="14"/>
-    </row>
-    <row r="284" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="284" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="16"/>
       <c r="B284" s="27" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C284" s="14">
+        <v>1</v>
+      </c>
+      <c r="D284" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" s="19"/>
+      <c r="B285" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="C285" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D285" s="14">
         <v>1.2</v>
       </c>
-      <c r="D284" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="E284" s="14"/>
-    </row>
-    <row r="285" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="16"/>
-      <c r="B285" s="27" t="s">
-        <v>467</v>
-      </c>
-      <c r="C285" s="14">
-        <v>1</v>
-      </c>
-      <c r="D285" s="14">
-        <v>1</v>
-      </c>
-      <c r="E285" s="14"/>
-    </row>
-    <row r="286" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="286" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="16"/>
       <c r="B286" s="27" t="s">
-        <v>468</v>
+        <v>373</v>
       </c>
       <c r="C286" s="14">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="D286" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E286" s="14"/>
-    </row>
-    <row r="287" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="16"/>
       <c r="B287" s="27" t="s">
-        <v>469</v>
+        <v>374</v>
       </c>
       <c r="C287" s="14">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D287" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E287" s="14"/>
-    </row>
-    <row r="288" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="16"/>
-      <c r="B288" s="27"/>
-      <c r="C288" s="14"/>
-      <c r="D288" s="14"/>
-      <c r="E288" s="14"/>
-    </row>
-    <row r="289" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="16" t="s">
-        <v>434</v>
-      </c>
-      <c r="B289" s="27"/>
-      <c r="C289" s="14"/>
-      <c r="D289" s="14"/>
-      <c r="E289" s="14"/>
-    </row>
-    <row r="290" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A290" s="28" t="s">
-        <v>348</v>
-      </c>
+      <c r="B288" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C288" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D288" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289" s="16"/>
+      <c r="B289" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="C289" s="14">
+        <v>2</v>
+      </c>
+      <c r="D289" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="16"/>
       <c r="B290" s="27" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C290" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D290" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="E290" s="14"/>
-    </row>
-    <row r="291" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A291" s="19"/>
-      <c r="B291" s="30" t="s">
-        <v>391</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="16"/>
+      <c r="B291" s="27" t="s">
+        <v>378</v>
       </c>
       <c r="C291" s="14">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D291" s="14">
-        <v>3</v>
-      </c>
-      <c r="E291" s="14"/>
-    </row>
-    <row r="292" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="16"/>
       <c r="B292" s="27" t="s">
-        <v>392</v>
+        <v>438</v>
       </c>
       <c r="C292" s="14">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D292" s="14">
-        <v>3.8</v>
-      </c>
-      <c r="E292" s="14"/>
-    </row>
-    <row r="293" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="16"/>
       <c r="B293" s="27" t="s">
-        <v>393</v>
+        <v>439</v>
       </c>
       <c r="C293" s="14">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D293" s="14">
-        <v>2</v>
-      </c>
-      <c r="E293" s="14"/>
-    </row>
-    <row r="294" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="16"/>
       <c r="B294" s="27" t="s">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="C294" s="14">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D294" s="14">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E294" s="14"/>
-    </row>
-    <row r="295" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="16"/>
-      <c r="B295" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="C295" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D295" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E295" s="14"/>
-    </row>
-    <row r="296" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="16"/>
-      <c r="B296" s="27" t="s">
-        <v>396</v>
-      </c>
-      <c r="C296" s="14">
-        <v>2</v>
-      </c>
-      <c r="D296" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="E296" s="14"/>
-    </row>
-    <row r="297" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A297" s="16"/>
+      <c r="B295" s="27"/>
+      <c r="C295" s="14"/>
+      <c r="D295" s="14"/>
+    </row>
+    <row r="296" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="B296" s="27"/>
+      <c r="C296" s="14"/>
+      <c r="D296" s="14"/>
+    </row>
+    <row r="297" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A297" s="28" t="s">
+        <v>337</v>
+      </c>
       <c r="B297" s="27" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C297" s="14">
         <v>2</v>
       </c>
       <c r="D297" s="14">
-        <v>4</v>
-      </c>
-      <c r="E297" s="14"/>
-    </row>
-    <row r="298" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="16"/>
-      <c r="B298" s="27" t="s">
-        <v>398</v>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A298" s="19"/>
+      <c r="B298" s="30" t="s">
+        <v>380</v>
       </c>
       <c r="C298" s="14">
         <v>2</v>
       </c>
       <c r="D298" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="E298" s="14"/>
-    </row>
-    <row r="299" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A299" s="16"/>
       <c r="B299" s="27" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="C299" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D299" s="14">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A300" s="16"/>
+      <c r="B300" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="C300" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D300" s="14">
         <v>2</v>
       </c>
-      <c r="D299" s="14">
-        <v>2</v>
-      </c>
-      <c r="E299" s="14"/>
-    </row>
-    <row r="300" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="19"/>
-      <c r="B300" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="C300" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D300" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="E300" s="14"/>
-    </row>
-    <row r="301" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="301" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="16"/>
       <c r="B301" s="27" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="C301" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D301" s="14">
-        <v>1</v>
-      </c>
-      <c r="E301" s="14"/>
-    </row>
-    <row r="302" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A302" s="16"/>
       <c r="B302" s="27" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="C302" s="14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D302" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="E302" s="14"/>
-    </row>
-    <row r="303" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="16"/>
       <c r="B303" s="27" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="C303" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D303" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="E303" s="14"/>
-    </row>
-    <row r="304" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A304" s="16"/>
       <c r="B304" s="27" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="C304" s="14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D304" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E304" s="14"/>
-    </row>
-    <row r="305" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="16"/>
       <c r="B305" s="27" t="s">
-        <v>476</v>
-      </c>
-      <c r="C305" s="8">
+        <v>387</v>
+      </c>
+      <c r="C305" s="14">
         <v>2</v>
       </c>
       <c r="D305" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E305" s="14"/>
-    </row>
-    <row r="306" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="16"/>
       <c r="B306" s="27" t="s">
-        <v>477</v>
-      </c>
-      <c r="C306" s="8">
-        <v>1</v>
+        <v>388</v>
+      </c>
+      <c r="C306" s="14">
+        <v>2</v>
       </c>
       <c r="D306" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="19"/>
+      <c r="B307" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="C307" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D307" s="14">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="16"/>
+      <c r="B308" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="C308" s="14">
+        <v>1</v>
+      </c>
+      <c r="D308" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309" s="16"/>
+      <c r="B309" s="27" t="s">
+        <v>391</v>
+      </c>
+      <c r="C309" s="14">
+        <v>3</v>
+      </c>
+      <c r="D309" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="16"/>
+      <c r="B310" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="C310" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D310" s="14">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311" s="16"/>
+      <c r="B311" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="C311" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D311" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A312" s="16"/>
+      <c r="B312" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="C312" s="8">
+        <v>2</v>
+      </c>
+      <c r="D312" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A313" s="16"/>
+      <c r="B313" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="C313" s="8">
+        <v>1</v>
+      </c>
+      <c r="D313" s="14">
         <v>0.5</v>
       </c>
-      <c r="E306" s="14"/>
-    </row>
-    <row r="307" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A307" s="16"/>
-      <c r="B307" s="27" t="s">
-        <v>478</v>
-      </c>
-      <c r="C307" s="8">
-        <v>1</v>
-      </c>
-      <c r="D307" s="14">
+    </row>
+    <row r="314" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="16"/>
+      <c r="B314" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="C314" s="8">
+        <v>1</v>
+      </c>
+      <c r="D314" s="14">
         <v>0.5</v>
       </c>
-      <c r="E307" s="14"/>
-    </row>
-    <row r="308" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="16" t="s">
-        <v>434</v>
-      </c>
-      <c r="B308" s="27"/>
-      <c r="C308" s="14"/>
-      <c r="D308" s="14"/>
-      <c r="E308" s="14"/>
-    </row>
-    <row r="309" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A309" s="28" t="s">
-        <v>351</v>
-      </c>
-      <c r="B309" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="C309" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D309" s="14">
+    </row>
+    <row r="315" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="B315" s="27"/>
+      <c r="C315" s="14"/>
+      <c r="D315" s="14"/>
+    </row>
+    <row r="316" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A316" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="B316" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="C316" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="D316" s="14">
         <v>0.5</v>
       </c>
-      <c r="E309" s="14"/>
-    </row>
-    <row r="310" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A310" s="16"/>
-      <c r="B310" s="18" t="s">
-        <v>406</v>
-      </c>
-      <c r="C310" s="14">
-        <v>2</v>
-      </c>
-      <c r="D310" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E310" s="14"/>
-    </row>
-    <row r="311" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A311" s="16"/>
-      <c r="B311" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="C311" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D311" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E311" s="14"/>
-    </row>
-    <row r="312" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A312" s="19"/>
-      <c r="B312" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="C312" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D312" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E312" s="14"/>
-    </row>
-    <row r="313" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A313" s="16"/>
-      <c r="B313" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="C313" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D313" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="E313" s="14"/>
-    </row>
-    <row r="314" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A314" s="16"/>
-      <c r="B314" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="C314" s="14">
-        <v>2</v>
-      </c>
-      <c r="D314" s="14">
-        <v>2</v>
-      </c>
-      <c r="E314" s="14"/>
-    </row>
-    <row r="315" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="16"/>
-      <c r="B315" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="C315" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D315" s="14">
-        <v>1</v>
-      </c>
-      <c r="E315" s="14"/>
-    </row>
-    <row r="316" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A316" s="16"/>
-      <c r="B316" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="C316" s="14">
-        <v>3</v>
-      </c>
-      <c r="D316" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="E316" s="14"/>
-    </row>
-    <row r="317" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="317" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="16"/>
       <c r="B317" s="18" t="s">
-        <v>491</v>
+        <v>395</v>
       </c>
       <c r="C317" s="14">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D317" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E317" s="14"/>
-    </row>
-    <row r="318" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="16"/>
       <c r="B318" s="18" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C318" s="14">
         <v>1.2</v>
       </c>
       <c r="D318" s="14">
-        <v>1</v>
-      </c>
-      <c r="E318" s="14"/>
-    </row>
-    <row r="319" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A319" s="16"/>
-      <c r="B319" s="18" t="s">
-        <v>479</v>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="19"/>
+      <c r="B319" s="14" t="s">
+        <v>397</v>
       </c>
       <c r="C319" s="14">
         <v>1.5</v>
       </c>
       <c r="D319" s="14">
-        <v>1</v>
-      </c>
-      <c r="E319" s="14"/>
-    </row>
-    <row r="320" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="16"/>
       <c r="B320" s="18" t="s">
-        <v>480</v>
+        <v>398</v>
       </c>
       <c r="C320" s="14">
-        <v>1</v>
-      </c>
-      <c r="D320" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>2.5</v>
+      </c>
+      <c r="D320" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="16"/>
       <c r="B321" s="18" t="s">
-        <v>481</v>
+        <v>399</v>
       </c>
       <c r="C321" s="14">
-        <v>1</v>
-      </c>
-      <c r="D321" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A322" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D321" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="16"/>
+      <c r="B322" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C322" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D322" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="16"/>
+      <c r="B323" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C323" s="14">
+        <v>3</v>
+      </c>
+      <c r="D323" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A324" s="16"/>
+      <c r="B324" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="C324" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D324" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="16"/>
+      <c r="B325" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="C325" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D325" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326" s="16"/>
+      <c r="B326" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="C326" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D326" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A327" s="16"/>
+      <c r="B327" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="C327" s="14">
+        <v>1</v>
+      </c>
+      <c r="D327" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B328" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C328" s="14">
+        <v>1</v>
+      </c>
+      <c r="D328" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A329" s="54" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B323" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C323" s="8">
+    <row r="330" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B330" s="27" t="s">
+        <v>509</v>
+      </c>
+      <c r="C330" s="8">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="324" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B324" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="C324" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B325" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="C325" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B326" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="C326" s="8">
+      <c r="D330" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B331" s="27" t="s">
+        <v>510</v>
+      </c>
+      <c r="C331" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="327" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B327" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="C327" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B328" s="27" t="s">
-        <v>232</v>
-      </c>
-      <c r="C328" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B329" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C329" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B330" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="C330" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B331" s="27"/>
+      <c r="D331" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="332" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A332" s="35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B332" s="27" t="s">
+        <v>511</v>
+      </c>
+      <c r="C332" s="8">
+        <v>1</v>
+      </c>
+      <c r="D332" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B333" s="27" t="s">
-        <v>235</v>
+        <v>512</v>
       </c>
       <c r="C333" s="8">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="334" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="D333" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B334" s="27" t="s">
-        <v>236</v>
+        <v>513</v>
       </c>
       <c r="C334" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="335" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="D334" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B335" s="27" t="s">
-        <v>237</v>
+        <v>518</v>
       </c>
       <c r="C335" s="8">
-        <v>1.2</v>
+        <v>0.8</v>
+      </c>
+      <c r="D335" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B336" s="27" t="s">
-        <v>238</v>
+        <v>514</v>
       </c>
       <c r="C336" s="8">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="337" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="D336" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B337" s="27" t="s">
-        <v>239</v>
+        <v>517</v>
       </c>
       <c r="C337" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B338" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="C338" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B339" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="C339" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B340" s="27"/>
-    </row>
-    <row r="341" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A341" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="B341" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D337" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B338" s="35" t="s">
+        <v>515</v>
+      </c>
+      <c r="C338" s="58">
+        <v>0.8</v>
+      </c>
+      <c r="D338" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B339" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="C339" s="58">
+        <v>1</v>
+      </c>
+      <c r="D339" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C340" s="58"/>
+    </row>
+    <row r="341" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A341" s="43" t="s">
+        <v>519</v>
+      </c>
+      <c r="C341" s="58"/>
+    </row>
+    <row r="342" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B342" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="C342" s="58">
+        <v>1</v>
+      </c>
+      <c r="D342" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B343" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="C343" s="58">
+        <v>2.5</v>
+      </c>
+      <c r="D343" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B344" s="35" t="s">
+        <v>524</v>
+      </c>
+      <c r="C344" s="58">
+        <v>0.8</v>
+      </c>
+      <c r="D344" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B345" s="35" t="s">
+        <v>525</v>
+      </c>
+      <c r="C345" s="58">
+        <v>0.8</v>
+      </c>
+      <c r="D345" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B346" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="C346" s="58">
+        <v>1</v>
+      </c>
+      <c r="D346" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A347" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="C341" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D341" s="14">
+      <c r="B347" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="C347" s="58">
+        <v>0.8</v>
+      </c>
+      <c r="D347" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B348" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="C348" s="58">
+        <v>0.8</v>
+      </c>
+      <c r="D348" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B349" s="35" t="s">
+        <v>529</v>
+      </c>
+      <c r="C349" s="58">
+        <v>0.5</v>
+      </c>
+      <c r="D349" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B350" s="35" t="s">
+        <v>530</v>
+      </c>
+      <c r="C350" s="58">
+        <v>1.8</v>
+      </c>
+      <c r="D350" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B351" s="35" t="s">
+        <v>531</v>
+      </c>
+      <c r="C351" s="58">
+        <v>1</v>
+      </c>
+      <c r="D351" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B352" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="C352" s="58">
+        <v>1</v>
+      </c>
+      <c r="D352" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B353" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="C353" s="58">
+        <v>1</v>
+      </c>
+      <c r="D353" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B354" s="27"/>
+    </row>
+    <row r="355" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A355" s="34" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B356" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C356" s="8">
         <v>1.2</v>
       </c>
-      <c r="E341" s="14"/>
-    </row>
-    <row r="342" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B342" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="C342" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D342" s="14">
+    </row>
+    <row r="357" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B357" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="C357" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B358" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C358" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B359" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C359" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B360" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C360" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B361" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C361" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B362" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C362" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B363" s="27"/>
+    </row>
+    <row r="364" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A364" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B364" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="C364" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D364" s="14">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B365" s="27" t="s">
+        <v>411</v>
+      </c>
+      <c r="C365" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D365" s="14">
         <v>2</v>
       </c>
-      <c r="E342" s="14"/>
-    </row>
-    <row r="343" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A343" s="16"/>
-      <c r="B343" s="27" t="s">
-        <v>423</v>
-      </c>
-      <c r="C343" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D343" s="14">
+    </row>
+    <row r="366" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A366" s="16"/>
+      <c r="B366" s="27" t="s">
+        <v>412</v>
+      </c>
+      <c r="C366" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D366" s="14">
         <v>2</v>
       </c>
-      <c r="E343" s="14"/>
-    </row>
-    <row r="344" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A344" s="16"/>
-      <c r="B344" s="27" t="s">
-        <v>424</v>
-      </c>
-      <c r="C344" s="14">
+    </row>
+    <row r="367" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A367" s="16"/>
+      <c r="B367" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="C367" s="14">
         <v>2</v>
       </c>
-      <c r="D344" s="14">
+      <c r="D367" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E344" s="14"/>
-    </row>
-    <row r="345" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A345" s="16"/>
-      <c r="B345" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="C345" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D345" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E345" s="14"/>
-    </row>
-    <row r="346" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A346" s="16"/>
-      <c r="B346" s="27" t="s">
-        <v>426</v>
-      </c>
-      <c r="C346" s="14">
+    </row>
+    <row r="368" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A368" s="16"/>
+      <c r="B368" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C368" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D368" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A369" s="16"/>
+      <c r="B369" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="C369" s="14">
         <v>1.2</v>
       </c>
-      <c r="D346" s="14">
-        <v>1</v>
-      </c>
-      <c r="E346" s="14"/>
-    </row>
-    <row r="347" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A347" s="16"/>
-      <c r="B347" s="27" t="s">
-        <v>427</v>
-      </c>
-      <c r="C347" s="14">
-        <v>1</v>
-      </c>
-      <c r="D347" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E347" s="14"/>
-    </row>
-    <row r="348" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A348" s="16"/>
-      <c r="B348" s="27" t="s">
-        <v>428</v>
-      </c>
-      <c r="C348" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D348" s="14">
+      <c r="D369" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A370" s="16"/>
+      <c r="B370" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="C370" s="14">
+        <v>1</v>
+      </c>
+      <c r="D370" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A371" s="16"/>
+      <c r="B371" s="27" t="s">
+        <v>417</v>
+      </c>
+      <c r="C371" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D371" s="14">
         <v>1.8</v>
       </c>
-      <c r="E348" s="14"/>
-    </row>
-    <row r="349" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A349" s="16"/>
-      <c r="B349" s="27" t="s">
-        <v>429</v>
-      </c>
-      <c r="C349" s="14">
+    </row>
+    <row r="372" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A372" s="16"/>
+      <c r="B372" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="C372" s="14">
         <v>2</v>
       </c>
-      <c r="D349" s="14">
+      <c r="D372" s="14">
         <v>2.5</v>
       </c>
-      <c r="E349" s="14"/>
-    </row>
-    <row r="350" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A350" s="16"/>
-      <c r="B350" s="27" t="s">
-        <v>430</v>
-      </c>
-      <c r="C350" s="14">
-        <v>1</v>
-      </c>
-      <c r="D350" s="14">
-        <v>1</v>
-      </c>
-      <c r="E350" s="14"/>
-    </row>
-    <row r="351" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A351" s="16"/>
-      <c r="B351" s="27" t="s">
-        <v>482</v>
-      </c>
-      <c r="C351" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D351" s="14">
-        <v>1</v>
-      </c>
-      <c r="E351" s="14"/>
-    </row>
-    <row r="352" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A352" s="16"/>
-      <c r="B352" s="27" t="s">
-        <v>483</v>
-      </c>
-      <c r="C352" s="8">
-        <v>1</v>
-      </c>
-      <c r="D352" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E352" s="14"/>
-    </row>
-    <row r="353" spans="1:5" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A353" s="16"/>
-      <c r="B353" s="27" t="s">
-        <v>484</v>
-      </c>
-      <c r="C353" s="8">
-        <v>1</v>
-      </c>
-      <c r="D353" s="8">
+    </row>
+    <row r="373" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A373" s="16"/>
+      <c r="B373" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="C373" s="14">
+        <v>1</v>
+      </c>
+      <c r="D373" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A374" s="16"/>
+      <c r="B374" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="C374" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D374" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A375" s="16"/>
+      <c r="B375" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="C375" s="8">
+        <v>1</v>
+      </c>
+      <c r="D375" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A376" s="16"/>
+      <c r="B376" s="27" t="s">
+        <v>452</v>
+      </c>
+      <c r="C376" s="8">
+        <v>1</v>
+      </c>
+      <c r="D376" s="8">
         <v>0.5</v>
       </c>
-      <c r="E353" s="14"/>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A354" s="16"/>
-      <c r="B354" s="27"/>
-    </row>
-    <row r="355" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A355" s="35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B356" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="C356" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B357" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="C357" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B358" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="C358" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B359" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="C359" s="8">
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A377" s="16"/>
+      <c r="B377" s="27"/>
+    </row>
+    <row r="378" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A378" s="34" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B379" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C379" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B380" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C380" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B381" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C381" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B382" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C382" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B360" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="C360" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B361" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="C361" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B362" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="C362" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B363" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="C363" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B364" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="C364" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B365" s="27"/>
-    </row>
-    <row r="366" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A366" s="35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B367" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="C367" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B368" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C368" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B369" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="C369" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B370" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C370" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B371" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="C371" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B372" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="C372" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B373" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C373" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B374" s="27"/>
-    </row>
-    <row r="375" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A375" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B376" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="C376" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B377" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="C377" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B378" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="C378" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B379" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C379" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B380" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="C380" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B381" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="C381" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B382" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="C382" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B383" s="27"/>
-    </row>
-    <row r="384" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A384" s="35" t="s">
-        <v>65</v>
+    <row r="383" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B383" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C383" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B384" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C384" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B385" s="27" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C385" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B386" s="27" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C386" s="8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B387" s="27" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C387" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B388" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C388" s="8">
-        <v>1</v>
-      </c>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B388" s="27"/>
     </row>
     <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B389" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C389" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A389" s="34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B390" s="27" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="C390" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B391" s="27" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="C391" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B392" s="27"/>
-    </row>
-    <row r="393" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A393" s="35" t="s">
-        <v>68</v>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B392" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C392" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B393" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C393" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B394" s="27" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="C394" s="8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B395" s="27" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="C395" s="8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B396" s="27" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="C396" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B397" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="C397" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B398" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="C398" s="8">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B397" s="27"/>
+    </row>
+    <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A398" s="34" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B399" s="27" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="C399" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B400" s="27"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B400" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="C400" s="8">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="401" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A401" s="35" t="s">
-        <v>71</v>
+      <c r="B401" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C401" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B402" s="27" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="C402" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B403" s="27" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="C403" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B404" s="27" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="C404" s="8">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B405" s="27" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="C405" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B406" s="27" t="s">
-        <v>282</v>
-      </c>
-      <c r="C406" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B407" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="C407" s="8">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B406" s="27"/>
+    </row>
+    <row r="407" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A407" s="34" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B408" s="27" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="C408" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B409" s="27"/>
+    <row r="409" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B409" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C409" s="8">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="410" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A410" s="35" t="s">
-        <v>74</v>
+      <c r="B410" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C410" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B411" s="27" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="C411" s="8">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B412" s="27" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="C412" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B413" s="27" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="C413" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B414" s="27" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="C414" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B415" s="27"/>
+    </row>
+    <row r="416" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A416" s="34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B417" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C417" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B418" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C418" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B419" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C419" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B415" s="27" t="s">
-        <v>289</v>
-      </c>
-      <c r="C415" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B416" s="27" t="s">
-        <v>290</v>
-      </c>
-      <c r="C416" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B417" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="C417" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B418" s="27"/>
-    </row>
-    <row r="419" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A419" s="35" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="420" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B420" s="27" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="C420" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B421" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C421" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B422" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C422" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B423" s="27"/>
+    </row>
+    <row r="424" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A424" s="34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B425" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C425" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B426" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C426" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B421" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="C421" s="8">
+    <row r="427" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B427" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="C427" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B428" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C428" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B429" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C429" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B430" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C430" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B431" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="C431" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B432" s="27"/>
+    </row>
+    <row r="433" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A433" s="34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B434" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C434" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B422" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="C422" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="423" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B423" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="C423" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B424" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="C424" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B425" s="27"/>
-      <c r="D425" s="14"/>
-      <c r="E425" s="14"/>
-    </row>
-    <row r="426" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A426" s="28" t="s">
-        <v>462</v>
-      </c>
-      <c r="B426" s="30" t="s">
-        <v>489</v>
-      </c>
-      <c r="C426" s="14">
+    <row r="435" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B435" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C435" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B436" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C436" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B437" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="C437" s="8">
         <v>1.2</v>
       </c>
-      <c r="D426" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E426" s="14"/>
-    </row>
-    <row r="427" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A427" s="16"/>
-      <c r="B427" s="30" t="s">
-        <v>452</v>
-      </c>
-      <c r="C427" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D427" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E427" s="14"/>
-    </row>
-    <row r="428" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A428" s="16"/>
-      <c r="B428" s="30" t="s">
-        <v>453</v>
-      </c>
-      <c r="C428" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="D428" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E428" s="14"/>
-    </row>
-    <row r="429" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A429" s="16"/>
-      <c r="B429" s="30" t="s">
-        <v>454</v>
-      </c>
-      <c r="C429" s="14">
-        <v>1</v>
-      </c>
-      <c r="D429" s="14">
-        <v>1</v>
-      </c>
-      <c r="E429" s="14"/>
-    </row>
-    <row r="430" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A430" s="16"/>
-      <c r="B430" s="30" t="s">
-        <v>455</v>
-      </c>
-      <c r="C430" s="14">
-        <v>2</v>
-      </c>
-      <c r="D430" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E430" s="14"/>
-    </row>
-    <row r="431" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A431" s="16"/>
-      <c r="B431" s="30" t="s">
-        <v>490</v>
-      </c>
-      <c r="C431" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D431" s="14">
-        <v>1</v>
-      </c>
-      <c r="E431" s="14"/>
-    </row>
-    <row r="432" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A432" s="16"/>
-      <c r="B432" s="30" t="s">
-        <v>456</v>
-      </c>
-      <c r="C432" s="14">
-        <v>1</v>
-      </c>
-      <c r="D432" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E432" s="14"/>
-    </row>
-    <row r="433" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A433" s="16"/>
-      <c r="B433" s="30" t="s">
-        <v>457</v>
-      </c>
-      <c r="C433" s="14">
-        <v>2</v>
-      </c>
-      <c r="D433" s="14">
-        <v>2</v>
-      </c>
-      <c r="E433" s="14"/>
-    </row>
-    <row r="434" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A434" s="16"/>
-      <c r="B434" s="30" t="s">
-        <v>458</v>
-      </c>
-      <c r="C434" s="14">
-        <v>2</v>
-      </c>
-      <c r="D434" s="14">
-        <v>2</v>
-      </c>
-      <c r="E434" s="14"/>
-    </row>
-    <row r="435" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A435" s="16"/>
-      <c r="B435" s="30" t="s">
-        <v>459</v>
-      </c>
-      <c r="C435" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D435" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="E435" s="14"/>
-    </row>
-    <row r="436" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A436" s="16"/>
-      <c r="B436" s="30" t="s">
-        <v>460</v>
-      </c>
-      <c r="C436" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="D436" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="E436" s="14"/>
-    </row>
-    <row r="437" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A437" s="16"/>
-      <c r="B437" s="36" t="s">
-        <v>461</v>
-      </c>
-      <c r="C437" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D437" s="14">
-        <v>1</v>
-      </c>
-      <c r="E437" s="14"/>
-    </row>
-    <row r="438" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A438" s="16"/>
-      <c r="B438" s="8" t="s">
-        <v>485</v>
+    </row>
+    <row r="438" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B438" s="27" t="s">
+        <v>278</v>
       </c>
       <c r="C438" s="8">
         <v>1.5</v>
       </c>
-      <c r="D438" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E438" s="14"/>
-    </row>
-    <row r="439" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A439" s="16"/>
-      <c r="B439" s="8" t="s">
-        <v>486</v>
+    </row>
+    <row r="439" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B439" s="27" t="s">
+        <v>279</v>
       </c>
       <c r="C439" s="8">
         <v>1</v>
       </c>
-      <c r="D439" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="440" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B440" s="8" t="s">
-        <v>487</v>
+    </row>
+    <row r="440" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B440" s="27" t="s">
+        <v>280</v>
       </c>
       <c r="C440" s="8">
         <v>1</v>
       </c>
-      <c r="D440" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="441" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A441" s="35" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="442" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B442" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C442" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="443" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B441" s="27"/>
+    </row>
+    <row r="442" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A442" s="34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B443" s="27" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="C443" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A444" s="25" t="s">
-        <v>434</v>
-      </c>
+    <row r="444" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B444" s="27" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="C444" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B445" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C445" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B446" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="C446" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B447" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C447" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B448" s="27"/>
+      <c r="D448" s="14"/>
+    </row>
+    <row r="449" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A449" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="B449" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="C449" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D449" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A450" s="16"/>
+      <c r="B450" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="C450" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D450" s="14">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A451" s="16"/>
+      <c r="B451" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="C451" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="D451" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A452" s="16"/>
+      <c r="B452" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="C452" s="14">
+        <v>1</v>
+      </c>
+      <c r="D452" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A453" s="16"/>
+      <c r="B453" s="30" t="s">
+        <v>426</v>
+      </c>
+      <c r="C453" s="14">
+        <v>2</v>
+      </c>
+      <c r="D453" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A454" s="16"/>
+      <c r="B454" s="30" t="s">
+        <v>458</v>
+      </c>
+      <c r="C454" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D454" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A455" s="16"/>
+      <c r="B455" s="30" t="s">
+        <v>427</v>
+      </c>
+      <c r="C455" s="14">
+        <v>1</v>
+      </c>
+      <c r="D455" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A456" s="16"/>
+      <c r="B456" s="30" t="s">
+        <v>428</v>
+      </c>
+      <c r="C456" s="14">
+        <v>2</v>
+      </c>
+      <c r="D456" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A457" s="16"/>
+      <c r="B457" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="C457" s="14">
+        <v>2</v>
+      </c>
+      <c r="D457" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A458" s="16"/>
+      <c r="B458" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="C458" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D458" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A459" s="16"/>
+      <c r="B459" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="C459" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="D459" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A460" s="16"/>
+      <c r="B460" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="C460" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D460" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A461" s="16"/>
+      <c r="B461" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="C461" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D461" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A462" s="16"/>
+      <c r="B462" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C462" s="8">
+        <v>1</v>
+      </c>
+      <c r="D462" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B463" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="C463" s="8">
+        <v>1</v>
+      </c>
+      <c r="D463" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A464" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B465" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C465" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B466" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="C466" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A467" s="25" t="s">
+        <v>421</v>
+      </c>
+      <c r="B467" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="C467" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B468" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="C468" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B469" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="C469" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B470" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="C470" s="8">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B471" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C471" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B472" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C472" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B473" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C473" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B474" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C474" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B475" s="27"/>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B476" s="27"/>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B477" s="27"/>
+    </row>
+    <row r="478" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A478" s="34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B479" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C479" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B480" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C480" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B481" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C481" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B482" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C482" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="B483" s="27" t="s">
         <v>300</v>
       </c>
-      <c r="C445" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="446" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B446" s="27" t="s">
+      <c r="C483" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B484" s="27" t="s">
         <v>301</v>
       </c>
-      <c r="C446" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="447" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B447" s="27" t="s">
+      <c r="C484" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B485" s="27" t="s">
         <v>302</v>
       </c>
-      <c r="C447" s="8">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="448" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="B448" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="C448" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B449" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="C449" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B450" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="C450" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B451" s="27" t="s">
-        <v>306</v>
-      </c>
-      <c r="C451" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B452" s="27"/>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B453" s="27"/>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B454" s="27"/>
-    </row>
-    <row r="455" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A455" s="35" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B456" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="C456" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B457" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="C457" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B458" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="C458" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B459" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="C459" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B460" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="C460" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B461" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C461" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B462" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="C462" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B463" s="27"/>
-    </row>
-    <row r="464" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A464" s="25" t="s">
-        <v>434</v>
+      <c r="C485" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B486" s="27"/>
+    </row>
+    <row r="487" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A487" s="25" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0422E04-F5C0-8F43-9F81-18EFF0447C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F59955-2D88-2C43-9BCD-1E06AEA35B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1921,7 +1921,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2091,12 +2091,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3508,7 +3502,7 @@
     <col min="5" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>87</v>
       </c>
@@ -6078,7 +6072,9 @@
       <c r="C257" s="14">
         <v>0.8</v>
       </c>
-      <c r="D257" s="14"/>
+      <c r="D257" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="258" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="16"/>
@@ -6088,7 +6084,9 @@
       <c r="C258" s="14">
         <v>1.2</v>
       </c>
-      <c r="D258" s="14"/>
+      <c r="D258" s="14">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="259" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="16"/>
@@ -6098,7 +6096,9 @@
       <c r="C259" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D259" s="14"/>
+      <c r="D259" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="260" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="16"/>
@@ -6108,7 +6108,9 @@
       <c r="C260" s="14">
         <v>1.3</v>
       </c>
-      <c r="D260" s="14"/>
+      <c r="D260" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="261" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A261" s="16"/>
@@ -6118,7 +6120,9 @@
       <c r="C261" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D261" s="14"/>
+      <c r="D261" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="262" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A262" s="16" t="s">
@@ -6130,7 +6134,9 @@
       <c r="C262" s="14">
         <v>0.9</v>
       </c>
-      <c r="D262" s="14"/>
+      <c r="D262" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="263" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A263" s="16"/>
@@ -6140,7 +6146,9 @@
       <c r="C263" s="14">
         <v>1</v>
       </c>
-      <c r="D263" s="14"/>
+      <c r="D263" s="14">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="264" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="16"/>
@@ -6208,17 +6216,17 @@
       <c r="C270" s="14"/>
       <c r="D270" s="14"/>
     </row>
-    <row r="271" spans="1:4" s="60" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A271" s="31" t="s">
         <v>331</v>
       </c>
       <c r="B271" s="30" t="s">
         <v>403</v>
       </c>
-      <c r="C271" s="59">
-        <v>1.5</v>
-      </c>
-      <c r="D271" s="59">
+      <c r="C271" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="D271" s="14">
         <v>1</v>
       </c>
     </row>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F59955-2D88-2C43-9BCD-1E06AEA35B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73490325-26C4-DD49-B8D6-3A8AB4C92D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="566">
   <si>
     <t>User story</t>
   </si>
@@ -276,12 +276,6 @@
     <t>RF20 — API de servicio (FastAPI) — opcional</t>
   </si>
   <si>
-    <t>[Opcional] Exponer endpoints para ejecutar runs, listar tests y hacer drilldown sin ejecutar SQL libre.</t>
-  </si>
-  <si>
-    <t>Existe un servicio FastAPI con endpoints: /health, /tests, /run, /runs/{id}/report, /runs/{id}/drilldown. Solo acepta test_ids allowlist y devuelve artefactos del run.</t>
-  </si>
-  <si>
     <t>Could</t>
   </si>
   <si>
@@ -892,36 +886,6 @@
   </si>
   <si>
     <t>AG02-05: Ejecutar verificación de criterios de aceptación y guardar evidencia (logs/reportes)</t>
-  </si>
-  <si>
-    <t>RF20-01: Definir contrato de API: endpoints, request/response schemas (OpenAPI) y límites</t>
-  </si>
-  <si>
-    <t>RF20-02: Implementar FastAPI app con /health y configuración (puerto, paths)</t>
-  </si>
-  <si>
-    <t>RF20-03: Implementar endpoint GET /tests que devuelva catálogo (ids, versiones, fraud_type)</t>
-  </si>
-  <si>
-    <t>RF20-04: Implementar endpoint POST /run que dispare un run (sincrónico o background simple) y devuelva run_id</t>
-  </si>
-  <si>
-    <t>RF20-05: Implementar endpoint GET /runs/{run_id}/report que devuelva report.json</t>
-  </si>
-  <si>
-    <t>RF20-06: Implementar endpoint POST /runs/{run_id}/drilldown que ejecute drilldown seguro (test_id + keys)</t>
-  </si>
-  <si>
-    <t>RF20-07: Aplicar guardrails: solo test_ids allowlist; validar inputs; limitar tamaños de respuesta</t>
-  </si>
-  <si>
-    <t>RF20-08: Añadir tests (pytest) de API usando TestClient y fixture de run</t>
-  </si>
-  <si>
-    <t>RF20-09: Documentar uso de API y ejemplos curl</t>
-  </si>
-  <si>
-    <t>RF20-10: Verificar criterios de aceptación y guardar evidencia (capturas/logs)</t>
   </si>
   <si>
     <t>RF21-01: Escribir docs/rag_extension.md: objetivo, no-objetivos, arquitectura, riesgos de alucinación, guardrails</t>
@@ -1736,6 +1700,54 @@
     S3 + logs en CloudWatch + trazas en LangSmith. El mismo despliegue soporta PROCESS_SCOPE=p2p, o2c y both sin duplicar
     infraestructura. Un trigger (S3/EventBridge+Lambda) relanza el pipeline solo si artifact_hash cambia (actualiza last_hash
     en S3). Documentación paso a paso (docs/cloud_aws.md) + runbook de troubleshooting.</t>
+  </si>
+  <si>
+    <t>RF20 — Capa de aplicación para carga de ERP y ejecución de análisis de fraude</t>
+  </si>
+  <si>
+    <t>[Aplicación] Construir una capa de aplicación con FastAPI como backend y Streamlit como interfaz operativa para que un usuario pueda cargar un dataset ERP controlado, lanzar runs cloud (P2P/O2C/both), monitorizar su estado y visualizar resultados multiagente sin usar CLI ni AWS directamente.</t>
+  </si>
+  <si>
+    <t>Existe una aplicación FastAPI + Streamlit que permite cargar un dataset ERP válido (ZIP controlado) o seleccionar uno disponible, lanzar análisis cloud en modo graph para P2P, O2C o both (both orquesta dos runs separados), consultar estado y resultados, y visualizar hypotheses, selected_tests, findings, scores, explanations y second_level_analysis, además de drilldown controlado. No expone SQL libre ni acceso directo a AWS.</t>
+  </si>
+  <si>
+    <t>RF20-01: Redefinir contrato funcional de la capa de aplicación y UX mínima: flujo de carga ERP, lanzamiento de run, monitorización, resultados y drilldown</t>
+  </si>
+  <si>
+    <t>RF20-02: Modelar schemas de API (Pydantic/OpenAPI) para datasets, runs, estado, resultados y drilldown; definir soporte para scope=p2p|o2c|both y kb_index_enabled</t>
+  </si>
+  <si>
+    <t>RF20-03: Implementar/ajustar endpoints FastAPI para alta/listado de datasets y validación de ZIP controlado</t>
+  </si>
+  <si>
+    <t>RF20-04: Implementar/ajustar endpoint POST /runs para lanzar análisis cloud en modo graph; both debe orquestar dos runs separados (p2p y o2c)</t>
+  </si>
+  <si>
+    <t>RF20-05: Implementar endpoints de consulta de runs, estado, report y resumen de artefactos graph (hypotheses, selected_tests, findings, scores)</t>
+  </si>
+  <si>
+    <t>RF20-06: Implementar endpoint de drilldown seguro sin SQL libre, con allowlist de acciones y validación de payload</t>
+  </si>
+  <si>
+    <t>RF20-07: Crear la app Streamlit base con navegación multipágina, tema visual cuidado, layout profesional y componentes reutilizables</t>
+  </si>
+  <si>
+    <t>RF20-08: Diseñar la página 'Nuevo análisis' para subir dataset, elegir scope (p2p/o2c/both), activar opcionalmente rebuild KB y lanzar ejecución</t>
+  </si>
+  <si>
+    <t>RF20-09: Diseñar la página 'Ejecuciones' para listar runs, ver estado, timestamps, scope y acceder a detalle/resultados</t>
+  </si>
+  <si>
+    <t>RF20-10: Diseñar la página 'Resultados' para mostrar hypotheses, selected_tests, findings, scores, explanations y second_level_analysis de forma clara y usable</t>
+  </si>
+  <si>
+    <t>RF20-11: Diseñar la página 'Detalle / drilldown' para navegar por un hallazgo concreto y ver evidencia, explicación y recomendaciones</t>
+  </si>
+  <si>
+    <t>RF20-12: Añadir tests de API e integración del flujo principal (upload/selección dataset -&gt; run -&gt; estado -&gt; resultados -&gt; drilldown) y documentarlos en integration_tests_registry.md</t>
+  </si>
+  <si>
+    <t>RF20-13: Actualizar README/runbook/docs, verificar criterios de aceptación y guardar evidencias visuales y técnicas del flujo completo</t>
   </si>
 </sst>
 </file>
@@ -1921,7 +1933,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2093,11 +2105,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2417,7 +2505,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G1" s="39" t="s">
         <v>5</v>
@@ -2431,13 +2519,13 @@
     </row>
     <row r="2" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -2453,13 +2541,13 @@
     </row>
     <row r="3" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -2497,7 +2585,7 @@
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2524,7 +2612,7 @@
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2551,7 +2639,7 @@
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2578,7 +2666,7 @@
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2605,7 +2693,7 @@
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2632,7 +2720,7 @@
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2659,7 +2747,7 @@
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2686,7 +2774,7 @@
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2713,7 +2801,7 @@
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2763,7 +2851,7 @@
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.2">
@@ -2779,13 +2867,13 @@
     </row>
     <row r="16" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A16" s="43" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="D16" s="5">
         <v>21</v>
@@ -2808,13 +2896,13 @@
         <v>47</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="D17" s="5">
         <v>8</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>75</v>
@@ -2831,7 +2919,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="D18" s="5">
         <v>13</v>
@@ -2847,18 +2935,18 @@
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
@@ -2874,18 +2962,18 @@
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="22" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="D20" s="14">
         <v>8</v>
@@ -2901,18 +2989,18 @@
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="45" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="D21" s="14">
         <v>18</v>
@@ -2929,13 +3017,13 @@
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D22" s="14">
         <v>8</v>
@@ -2951,18 +3039,18 @@
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="22" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
@@ -2978,18 +3066,18 @@
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D24" s="14">
         <v>13</v>
@@ -3005,18 +3093,18 @@
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="22" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D25" s="14">
         <v>10</v>
@@ -3032,18 +3120,18 @@
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="85" x14ac:dyDescent="0.2">
       <c r="A26" s="43" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D26" s="5">
         <v>10</v>
@@ -3060,13 +3148,13 @@
     </row>
     <row r="27" spans="1:9" ht="85" x14ac:dyDescent="0.2">
       <c r="A27" s="43" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="D27" s="5">
         <v>12</v>
@@ -3106,13 +3194,13 @@
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="22" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D29" s="14">
         <v>13</v>
@@ -3128,7 +3216,7 @@
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="19" x14ac:dyDescent="0.2">
@@ -3317,13 +3405,13 @@
     </row>
     <row r="38" spans="1:9" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="28" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="D38" s="14">
         <v>5</v>
@@ -3339,24 +3427,24 @@
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A39" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>81</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+      <c r="A39" s="59" t="s">
+        <v>550</v>
+      </c>
+      <c r="B39" s="60" t="s">
+        <v>551</v>
+      </c>
+      <c r="C39" s="60" t="s">
+        <v>552</v>
       </c>
       <c r="D39" s="5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>16</v>
@@ -3367,19 +3455,19 @@
     </row>
     <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="D40" s="5">
         <v>5</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>75</v>
@@ -3396,30 +3484,30 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="50" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="B44" s="9"/>
     </row>
     <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="51" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="52" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B46" s="2"/>
     </row>
     <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="53" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="B47" s="2"/>
     </row>
@@ -3436,63 +3524,166 @@
       <c r="B51" s="9"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="Won't">
+  <conditionalFormatting sqref="E1:E38 E40:E1048576">
+    <cfRule type="containsText" dxfId="18" priority="15" operator="containsText" text="Won't">
       <formula>NOT(ISERROR(SEARCH("Won't",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Could">
+    <cfRule type="containsText" dxfId="17" priority="16" operator="containsText" text="Could">
       <formula>NOT(ISERROR(SEARCH("Could",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="Should">
+    <cfRule type="containsText" dxfId="16" priority="17" operator="containsText" text="Should">
       <formula>NOT(ISERROR(SEARCH("Should",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="Must">
+    <cfRule type="containsText" dxfId="15" priority="18" operator="containsText" text="Must">
       <formula>NOT(ISERROR(SEARCH("Must",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="Bajo">
+  <conditionalFormatting sqref="F1:F38 F40:F1048576">
+    <cfRule type="containsText" dxfId="14" priority="19" operator="containsText" text="Bajo">
       <formula>NOT(ISERROR(SEARCH("Bajo",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="Medio">
+    <cfRule type="containsText" dxfId="13" priority="20" operator="containsText" text="Medio">
       <formula>NOT(ISERROR(SEARCH("Medio",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="14" operator="containsText" text="Alto">
+    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="Alto">
       <formula>NOT(ISERROR(SEARCH("Alto",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18:I20">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:I25">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="10" priority="10" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:I29">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:I38">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I17 I39:I1048576">
-    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{F603C862-5BFF-AA4F-A3F0-AFDA4F6D8639}">
+            <xm:f>NOT(ISERROR(SEARCH("Won't",E39)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{6925889A-7A76-5047-BA15-9041DDE9A394}">
+            <xm:f>NOT(ISERROR(SEARCH("Could",E39)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{FFAE8A3E-5305-F74B-A1C9-6BDD0E78503E}">
+            <xm:f>NOT(ISERROR(SEARCH("Should",E39)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{AE048A56-DCAB-A442-A3C5-BE50CE6EC692}">
+            <xm:f>NOT(ISERROR(SEARCH("Must",E39)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E39</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{6DCEA9A2-72AD-3C45-A6E4-76187190F144}">
+            <xm:f>NOT(ISERROR(SEARCH("Bajo",F39)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{89451CA2-693D-5D44-90D6-5C93F5286255}">
+            <xm:f>NOT(ISERROR(SEARCH("Medio",F39)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{A9951BA2-58D1-BB48-8DDD-F6D56CF5196C}">
+            <xm:f>NOT(ISERROR(SEARCH("Alto",F39)))</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>F39</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:D487"/>
+  <dimension ref="A2:D486"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.33203125" style="25" bestFit="1" customWidth="1"/>
@@ -3504,24 +3695,24 @@
   <sheetData>
     <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="D2" s="33" t="s">
         <v>88</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C3" s="14">
         <v>0.6</v>
@@ -3531,7 +3722,7 @@
     <row r="4" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="30" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C4" s="14">
         <v>0.8</v>
@@ -3541,7 +3732,7 @@
     <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
       <c r="B5" s="30" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C5" s="14">
         <v>0.8</v>
@@ -3551,7 +3742,7 @@
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
       <c r="B6" s="30" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C6" s="14">
         <v>0.8</v>
@@ -3561,7 +3752,7 @@
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
       <c r="B7" s="30" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C7" s="14">
         <v>0.5</v>
@@ -3571,7 +3762,7 @@
     <row r="8" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
       <c r="B8" s="30" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C8" s="14">
         <v>0.5</v>
@@ -3580,10 +3771,10 @@
     </row>
     <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C9" s="14">
         <v>1</v>
@@ -3593,7 +3784,7 @@
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="16"/>
       <c r="B10" s="30" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C10" s="14">
         <v>1</v>
@@ -3603,7 +3794,7 @@
     <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="30" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C11" s="14">
         <v>1</v>
@@ -3613,7 +3804,7 @@
     <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="16"/>
       <c r="B12" s="30" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C12" s="14">
         <v>1</v>
@@ -3623,7 +3814,7 @@
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="16"/>
       <c r="B13" s="30" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="C13" s="14">
         <v>1</v>
@@ -3633,7 +3824,7 @@
     <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="16"/>
       <c r="B14" s="30" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C14" s="14">
         <v>1.2</v>
@@ -3643,7 +3834,7 @@
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="30" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C15" s="14">
         <v>0.6</v>
@@ -3657,7 +3848,7 @@
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B18" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" s="8">
         <v>0.5</v>
@@ -3668,7 +3859,7 @@
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B19" s="27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C19" s="8">
         <v>0.5</v>
@@ -3679,7 +3870,7 @@
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B20" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C20" s="8">
         <v>1</v>
@@ -3690,7 +3881,7 @@
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C21" s="8">
         <v>1</v>
@@ -3701,7 +3892,7 @@
     </row>
     <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B22" s="27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C22" s="8">
         <v>1.5</v>
@@ -3712,7 +3903,7 @@
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B23" s="27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C23" s="8">
         <v>2</v>
@@ -3723,7 +3914,7 @@
     </row>
     <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B24" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C24" s="8">
         <v>1</v>
@@ -3734,7 +3925,7 @@
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C25" s="8">
         <v>0.7</v>
@@ -3745,7 +3936,7 @@
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B26" s="27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C26" s="8">
         <v>1.2</v>
@@ -3756,7 +3947,7 @@
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B27" s="27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" s="8">
         <v>0.8</v>
@@ -3767,7 +3958,7 @@
     </row>
     <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B28" s="27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C28" s="8">
         <v>1.5</v>
@@ -3778,7 +3969,7 @@
     </row>
     <row r="29" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C29" s="8">
         <v>1.5</v>
@@ -3789,7 +3980,7 @@
     </row>
     <row r="30" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="27" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C30" s="8">
         <v>1.2</v>
@@ -3800,7 +3991,7 @@
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B31" s="27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C31" s="8">
         <v>1.2</v>
@@ -3811,7 +4002,7 @@
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B32" s="27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C32" s="8">
         <v>1.2</v>
@@ -3822,7 +4013,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B33" s="37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C33" s="8">
         <v>1.5</v>
@@ -3833,7 +4024,7 @@
     </row>
     <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B34" s="27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C34" s="8">
         <v>1</v>
@@ -3844,7 +4035,7 @@
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B35" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C35" s="8">
         <v>1</v>
@@ -3863,7 +4054,7 @@
     </row>
     <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B38" s="27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C38" s="8">
         <v>0.8</v>
@@ -3874,7 +4065,7 @@
     </row>
     <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B39" s="27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C39" s="8">
         <v>1</v>
@@ -3885,7 +4076,7 @@
     </row>
     <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B40" s="27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C40" s="8">
         <v>1</v>
@@ -3896,7 +4087,7 @@
     </row>
     <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B41" s="27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C41" s="8">
         <v>0.7</v>
@@ -3907,7 +4098,7 @@
     </row>
     <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B42" s="27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42" s="8">
         <v>1</v>
@@ -3918,7 +4109,7 @@
     </row>
     <row r="43" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B43" s="27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C43" s="8">
         <v>1.2</v>
@@ -3929,7 +4120,7 @@
     </row>
     <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C44" s="8">
         <v>0.8</v>
@@ -3940,7 +4131,7 @@
     </row>
     <row r="45" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B45" s="27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C45" s="8">
         <v>1.5</v>
@@ -3951,7 +4142,7 @@
     </row>
     <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B46" s="27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C46" s="8">
         <v>1.5</v>
@@ -3962,7 +4153,7 @@
     </row>
     <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B47" s="27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C47" s="8">
         <v>1</v>
@@ -3973,7 +4164,7 @@
     </row>
     <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B48" s="27" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C48" s="8">
         <v>1</v>
@@ -3992,7 +4183,7 @@
     </row>
     <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B51" s="27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C51" s="8">
         <v>0.8</v>
@@ -4003,7 +4194,7 @@
     </row>
     <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B52" s="27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C52" s="8">
         <v>0.8</v>
@@ -4014,7 +4205,7 @@
     </row>
     <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B53" s="27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C53" s="8">
         <v>0.8</v>
@@ -4025,7 +4216,7 @@
     </row>
     <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B54" s="27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C54" s="8">
         <v>1.2</v>
@@ -4036,7 +4227,7 @@
     </row>
     <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C55" s="8">
         <v>1</v>
@@ -4047,7 +4238,7 @@
     </row>
     <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C56" s="8">
         <v>1</v>
@@ -4058,7 +4249,7 @@
     </row>
     <row r="57" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B57" s="27" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C57" s="8">
         <v>1</v>
@@ -4069,7 +4260,7 @@
     </row>
     <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B58" s="27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C58" s="8">
         <v>1.2</v>
@@ -4080,7 +4271,7 @@
     </row>
     <row r="59" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B59" s="27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C59" s="8">
         <v>0.7</v>
@@ -4091,7 +4282,7 @@
     </row>
     <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B60" s="27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C60" s="8">
         <v>1.5</v>
@@ -4102,7 +4293,7 @@
     </row>
     <row r="61" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B61" s="27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C61" s="8">
         <v>1</v>
@@ -4113,7 +4304,7 @@
     </row>
     <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B62" s="27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C62" s="8">
         <v>1</v>
@@ -4132,7 +4323,7 @@
     </row>
     <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B65" s="27" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C65" s="8">
         <v>1</v>
@@ -4143,7 +4334,7 @@
     </row>
     <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B66" s="27" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C66" s="8">
         <v>0.8</v>
@@ -4154,7 +4345,7 @@
     </row>
     <row r="67" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B67" s="27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C67" s="8">
         <v>1.2</v>
@@ -4165,7 +4356,7 @@
     </row>
     <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B68" s="27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C68" s="8">
         <v>1</v>
@@ -4176,7 +4367,7 @@
     </row>
     <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B69" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C69" s="8">
         <v>2</v>
@@ -4187,7 +4378,7 @@
     </row>
     <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B70" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C70" s="8">
         <v>2</v>
@@ -4198,7 +4389,7 @@
     </row>
     <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B71" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C71" s="8">
         <v>0.8</v>
@@ -4209,7 +4400,7 @@
     </row>
     <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B72" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C72" s="8">
         <v>0.8</v>
@@ -4220,7 +4411,7 @@
     </row>
     <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B73" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C73" s="8">
         <v>1.5</v>
@@ -4231,7 +4422,7 @@
     </row>
     <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B74" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C74" s="8">
         <v>1</v>
@@ -4242,7 +4433,7 @@
     </row>
     <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B75" s="27" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C75" s="8">
         <v>1</v>
@@ -4254,7 +4445,7 @@
     <row r="76" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A76" s="8"/>
       <c r="B76" s="26" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="C76" s="8">
         <v>0.8</v>
@@ -4273,7 +4464,7 @@
     </row>
     <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B79" s="27" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C79" s="8">
         <v>1.2</v>
@@ -4284,7 +4475,7 @@
     </row>
     <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B80" s="27" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C80" s="8">
         <v>0.8</v>
@@ -4295,7 +4486,7 @@
     </row>
     <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B81" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C81" s="8">
         <v>0.8</v>
@@ -4306,7 +4497,7 @@
     </row>
     <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B82" s="27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C82" s="8">
         <v>1</v>
@@ -4317,7 +4508,7 @@
     </row>
     <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B83" s="27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C83" s="8">
         <v>1.5</v>
@@ -4328,7 +4519,7 @@
     </row>
     <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B84" s="27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C84" s="8">
         <v>1</v>
@@ -4339,7 +4530,7 @@
     </row>
     <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B85" s="27" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C85" s="8">
         <v>0.8</v>
@@ -4350,7 +4541,7 @@
     </row>
     <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B86" s="27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C86" s="8">
         <v>1.5</v>
@@ -4361,7 +4552,7 @@
     </row>
     <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B87" s="27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C87" s="8">
         <v>1</v>
@@ -4372,7 +4563,7 @@
     </row>
     <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B88" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C88" s="8">
         <v>1</v>
@@ -4391,7 +4582,7 @@
     </row>
     <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B91" s="27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C91" s="8">
         <v>1</v>
@@ -4402,7 +4593,7 @@
     </row>
     <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B92" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C92" s="8">
         <v>1.2</v>
@@ -4413,7 +4604,7 @@
     </row>
     <row r="93" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B93" s="27" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C93" s="8">
         <v>0.8</v>
@@ -4424,7 +4615,7 @@
     </row>
     <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B94" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C94" s="8">
         <v>1</v>
@@ -4435,7 +4626,7 @@
     </row>
     <row r="95" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B95" s="27" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C95" s="8">
         <v>1</v>
@@ -4446,7 +4637,7 @@
     </row>
     <row r="96" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B96" s="27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C96" s="8">
         <v>0.8</v>
@@ -4457,7 +4648,7 @@
     </row>
     <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B97" s="27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C97" s="8">
         <v>1.5</v>
@@ -4468,7 +4659,7 @@
     </row>
     <row r="98" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B98" s="27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C98" s="8">
         <v>1</v>
@@ -4479,7 +4670,7 @@
     </row>
     <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B99" s="27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C99" s="8">
         <v>1</v>
@@ -4498,7 +4689,7 @@
     </row>
     <row r="102" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B102" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C102" s="8">
         <v>1</v>
@@ -4509,7 +4700,7 @@
     </row>
     <row r="103" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B103" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C103" s="8">
         <v>1.2</v>
@@ -4520,7 +4711,7 @@
     </row>
     <row r="104" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B104" s="27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C104" s="8">
         <v>1.5</v>
@@ -4531,7 +4722,7 @@
     </row>
     <row r="105" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B105" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C105" s="8">
         <v>0.8</v>
@@ -4542,7 +4733,7 @@
     </row>
     <row r="106" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B106" s="27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C106" s="8">
         <v>1.2</v>
@@ -4553,7 +4744,7 @@
     </row>
     <row r="107" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B107" s="27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C107" s="8">
         <v>0.7</v>
@@ -4564,7 +4755,7 @@
     </row>
     <row r="108" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B108" s="27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C108" s="8">
         <v>1.5</v>
@@ -4575,7 +4766,7 @@
     </row>
     <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B109" s="27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C109" s="8">
         <v>1.5</v>
@@ -4586,7 +4777,7 @@
     </row>
     <row r="110" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B110" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C110" s="8">
         <v>1</v>
@@ -4597,7 +4788,7 @@
     </row>
     <row r="111" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B111" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C111" s="8">
         <v>1</v>
@@ -4616,7 +4807,7 @@
     </row>
     <row r="114" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B114" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C114" s="8">
         <v>0.8</v>
@@ -4627,7 +4818,7 @@
     </row>
     <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B115" s="27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C115" s="8">
         <v>1.2</v>
@@ -4638,7 +4829,7 @@
     </row>
     <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B116" s="27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C116" s="8">
         <v>1.2</v>
@@ -4649,7 +4840,7 @@
     </row>
     <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B117" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C117" s="8">
         <v>1</v>
@@ -4660,7 +4851,7 @@
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B118" s="27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C118" s="8">
         <v>0.6</v>
@@ -4671,7 +4862,7 @@
     </row>
     <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B119" s="27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C119" s="8">
         <v>1.2</v>
@@ -4682,7 +4873,7 @@
     </row>
     <row r="120" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B120" s="27" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C120" s="8">
         <v>1</v>
@@ -4693,7 +4884,7 @@
     </row>
     <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B121" s="27" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C121" s="8">
         <v>1</v>
@@ -4712,7 +4903,7 @@
     </row>
     <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B124" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C124" s="8">
         <v>1</v>
@@ -4723,7 +4914,7 @@
     </row>
     <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B125" s="27" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C125" s="8">
         <v>1.2</v>
@@ -4734,7 +4925,7 @@
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B126" s="27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C126" s="8">
         <v>1.2</v>
@@ -4745,7 +4936,7 @@
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B127" s="27" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C127" s="8">
         <v>1</v>
@@ -4756,7 +4947,7 @@
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B128" s="27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C128" s="8">
         <v>0.8</v>
@@ -4767,7 +4958,7 @@
     </row>
     <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B129" s="27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C129" s="8">
         <v>0.8</v>
@@ -4778,7 +4969,7 @@
     </row>
     <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B130" s="27" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C130" s="8">
         <v>0.8</v>
@@ -4789,7 +4980,7 @@
     </row>
     <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B131" s="27" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C131" s="8">
         <v>1.5</v>
@@ -4800,7 +4991,7 @@
     </row>
     <row r="132" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B132" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C132" s="8">
         <v>1</v>
@@ -4811,7 +5002,7 @@
     </row>
     <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B133" s="27" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C133" s="8">
         <v>1</v>
@@ -4830,7 +5021,7 @@
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B136" s="27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C136" s="8">
         <v>1.5</v>
@@ -4838,7 +5029,7 @@
     </row>
     <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B137" s="27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C137" s="8">
         <v>0.8</v>
@@ -4846,7 +5037,7 @@
     </row>
     <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B138" s="27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C138" s="8">
         <v>1.5</v>
@@ -4854,7 +5045,7 @@
     </row>
     <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B139" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C139" s="8">
         <v>1.2</v>
@@ -4862,7 +5053,7 @@
     </row>
     <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B140" s="27" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C140" s="8">
         <v>2</v>
@@ -4870,7 +5061,7 @@
     </row>
     <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B141" s="27" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C141" s="8">
         <v>1.5</v>
@@ -4878,7 +5069,7 @@
     </row>
     <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B142" s="27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C142" s="8">
         <v>1</v>
@@ -4886,7 +5077,7 @@
     </row>
     <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B143" s="27" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C143" s="8">
         <v>1</v>
@@ -4894,7 +5085,7 @@
     </row>
     <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C144" s="8">
         <v>1.5</v>
@@ -4902,7 +5093,7 @@
     </row>
     <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B145" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C145" s="8">
         <v>1</v>
@@ -4918,7 +5109,7 @@
     </row>
     <row r="148" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B148" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C148" s="8">
         <v>2</v>
@@ -4929,7 +5120,7 @@
     </row>
     <row r="149" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B149" s="27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C149" s="8">
         <v>1.2</v>
@@ -4940,7 +5131,7 @@
     </row>
     <row r="150" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B150" s="27" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C150" s="8">
         <v>1</v>
@@ -4951,7 +5142,7 @@
     </row>
     <row r="151" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B151" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C151" s="8">
         <v>1.5</v>
@@ -4962,7 +5153,7 @@
     </row>
     <row r="152" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B152" s="27" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C152" s="8">
         <v>0.8</v>
@@ -4973,7 +5164,7 @@
     </row>
     <row r="153" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B153" s="27" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C153" s="8">
         <v>1.5</v>
@@ -4984,7 +5175,7 @@
     </row>
     <row r="154" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B154" s="27" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C154" s="8">
         <v>1</v>
@@ -4995,7 +5186,7 @@
     </row>
     <row r="155" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B155" s="27" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C155" s="8">
         <v>1</v>
@@ -5014,7 +5205,7 @@
     </row>
     <row r="158" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B158" s="27" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C158" s="8">
         <v>1</v>
@@ -5025,7 +5216,7 @@
     </row>
     <row r="159" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B159" s="27" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C159" s="8">
         <v>1.5</v>
@@ -5036,7 +5227,7 @@
     </row>
     <row r="160" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B160" s="27" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="C160" s="8">
         <v>2</v>
@@ -5047,7 +5238,7 @@
     </row>
     <row r="161" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B161" s="27" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C161" s="8">
         <v>1.2</v>
@@ -5058,7 +5249,7 @@
     </row>
     <row r="162" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B162" s="27" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C162" s="8">
         <v>3</v>
@@ -5069,7 +5260,7 @@
     </row>
     <row r="163" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B163" s="27" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="C163" s="8">
         <v>2</v>
@@ -5080,7 +5271,7 @@
     </row>
     <row r="164" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B164" s="27" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C164" s="8">
         <v>1.2</v>
@@ -5091,7 +5282,7 @@
     </row>
     <row r="165" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B165" s="27" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C165" s="8">
         <v>2</v>
@@ -5102,7 +5293,7 @@
     </row>
     <row r="166" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B166" s="27" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="C166" s="8">
         <v>1.8</v>
@@ -5113,7 +5304,7 @@
     </row>
     <row r="167" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B167" s="27" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="C167" s="8">
         <v>1.5</v>
@@ -5124,7 +5315,7 @@
     </row>
     <row r="168" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B168" s="27" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C168" s="8">
         <v>1.5</v>
@@ -5135,7 +5326,7 @@
     </row>
     <row r="169" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B169" s="27" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="C169" s="8">
         <v>1</v>
@@ -5146,7 +5337,7 @@
     </row>
     <row r="170" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B170" s="27" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C170" s="8">
         <v>2.5</v>
@@ -5157,7 +5348,7 @@
     </row>
     <row r="171" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B171" s="27" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C171" s="8">
         <v>1.5</v>
@@ -5168,7 +5359,7 @@
     </row>
     <row r="172" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B172" s="27" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C172" s="8">
         <v>1.5</v>
@@ -5179,7 +5370,7 @@
     </row>
     <row r="173" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B173" s="35" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C173" s="8">
         <v>1.5</v>
@@ -5198,42 +5389,42 @@
     </row>
     <row r="176" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B176" s="27" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B177" s="27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B178" s="27" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B179" s="27" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B180" s="27" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B181" s="27" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B182" s="27" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B183" s="27" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
@@ -5246,7 +5437,7 @@
     </row>
     <row r="186" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B186" s="27" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C186" s="8">
         <v>1.5</v>
@@ -5257,7 +5448,7 @@
     </row>
     <row r="187" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B187" s="27" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C187" s="8">
         <v>0.6</v>
@@ -5268,7 +5459,7 @@
     </row>
     <row r="188" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B188" s="27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C188" s="8">
         <v>1.2</v>
@@ -5279,7 +5470,7 @@
     </row>
     <row r="189" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B189" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C189" s="8">
         <v>0.6</v>
@@ -5290,7 +5481,7 @@
     </row>
     <row r="190" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B190" s="27" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C190" s="8">
         <v>1.2</v>
@@ -5301,7 +5492,7 @@
     </row>
     <row r="191" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B191" s="27" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C191" s="8">
         <v>2</v>
@@ -5312,7 +5503,7 @@
     </row>
     <row r="192" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B192" s="27" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C192" s="8">
         <v>1.5</v>
@@ -5320,7 +5511,7 @@
     </row>
     <row r="193" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B193" s="27" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C193" s="8">
         <v>1</v>
@@ -5331,7 +5522,7 @@
     </row>
     <row r="194" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B194" s="27" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C194" s="8">
         <v>1</v>
@@ -5343,7 +5534,7 @@
     <row r="195" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A195" s="14"/>
       <c r="B195" s="27" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C195" s="14">
         <v>1</v>
@@ -5355,7 +5546,7 @@
     <row r="196" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A196" s="14"/>
       <c r="B196" s="27" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C196" s="14">
         <v>1</v>
@@ -5367,7 +5558,7 @@
     <row r="197" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A197" s="14"/>
       <c r="B197" s="27" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="C197" s="14">
         <v>1.2</v>
@@ -5379,7 +5570,7 @@
     <row r="198" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A198" s="14"/>
       <c r="B198" s="27" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C198" s="14">
         <v>1.2</v>
@@ -5391,7 +5582,7 @@
     <row r="199" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A199" s="14"/>
       <c r="B199" s="27" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C199" s="14">
         <v>1</v>
@@ -5403,7 +5594,7 @@
     <row r="200" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A200" s="14"/>
       <c r="B200" s="27" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="C200" s="14">
         <v>0.5</v>
@@ -5420,10 +5611,10 @@
     </row>
     <row r="202" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A202" s="28" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B202" s="27" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C202" s="14">
         <v>1.5</v>
@@ -5435,7 +5626,7 @@
     <row r="203" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="16"/>
       <c r="B203" s="27" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C203" s="14">
         <v>1</v>
@@ -5447,7 +5638,7 @@
     <row r="204" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="16"/>
       <c r="B204" s="27" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C204" s="14">
         <v>1</v>
@@ -5459,7 +5650,7 @@
     <row r="205" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A205" s="19"/>
       <c r="B205" s="30" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C205" s="14">
         <v>1.5</v>
@@ -5471,7 +5662,7 @@
     <row r="206" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="16"/>
       <c r="B206" s="27" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="C206" s="14">
         <v>2</v>
@@ -5482,10 +5673,10 @@
     </row>
     <row r="207" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="16" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B207" s="27" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C207" s="14">
         <v>1.5</v>
@@ -5497,7 +5688,7 @@
     <row r="208" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="16"/>
       <c r="B208" s="27" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C208" s="14">
         <v>1.5</v>
@@ -5509,7 +5700,7 @@
     <row r="209" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="16"/>
       <c r="B209" s="27" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C209" s="14">
         <v>1.5</v>
@@ -5521,7 +5712,7 @@
     <row r="210" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="16"/>
       <c r="B210" s="27" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C210" s="14">
         <v>1.5</v>
@@ -5533,7 +5724,7 @@
     <row r="211" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="16"/>
       <c r="B211" s="27" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C211" s="14">
         <v>1</v>
@@ -5545,7 +5736,7 @@
     <row r="212" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="16"/>
       <c r="B212" s="27" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C212" s="14">
         <v>2</v>
@@ -5557,7 +5748,7 @@
     <row r="213" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="16"/>
       <c r="B213" s="27" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C213" s="14">
         <v>1</v>
@@ -5569,7 +5760,7 @@
     <row r="214" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="16"/>
       <c r="B214" s="27" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C214" s="14">
         <v>2.5</v>
@@ -5581,7 +5772,7 @@
     <row r="215" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="19"/>
       <c r="B215" s="30" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C215" s="14">
         <v>1.2</v>
@@ -5593,7 +5784,7 @@
     <row r="216" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="19"/>
       <c r="B216" s="27" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="C216" s="14">
         <v>0.5</v>
@@ -5605,7 +5796,7 @@
     <row r="217" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="19"/>
       <c r="B217" s="27" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C217" s="14">
         <v>0.5</v>
@@ -5617,7 +5808,7 @@
     <row r="218" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="19"/>
       <c r="B218" s="27" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="C218" s="14">
         <v>0.5</v>
@@ -5629,7 +5820,7 @@
     <row r="219" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="19"/>
       <c r="B219" s="27" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="C219" s="14">
         <v>0.5</v>
@@ -5646,7 +5837,7 @@
     </row>
     <row r="221" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="28" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="B221" s="27"/>
       <c r="C221" s="14"/>
@@ -5655,7 +5846,7 @@
     <row r="222" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="16"/>
       <c r="B222" s="27" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -5663,7 +5854,7 @@
     <row r="223" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="16"/>
       <c r="B223" s="27" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="C223" s="14">
         <v>1.2</v>
@@ -5675,7 +5866,7 @@
     <row r="224" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="16"/>
       <c r="B224" s="27" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="C224" s="14">
         <v>1.2</v>
@@ -5687,7 +5878,7 @@
     <row r="225" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="16"/>
       <c r="B225" s="27" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="C225" s="14">
         <v>1</v>
@@ -5699,7 +5890,7 @@
     <row r="226" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="16"/>
       <c r="B226" s="27" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C226" s="14">
         <v>1</v>
@@ -5711,7 +5902,7 @@
     <row r="227" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="16"/>
       <c r="B227" s="27" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C227" s="14">
         <v>0.8</v>
@@ -5723,7 +5914,7 @@
     <row r="228" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="16"/>
       <c r="B228" s="27" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C228" s="14">
         <v>0.5</v>
@@ -5735,7 +5926,7 @@
     <row r="229" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A229" s="8"/>
       <c r="B229" s="27" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C229" s="14">
         <v>0.8</v>
@@ -5747,7 +5938,7 @@
     <row r="230" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="16"/>
       <c r="B230" s="27" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C230" s="14">
         <v>1.2</v>
@@ -5759,7 +5950,7 @@
     <row r="231" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="16"/>
       <c r="B231" s="27" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C231" s="14">
         <v>1</v>
@@ -5771,7 +5962,7 @@
     <row r="232" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="16"/>
       <c r="B232" s="27" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C232" s="14">
         <v>0.8</v>
@@ -5783,7 +5974,7 @@
     <row r="233" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="16"/>
       <c r="B233" s="27" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C233" s="14">
         <v>2.5</v>
@@ -5795,7 +5986,7 @@
     <row r="234" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="16"/>
       <c r="B234" s="27" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C234" s="14">
         <v>1.5</v>
@@ -5807,7 +5998,7 @@
     <row r="235" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="16"/>
       <c r="B235" s="27" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="C235" s="14">
         <v>1.5</v>
@@ -5819,7 +6010,7 @@
     <row r="236" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="19"/>
       <c r="B236" s="30" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="C236" s="14">
         <v>2</v>
@@ -5831,7 +6022,7 @@
     <row r="237" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="16"/>
       <c r="B237" s="27" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C237" s="14">
         <v>1.2</v>
@@ -5843,7 +6034,7 @@
     <row r="238" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="16"/>
       <c r="B238" s="27" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C238" s="14">
         <v>1</v>
@@ -5855,7 +6046,7 @@
     <row r="239" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A239" s="16"/>
       <c r="B239" s="8" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C239" s="14">
         <v>2</v>
@@ -5867,7 +6058,7 @@
     <row r="240" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A240" s="16"/>
       <c r="B240" s="8" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C240" s="14">
         <v>1</v>
@@ -5879,7 +6070,7 @@
     <row r="241" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A241" s="16"/>
       <c r="B241" s="8" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="C241" s="14">
         <v>1</v>
@@ -5896,10 +6087,10 @@
     </row>
     <row r="243" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A243" s="57" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B243" s="27" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="C243" s="14">
         <v>1.5</v>
@@ -5911,7 +6102,7 @@
     <row r="244" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A244" s="16"/>
       <c r="B244" s="27" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="C244" s="14">
         <v>0.8</v>
@@ -5923,7 +6114,7 @@
     <row r="245" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A245" s="16"/>
       <c r="B245" s="27" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C245" s="14">
         <v>0.6</v>
@@ -5935,7 +6126,7 @@
     <row r="246" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A246" s="16"/>
       <c r="B246" s="27" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C246" s="14">
         <v>0.8</v>
@@ -5947,7 +6138,7 @@
     <row r="247" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A247" s="16"/>
       <c r="B247" s="27" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="C247" s="14">
         <v>0.8</v>
@@ -5959,7 +6150,7 @@
     <row r="248" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A248" s="16"/>
       <c r="B248" s="27" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C248" s="14">
         <v>1.3</v>
@@ -5971,7 +6162,7 @@
     <row r="249" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A249" s="19"/>
       <c r="B249" s="27" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C249" s="14">
         <v>1</v>
@@ -5983,7 +6174,7 @@
     <row r="250" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="16"/>
       <c r="B250" s="30" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C250" s="14">
         <v>2</v>
@@ -5995,7 +6186,7 @@
     <row r="251" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A251" s="16"/>
       <c r="B251" s="27" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C251" s="14">
         <v>1.4</v>
@@ -6007,7 +6198,7 @@
     <row r="252" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="16"/>
       <c r="B252" s="27" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C252" s="14">
         <v>1.2</v>
@@ -6019,7 +6210,7 @@
     <row r="253" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="16"/>
       <c r="B253" s="27" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="C253" s="14">
         <v>2.2000000000000002</v>
@@ -6031,7 +6222,7 @@
     <row r="254" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="16"/>
       <c r="B254" s="27" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C254" s="14">
         <v>0.9</v>
@@ -6043,7 +6234,7 @@
     <row r="255" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A255" s="16"/>
       <c r="B255" s="27" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="C255" s="14">
         <v>1.8</v>
@@ -6055,7 +6246,7 @@
     <row r="256" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="16"/>
       <c r="B256" s="27" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="C256" s="14">
         <v>1.5</v>
@@ -6067,7 +6258,7 @@
     <row r="257" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="16"/>
       <c r="B257" s="27" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C257" s="14">
         <v>0.8</v>
@@ -6079,7 +6270,7 @@
     <row r="258" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="16"/>
       <c r="B258" s="27" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="C258" s="14">
         <v>1.2</v>
@@ -6091,7 +6282,7 @@
     <row r="259" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="16"/>
       <c r="B259" s="27" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C259" s="14">
         <v>2.2000000000000002</v>
@@ -6103,7 +6294,7 @@
     <row r="260" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="16"/>
       <c r="B260" s="27" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C260" s="14">
         <v>1.3</v>
@@ -6115,7 +6306,7 @@
     <row r="261" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A261" s="16"/>
       <c r="B261" s="27" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="C261" s="14">
         <v>2.2000000000000002</v>
@@ -6126,10 +6317,10 @@
     </row>
     <row r="262" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A262" s="16" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B262" s="27" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C262" s="14">
         <v>0.9</v>
@@ -6141,7 +6332,7 @@
     <row r="263" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A263" s="16"/>
       <c r="B263" s="27" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="C263" s="14">
         <v>1</v>
@@ -6150,65 +6341,77 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A264" s="16"/>
       <c r="B264" s="27" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C264" s="14">
         <v>1.2</v>
       </c>
-      <c r="D264" s="14"/>
-    </row>
-    <row r="265" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D264" s="14">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A265" s="16"/>
       <c r="B265" s="27" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C265" s="14">
         <v>2</v>
       </c>
-      <c r="D265" s="14"/>
+      <c r="D265" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="266" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="16"/>
       <c r="B266" s="27" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="C266" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D266" s="14"/>
+      <c r="D266" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="267" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="16"/>
       <c r="B267" s="27" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C267" s="14">
         <v>1.2</v>
       </c>
-      <c r="D267" s="14"/>
+      <c r="D267" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="268" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A268" s="16"/>
       <c r="B268" s="27" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C268" s="14">
         <v>1</v>
       </c>
-      <c r="D268" s="14"/>
+      <c r="D268" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="269" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="16"/>
       <c r="B269" s="27" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="C269" s="14">
         <v>2</v>
       </c>
-      <c r="D269" s="14"/>
+      <c r="D269" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="270" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="16"/>
@@ -6218,10 +6421,10 @@
     </row>
     <row r="271" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A271" s="31" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B271" s="30" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C271" s="14">
         <v>1.5</v>
@@ -6233,7 +6436,7 @@
     <row r="272" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A272" s="16"/>
       <c r="B272" s="27" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C272" s="14">
         <v>1.5</v>
@@ -6245,7 +6448,7 @@
     <row r="273" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="16"/>
       <c r="B273" s="27" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C273" s="14">
         <v>2</v>
@@ -6257,7 +6460,7 @@
     <row r="274" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="16"/>
       <c r="B274" s="27" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C274" s="14">
         <v>2</v>
@@ -6269,7 +6472,7 @@
     <row r="275" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="16"/>
       <c r="B275" s="27" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C275" s="14">
         <v>1.5</v>
@@ -6281,7 +6484,7 @@
     <row r="276" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="16"/>
       <c r="B276" s="27" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="C276" s="14">
         <v>1</v>
@@ -6293,7 +6496,7 @@
     <row r="277" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="16"/>
       <c r="B277" s="27" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="C277" s="14">
         <v>2</v>
@@ -6305,7 +6508,7 @@
     <row r="278" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="16"/>
       <c r="B278" s="27" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C278" s="14">
         <v>1.5</v>
@@ -6316,10 +6519,10 @@
     </row>
     <row r="279" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="16" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B279" s="27" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C279" s="14">
         <v>1</v>
@@ -6331,7 +6534,7 @@
     <row r="280" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="16"/>
       <c r="B280" s="27" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C280" s="14">
         <v>1</v>
@@ -6343,7 +6546,7 @@
     <row r="281" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="16"/>
       <c r="B281" s="27" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C281" s="14">
         <v>1.5</v>
@@ -6360,10 +6563,10 @@
     </row>
     <row r="283" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A283" s="28" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B283" s="27" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C283" s="14">
         <v>1.5</v>
@@ -6375,7 +6578,7 @@
     <row r="284" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="16"/>
       <c r="B284" s="27" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C284" s="14">
         <v>1</v>
@@ -6387,7 +6590,7 @@
     <row r="285" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="19"/>
       <c r="B285" s="30" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C285" s="14">
         <v>1.5</v>
@@ -6399,7 +6602,7 @@
     <row r="286" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="16"/>
       <c r="B286" s="27" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C286" s="14">
         <v>2</v>
@@ -6411,7 +6614,7 @@
     <row r="287" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="16"/>
       <c r="B287" s="27" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C287" s="14">
         <v>1.5</v>
@@ -6423,7 +6626,7 @@
     <row r="288" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="16"/>
       <c r="B288" s="27" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C288" s="14">
         <v>2.5</v>
@@ -6435,7 +6638,7 @@
     <row r="289" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="16"/>
       <c r="B289" s="27" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C289" s="14">
         <v>2</v>
@@ -6447,7 +6650,7 @@
     <row r="290" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="16"/>
       <c r="B290" s="27" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C290" s="14">
         <v>1</v>
@@ -6459,7 +6662,7 @@
     <row r="291" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="16"/>
       <c r="B291" s="27" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C291" s="14">
         <v>1.2</v>
@@ -6471,7 +6674,7 @@
     <row r="292" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="16"/>
       <c r="B292" s="27" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C292" s="14">
         <v>1</v>
@@ -6483,7 +6686,7 @@
     <row r="293" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="16"/>
       <c r="B293" s="27" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C293" s="14">
         <v>0.8</v>
@@ -6495,7 +6698,7 @@
     <row r="294" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="16"/>
       <c r="B294" s="27" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C294" s="14">
         <v>0.5</v>
@@ -6512,7 +6715,7 @@
     </row>
     <row r="296" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="16" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B296" s="27"/>
       <c r="C296" s="14"/>
@@ -6520,10 +6723,10 @@
     </row>
     <row r="297" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A297" s="28" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B297" s="27" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C297" s="14">
         <v>2</v>
@@ -6535,7 +6738,7 @@
     <row r="298" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A298" s="19"/>
       <c r="B298" s="30" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="C298" s="14">
         <v>2</v>
@@ -6547,7 +6750,7 @@
     <row r="299" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A299" s="16"/>
       <c r="B299" s="27" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C299" s="14">
         <v>2.5</v>
@@ -6559,7 +6762,7 @@
     <row r="300" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A300" s="16"/>
       <c r="B300" s="27" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C300" s="14">
         <v>1.5</v>
@@ -6571,7 +6774,7 @@
     <row r="301" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="16"/>
       <c r="B301" s="27" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C301" s="14">
         <v>2</v>
@@ -6583,7 +6786,7 @@
     <row r="302" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A302" s="16"/>
       <c r="B302" s="27" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C302" s="14">
         <v>1.5</v>
@@ -6595,7 +6798,7 @@
     <row r="303" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="16"/>
       <c r="B303" s="27" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C303" s="14">
         <v>2</v>
@@ -6607,7 +6810,7 @@
     <row r="304" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A304" s="16"/>
       <c r="B304" s="27" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C304" s="14">
         <v>2</v>
@@ -6619,7 +6822,7 @@
     <row r="305" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="16"/>
       <c r="B305" s="27" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C305" s="14">
         <v>2</v>
@@ -6631,7 +6834,7 @@
     <row r="306" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="16"/>
       <c r="B306" s="27" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C306" s="14">
         <v>2</v>
@@ -6643,7 +6846,7 @@
     <row r="307" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="19"/>
       <c r="B307" s="30" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C307" s="14">
         <v>1.5</v>
@@ -6655,7 +6858,7 @@
     <row r="308" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="16"/>
       <c r="B308" s="27" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C308" s="14">
         <v>1</v>
@@ -6667,7 +6870,7 @@
     <row r="309" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="16"/>
       <c r="B309" s="27" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C309" s="14">
         <v>3</v>
@@ -6679,7 +6882,7 @@
     <row r="310" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="16"/>
       <c r="B310" s="27" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C310" s="14">
         <v>1.5</v>
@@ -6691,7 +6894,7 @@
     <row r="311" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="16"/>
       <c r="B311" s="27" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="C311" s="14">
         <v>1.5</v>
@@ -6703,7 +6906,7 @@
     <row r="312" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="16"/>
       <c r="B312" s="27" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C312" s="8">
         <v>2</v>
@@ -6715,7 +6918,7 @@
     <row r="313" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="16"/>
       <c r="B313" s="27" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C313" s="8">
         <v>1</v>
@@ -6727,7 +6930,7 @@
     <row r="314" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="16"/>
       <c r="B314" s="27" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C314" s="8">
         <v>1</v>
@@ -6738,7 +6941,7 @@
     </row>
     <row r="315" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="16" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B315" s="27"/>
       <c r="C315" s="14"/>
@@ -6746,10 +6949,10 @@
     </row>
     <row r="316" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A316" s="28" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B316" s="18" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C316" s="14">
         <v>0.8</v>
@@ -6761,7 +6964,7 @@
     <row r="317" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="16"/>
       <c r="B317" s="18" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C317" s="14">
         <v>2</v>
@@ -6773,7 +6976,7 @@
     <row r="318" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="16"/>
       <c r="B318" s="18" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C318" s="14">
         <v>1.2</v>
@@ -6785,7 +6988,7 @@
     <row r="319" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="19"/>
       <c r="B319" s="14" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C319" s="14">
         <v>1.5</v>
@@ -6797,7 +7000,7 @@
     <row r="320" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="16"/>
       <c r="B320" s="18" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="C320" s="14">
         <v>2.5</v>
@@ -6809,7 +7012,7 @@
     <row r="321" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="16"/>
       <c r="B321" s="18" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C321" s="14">
         <v>2</v>
@@ -6821,7 +7024,7 @@
     <row r="322" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="16"/>
       <c r="B322" s="18" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="C322" s="14">
         <v>1.5</v>
@@ -6833,7 +7036,7 @@
     <row r="323" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="16"/>
       <c r="B323" s="18" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="C323" s="14">
         <v>3</v>
@@ -6845,7 +7048,7 @@
     <row r="324" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="16"/>
       <c r="B324" s="18" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C324" s="14">
         <v>1.2</v>
@@ -6857,7 +7060,7 @@
     <row r="325" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="16"/>
       <c r="B325" s="18" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C325" s="14">
         <v>1.2</v>
@@ -6869,7 +7072,7 @@
     <row r="326" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="16"/>
       <c r="B326" s="18" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="C326" s="14">
         <v>1.5</v>
@@ -6881,7 +7084,7 @@
     <row r="327" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A327" s="16"/>
       <c r="B327" s="18" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C327" s="14">
         <v>1</v>
@@ -6892,7 +7095,7 @@
     </row>
     <row r="328" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B328" s="18" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C328" s="14">
         <v>1</v>
@@ -6908,7 +7111,7 @@
     </row>
     <row r="330" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B330" s="27" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="C330" s="8">
         <v>1.2</v>
@@ -6919,7 +7122,7 @@
     </row>
     <row r="331" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B331" s="27" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="C331" s="8">
         <v>2</v>
@@ -6930,7 +7133,7 @@
     </row>
     <row r="332" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B332" s="27" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="C332" s="8">
         <v>1</v>
@@ -6941,7 +7144,7 @@
     </row>
     <row r="333" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B333" s="27" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C333" s="8">
         <v>1.2</v>
@@ -6952,7 +7155,7 @@
     </row>
     <row r="334" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B334" s="27" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="C334" s="8">
         <v>1</v>
@@ -6963,7 +7166,7 @@
     </row>
     <row r="335" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B335" s="27" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C335" s="8">
         <v>0.8</v>
@@ -6974,7 +7177,7 @@
     </row>
     <row r="336" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B336" s="27" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="C336" s="8">
         <v>1.5</v>
@@ -6985,7 +7188,7 @@
     </row>
     <row r="337" spans="1:4" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B337" s="27" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C337" s="8">
         <v>1</v>
@@ -6996,7 +7199,7 @@
     </row>
     <row r="338" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B338" s="35" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="C338" s="58">
         <v>0.8</v>
@@ -7007,7 +7210,7 @@
     </row>
     <row r="339" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B339" s="35" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C339" s="58">
         <v>1</v>
@@ -7021,13 +7224,13 @@
     </row>
     <row r="341" spans="1:4" ht="19" x14ac:dyDescent="0.2">
       <c r="A341" s="43" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C341" s="58"/>
     </row>
     <row r="342" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B342" s="35" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C342" s="58">
         <v>1</v>
@@ -7038,7 +7241,7 @@
     </row>
     <row r="343" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B343" s="35" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="C343" s="58">
         <v>2.5</v>
@@ -7049,7 +7252,7 @@
     </row>
     <row r="344" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B344" s="35" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C344" s="58">
         <v>0.8</v>
@@ -7060,7 +7263,7 @@
     </row>
     <row r="345" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B345" s="35" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="C345" s="58">
         <v>0.8</v>
@@ -7071,7 +7274,7 @@
     </row>
     <row r="346" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B346" s="35" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="C346" s="58">
         <v>1</v>
@@ -7082,10 +7285,10 @@
     </row>
     <row r="347" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A347" s="25" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B347" s="35" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C347" s="58">
         <v>0.8</v>
@@ -7096,7 +7299,7 @@
     </row>
     <row r="348" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B348" s="35" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="C348" s="58">
         <v>0.8</v>
@@ -7107,7 +7310,7 @@
     </row>
     <row r="349" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B349" s="35" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C349" s="58">
         <v>0.5</v>
@@ -7118,7 +7321,7 @@
     </row>
     <row r="350" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B350" s="35" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C350" s="58">
         <v>1.8</v>
@@ -7129,7 +7332,7 @@
     </row>
     <row r="351" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B351" s="35" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C351" s="58">
         <v>1</v>
@@ -7140,7 +7343,7 @@
     </row>
     <row r="352" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B352" s="27" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="C352" s="58">
         <v>1</v>
@@ -7151,7 +7354,7 @@
     </row>
     <row r="353" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B353" s="27" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="C353" s="58">
         <v>1</v>
@@ -7170,7 +7373,7 @@
     </row>
     <row r="356" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B356" s="27" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C356" s="8">
         <v>1.2</v>
@@ -7178,7 +7381,7 @@
     </row>
     <row r="357" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B357" s="27" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C357" s="8">
         <v>1</v>
@@ -7186,7 +7389,7 @@
     </row>
     <row r="358" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B358" s="27" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C358" s="8">
         <v>1.2</v>
@@ -7194,7 +7397,7 @@
     </row>
     <row r="359" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B359" s="27" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C359" s="8">
         <v>1.5</v>
@@ -7202,7 +7405,7 @@
     </row>
     <row r="360" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B360" s="27" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C360" s="8">
         <v>1.5</v>
@@ -7210,7 +7413,7 @@
     </row>
     <row r="361" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B361" s="27" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C361" s="8">
         <v>1</v>
@@ -7218,7 +7421,7 @@
     </row>
     <row r="362" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B362" s="27" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C362" s="8">
         <v>1</v>
@@ -7229,10 +7432,10 @@
     </row>
     <row r="364" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="28" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B364" s="27" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="C364" s="14">
         <v>1.5</v>
@@ -7243,7 +7446,7 @@
     </row>
     <row r="365" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B365" s="27" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="C365" s="14">
         <v>1.5</v>
@@ -7255,7 +7458,7 @@
     <row r="366" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="16"/>
       <c r="B366" s="27" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C366" s="14">
         <v>1.5</v>
@@ -7267,7 +7470,7 @@
     <row r="367" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="16"/>
       <c r="B367" s="27" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="C367" s="14">
         <v>2</v>
@@ -7279,7 +7482,7 @@
     <row r="368" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="16"/>
       <c r="B368" s="27" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C368" s="14">
         <v>1.5</v>
@@ -7291,7 +7494,7 @@
     <row r="369" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="16"/>
       <c r="B369" s="27" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="C369" s="14">
         <v>1.2</v>
@@ -7303,7 +7506,7 @@
     <row r="370" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="16"/>
       <c r="B370" s="27" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C370" s="14">
         <v>1</v>
@@ -7315,7 +7518,7 @@
     <row r="371" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A371" s="16"/>
       <c r="B371" s="27" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="C371" s="14">
         <v>1.5</v>
@@ -7327,7 +7530,7 @@
     <row r="372" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="16"/>
       <c r="B372" s="27" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C372" s="14">
         <v>2</v>
@@ -7339,7 +7542,7 @@
     <row r="373" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="16"/>
       <c r="B373" s="27" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C373" s="14">
         <v>1</v>
@@ -7351,7 +7554,7 @@
     <row r="374" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="16"/>
       <c r="B374" s="27" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="C374" s="8">
         <v>1.5</v>
@@ -7363,7 +7566,7 @@
     <row r="375" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="16"/>
       <c r="B375" s="27" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="C375" s="8">
         <v>1</v>
@@ -7375,7 +7578,7 @@
     <row r="376" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="16"/>
       <c r="B376" s="27" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C376" s="8">
         <v>1</v>
@@ -7395,7 +7598,7 @@
     </row>
     <row r="379" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B379" s="27" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C379" s="8">
         <v>1</v>
@@ -7403,7 +7606,7 @@
     </row>
     <row r="380" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B380" s="27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C380" s="8">
         <v>1.5</v>
@@ -7411,7 +7614,7 @@
     </row>
     <row r="381" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B381" s="27" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C381" s="8">
         <v>1.5</v>
@@ -7419,7 +7622,7 @@
     </row>
     <row r="382" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B382" s="27" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C382" s="8">
         <v>2</v>
@@ -7427,7 +7630,7 @@
     </row>
     <row r="383" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B383" s="27" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C383" s="8">
         <v>1.5</v>
@@ -7435,7 +7638,7 @@
     </row>
     <row r="384" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B384" s="27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C384" s="8">
         <v>1</v>
@@ -7443,7 +7646,7 @@
     </row>
     <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B385" s="27" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C385" s="8">
         <v>1.5</v>
@@ -7451,7 +7654,7 @@
     </row>
     <row r="386" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B386" s="27" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C386" s="8">
         <v>1</v>
@@ -7459,7 +7662,7 @@
     </row>
     <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B387" s="27" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C387" s="8">
         <v>1</v>
@@ -7475,7 +7678,7 @@
     </row>
     <row r="390" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B390" s="27" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C390" s="8">
         <v>1.2</v>
@@ -7483,7 +7686,7 @@
     </row>
     <row r="391" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B391" s="27" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C391" s="8">
         <v>1.2</v>
@@ -7491,7 +7694,7 @@
     </row>
     <row r="392" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B392" s="27" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C392" s="8">
         <v>1.2</v>
@@ -7499,7 +7702,7 @@
     </row>
     <row r="393" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B393" s="27" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C393" s="8">
         <v>2</v>
@@ -7507,7 +7710,7 @@
     </row>
     <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B394" s="27" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C394" s="8">
         <v>1.5</v>
@@ -7515,7 +7718,7 @@
     </row>
     <row r="395" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B395" s="27" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C395" s="8">
         <v>1</v>
@@ -7523,7 +7726,7 @@
     </row>
     <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B396" s="27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C396" s="8">
         <v>1</v>
@@ -7539,7 +7742,7 @@
     </row>
     <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B399" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C399" s="8">
         <v>0.8</v>
@@ -7547,7 +7750,7 @@
     </row>
     <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B400" s="27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C400" s="8">
         <v>0.8</v>
@@ -7555,7 +7758,7 @@
     </row>
     <row r="401" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B401" s="27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C401" s="8">
         <v>1</v>
@@ -7563,7 +7766,7 @@
     </row>
     <row r="402" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B402" s="27" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C402" s="8">
         <v>1.5</v>
@@ -7571,7 +7774,7 @@
     </row>
     <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B403" s="27" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C403" s="8">
         <v>1.5</v>
@@ -7579,7 +7782,7 @@
     </row>
     <row r="404" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B404" s="27" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C404" s="8">
         <v>1</v>
@@ -7587,7 +7790,7 @@
     </row>
     <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B405" s="27" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C405" s="8">
         <v>1</v>
@@ -7603,7 +7806,7 @@
     </row>
     <row r="408" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B408" s="27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C408" s="8">
         <v>1</v>
@@ -7611,7 +7814,7 @@
     </row>
     <row r="409" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B409" s="27" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C409" s="8">
         <v>1.5</v>
@@ -7619,7 +7822,7 @@
     </row>
     <row r="410" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B410" s="27" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C410" s="8">
         <v>1</v>
@@ -7627,7 +7830,7 @@
     </row>
     <row r="411" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B411" s="27" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C411" s="8">
         <v>1</v>
@@ -7635,7 +7838,7 @@
     </row>
     <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B412" s="27" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C412" s="8">
         <v>1.5</v>
@@ -7643,7 +7846,7 @@
     </row>
     <row r="413" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B413" s="27" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C413" s="8">
         <v>1</v>
@@ -7651,7 +7854,7 @@
     </row>
     <row r="414" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B414" s="27" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C414" s="8">
         <v>1</v>
@@ -7667,7 +7870,7 @@
     </row>
     <row r="417" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B417" s="27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C417" s="8">
         <v>1.5</v>
@@ -7675,7 +7878,7 @@
     </row>
     <row r="418" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B418" s="27" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C418" s="8">
         <v>1.5</v>
@@ -7683,7 +7886,7 @@
     </row>
     <row r="419" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B419" s="27" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C419" s="8">
         <v>1.2</v>
@@ -7691,7 +7894,7 @@
     </row>
     <row r="420" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B420" s="27" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C420" s="8">
         <v>0.8</v>
@@ -7699,7 +7902,7 @@
     </row>
     <row r="421" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B421" s="27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C421" s="8">
         <v>1</v>
@@ -7707,7 +7910,7 @@
     </row>
     <row r="422" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B422" s="27" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C422" s="8">
         <v>1</v>
@@ -7723,7 +7926,7 @@
     </row>
     <row r="425" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B425" s="27" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C425" s="8">
         <v>1</v>
@@ -7731,7 +7934,7 @@
     </row>
     <row r="426" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B426" s="27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C426" s="8">
         <v>1.2</v>
@@ -7739,7 +7942,7 @@
     </row>
     <row r="427" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B427" s="27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C427" s="8">
         <v>0.8</v>
@@ -7747,7 +7950,7 @@
     </row>
     <row r="428" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B428" s="27" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C428" s="8">
         <v>0.8</v>
@@ -7755,7 +7958,7 @@
     </row>
     <row r="429" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B429" s="27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C429" s="8">
         <v>1.5</v>
@@ -7763,7 +7966,7 @@
     </row>
     <row r="430" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B430" s="27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C430" s="8">
         <v>1</v>
@@ -7771,7 +7974,7 @@
     </row>
     <row r="431" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B431" s="27" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C431" s="8">
         <v>1</v>
@@ -7787,7 +7990,7 @@
     </row>
     <row r="434" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B434" s="27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C434" s="8">
         <v>1.2</v>
@@ -7795,7 +7998,7 @@
     </row>
     <row r="435" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B435" s="27" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C435" s="8">
         <v>1</v>
@@ -7803,7 +8006,7 @@
     </row>
     <row r="436" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B436" s="27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C436" s="8">
         <v>1</v>
@@ -7811,7 +8014,7 @@
     </row>
     <row r="437" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B437" s="27" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C437" s="8">
         <v>1.2</v>
@@ -7819,7 +8022,7 @@
     </row>
     <row r="438" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B438" s="27" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C438" s="8">
         <v>1.5</v>
@@ -7827,7 +8030,7 @@
     </row>
     <row r="439" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B439" s="27" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C439" s="8">
         <v>1</v>
@@ -7835,7 +8038,7 @@
     </row>
     <row r="440" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B440" s="27" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C440" s="8">
         <v>1</v>
@@ -7851,7 +8054,7 @@
     </row>
     <row r="443" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B443" s="27" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C443" s="8">
         <v>1.2</v>
@@ -7859,7 +8062,7 @@
     </row>
     <row r="444" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B444" s="27" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C444" s="8">
         <v>1.2</v>
@@ -7867,7 +8070,7 @@
     </row>
     <row r="445" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B445" s="27" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C445" s="8">
         <v>1.5</v>
@@ -7875,7 +8078,7 @@
     </row>
     <row r="446" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B446" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C446" s="8">
         <v>0.8</v>
@@ -7883,7 +8086,7 @@
     </row>
     <row r="447" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B447" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C447" s="8">
         <v>1</v>
@@ -7895,10 +8098,10 @@
     </row>
     <row r="449" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A449" s="28" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="B449" s="30" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C449" s="14">
         <v>1.2</v>
@@ -7910,7 +8113,7 @@
     <row r="450" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A450" s="16"/>
       <c r="B450" s="30" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C450" s="14">
         <v>1.2</v>
@@ -7922,7 +8125,7 @@
     <row r="451" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A451" s="16"/>
       <c r="B451" s="30" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C451" s="14">
         <v>0.8</v>
@@ -7934,7 +8137,7 @@
     <row r="452" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A452" s="16"/>
       <c r="B452" s="30" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C452" s="14">
         <v>1</v>
@@ -7946,7 +8149,7 @@
     <row r="453" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A453" s="16"/>
       <c r="B453" s="30" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="C453" s="14">
         <v>2</v>
@@ -7958,7 +8161,7 @@
     <row r="454" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A454" s="16"/>
       <c r="B454" s="30" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C454" s="14">
         <v>1.2</v>
@@ -7970,7 +8173,7 @@
     <row r="455" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A455" s="16"/>
       <c r="B455" s="30" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C455" s="14">
         <v>1</v>
@@ -7982,7 +8185,7 @@
     <row r="456" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A456" s="16"/>
       <c r="B456" s="30" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C456" s="14">
         <v>2</v>
@@ -7994,7 +8197,7 @@
     <row r="457" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A457" s="16"/>
       <c r="B457" s="30" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C457" s="14">
         <v>2</v>
@@ -8006,7 +8209,7 @@
     <row r="458" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A458" s="16"/>
       <c r="B458" s="30" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C458" s="14">
         <v>1.5</v>
@@ -8018,7 +8221,7 @@
     <row r="459" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A459" s="16"/>
       <c r="B459" s="30" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C459" s="14">
         <v>2.5</v>
@@ -8030,7 +8233,7 @@
     <row r="460" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A460" s="16"/>
       <c r="B460" s="35" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C460" s="8">
         <v>1.5</v>
@@ -8042,7 +8245,7 @@
     <row r="461" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A461" s="16"/>
       <c r="B461" s="8" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C461" s="8">
         <v>1.5</v>
@@ -8054,7 +8257,7 @@
     <row r="462" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A462" s="16"/>
       <c r="B462" s="8" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="C462" s="8">
         <v>1</v>
@@ -8065,7 +8268,7 @@
     </row>
     <row r="463" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B463" s="8" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C463" s="8">
         <v>1</v>
@@ -8079,165 +8282,211 @@
         <v>79</v>
       </c>
     </row>
-    <row r="465" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B465" s="27" t="s">
-        <v>286</v>
+        <v>553</v>
       </c>
       <c r="C465" s="8">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="466" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="D465" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B466" s="27" t="s">
-        <v>287</v>
+        <v>554</v>
       </c>
       <c r="C466" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D466" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A467" s="25" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B467" s="27" t="s">
-        <v>288</v>
+        <v>555</v>
       </c>
       <c r="C467" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D467" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B468" s="27" t="s">
-        <v>289</v>
-      </c>
-      <c r="C468" s="8">
+        <v>556</v>
+      </c>
+      <c r="C468">
+        <v>2.5</v>
+      </c>
+      <c r="D468" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B469" s="27" t="s">
+        <v>557</v>
+      </c>
+      <c r="C469">
         <v>2</v>
       </c>
-    </row>
-    <row r="469" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B469" s="27" t="s">
-        <v>290</v>
-      </c>
-      <c r="C469" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="D469" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B470" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="C470" s="8">
+        <v>558</v>
+      </c>
+      <c r="C470">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="471" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B471" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="C471" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="D470" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B471" t="s">
+        <v>559</v>
+      </c>
+      <c r="C471">
+        <v>2</v>
+      </c>
+      <c r="D471" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B472" s="27" t="s">
-        <v>293</v>
+        <v>560</v>
       </c>
       <c r="C472" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="473" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="D472" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B473" s="27" t="s">
-        <v>294</v>
+        <v>561</v>
       </c>
       <c r="C473" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1.8</v>
+      </c>
+      <c r="D473" s="8">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B474" s="27" t="s">
-        <v>295</v>
+        <v>562</v>
       </c>
       <c r="C474" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B475" s="27"/>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B476" s="27"/>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B477" s="27"/>
-    </row>
-    <row r="478" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A478" s="34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B479" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="C479" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D474" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B475" s="27" t="s">
+        <v>563</v>
+      </c>
+      <c r="C475" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="480" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="D475" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B476" s="27" t="s">
+        <v>564</v>
+      </c>
+      <c r="C476" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D476" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B477" s="27" t="s">
+        <v>565</v>
+      </c>
+      <c r="C477" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D477" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A479" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B480" s="27" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="C480" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="481" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B481" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C481" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="481" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B481" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="C481" s="8">
+    <row r="482" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B482" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C482" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="482" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B482" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="C482" s="8">
+    <row r="483" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B483" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="C483" s="8">
         <v>2.5</v>
       </c>
     </row>
-    <row r="483" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B483" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C483" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="484" spans="2:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B484" s="27" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C484" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="485" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B485" s="27" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C485" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B486" s="27"/>
-    </row>
-    <row r="487" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A487" s="25" t="s">
-        <v>421</v>
+    <row r="486" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B486" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="C486" s="8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73490325-26C4-DD49-B8D6-3A8AB4C92D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901B28D4-37C9-5042-BFD4-F4A1658DC090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REQUISITOS" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="567">
   <si>
     <t>User story</t>
   </si>
@@ -1748,6 +1748,9 @@
   </si>
   <si>
     <t>RF20-13: Actualizar README/runbook/docs, verificar criterios de aceptación y guardar evidencias visuales y técnicas del flujo completo</t>
+  </si>
+  <si>
+    <t>Realizado No explicitamente</t>
   </si>
 </sst>
 </file>
@@ -1876,12 +1879,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1889,6 +1886,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1933,7 +1936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1948,9 +1951,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2040,9 +2040,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2059,83 +2056,90 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2148,21 +2152,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2476,16 +2470,16 @@
   <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="101.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.1640625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="15.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="8" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="42" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.1640625" style="8" customWidth="1"/>
-    <col min="9" max="9" width="3.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="8"/>
+    <col min="1" max="1" width="70.1640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="101.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.1640625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="7" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="7" customWidth="1"/>
+    <col min="7" max="7" width="25.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="3.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
@@ -2507,24 +2501,24 @@
       <c r="F1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>294</v>
       </c>
       <c r="D2">
@@ -2536,17 +2530,17 @@
       <c r="F2" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="L2" s="8"/>
+      <c r="G2" s="38"/>
+      <c r="L2" s="7"/>
     </row>
     <row r="3" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>297</v>
       </c>
       <c r="D3">
@@ -2558,17 +2552,17 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="L3" s="8"/>
+      <c r="G3" s="38"/>
+      <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12" ht="51" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="5">
@@ -2580,7 +2574,7 @@
       <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="38">
+      <c r="G4" s="36">
         <v>46094</v>
       </c>
       <c r="H4" s="5"/>
@@ -2589,13 +2583,13 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="5">
@@ -2607,7 +2601,7 @@
       <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="36">
         <v>46094</v>
       </c>
       <c r="H5" s="5"/>
@@ -2616,13 +2610,13 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="5">
@@ -2634,7 +2628,7 @@
       <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="36">
         <v>46094</v>
       </c>
       <c r="H6" s="5"/>
@@ -2643,13 +2637,13 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="5">
@@ -2661,7 +2655,7 @@
       <c r="F7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="36">
         <v>46094</v>
       </c>
       <c r="H7" s="5"/>
@@ -2670,13 +2664,13 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="5">
@@ -2688,7 +2682,7 @@
       <c r="F8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="36">
         <v>46094</v>
       </c>
       <c r="H8" s="5"/>
@@ -2697,13 +2691,13 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="5">
@@ -2715,7 +2709,7 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="36">
         <v>46094</v>
       </c>
       <c r="H9" s="5"/>
@@ -2724,13 +2718,13 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5">
@@ -2742,7 +2736,7 @@
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="36">
         <v>46094</v>
       </c>
       <c r="H10" s="5"/>
@@ -2751,13 +2745,13 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="5">
@@ -2769,7 +2763,7 @@
       <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="36">
         <v>46094</v>
       </c>
       <c r="H11" s="5"/>
@@ -2778,13 +2772,13 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="5">
@@ -2796,7 +2790,7 @@
       <c r="F12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="36">
         <v>46094</v>
       </c>
       <c r="H12" s="5"/>
@@ -2805,13 +2799,13 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="42" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="5">
@@ -2823,18 +2817,20 @@
       <c r="F13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="38"/>
+      <c r="G13" s="36"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="38" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="5">
@@ -2846,7 +2842,7 @@
       <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="36">
         <v>46094</v>
       </c>
       <c r="H14" s="5"/>
@@ -2861,18 +2857,18 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="38"/>
+      <c r="G15" s="36"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:12" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="41" t="s">
         <v>468</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="42" t="s">
         <v>471</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="42" t="s">
         <v>472</v>
       </c>
       <c r="D16" s="5">
@@ -2884,18 +2880,20 @@
       <c r="F16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="38"/>
+      <c r="G16" s="36"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="I16" s="5" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="49" t="s">
+      <c r="C17" s="47" t="s">
         <v>469</v>
       </c>
       <c r="D17" s="5">
@@ -2907,18 +2905,18 @@
       <c r="F17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="38"/>
+      <c r="G17" s="36"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="20" t="s">
         <v>470</v>
       </c>
       <c r="D18" s="5">
@@ -2930,7 +2928,7 @@
       <c r="F18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="38">
+      <c r="G18" s="36">
         <v>46121</v>
       </c>
       <c r="H18" s="5"/>
@@ -2939,25 +2937,25 @@
       </c>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="21" t="s">
         <v>312</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="22" t="s">
         <v>313</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>10</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="36">
         <v>46121</v>
       </c>
       <c r="H19" s="5"/>
@@ -2966,25 +2964,25 @@
       </c>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <v>8</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20" s="36">
         <v>46121</v>
       </c>
       <c r="H20" s="5"/>
@@ -2993,48 +2991,50 @@
       </c>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="43" t="s">
         <v>318</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="44" t="s">
         <v>548</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="45" t="s">
         <v>549</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <v>18</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="41"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="5" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>321</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <v>8</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="36">
         <v>46121</v>
       </c>
       <c r="H22" s="5"/>
@@ -3043,25 +3043,25 @@
       </c>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="22" t="s">
         <v>323</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <v>8</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="36">
         <v>46121</v>
       </c>
       <c r="H23" s="5"/>
@@ -3070,25 +3070,25 @@
       </c>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="13">
         <v>13</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24" s="36">
         <v>46121</v>
       </c>
       <c r="H24" s="5"/>
@@ -3097,25 +3097,25 @@
       </c>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="22" t="s">
         <v>329</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <v>10</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="38">
+      <c r="G25" s="36">
         <v>46121</v>
       </c>
       <c r="H25" s="5"/>
@@ -3124,13 +3124,13 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="85" x14ac:dyDescent="0.2">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="41" t="s">
         <v>494</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="B26" s="42" t="s">
         <v>495</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="C26" s="42" t="s">
         <v>496</v>
       </c>
       <c r="D26" s="5">
@@ -3142,18 +3142,20 @@
       <c r="F26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="38"/>
+      <c r="G26" s="36"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="27" spans="1:9" ht="85" x14ac:dyDescent="0.2">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="41" t="s">
         <v>507</v>
       </c>
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="42" t="s">
         <v>508</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="42" t="s">
         <v>509</v>
       </c>
       <c r="D27" s="5">
@@ -3165,18 +3167,20 @@
       <c r="F27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="38"/>
+      <c r="G27" s="36"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="63" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="5">
@@ -3188,30 +3192,32 @@
       <c r="F28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="38"/>
+      <c r="G28" s="36"/>
       <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="I28" s="5" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="22" t="s">
         <v>332</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="22" t="s">
         <v>333</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="13">
         <v>13</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29" s="36">
         <v>46121</v>
       </c>
       <c r="H29" s="5"/>
@@ -3220,13 +3226,13 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="65" t="s">
         <v>56</v>
       </c>
       <c r="D30" s="5">
@@ -3236,9 +3242,9 @@
         <v>45</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="38"/>
+        <v>75</v>
+      </c>
+      <c r="G30" s="36"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
@@ -3261,7 +3267,7 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="38"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
     </row>
@@ -3284,7 +3290,7 @@
       <c r="F32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="38"/>
+      <c r="G32" s="36"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
@@ -3307,7 +3313,7 @@
       <c r="F33" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="38"/>
+      <c r="G33" s="36"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
     </row>
@@ -3330,7 +3336,7 @@
       <c r="F34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="38"/>
+      <c r="G34" s="36"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
     </row>
@@ -3353,7 +3359,7 @@
       <c r="F35" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="38"/>
+      <c r="G35" s="36"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
     </row>
@@ -3376,12 +3382,12 @@
       <c r="F36" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G36" s="38"/>
+      <c r="G36" s="36"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>76</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -3399,30 +3405,30 @@
       <c r="F37" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="38"/>
+      <c r="G37" s="36"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="27" t="s">
         <v>444</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="23" t="s">
         <v>422</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="13">
         <v>5</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="38">
+      <c r="G38" s="36">
         <v>46121</v>
       </c>
       <c r="H38" s="5"/>
@@ -3431,13 +3437,13 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="68" x14ac:dyDescent="0.2">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="57" t="s">
         <v>550</v>
       </c>
-      <c r="B39" s="60" t="s">
+      <c r="B39" s="58" t="s">
         <v>551</v>
       </c>
-      <c r="C39" s="60" t="s">
+      <c r="C39" s="58" t="s">
         <v>552</v>
       </c>
       <c r="D39" s="5">
@@ -3449,18 +3455,18 @@
       <c r="F39" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="38"/>
+      <c r="G39" s="36"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="61" t="s">
         <v>83</v>
       </c>
       <c r="D40" s="5">
@@ -3472,7 +3478,7 @@
       <c r="F40" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G40" s="38"/>
+      <c r="G40" s="36"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
     </row>
@@ -3489,89 +3495,87 @@
       <c r="B43" s="2"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="50" t="s">
+      <c r="A44" s="48" t="s">
         <v>474</v>
       </c>
-      <c r="B44" s="9"/>
+      <c r="B44" s="8"/>
     </row>
     <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="51" t="s">
+      <c r="A45" s="49" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="52" t="s">
+      <c r="A46" s="50" t="s">
         <v>476</v>
       </c>
       <c r="B46" s="2"/>
     </row>
     <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="53" t="s">
+      <c r="A47" s="51" t="s">
         <v>477</v>
       </c>
       <c r="B47" s="2"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="64" t="s">
+        <v>566</v>
+      </c>
       <c r="B48" s="2"/>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="9"/>
+      <c r="B49" s="8"/>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B50" s="2"/>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51" s="9"/>
+      <c r="B51" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E38 E40:E1048576">
-    <cfRule type="containsText" dxfId="18" priority="15" operator="containsText" text="Won't">
-      <formula>NOT(ISERROR(SEARCH("Won't",E1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="16" operator="containsText" text="Could">
-      <formula>NOT(ISERROR(SEARCH("Could",E1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="17" operator="containsText" text="Should">
-      <formula>NOT(ISERROR(SEARCH("Should",E1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="18" operator="containsText" text="Must">
-      <formula>NOT(ISERROR(SEARCH("Must",E1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F38 F40:F1048576">
-    <cfRule type="containsText" dxfId="14" priority="19" operator="containsText" text="Bajo">
-      <formula>NOT(ISERROR(SEARCH("Bajo",F1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="20" operator="containsText" text="Medio">
-      <formula>NOT(ISERROR(SEARCH("Medio",F1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="Alto">
-      <formula>NOT(ISERROR(SEARCH("Alto",F1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H18:I20">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H18)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I25">
-    <cfRule type="containsText" dxfId="10" priority="10" operator="containsText" text="Sí">
+  <conditionalFormatting sqref="H22:I25 I26:I27">
+    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:I29">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:I38">
-    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="5" priority="12" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H38)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I17 I39:I1048576">
-    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="Sí">
+  <conditionalFormatting sqref="I1:I12 I39:I1048576 I14:I15 I17">
+    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",I28)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",I21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",I13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",I16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3579,8 +3583,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{F603C862-5BFF-AA4F-A3F0-AFDA4F6D8639}">
-            <xm:f>NOT(ISERROR(SEARCH("Won't",E39)))</xm:f>
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{F603C862-5BFF-AA4F-A3F0-AFDA4F6D8639}">
+            <xm:f>NOT(ISERROR(SEARCH("Won't",E1)))</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF006100"/>
@@ -3592,8 +3596,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{6925889A-7A76-5047-BA15-9041DDE9A394}">
-            <xm:f>NOT(ISERROR(SEARCH("Could",E39)))</xm:f>
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{6925889A-7A76-5047-BA15-9041DDE9A394}">
+            <xm:f>NOT(ISERROR(SEARCH("Could",E1)))</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF006100"/>
@@ -3605,8 +3609,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{FFAE8A3E-5305-F74B-A1C9-6BDD0E78503E}">
-            <xm:f>NOT(ISERROR(SEARCH("Should",E39)))</xm:f>
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{FFAE8A3E-5305-F74B-A1C9-6BDD0E78503E}">
+            <xm:f>NOT(ISERROR(SEARCH("Should",E1)))</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF9C5700"/>
@@ -3618,8 +3622,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{AE048A56-DCAB-A442-A3C5-BE50CE6EC692}">
-            <xm:f>NOT(ISERROR(SEARCH("Must",E39)))</xm:f>
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{AE048A56-DCAB-A442-A3C5-BE50CE6EC692}">
+            <xm:f>NOT(ISERROR(SEARCH("Must",E1)))</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -3631,11 +3635,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E39</xm:sqref>
+          <xm:sqref>E1:E1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{6DCEA9A2-72AD-3C45-A6E4-76187190F144}">
-            <xm:f>NOT(ISERROR(SEARCH("Bajo",F39)))</xm:f>
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{6DCEA9A2-72AD-3C45-A6E4-76187190F144}">
+            <xm:f>NOT(ISERROR(SEARCH("Bajo",F1)))</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF006100"/>
@@ -3647,8 +3651,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{89451CA2-693D-5D44-90D6-5C93F5286255}">
-            <xm:f>NOT(ISERROR(SEARCH("Medio",F39)))</xm:f>
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{89451CA2-693D-5D44-90D6-5C93F5286255}">
+            <xm:f>NOT(ISERROR(SEARCH("Medio",F1)))</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF9C5700"/>
@@ -3660,8 +3664,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{A9951BA2-58D1-BB48-8DDD-F6D56CF5196C}">
-            <xm:f>NOT(ISERROR(SEARCH("Alto",F39)))</xm:f>
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{A9951BA2-58D1-BB48-8DDD-F6D56CF5196C}">
+            <xm:f>NOT(ISERROR(SEARCH("Alto",F1)))</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -3673,7 +3677,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F39</xm:sqref>
+          <xm:sqref>F1:F1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3686,4668 +3690,4668 @@
   <dimension ref="A2:D486"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="71.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="87.33203125" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="8"/>
+    <col min="1" max="1" width="71.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="87.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="32" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <v>0.6</v>
       </c>
-      <c r="D3" s="14"/>
+      <c r="D3" s="13"/>
     </row>
     <row r="4" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="16"/>
-      <c r="B4" s="30" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <v>0.8</v>
       </c>
-      <c r="D4" s="14"/>
+      <c r="D4" s="13"/>
     </row>
     <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="16"/>
-      <c r="B5" s="30" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>0.8</v>
       </c>
-      <c r="D5" s="14"/>
+      <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="16"/>
-      <c r="B6" s="30" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <v>0.8</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="16"/>
-      <c r="B7" s="30" t="s">
+      <c r="A7" s="15"/>
+      <c r="B7" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>0.5</v>
       </c>
-      <c r="D7" s="14"/>
+      <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="16"/>
-      <c r="B8" s="30" t="s">
+      <c r="A8" s="15"/>
+      <c r="B8" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>0.5</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="14">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14"/>
+      <c r="C9" s="13">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="16"/>
-      <c r="B10" s="30" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="C10" s="14">
-        <v>1</v>
-      </c>
-      <c r="D10" s="14"/>
+      <c r="C10" s="13">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="16"/>
-      <c r="B11" s="30" t="s">
+      <c r="A11" s="15"/>
+      <c r="B11" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C11" s="14">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14"/>
+      <c r="C11" s="13">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="16"/>
-      <c r="B12" s="30" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="C12" s="14">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14"/>
+      <c r="C12" s="13">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13"/>
     </row>
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="30" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="14">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14"/>
+      <c r="C13" s="13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13"/>
     </row>
     <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="30" t="s">
+      <c r="A14" s="15"/>
+      <c r="B14" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13">
         <v>1.2</v>
       </c>
-      <c r="D14" s="14"/>
+      <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="30" t="s">
+      <c r="A15" s="15"/>
+      <c r="B15" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13">
         <v>0.6</v>
       </c>
-      <c r="D15" s="14"/>
+      <c r="D15" s="13"/>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="54" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>0.5</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>0.5</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="8">
-        <v>1</v>
-      </c>
-      <c r="D20" s="8">
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="8">
-        <v>1</v>
-      </c>
-      <c r="D21" s="8">
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="C22" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D22" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>2</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="8">
-        <v>1</v>
-      </c>
-      <c r="D24" s="8">
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7">
         <v>0.75</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="7">
         <v>0.7</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="7">
         <v>1.2</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>0.8</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D28" s="8">
+      <c r="C28" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D29" s="8">
+      <c r="C29" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D29" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="7">
         <v>1.2</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <v>1.2</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <v>1.2</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D33" s="8">
+      <c r="C33" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D33" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="8">
-        <v>1</v>
-      </c>
-      <c r="D34" s="8">
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="8">
-        <v>1</v>
-      </c>
-      <c r="D35" s="8">
+      <c r="C35" s="7">
+        <v>1</v>
+      </c>
+      <c r="D35" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="27"/>
+      <c r="B36" s="26"/>
     </row>
     <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="56" t="s">
+      <c r="A37" s="54" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="7">
         <v>0.8</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="C39" s="8">
-        <v>1</v>
-      </c>
-      <c r="D39" s="8">
+      <c r="C39" s="7">
+        <v>1</v>
+      </c>
+      <c r="D39" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="C40" s="8">
-        <v>1</v>
-      </c>
-      <c r="D40" s="8">
+      <c r="C40" s="7">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="7">
         <v>0.7</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="8">
-        <v>1</v>
-      </c>
-      <c r="D42" s="8">
+      <c r="C42" s="7">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="7">
         <v>1.2</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="7">
         <v>0.8</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D45" s="8">
+      <c r="C45" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D45" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D46" s="8">
+      <c r="C46" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D46" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="8">
-        <v>1</v>
-      </c>
-      <c r="D47" s="8">
+      <c r="C47" s="7">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="8">
-        <v>1</v>
-      </c>
-      <c r="D48" s="8">
+      <c r="C48" s="7">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B49" s="27"/>
+      <c r="B49" s="26"/>
     </row>
     <row r="50" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="56" t="s">
+      <c r="A50" s="54" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="7">
         <v>0.8</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="7">
         <v>0.8</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="7">
         <v>0.8</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="7">
         <v>1.2</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="C55" s="8">
-        <v>1</v>
-      </c>
-      <c r="D55" s="8">
+      <c r="C55" s="7">
+        <v>1</v>
+      </c>
+      <c r="D55" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="C56" s="8">
-        <v>1</v>
-      </c>
-      <c r="D56" s="8">
+      <c r="C56" s="7">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C57" s="8">
-        <v>1</v>
-      </c>
-      <c r="D57" s="8">
+      <c r="C57" s="7">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7">
         <v>0.7</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="7">
         <v>1.2</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="7">
         <v>0.7</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="7">
         <v>0.7</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="7">
         <v>0.7</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C60" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D60" s="8">
+      <c r="C60" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="8">
-        <v>1</v>
-      </c>
-      <c r="D61" s="8">
+      <c r="C61" s="7">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="C62" s="8">
-        <v>1</v>
-      </c>
-      <c r="D62" s="8">
+      <c r="C62" s="7">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B63" s="27"/>
+      <c r="B63" s="26"/>
     </row>
     <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="56" t="s">
+      <c r="A64" s="54" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="C65" s="8">
-        <v>1</v>
-      </c>
-      <c r="D65" s="8">
+      <c r="C65" s="7">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7">
         <v>0.3</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="7">
         <v>0.8</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="7">
         <v>1.2</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="C68" s="8">
-        <v>1</v>
-      </c>
-      <c r="D68" s="8">
+      <c r="C68" s="7">
+        <v>1</v>
+      </c>
+      <c r="D68" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="7">
         <v>2</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="7">
         <v>2</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="C71" s="8">
+      <c r="C71" s="7">
         <v>0.8</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="7">
         <v>0.8</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="C73" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D73" s="8">
+      <c r="C73" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D73" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B74" s="27" t="s">
+      <c r="B74" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="C74" s="8">
-        <v>1</v>
-      </c>
-      <c r="D74" s="8">
+      <c r="C74" s="7">
+        <v>1</v>
+      </c>
+      <c r="D74" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="C75" s="8">
-        <v>1</v>
-      </c>
-      <c r="D75" s="8">
+      <c r="C75" s="7">
+        <v>1</v>
+      </c>
+      <c r="D75" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A76" s="8"/>
-      <c r="B76" s="26" t="s">
+      <c r="A76" s="7"/>
+      <c r="B76" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="C76" s="8">
+      <c r="C76" s="7">
         <v>0.8</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B77" s="27"/>
+      <c r="B77" s="26"/>
     </row>
     <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A78" s="56" t="s">
+      <c r="A78" s="54" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B79" s="27" t="s">
+      <c r="B79" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="7">
         <v>1.2</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C80" s="8">
+      <c r="C80" s="7">
         <v>0.8</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="C81" s="8">
+      <c r="C81" s="7">
         <v>0.8</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B82" s="27" t="s">
+      <c r="B82" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C82" s="8">
-        <v>1</v>
-      </c>
-      <c r="D82" s="8">
+      <c r="C82" s="7">
+        <v>1</v>
+      </c>
+      <c r="D82" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="C83" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D83" s="8">
+      <c r="C83" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D83" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B84" s="27" t="s">
+      <c r="B84" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C84" s="8">
-        <v>1</v>
-      </c>
-      <c r="D84" s="8">
+      <c r="C84" s="7">
+        <v>1</v>
+      </c>
+      <c r="D84" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="C85" s="8">
+      <c r="C85" s="7">
         <v>0.8</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B86" s="27" t="s">
+      <c r="B86" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="C86" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D86" s="8">
+      <c r="C86" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D86" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="C87" s="8">
-        <v>1</v>
-      </c>
-      <c r="D87" s="8">
+      <c r="C87" s="7">
+        <v>1</v>
+      </c>
+      <c r="D87" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="C88" s="8">
-        <v>1</v>
-      </c>
-      <c r="D88" s="8">
+      <c r="C88" s="7">
+        <v>1</v>
+      </c>
+      <c r="D88" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B89" s="27"/>
+      <c r="B89" s="26"/>
     </row>
     <row r="90" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="56" t="s">
+      <c r="A90" s="54" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="C91" s="8">
-        <v>1</v>
-      </c>
-      <c r="D91" s="8">
+      <c r="C91" s="7">
+        <v>1</v>
+      </c>
+      <c r="D91" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B92" s="27" t="s">
+      <c r="B92" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="C92" s="8">
+      <c r="C92" s="7">
         <v>1.2</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B93" s="27" t="s">
+      <c r="B93" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="C93" s="8">
+      <c r="C93" s="7">
         <v>0.8</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B94" s="27" t="s">
+      <c r="B94" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="C94" s="8">
-        <v>1</v>
-      </c>
-      <c r="D94" s="8">
+      <c r="C94" s="7">
+        <v>1</v>
+      </c>
+      <c r="D94" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B95" s="27" t="s">
+      <c r="B95" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="C95" s="8">
-        <v>1</v>
-      </c>
-      <c r="D95" s="8">
+      <c r="C95" s="7">
+        <v>1</v>
+      </c>
+      <c r="D95" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B96" s="27" t="s">
+      <c r="B96" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="C96" s="8">
+      <c r="C96" s="7">
         <v>0.8</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B97" s="27" t="s">
+      <c r="B97" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="C97" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D97" s="8">
+      <c r="C97" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D97" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B98" s="27" t="s">
+      <c r="B98" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="C98" s="8">
-        <v>1</v>
-      </c>
-      <c r="D98" s="8">
+      <c r="C98" s="7">
+        <v>1</v>
+      </c>
+      <c r="D98" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B99" s="27" t="s">
+      <c r="B99" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="C99" s="8">
-        <v>1</v>
-      </c>
-      <c r="D99" s="8">
+      <c r="C99" s="7">
+        <v>1</v>
+      </c>
+      <c r="D99" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B100" s="27"/>
+      <c r="B100" s="26"/>
     </row>
     <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="56" t="s">
+      <c r="A101" s="54" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B102" s="27" t="s">
+      <c r="B102" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="C102" s="8">
-        <v>1</v>
-      </c>
-      <c r="D102" s="8">
+      <c r="C102" s="7">
+        <v>1</v>
+      </c>
+      <c r="D102" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B103" s="27" t="s">
+      <c r="B103" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C103" s="8">
+      <c r="C103" s="7">
         <v>1.2</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D103" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B104" s="27" t="s">
+      <c r="B104" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="C104" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D104" s="8">
+      <c r="C104" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D104" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B105" s="27" t="s">
+      <c r="B105" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C105" s="8">
+      <c r="C105" s="7">
         <v>0.8</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B106" s="27" t="s">
+      <c r="B106" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="C106" s="8">
+      <c r="C106" s="7">
         <v>1.2</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B107" s="27" t="s">
+      <c r="B107" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="C107" s="8">
+      <c r="C107" s="7">
         <v>0.7</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B108" s="27" t="s">
+      <c r="B108" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="C108" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D108" s="8">
+      <c r="C108" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D108" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="C109" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D109" s="8">
+      <c r="C109" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D109" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B110" s="27" t="s">
+      <c r="B110" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="C110" s="8">
-        <v>1</v>
-      </c>
-      <c r="D110" s="8">
+      <c r="C110" s="7">
+        <v>1</v>
+      </c>
+      <c r="D110" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="C111" s="8">
-        <v>1</v>
-      </c>
-      <c r="D111" s="8">
+      <c r="C111" s="7">
+        <v>1</v>
+      </c>
+      <c r="D111" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B112" s="27"/>
+      <c r="B112" s="26"/>
     </row>
     <row r="113" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A113" s="56" t="s">
+      <c r="A113" s="54" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B114" s="27" t="s">
+      <c r="B114" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="C114" s="8">
+      <c r="C114" s="7">
         <v>0.8</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D114" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B115" s="27" t="s">
+      <c r="B115" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C115" s="8">
+      <c r="C115" s="7">
         <v>1.2</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D115" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B116" s="27" t="s">
+      <c r="B116" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C116" s="8">
+      <c r="C116" s="7">
         <v>1.2</v>
       </c>
-      <c r="D116" s="8">
+      <c r="D116" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B117" s="27" t="s">
+      <c r="B117" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C117" s="8">
-        <v>1</v>
-      </c>
-      <c r="D117" s="8">
+      <c r="C117" s="7">
+        <v>1</v>
+      </c>
+      <c r="D117" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B118" s="27" t="s">
+      <c r="B118" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C118" s="8">
+      <c r="C118" s="7">
         <v>0.6</v>
       </c>
-      <c r="D118" s="8">
+      <c r="D118" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B119" s="27" t="s">
+      <c r="B119" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="C119" s="8">
+      <c r="C119" s="7">
         <v>1.2</v>
       </c>
-      <c r="D119" s="8">
+      <c r="D119" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B120" s="27" t="s">
+      <c r="B120" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="C120" s="8">
-        <v>1</v>
-      </c>
-      <c r="D120" s="8">
+      <c r="C120" s="7">
+        <v>1</v>
+      </c>
+      <c r="D120" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B121" s="27" t="s">
+      <c r="B121" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="C121" s="8">
-        <v>1</v>
-      </c>
-      <c r="D121" s="8">
+      <c r="C121" s="7">
+        <v>1</v>
+      </c>
+      <c r="D121" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B122" s="27"/>
+      <c r="B122" s="26"/>
     </row>
     <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A123" s="56" t="s">
+      <c r="A123" s="54" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B124" s="27" t="s">
+      <c r="B124" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="C124" s="8">
-        <v>1</v>
-      </c>
-      <c r="D124" s="8">
+      <c r="C124" s="7">
+        <v>1</v>
+      </c>
+      <c r="D124" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B125" s="27" t="s">
+      <c r="B125" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="C125" s="8">
+      <c r="C125" s="7">
         <v>1.2</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B126" s="27" t="s">
+      <c r="B126" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C126" s="8">
+      <c r="C126" s="7">
         <v>1.2</v>
       </c>
-      <c r="D126" s="8">
+      <c r="D126" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B127" s="27" t="s">
+      <c r="B127" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="C127" s="8">
-        <v>1</v>
-      </c>
-      <c r="D127" s="8">
+      <c r="C127" s="7">
+        <v>1</v>
+      </c>
+      <c r="D127" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B128" s="27" t="s">
+      <c r="B128" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="C128" s="8">
+      <c r="C128" s="7">
         <v>0.8</v>
       </c>
-      <c r="D128" s="8">
+      <c r="D128" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B129" s="27" t="s">
+      <c r="B129" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C129" s="8">
+      <c r="C129" s="7">
         <v>0.8</v>
       </c>
-      <c r="D129" s="8">
+      <c r="D129" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B130" s="27" t="s">
+      <c r="B130" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="C130" s="8">
+      <c r="C130" s="7">
         <v>0.8</v>
       </c>
-      <c r="D130" s="8">
+      <c r="D130" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B131" s="27" t="s">
+      <c r="B131" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="C131" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D131" s="8">
+      <c r="C131" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D131" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B132" s="27" t="s">
+      <c r="B132" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="C132" s="8">
-        <v>1</v>
-      </c>
-      <c r="D132" s="8">
+      <c r="C132" s="7">
+        <v>1</v>
+      </c>
+      <c r="D132" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B133" s="27" t="s">
+      <c r="B133" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="C133" s="8">
-        <v>1</v>
-      </c>
-      <c r="D133" s="8">
+      <c r="C133" s="7">
+        <v>1</v>
+      </c>
+      <c r="D133" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B134" s="27"/>
+      <c r="B134" s="26"/>
     </row>
     <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A135" s="54" t="s">
+      <c r="A135" s="52" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B136" s="27" t="s">
+      <c r="B136" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="C136" s="8">
+      <c r="C136" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B137" s="27" t="s">
+      <c r="B137" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="C137" s="8">
+      <c r="C137" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B138" s="27" t="s">
+      <c r="B138" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="C138" s="8">
+      <c r="C138" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B139" s="27" t="s">
+      <c r="B139" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C139" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B140" s="27" t="s">
+      <c r="B140" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="C140" s="8">
+      <c r="C140" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B141" s="27" t="s">
+      <c r="B141" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="C141" s="8">
+      <c r="C141" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B142" s="27" t="s">
+      <c r="B142" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="C142" s="8">
+      <c r="C142" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B143" s="27" t="s">
+      <c r="B143" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="C143" s="8">
+      <c r="C143" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B144" s="27" t="s">
+      <c r="B144" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="C144" s="8">
+      <c r="C144" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B145" s="27" t="s">
+      <c r="B145" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="C145" s="8">
+      <c r="C145" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B146" s="27"/>
+      <c r="B146" s="26"/>
     </row>
     <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A147" s="56" t="s">
+      <c r="A147" s="54" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B148" s="27" t="s">
+      <c r="B148" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="C148" s="8">
+      <c r="C148" s="7">
         <v>2</v>
       </c>
-      <c r="D148" s="8">
+      <c r="D148" s="7">
         <v>2.5</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B149" s="27" t="s">
+      <c r="B149" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C149" s="8">
+      <c r="C149" s="7">
         <v>1.2</v>
       </c>
-      <c r="D149" s="8">
+      <c r="D149" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B150" s="27" t="s">
+      <c r="B150" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="C150" s="8">
-        <v>1</v>
-      </c>
-      <c r="D150" s="8">
+      <c r="C150" s="7">
+        <v>1</v>
+      </c>
+      <c r="D150" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="C151" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D151" s="8">
+      <c r="C151" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D151" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B152" s="27" t="s">
+      <c r="B152" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="C152" s="8">
+      <c r="C152" s="7">
         <v>0.8</v>
       </c>
-      <c r="D152" s="8">
+      <c r="D152" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B153" s="27" t="s">
+      <c r="B153" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C153" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D153" s="8">
+      <c r="C153" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D153" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B154" s="27" t="s">
+      <c r="B154" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="C154" s="8">
-        <v>1</v>
-      </c>
-      <c r="D154" s="8">
+      <c r="C154" s="7">
+        <v>1</v>
+      </c>
+      <c r="D154" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B155" s="27" t="s">
+      <c r="B155" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="C155" s="8">
-        <v>1</v>
-      </c>
-      <c r="D155" s="8">
+      <c r="C155" s="7">
+        <v>1</v>
+      </c>
+      <c r="D155" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B156" s="27"/>
+      <c r="B156" s="26"/>
     </row>
     <row r="157" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A157" s="54" t="s">
+      <c r="A157" s="52" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B158" s="27" t="s">
+      <c r="B158" s="26" t="s">
         <v>478</v>
       </c>
-      <c r="C158" s="8">
-        <v>1</v>
-      </c>
-      <c r="D158" s="8">
+      <c r="C158" s="7">
+        <v>1</v>
+      </c>
+      <c r="D158" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B159" s="27" t="s">
+      <c r="B159" s="26" t="s">
         <v>479</v>
       </c>
-      <c r="C159" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D159" s="8">
+      <c r="C159" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D159" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B160" s="27" t="s">
+      <c r="B160" s="26" t="s">
         <v>480</v>
       </c>
-      <c r="C160" s="8">
+      <c r="C160" s="7">
         <v>2</v>
       </c>
-      <c r="D160" s="8">
+      <c r="D160" s="7">
         <v>2.8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B161" s="27" t="s">
+      <c r="B161" s="26" t="s">
         <v>481</v>
       </c>
-      <c r="C161" s="8">
+      <c r="C161" s="7">
         <v>1.2</v>
       </c>
-      <c r="D161" s="8">
+      <c r="D161" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B162" s="27" t="s">
+      <c r="B162" s="26" t="s">
         <v>482</v>
       </c>
-      <c r="C162" s="8">
+      <c r="C162" s="7">
         <v>3</v>
       </c>
-      <c r="D162" s="8">
+      <c r="D162" s="7">
         <v>3.8</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B163" s="27" t="s">
+      <c r="B163" s="26" t="s">
         <v>483</v>
       </c>
-      <c r="C163" s="8">
+      <c r="C163" s="7">
         <v>2</v>
       </c>
-      <c r="D163" s="8">
+      <c r="D163" s="7">
         <v>1.8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B164" s="27" t="s">
+      <c r="B164" s="26" t="s">
         <v>484</v>
       </c>
-      <c r="C164" s="8">
+      <c r="C164" s="7">
         <v>1.2</v>
       </c>
-      <c r="D164" s="8">
+      <c r="D164" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B165" s="27" t="s">
+      <c r="B165" s="26" t="s">
         <v>485</v>
       </c>
-      <c r="C165" s="8">
+      <c r="C165" s="7">
         <v>2</v>
       </c>
-      <c r="D165" s="8">
+      <c r="D165" s="7">
         <v>3.5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B166" s="27" t="s">
+      <c r="B166" s="26" t="s">
         <v>486</v>
       </c>
-      <c r="C166" s="8">
+      <c r="C166" s="7">
         <v>1.8</v>
       </c>
-      <c r="D166" s="8">
+      <c r="D166" s="7">
         <v>2.5</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B167" s="27" t="s">
+      <c r="B167" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="C167" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D167" s="8">
+      <c r="C167" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D167" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B168" s="27" t="s">
+      <c r="B168" s="26" t="s">
         <v>488</v>
       </c>
-      <c r="C168" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D168" s="8">
+      <c r="C168" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D168" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B169" s="27" t="s">
+      <c r="B169" s="26" t="s">
         <v>489</v>
       </c>
-      <c r="C169" s="8">
-        <v>1</v>
-      </c>
-      <c r="D169" s="8">
+      <c r="C169" s="7">
+        <v>1</v>
+      </c>
+      <c r="D169" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B170" s="27" t="s">
+      <c r="B170" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="C170" s="8">
+      <c r="C170" s="7">
         <v>2.5</v>
       </c>
-      <c r="D170" s="8">
+      <c r="D170" s="7">
         <v>2.8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B171" s="27" t="s">
+      <c r="B171" s="26" t="s">
         <v>491</v>
       </c>
-      <c r="C171" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D171" s="8">
+      <c r="C171" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D171" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B172" s="27" t="s">
+      <c r="B172" s="26" t="s">
         <v>492</v>
       </c>
-      <c r="C172" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D172" s="8">
+      <c r="C172" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D172" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B173" s="35" t="s">
+      <c r="B173" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="C173" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D173" s="8">
+      <c r="C173" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D173" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B174" s="27"/>
+      <c r="B174" s="26"/>
     </row>
     <row r="175" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A175" s="55" t="s">
+      <c r="A175" s="53" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B176" s="27" t="s">
+      <c r="B176" s="26" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B177" s="27" t="s">
+      <c r="B177" s="26" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B178" s="27" t="s">
+      <c r="B178" s="26" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B179" s="27" t="s">
+      <c r="B179" s="26" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B180" s="27" t="s">
+      <c r="B180" s="26" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B181" s="27" t="s">
+      <c r="B181" s="26" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B182" s="27" t="s">
+      <c r="B182" s="26" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B183" s="27" t="s">
+      <c r="B183" s="26" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B184" s="27"/>
+      <c r="B184" s="26"/>
     </row>
     <row r="185" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A185" s="36" t="s">
+      <c r="A185" s="66" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B186" s="27" t="s">
+      <c r="B186" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="C186" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D186" s="8">
+      <c r="C186" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D186" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B187" s="27" t="s">
+      <c r="B187" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="C187" s="8">
+      <c r="C187" s="7">
         <v>0.6</v>
       </c>
-      <c r="D187" s="8">
+      <c r="D187" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B188" s="27" t="s">
+      <c r="B188" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="C188" s="8">
+      <c r="C188" s="7">
         <v>1.2</v>
       </c>
-      <c r="D188" s="8">
+      <c r="D188" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B189" s="27" t="s">
+      <c r="B189" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="C189" s="8">
+      <c r="C189" s="7">
         <v>0.6</v>
       </c>
-      <c r="D189" s="8">
+      <c r="D189" s="7">
         <v>0.6</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B190" s="27" t="s">
+      <c r="B190" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="C190" s="8">
+      <c r="C190" s="7">
         <v>1.2</v>
       </c>
-      <c r="D190" s="8">
+      <c r="D190" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B191" s="27" t="s">
+      <c r="B191" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="C191" s="8">
+      <c r="C191" s="7">
         <v>2</v>
       </c>
-      <c r="D191" s="8">
+      <c r="D191" s="7">
         <v>2.5</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B192" s="27" t="s">
+      <c r="B192" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C192" s="8">
+      <c r="C192" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B193" s="27" t="s">
+      <c r="B193" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="C193" s="8">
-        <v>1</v>
-      </c>
-      <c r="D193" s="8">
+      <c r="C193" s="7">
+        <v>1</v>
+      </c>
+      <c r="D193" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B194" s="27" t="s">
+      <c r="B194" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="C194" s="8">
-        <v>1</v>
-      </c>
-      <c r="D194" s="8">
+      <c r="C194" s="7">
+        <v>1</v>
+      </c>
+      <c r="D194" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A195" s="14"/>
-      <c r="B195" s="27" t="s">
+      <c r="A195" s="13"/>
+      <c r="B195" s="26" t="s">
         <v>425</v>
       </c>
-      <c r="C195" s="14">
-        <v>1</v>
-      </c>
-      <c r="D195" s="14">
+      <c r="C195" s="13">
+        <v>1</v>
+      </c>
+      <c r="D195" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A196" s="14"/>
-      <c r="B196" s="27" t="s">
+      <c r="A196" s="13"/>
+      <c r="B196" s="26" t="s">
         <v>448</v>
       </c>
-      <c r="C196" s="14">
-        <v>1</v>
-      </c>
-      <c r="D196" s="14">
+      <c r="C196" s="13">
+        <v>1</v>
+      </c>
+      <c r="D196" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A197" s="14"/>
-      <c r="B197" s="27" t="s">
+      <c r="A197" s="13"/>
+      <c r="B197" s="26" t="s">
         <v>450</v>
       </c>
-      <c r="C197" s="14">
+      <c r="C197" s="13">
         <v>1.2</v>
       </c>
-      <c r="D197" s="14">
+      <c r="D197" s="13">
         <v>1.2</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A198" s="14"/>
-      <c r="B198" s="27" t="s">
+      <c r="A198" s="13"/>
+      <c r="B198" s="26" t="s">
         <v>449</v>
       </c>
-      <c r="C198" s="14">
+      <c r="C198" s="13">
         <v>1.2</v>
       </c>
-      <c r="D198" s="14">
+      <c r="D198" s="13">
         <v>1.2</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A199" s="14"/>
-      <c r="B199" s="27" t="s">
+      <c r="A199" s="13"/>
+      <c r="B199" s="26" t="s">
         <v>451</v>
       </c>
-      <c r="C199" s="14">
-        <v>1</v>
-      </c>
-      <c r="D199" s="14">
+      <c r="C199" s="13">
+        <v>1</v>
+      </c>
+      <c r="D199" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A200" s="14"/>
-      <c r="B200" s="27" t="s">
+      <c r="A200" s="13"/>
+      <c r="B200" s="26" t="s">
         <v>452</v>
       </c>
-      <c r="C200" s="14">
+      <c r="C200" s="13">
         <v>0.5</v>
       </c>
-      <c r="D200" s="14">
+      <c r="D200" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201" s="14"/>
-      <c r="B201" s="8"/>
-      <c r="C201" s="14"/>
-      <c r="D201" s="14"/>
+      <c r="A201" s="13"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="13"/>
+      <c r="D201" s="13"/>
     </row>
     <row r="202" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A202" s="28" t="s">
+      <c r="A202" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="B202" s="27" t="s">
+      <c r="B202" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="C202" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D202" s="14">
+      <c r="C202" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D202" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="16"/>
-      <c r="B203" s="27" t="s">
+      <c r="A203" s="15"/>
+      <c r="B203" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="C203" s="14">
-        <v>1</v>
-      </c>
-      <c r="D203" s="14">
+      <c r="C203" s="13">
+        <v>1</v>
+      </c>
+      <c r="D203" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="16"/>
-      <c r="B204" s="27" t="s">
+      <c r="A204" s="15"/>
+      <c r="B204" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="C204" s="14">
-        <v>1</v>
-      </c>
-      <c r="D204" s="14">
+      <c r="C204" s="13">
+        <v>1</v>
+      </c>
+      <c r="D204" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A205" s="19"/>
-      <c r="B205" s="30" t="s">
+      <c r="A205" s="18"/>
+      <c r="B205" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="C205" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D205" s="14">
+      <c r="C205" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D205" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="16"/>
-      <c r="B206" s="27" t="s">
+      <c r="A206" s="15"/>
+      <c r="B206" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="C206" s="14">
+      <c r="C206" s="13">
         <v>2</v>
       </c>
-      <c r="D206" s="14">
+      <c r="D206" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="16" t="s">
+      <c r="A207" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="B207" s="27" t="s">
+      <c r="B207" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="C207" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D207" s="14">
+      <c r="C207" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D207" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="16"/>
-      <c r="B208" s="27" t="s">
+      <c r="A208" s="15"/>
+      <c r="B208" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="C208" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D208" s="14">
+      <c r="C208" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D208" s="13">
         <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="16"/>
-      <c r="B209" s="27" t="s">
+      <c r="A209" s="15"/>
+      <c r="B209" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="C209" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D209" s="14">
+      <c r="C209" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D209" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="16"/>
-      <c r="B210" s="27" t="s">
+      <c r="A210" s="15"/>
+      <c r="B210" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="C210" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D210" s="14">
+      <c r="C210" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D210" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="16"/>
-      <c r="B211" s="27" t="s">
+      <c r="A211" s="15"/>
+      <c r="B211" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="C211" s="14">
-        <v>1</v>
-      </c>
-      <c r="D211" s="14">
+      <c r="C211" s="13">
+        <v>1</v>
+      </c>
+      <c r="D211" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="16"/>
-      <c r="B212" s="27" t="s">
+      <c r="A212" s="15"/>
+      <c r="B212" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="C212" s="14">
+      <c r="C212" s="13">
         <v>2</v>
       </c>
-      <c r="D212" s="14">
+      <c r="D212" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="16"/>
-      <c r="B213" s="27" t="s">
+      <c r="A213" s="15"/>
+      <c r="B213" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="C213" s="14">
-        <v>1</v>
-      </c>
-      <c r="D213" s="14">
+      <c r="C213" s="13">
+        <v>1</v>
+      </c>
+      <c r="D213" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="16"/>
-      <c r="B214" s="27" t="s">
+      <c r="A214" s="15"/>
+      <c r="B214" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="C214" s="14">
+      <c r="C214" s="13">
         <v>2.5</v>
       </c>
-      <c r="D214" s="14">
+      <c r="D214" s="13">
         <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="19"/>
-      <c r="B215" s="30" t="s">
+      <c r="A215" s="18"/>
+      <c r="B215" s="29" t="s">
         <v>347</v>
       </c>
-      <c r="C215" s="14">
+      <c r="C215" s="13">
         <v>1.2</v>
       </c>
-      <c r="D215" s="14">
+      <c r="D215" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="19"/>
-      <c r="B216" s="27" t="s">
+      <c r="A216" s="18"/>
+      <c r="B216" s="26" t="s">
         <v>453</v>
       </c>
-      <c r="C216" s="14">
+      <c r="C216" s="13">
         <v>0.5</v>
       </c>
-      <c r="D216" s="14">
+      <c r="D216" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="19"/>
-      <c r="B217" s="27" t="s">
+      <c r="A217" s="18"/>
+      <c r="B217" s="26" t="s">
         <v>454</v>
       </c>
-      <c r="C217" s="14">
+      <c r="C217" s="13">
         <v>0.5</v>
       </c>
-      <c r="D217" s="14">
+      <c r="D217" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="19"/>
-      <c r="B218" s="27" t="s">
+      <c r="A218" s="18"/>
+      <c r="B218" s="26" t="s">
         <v>455</v>
       </c>
-      <c r="C218" s="14">
+      <c r="C218" s="13">
         <v>0.5</v>
       </c>
-      <c r="D218" s="14">
+      <c r="D218" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="19"/>
-      <c r="B219" s="27" t="s">
+      <c r="A219" s="18"/>
+      <c r="B219" s="26" t="s">
         <v>456</v>
       </c>
-      <c r="C219" s="14">
+      <c r="C219" s="13">
         <v>0.5</v>
       </c>
-      <c r="D219" s="14">
+      <c r="D219" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="19"/>
-      <c r="B220" s="27"/>
-      <c r="C220" s="14"/>
-      <c r="D220" s="14"/>
+      <c r="A220" s="18"/>
+      <c r="B220" s="26"/>
+      <c r="C220" s="13"/>
+      <c r="D220" s="13"/>
     </row>
     <row r="221" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="28" t="s">
+      <c r="A221" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="B221" s="27"/>
-      <c r="C221" s="14"/>
-      <c r="D221" s="14"/>
+      <c r="B221" s="26"/>
+      <c r="C221" s="13"/>
+      <c r="D221" s="13"/>
     </row>
     <row r="222" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="16"/>
-      <c r="B222" s="27" t="s">
+      <c r="A222" s="15"/>
+      <c r="B222" s="26" t="s">
         <v>457</v>
       </c>
-      <c r="C222" s="14"/>
-      <c r="D222" s="14"/>
+      <c r="C222" s="13"/>
+      <c r="D222" s="13"/>
     </row>
     <row r="223" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="16"/>
-      <c r="B223" s="27" t="s">
+      <c r="A223" s="15"/>
+      <c r="B223" s="26" t="s">
         <v>458</v>
       </c>
-      <c r="C223" s="14">
+      <c r="C223" s="13">
         <v>1.2</v>
       </c>
-      <c r="D223" s="14">
+      <c r="D223" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="16"/>
-      <c r="B224" s="27" t="s">
+      <c r="A224" s="15"/>
+      <c r="B224" s="26" t="s">
         <v>459</v>
       </c>
-      <c r="C224" s="14">
+      <c r="C224" s="13">
         <v>1.2</v>
       </c>
-      <c r="D224" s="14">
+      <c r="D224" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="16"/>
-      <c r="B225" s="27" t="s">
+      <c r="A225" s="15"/>
+      <c r="B225" s="26" t="s">
         <v>460</v>
       </c>
-      <c r="C225" s="14">
-        <v>1</v>
-      </c>
-      <c r="D225" s="14">
+      <c r="C225" s="13">
+        <v>1</v>
+      </c>
+      <c r="D225" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="16"/>
-      <c r="B226" s="27" t="s">
+      <c r="A226" s="15"/>
+      <c r="B226" s="26" t="s">
         <v>461</v>
       </c>
-      <c r="C226" s="14">
-        <v>1</v>
-      </c>
-      <c r="D226" s="14">
+      <c r="C226" s="13">
+        <v>1</v>
+      </c>
+      <c r="D226" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="16"/>
-      <c r="B227" s="27" t="s">
+      <c r="A227" s="15"/>
+      <c r="B227" s="26" t="s">
         <v>462</v>
       </c>
-      <c r="C227" s="14">
+      <c r="C227" s="13">
         <v>0.8</v>
       </c>
-      <c r="D227" s="14">
+      <c r="D227" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="16"/>
-      <c r="B228" s="27" t="s">
+      <c r="A228" s="15"/>
+      <c r="B228" s="26" t="s">
         <v>463</v>
       </c>
-      <c r="C228" s="14">
+      <c r="C228" s="13">
         <v>0.5</v>
       </c>
-      <c r="D228" s="14">
+      <c r="D228" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A229" s="8"/>
-      <c r="B229" s="27" t="s">
+      <c r="A229" s="7"/>
+      <c r="B229" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="C229" s="14">
+      <c r="C229" s="13">
         <v>0.8</v>
       </c>
-      <c r="D229" s="14">
+      <c r="D229" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="16"/>
-      <c r="B230" s="27" t="s">
+      <c r="A230" s="15"/>
+      <c r="B230" s="26" t="s">
         <v>349</v>
       </c>
-      <c r="C230" s="14">
+      <c r="C230" s="13">
         <v>1.2</v>
       </c>
-      <c r="D230" s="14">
+      <c r="D230" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="16"/>
-      <c r="B231" s="27" t="s">
+      <c r="A231" s="15"/>
+      <c r="B231" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="C231" s="14">
-        <v>1</v>
-      </c>
-      <c r="D231" s="14">
+      <c r="C231" s="13">
+        <v>1</v>
+      </c>
+      <c r="D231" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="16"/>
-      <c r="B232" s="27" t="s">
+      <c r="A232" s="15"/>
+      <c r="B232" s="26" t="s">
         <v>351</v>
       </c>
-      <c r="C232" s="14">
+      <c r="C232" s="13">
         <v>0.8</v>
       </c>
-      <c r="D232" s="14">
+      <c r="D232" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="16"/>
-      <c r="B233" s="27" t="s">
+      <c r="A233" s="15"/>
+      <c r="B233" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="C233" s="14">
+      <c r="C233" s="13">
         <v>2.5</v>
       </c>
-      <c r="D233" s="14">
+      <c r="D233" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="16"/>
-      <c r="B234" s="27" t="s">
+      <c r="A234" s="15"/>
+      <c r="B234" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="C234" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D234" s="14">
+      <c r="C234" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D234" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="16"/>
-      <c r="B235" s="27" t="s">
+      <c r="A235" s="15"/>
+      <c r="B235" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="C235" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D235" s="14">
+      <c r="C235" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D235" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="19"/>
-      <c r="B236" s="30" t="s">
+      <c r="A236" s="18"/>
+      <c r="B236" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="C236" s="14">
+      <c r="C236" s="13">
         <v>2</v>
       </c>
-      <c r="D236" s="14">
+      <c r="D236" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="16"/>
-      <c r="B237" s="27" t="s">
+      <c r="A237" s="15"/>
+      <c r="B237" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="C237" s="14">
+      <c r="C237" s="13">
         <v>1.2</v>
       </c>
-      <c r="D237" s="14">
+      <c r="D237" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="16"/>
-      <c r="B238" s="27" t="s">
+      <c r="A238" s="15"/>
+      <c r="B238" s="26" t="s">
         <v>357</v>
       </c>
-      <c r="C238" s="14">
-        <v>1</v>
-      </c>
-      <c r="D238" s="14">
+      <c r="C238" s="13">
+        <v>1</v>
+      </c>
+      <c r="D238" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A239" s="16"/>
-      <c r="B239" s="8" t="s">
+      <c r="A239" s="15"/>
+      <c r="B239" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="C239" s="14">
+      <c r="C239" s="13">
         <v>2</v>
       </c>
-      <c r="D239" s="14">
+      <c r="D239" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A240" s="16"/>
-      <c r="B240" s="8" t="s">
+      <c r="A240" s="15"/>
+      <c r="B240" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="C240" s="14">
-        <v>1</v>
-      </c>
-      <c r="D240" s="14">
+      <c r="C240" s="13">
+        <v>1</v>
+      </c>
+      <c r="D240" s="13">
         <v>1.2</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A241" s="16"/>
-      <c r="B241" s="8" t="s">
+      <c r="A241" s="15"/>
+      <c r="B241" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="C241" s="14">
-        <v>1</v>
-      </c>
-      <c r="D241" s="14">
+      <c r="C241" s="13">
+        <v>1</v>
+      </c>
+      <c r="D241" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="16"/>
-      <c r="B242" s="27"/>
-      <c r="C242" s="14"/>
-      <c r="D242" s="14"/>
+      <c r="A242" s="15"/>
+      <c r="B242" s="26"/>
+      <c r="C242" s="13"/>
+      <c r="D242" s="13"/>
     </row>
     <row r="243" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A243" s="57" t="s">
+      <c r="A243" s="55" t="s">
         <v>318</v>
       </c>
-      <c r="B243" s="27" t="s">
+      <c r="B243" s="26" t="s">
         <v>522</v>
       </c>
-      <c r="C243" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D243" s="14">
+      <c r="C243" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D243" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A244" s="16"/>
-      <c r="B244" s="27" t="s">
+      <c r="A244" s="15"/>
+      <c r="B244" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="C244" s="14">
+      <c r="C244" s="13">
         <v>0.8</v>
       </c>
-      <c r="D244" s="14">
+      <c r="D244" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A245" s="16"/>
-      <c r="B245" s="27" t="s">
+      <c r="A245" s="15"/>
+      <c r="B245" s="26" t="s">
         <v>410</v>
       </c>
-      <c r="C245" s="14">
+      <c r="C245" s="13">
         <v>0.6</v>
       </c>
-      <c r="D245" s="14">
+      <c r="D245" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A246" s="16"/>
-      <c r="B246" s="27" t="s">
+      <c r="A246" s="15"/>
+      <c r="B246" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="C246" s="14">
+      <c r="C246" s="13">
         <v>0.8</v>
       </c>
-      <c r="D246" s="14">
+      <c r="D246" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A247" s="16"/>
-      <c r="B247" s="27" t="s">
+      <c r="A247" s="15"/>
+      <c r="B247" s="26" t="s">
         <v>525</v>
       </c>
-      <c r="C247" s="14">
+      <c r="C247" s="13">
         <v>0.8</v>
       </c>
-      <c r="D247" s="14">
+      <c r="D247" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A248" s="16"/>
-      <c r="B248" s="27" t="s">
+      <c r="A248" s="15"/>
+      <c r="B248" s="26" t="s">
         <v>526</v>
       </c>
-      <c r="C248" s="14">
+      <c r="C248" s="13">
         <v>1.3</v>
       </c>
-      <c r="D248" s="14">
+      <c r="D248" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A249" s="19"/>
-      <c r="B249" s="27" t="s">
+      <c r="A249" s="18"/>
+      <c r="B249" s="26" t="s">
         <v>527</v>
       </c>
-      <c r="C249" s="14">
-        <v>1</v>
-      </c>
-      <c r="D249" s="14">
+      <c r="C249" s="13">
+        <v>1</v>
+      </c>
+      <c r="D249" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="16"/>
-      <c r="B250" s="30" t="s">
+      <c r="A250" s="15"/>
+      <c r="B250" s="29" t="s">
         <v>528</v>
       </c>
-      <c r="C250" s="14">
+      <c r="C250" s="13">
         <v>2</v>
       </c>
-      <c r="D250" s="14">
+      <c r="D250" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A251" s="16"/>
-      <c r="B251" s="27" t="s">
+      <c r="A251" s="15"/>
+      <c r="B251" s="26" t="s">
         <v>529</v>
       </c>
-      <c r="C251" s="14">
+      <c r="C251" s="13">
         <v>1.4</v>
       </c>
-      <c r="D251" s="14">
+      <c r="D251" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="16"/>
-      <c r="B252" s="27" t="s">
+      <c r="A252" s="15"/>
+      <c r="B252" s="26" t="s">
         <v>530</v>
       </c>
-      <c r="C252" s="14">
+      <c r="C252" s="13">
         <v>1.2</v>
       </c>
-      <c r="D252" s="14">
+      <c r="D252" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A253" s="16"/>
-      <c r="B253" s="27" t="s">
+      <c r="A253" s="15"/>
+      <c r="B253" s="26" t="s">
         <v>531</v>
       </c>
-      <c r="C253" s="14">
+      <c r="C253" s="13">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D253" s="14">
+      <c r="D253" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="16"/>
-      <c r="B254" s="27" t="s">
+      <c r="A254" s="15"/>
+      <c r="B254" s="26" t="s">
         <v>532</v>
       </c>
-      <c r="C254" s="14">
+      <c r="C254" s="13">
         <v>0.9</v>
       </c>
-      <c r="D254" s="14">
+      <c r="D254" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A255" s="16"/>
-      <c r="B255" s="27" t="s">
+      <c r="A255" s="15"/>
+      <c r="B255" s="26" t="s">
         <v>533</v>
       </c>
-      <c r="C255" s="14">
+      <c r="C255" s="13">
         <v>1.8</v>
       </c>
-      <c r="D255" s="14">
+      <c r="D255" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A256" s="16"/>
-      <c r="B256" s="27" t="s">
+      <c r="A256" s="15"/>
+      <c r="B256" s="26" t="s">
         <v>534</v>
       </c>
-      <c r="C256" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D256" s="14">
+      <c r="C256" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D256" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="16"/>
-      <c r="B257" s="27" t="s">
+      <c r="A257" s="15"/>
+      <c r="B257" s="26" t="s">
         <v>535</v>
       </c>
-      <c r="C257" s="14">
+      <c r="C257" s="13">
         <v>0.8</v>
       </c>
-      <c r="D257" s="14">
+      <c r="D257" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="16"/>
-      <c r="B258" s="27" t="s">
+      <c r="A258" s="15"/>
+      <c r="B258" s="26" t="s">
         <v>536</v>
       </c>
-      <c r="C258" s="14">
+      <c r="C258" s="13">
         <v>1.2</v>
       </c>
-      <c r="D258" s="14">
+      <c r="D258" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="16"/>
-      <c r="B259" s="27" t="s">
+      <c r="A259" s="15"/>
+      <c r="B259" s="26" t="s">
         <v>537</v>
       </c>
-      <c r="C259" s="14">
+      <c r="C259" s="13">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D259" s="14">
+      <c r="D259" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="16"/>
-      <c r="B260" s="27" t="s">
+      <c r="A260" s="15"/>
+      <c r="B260" s="26" t="s">
         <v>538</v>
       </c>
-      <c r="C260" s="14">
+      <c r="C260" s="13">
         <v>1.3</v>
       </c>
-      <c r="D260" s="14">
+      <c r="D260" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A261" s="16"/>
-      <c r="B261" s="27" t="s">
+      <c r="A261" s="15"/>
+      <c r="B261" s="26" t="s">
         <v>539</v>
       </c>
-      <c r="C261" s="14">
+      <c r="C261" s="13">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D261" s="14">
+      <c r="D261" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A262" s="16" t="s">
+      <c r="A262" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="B262" s="27" t="s">
+      <c r="B262" s="26" t="s">
         <v>540</v>
       </c>
-      <c r="C262" s="14">
+      <c r="C262" s="13">
         <v>0.9</v>
       </c>
-      <c r="D262" s="14">
+      <c r="D262" s="13">
         <v>3</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A263" s="16"/>
-      <c r="B263" s="27" t="s">
+      <c r="A263" s="15"/>
+      <c r="B263" s="26" t="s">
         <v>541</v>
       </c>
-      <c r="C263" s="14">
-        <v>1</v>
-      </c>
-      <c r="D263" s="14">
+      <c r="C263" s="13">
+        <v>1</v>
+      </c>
+      <c r="D263" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A264" s="16"/>
-      <c r="B264" s="27" t="s">
+      <c r="A264" s="15"/>
+      <c r="B264" s="26" t="s">
         <v>542</v>
       </c>
-      <c r="C264" s="14">
+      <c r="C264" s="13">
         <v>1.2</v>
       </c>
-      <c r="D264" s="14">
+      <c r="D264" s="13">
         <v>1.2</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A265" s="16"/>
-      <c r="B265" s="27" t="s">
+      <c r="A265" s="15"/>
+      <c r="B265" s="26" t="s">
         <v>543</v>
       </c>
-      <c r="C265" s="14">
+      <c r="C265" s="13">
         <v>2</v>
       </c>
-      <c r="D265" s="14">
+      <c r="D265" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="16"/>
-      <c r="B266" s="27" t="s">
+      <c r="A266" s="15"/>
+      <c r="B266" s="26" t="s">
         <v>544</v>
       </c>
-      <c r="C266" s="14">
+      <c r="C266" s="13">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D266" s="14">
+      <c r="D266" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="16"/>
-      <c r="B267" s="27" t="s">
+      <c r="A267" s="15"/>
+      <c r="B267" s="26" t="s">
         <v>545</v>
       </c>
-      <c r="C267" s="14">
+      <c r="C267" s="13">
         <v>1.2</v>
       </c>
-      <c r="D267" s="14">
+      <c r="D267" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A268" s="16"/>
-      <c r="B268" s="27" t="s">
+      <c r="A268" s="15"/>
+      <c r="B268" s="26" t="s">
         <v>546</v>
       </c>
-      <c r="C268" s="14">
-        <v>1</v>
-      </c>
-      <c r="D268" s="14">
+      <c r="C268" s="13">
+        <v>1</v>
+      </c>
+      <c r="D268" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="16"/>
-      <c r="B269" s="27" t="s">
+      <c r="A269" s="15"/>
+      <c r="B269" s="26" t="s">
         <v>547</v>
       </c>
-      <c r="C269" s="14">
+      <c r="C269" s="13">
         <v>2</v>
       </c>
-      <c r="D269" s="14">
+      <c r="D269" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="16"/>
-      <c r="B270" s="27"/>
-      <c r="C270" s="14"/>
-      <c r="D270" s="14"/>
+      <c r="A270" s="15"/>
+      <c r="B270" s="26"/>
+      <c r="C270" s="13"/>
+      <c r="D270" s="13"/>
     </row>
     <row r="271" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A271" s="31" t="s">
+      <c r="A271" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="B271" s="30" t="s">
+      <c r="B271" s="29" t="s">
         <v>391</v>
       </c>
-      <c r="C271" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D271" s="14">
+      <c r="C271" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D271" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A272" s="16"/>
-      <c r="B272" s="27" t="s">
+      <c r="A272" s="15"/>
+      <c r="B272" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="C272" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D272" s="14">
+      <c r="C272" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D272" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="16"/>
-      <c r="B273" s="27" t="s">
+      <c r="A273" s="15"/>
+      <c r="B273" s="26" t="s">
         <v>393</v>
       </c>
-      <c r="C273" s="14">
+      <c r="C273" s="13">
         <v>2</v>
       </c>
-      <c r="D273" s="14">
+      <c r="D273" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A274" s="16"/>
-      <c r="B274" s="27" t="s">
+      <c r="A274" s="15"/>
+      <c r="B274" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="C274" s="14">
+      <c r="C274" s="13">
         <v>2</v>
       </c>
-      <c r="D274" s="14">
+      <c r="D274" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="16"/>
-      <c r="B275" s="27" t="s">
+      <c r="A275" s="15"/>
+      <c r="B275" s="26" t="s">
         <v>395</v>
       </c>
-      <c r="C275" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D275" s="14">
+      <c r="C275" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D275" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="16"/>
-      <c r="B276" s="27" t="s">
+      <c r="A276" s="15"/>
+      <c r="B276" s="26" t="s">
         <v>396</v>
       </c>
-      <c r="C276" s="14">
-        <v>1</v>
-      </c>
-      <c r="D276" s="14">
+      <c r="C276" s="13">
+        <v>1</v>
+      </c>
+      <c r="D276" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="16"/>
-      <c r="B277" s="27" t="s">
+      <c r="A277" s="15"/>
+      <c r="B277" s="26" t="s">
         <v>397</v>
       </c>
-      <c r="C277" s="14">
+      <c r="C277" s="13">
         <v>2</v>
       </c>
-      <c r="D277" s="14">
+      <c r="D277" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="16"/>
-      <c r="B278" s="27" t="s">
+      <c r="A278" s="15"/>
+      <c r="B278" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="C278" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D278" s="14">
+      <c r="C278" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D278" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="16" t="s">
+      <c r="A279" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="B279" s="27" t="s">
+      <c r="B279" s="26" t="s">
         <v>430</v>
       </c>
-      <c r="C279" s="14">
-        <v>1</v>
-      </c>
-      <c r="D279" s="14">
+      <c r="C279" s="13">
+        <v>1</v>
+      </c>
+      <c r="D279" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="16"/>
-      <c r="B280" s="27" t="s">
+      <c r="A280" s="15"/>
+      <c r="B280" s="26" t="s">
         <v>431</v>
       </c>
-      <c r="C280" s="14">
-        <v>1</v>
-      </c>
-      <c r="D280" s="14">
+      <c r="C280" s="13">
+        <v>1</v>
+      </c>
+      <c r="D280" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="16"/>
-      <c r="B281" s="27" t="s">
+      <c r="A281" s="15"/>
+      <c r="B281" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="C281" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D281" s="14">
+      <c r="C281" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D281" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="16"/>
-      <c r="B282" s="27"/>
-      <c r="C282" s="14"/>
-      <c r="D282" s="14"/>
+      <c r="A282" s="15"/>
+      <c r="B282" s="26"/>
+      <c r="C282" s="13"/>
+      <c r="D282" s="13"/>
     </row>
     <row r="283" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A283" s="28" t="s">
+      <c r="A283" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="B283" s="27" t="s">
+      <c r="B283" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="C283" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D283" s="14">
+      <c r="C283" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D283" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="16"/>
-      <c r="B284" s="27" t="s">
+      <c r="A284" s="15"/>
+      <c r="B284" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="C284" s="14">
-        <v>1</v>
-      </c>
-      <c r="D284" s="14">
+      <c r="C284" s="13">
+        <v>1</v>
+      </c>
+      <c r="D284" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="19"/>
-      <c r="B285" s="30" t="s">
+      <c r="A285" s="18"/>
+      <c r="B285" s="29" t="s">
         <v>360</v>
       </c>
-      <c r="C285" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D285" s="14">
+      <c r="C285" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D285" s="13">
         <v>1.2</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="16"/>
-      <c r="B286" s="27" t="s">
+      <c r="A286" s="15"/>
+      <c r="B286" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="C286" s="14">
+      <c r="C286" s="13">
         <v>2</v>
       </c>
-      <c r="D286" s="14">
+      <c r="D286" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="16"/>
-      <c r="B287" s="27" t="s">
+      <c r="A287" s="15"/>
+      <c r="B287" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="C287" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D287" s="14">
+      <c r="C287" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D287" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="16"/>
-      <c r="B288" s="27" t="s">
+      <c r="A288" s="15"/>
+      <c r="B288" s="26" t="s">
         <v>363</v>
       </c>
-      <c r="C288" s="14">
+      <c r="C288" s="13">
         <v>2.5</v>
       </c>
-      <c r="D288" s="14">
+      <c r="D288" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="16"/>
-      <c r="B289" s="27" t="s">
+      <c r="A289" s="15"/>
+      <c r="B289" s="26" t="s">
         <v>364</v>
       </c>
-      <c r="C289" s="14">
+      <c r="C289" s="13">
         <v>2</v>
       </c>
-      <c r="D289" s="14">
+      <c r="D289" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="16"/>
-      <c r="B290" s="27" t="s">
+      <c r="A290" s="15"/>
+      <c r="B290" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="C290" s="14">
-        <v>1</v>
-      </c>
-      <c r="D290" s="14">
+      <c r="C290" s="13">
+        <v>1</v>
+      </c>
+      <c r="D290" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="16"/>
-      <c r="B291" s="27" t="s">
+      <c r="A291" s="15"/>
+      <c r="B291" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="C291" s="14">
+      <c r="C291" s="13">
         <v>1.2</v>
       </c>
-      <c r="D291" s="14">
+      <c r="D291" s="13">
         <v>1.2</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="16"/>
-      <c r="B292" s="27" t="s">
+      <c r="A292" s="15"/>
+      <c r="B292" s="26" t="s">
         <v>426</v>
       </c>
-      <c r="C292" s="14">
-        <v>1</v>
-      </c>
-      <c r="D292" s="14">
+      <c r="C292" s="13">
+        <v>1</v>
+      </c>
+      <c r="D292" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="16"/>
-      <c r="B293" s="27" t="s">
+      <c r="A293" s="15"/>
+      <c r="B293" s="26" t="s">
         <v>427</v>
       </c>
-      <c r="C293" s="14">
+      <c r="C293" s="13">
         <v>0.8</v>
       </c>
-      <c r="D293" s="14">
+      <c r="D293" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="16"/>
-      <c r="B294" s="27" t="s">
+      <c r="A294" s="15"/>
+      <c r="B294" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="C294" s="14">
+      <c r="C294" s="13">
         <v>0.5</v>
       </c>
-      <c r="D294" s="14">
+      <c r="D294" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="16"/>
-      <c r="B295" s="27"/>
-      <c r="C295" s="14"/>
-      <c r="D295" s="14"/>
+      <c r="A295" s="15"/>
+      <c r="B295" s="26"/>
+      <c r="C295" s="13"/>
+      <c r="D295" s="13"/>
     </row>
     <row r="296" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="16" t="s">
+      <c r="A296" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="B296" s="27"/>
-      <c r="C296" s="14"/>
-      <c r="D296" s="14"/>
+      <c r="B296" s="26"/>
+      <c r="C296" s="13"/>
+      <c r="D296" s="13"/>
     </row>
     <row r="297" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A297" s="28" t="s">
+      <c r="A297" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="B297" s="27" t="s">
+      <c r="B297" s="26" t="s">
         <v>367</v>
       </c>
-      <c r="C297" s="14">
+      <c r="C297" s="13">
         <v>2</v>
       </c>
-      <c r="D297" s="14">
+      <c r="D297" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A298" s="19"/>
-      <c r="B298" s="30" t="s">
+      <c r="A298" s="18"/>
+      <c r="B298" s="29" t="s">
         <v>368</v>
       </c>
-      <c r="C298" s="14">
+      <c r="C298" s="13">
         <v>2</v>
       </c>
-      <c r="D298" s="14">
+      <c r="D298" s="13">
         <v>3</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A299" s="16"/>
-      <c r="B299" s="27" t="s">
+      <c r="A299" s="15"/>
+      <c r="B299" s="26" t="s">
         <v>369</v>
       </c>
-      <c r="C299" s="14">
+      <c r="C299" s="13">
         <v>2.5</v>
       </c>
-      <c r="D299" s="14">
+      <c r="D299" s="13">
         <v>3.8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A300" s="16"/>
-      <c r="B300" s="27" t="s">
+      <c r="A300" s="15"/>
+      <c r="B300" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="C300" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D300" s="14">
+      <c r="C300" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D300" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="16"/>
-      <c r="B301" s="27" t="s">
+      <c r="A301" s="15"/>
+      <c r="B301" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="C301" s="14">
+      <c r="C301" s="13">
         <v>2</v>
       </c>
-      <c r="D301" s="14">
+      <c r="D301" s="13">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A302" s="16"/>
-      <c r="B302" s="27" t="s">
+      <c r="A302" s="15"/>
+      <c r="B302" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="C302" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D302" s="14">
+      <c r="C302" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D302" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="16"/>
-      <c r="B303" s="27" t="s">
+      <c r="A303" s="15"/>
+      <c r="B303" s="26" t="s">
         <v>373</v>
       </c>
-      <c r="C303" s="14">
+      <c r="C303" s="13">
         <v>2</v>
       </c>
-      <c r="D303" s="14">
+      <c r="D303" s="13">
         <v>3.5</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A304" s="16"/>
-      <c r="B304" s="27" t="s">
+      <c r="A304" s="15"/>
+      <c r="B304" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="C304" s="14">
+      <c r="C304" s="13">
         <v>2</v>
       </c>
-      <c r="D304" s="14">
+      <c r="D304" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="16"/>
-      <c r="B305" s="27" t="s">
+      <c r="A305" s="15"/>
+      <c r="B305" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="C305" s="14">
+      <c r="C305" s="13">
         <v>2</v>
       </c>
-      <c r="D305" s="14">
+      <c r="D305" s="13">
         <v>2.8</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A306" s="16"/>
-      <c r="B306" s="27" t="s">
+      <c r="A306" s="15"/>
+      <c r="B306" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="C306" s="14">
+      <c r="C306" s="13">
         <v>2</v>
       </c>
-      <c r="D306" s="14">
+      <c r="D306" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A307" s="19"/>
-      <c r="B307" s="30" t="s">
+      <c r="A307" s="18"/>
+      <c r="B307" s="29" t="s">
         <v>377</v>
       </c>
-      <c r="C307" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D307" s="14">
+      <c r="C307" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D307" s="13">
         <v>1.2</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="16"/>
-      <c r="B308" s="27" t="s">
+      <c r="A308" s="15"/>
+      <c r="B308" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="C308" s="14">
-        <v>1</v>
-      </c>
-      <c r="D308" s="14">
+      <c r="C308" s="13">
+        <v>1</v>
+      </c>
+      <c r="D308" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A309" s="16"/>
-      <c r="B309" s="27" t="s">
+      <c r="A309" s="15"/>
+      <c r="B309" s="26" t="s">
         <v>379</v>
       </c>
-      <c r="C309" s="14">
+      <c r="C309" s="13">
         <v>3</v>
       </c>
-      <c r="D309" s="14">
+      <c r="D309" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A310" s="16"/>
-      <c r="B310" s="27" t="s">
+      <c r="A310" s="15"/>
+      <c r="B310" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="C310" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D310" s="14">
+      <c r="C310" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D310" s="13">
         <v>2.8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A311" s="16"/>
-      <c r="B311" s="27" t="s">
+      <c r="A311" s="15"/>
+      <c r="B311" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="C311" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D311" s="14">
+      <c r="C311" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D311" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A312" s="16"/>
-      <c r="B312" s="27" t="s">
+      <c r="A312" s="15"/>
+      <c r="B312" s="26" t="s">
         <v>432</v>
       </c>
-      <c r="C312" s="8">
+      <c r="C312" s="7">
         <v>2</v>
       </c>
-      <c r="D312" s="14">
+      <c r="D312" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A313" s="16"/>
-      <c r="B313" s="27" t="s">
+      <c r="A313" s="15"/>
+      <c r="B313" s="26" t="s">
         <v>433</v>
       </c>
-      <c r="C313" s="8">
-        <v>1</v>
-      </c>
-      <c r="D313" s="14">
+      <c r="C313" s="7">
+        <v>1</v>
+      </c>
+      <c r="D313" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A314" s="16"/>
-      <c r="B314" s="27" t="s">
+      <c r="A314" s="15"/>
+      <c r="B314" s="26" t="s">
         <v>434</v>
       </c>
-      <c r="C314" s="8">
-        <v>1</v>
-      </c>
-      <c r="D314" s="14">
+      <c r="C314" s="7">
+        <v>1</v>
+      </c>
+      <c r="D314" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="16" t="s">
+      <c r="A315" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="B315" s="27"/>
-      <c r="C315" s="14"/>
-      <c r="D315" s="14"/>
+      <c r="B315" s="26"/>
+      <c r="C315" s="13"/>
+      <c r="D315" s="13"/>
     </row>
     <row r="316" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A316" s="28" t="s">
+      <c r="A316" s="27" t="s">
         <v>328</v>
       </c>
-      <c r="B316" s="18" t="s">
+      <c r="B316" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="C316" s="14">
+      <c r="C316" s="13">
         <v>0.8</v>
       </c>
-      <c r="D316" s="14">
+      <c r="D316" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A317" s="16"/>
-      <c r="B317" s="18" t="s">
+      <c r="A317" s="15"/>
+      <c r="B317" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="C317" s="14">
+      <c r="C317" s="13">
         <v>2</v>
       </c>
-      <c r="D317" s="14">
+      <c r="D317" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="16"/>
-      <c r="B318" s="18" t="s">
+      <c r="A318" s="15"/>
+      <c r="B318" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="C318" s="14">
+      <c r="C318" s="13">
         <v>1.2</v>
       </c>
-      <c r="D318" s="14">
+      <c r="D318" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A319" s="19"/>
-      <c r="B319" s="14" t="s">
+      <c r="A319" s="18"/>
+      <c r="B319" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="C319" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D319" s="14">
+      <c r="C319" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D319" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A320" s="16"/>
-      <c r="B320" s="18" t="s">
+      <c r="A320" s="15"/>
+      <c r="B320" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="C320" s="14">
+      <c r="C320" s="13">
         <v>2.5</v>
       </c>
-      <c r="D320" s="14">
+      <c r="D320" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A321" s="16"/>
-      <c r="B321" s="18" t="s">
+      <c r="A321" s="15"/>
+      <c r="B321" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="C321" s="14">
+      <c r="C321" s="13">
         <v>2</v>
       </c>
-      <c r="D321" s="14">
+      <c r="D321" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A322" s="16"/>
-      <c r="B322" s="18" t="s">
+      <c r="A322" s="15"/>
+      <c r="B322" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="C322" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D322" s="14">
+      <c r="C322" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D322" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A323" s="16"/>
-      <c r="B323" s="18" t="s">
+      <c r="A323" s="15"/>
+      <c r="B323" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="C323" s="14">
+      <c r="C323" s="13">
         <v>3</v>
       </c>
-      <c r="D323" s="14">
+      <c r="D323" s="13">
         <v>3.5</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A324" s="16"/>
-      <c r="B324" s="18" t="s">
+      <c r="A324" s="15"/>
+      <c r="B324" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="C324" s="14">
+      <c r="C324" s="13">
         <v>1.2</v>
       </c>
-      <c r="D324" s="14">
+      <c r="D324" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A325" s="16"/>
-      <c r="B325" s="18" t="s">
+      <c r="A325" s="15"/>
+      <c r="B325" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="C325" s="14">
+      <c r="C325" s="13">
         <v>1.2</v>
       </c>
-      <c r="D325" s="14">
+      <c r="D325" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A326" s="16"/>
-      <c r="B326" s="18" t="s">
+      <c r="A326" s="15"/>
+      <c r="B326" s="17" t="s">
         <v>435</v>
       </c>
-      <c r="C326" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D326" s="14">
+      <c r="C326" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D326" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A327" s="16"/>
-      <c r="B327" s="18" t="s">
+      <c r="A327" s="15"/>
+      <c r="B327" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="C327" s="14">
-        <v>1</v>
-      </c>
-      <c r="D327" s="8">
+      <c r="C327" s="13">
+        <v>1</v>
+      </c>
+      <c r="D327" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B328" s="18" t="s">
+      <c r="B328" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="C328" s="14">
-        <v>1</v>
-      </c>
-      <c r="D328" s="8">
+      <c r="C328" s="13">
+        <v>1</v>
+      </c>
+      <c r="D328" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A329" s="54" t="s">
+      <c r="A329" s="52" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B330" s="27" t="s">
+      <c r="B330" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="C330" s="8">
+      <c r="C330" s="7">
         <v>1.2</v>
       </c>
-      <c r="D330" s="8">
+      <c r="D330" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B331" s="27" t="s">
+      <c r="B331" s="26" t="s">
         <v>498</v>
       </c>
-      <c r="C331" s="8">
+      <c r="C331" s="7">
         <v>2</v>
       </c>
-      <c r="D331" s="8">
+      <c r="D331" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B332" s="27" t="s">
+      <c r="B332" s="26" t="s">
         <v>499</v>
       </c>
-      <c r="C332" s="8">
-        <v>1</v>
-      </c>
-      <c r="D332" s="8">
+      <c r="C332" s="7">
+        <v>1</v>
+      </c>
+      <c r="D332" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B333" s="27" t="s">
+      <c r="B333" s="26" t="s">
         <v>500</v>
       </c>
-      <c r="C333" s="8">
+      <c r="C333" s="7">
         <v>1.2</v>
       </c>
-      <c r="D333" s="8">
+      <c r="D333" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B334" s="27" t="s">
+      <c r="B334" s="26" t="s">
         <v>501</v>
       </c>
-      <c r="C334" s="8">
-        <v>1</v>
-      </c>
-      <c r="D334" s="8">
+      <c r="C334" s="7">
+        <v>1</v>
+      </c>
+      <c r="D334" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B335" s="27" t="s">
+      <c r="B335" s="26" t="s">
         <v>506</v>
       </c>
-      <c r="C335" s="8">
+      <c r="C335" s="7">
         <v>0.8</v>
       </c>
-      <c r="D335" s="8">
+      <c r="D335" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B336" s="27" t="s">
+      <c r="B336" s="26" t="s">
         <v>502</v>
       </c>
-      <c r="C336" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D336" s="8">
+      <c r="C336" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D336" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B337" s="27" t="s">
+      <c r="B337" s="26" t="s">
         <v>505</v>
       </c>
-      <c r="C337" s="8">
-        <v>1</v>
-      </c>
-      <c r="D337" s="8">
+      <c r="C337" s="7">
+        <v>1</v>
+      </c>
+      <c r="D337" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B338" s="35" t="s">
+      <c r="B338" s="34" t="s">
         <v>503</v>
       </c>
-      <c r="C338" s="58">
+      <c r="C338" s="56">
         <v>0.8</v>
       </c>
-      <c r="D338" s="8">
+      <c r="D338" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B339" s="35" t="s">
+      <c r="B339" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="C339" s="58">
-        <v>1</v>
-      </c>
-      <c r="D339" s="8">
+      <c r="C339" s="56">
+        <v>1</v>
+      </c>
+      <c r="D339" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C340" s="58"/>
+      <c r="C340" s="56"/>
     </row>
     <row r="341" spans="1:4" ht="19" x14ac:dyDescent="0.2">
-      <c r="A341" s="43" t="s">
+      <c r="A341" s="41" t="s">
         <v>507</v>
       </c>
-      <c r="C341" s="58"/>
+      <c r="C341" s="56"/>
     </row>
     <row r="342" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B342" s="35" t="s">
+      <c r="B342" s="34" t="s">
         <v>510</v>
       </c>
-      <c r="C342" s="58">
-        <v>1</v>
-      </c>
-      <c r="D342" s="8">
+      <c r="C342" s="56">
+        <v>1</v>
+      </c>
+      <c r="D342" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B343" s="35" t="s">
+      <c r="B343" s="34" t="s">
         <v>511</v>
       </c>
-      <c r="C343" s="58">
+      <c r="C343" s="56">
         <v>2.5</v>
       </c>
-      <c r="D343" s="8">
+      <c r="D343" s="7">
         <v>3.5</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B344" s="35" t="s">
+      <c r="B344" s="34" t="s">
         <v>512</v>
       </c>
-      <c r="C344" s="58">
+      <c r="C344" s="56">
         <v>0.8</v>
       </c>
-      <c r="D344" s="8">
+      <c r="D344" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B345" s="35" t="s">
+      <c r="B345" s="34" t="s">
         <v>513</v>
       </c>
-      <c r="C345" s="58">
+      <c r="C345" s="56">
         <v>0.8</v>
       </c>
-      <c r="D345" s="8">
+      <c r="D345" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B346" s="35" t="s">
+      <c r="B346" s="34" t="s">
         <v>514</v>
       </c>
-      <c r="C346" s="58">
-        <v>1</v>
-      </c>
-      <c r="D346" s="8">
+      <c r="C346" s="56">
+        <v>1</v>
+      </c>
+      <c r="D346" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A347" s="25" t="s">
+      <c r="A347" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="B347" s="35" t="s">
+      <c r="B347" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="C347" s="58">
+      <c r="C347" s="56">
         <v>0.8</v>
       </c>
-      <c r="D347" s="8">
+      <c r="D347" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B348" s="35" t="s">
+      <c r="B348" s="34" t="s">
         <v>516</v>
       </c>
-      <c r="C348" s="58">
+      <c r="C348" s="56">
         <v>0.8</v>
       </c>
-      <c r="D348" s="8">
+      <c r="D348" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B349" s="35" t="s">
+      <c r="B349" s="34" t="s">
         <v>517</v>
       </c>
-      <c r="C349" s="58">
+      <c r="C349" s="56">
         <v>0.5</v>
       </c>
-      <c r="D349" s="8">
+      <c r="D349" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B350" s="35" t="s">
+      <c r="B350" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="C350" s="58">
+      <c r="C350" s="56">
         <v>1.8</v>
       </c>
-      <c r="D350" s="8">
+      <c r="D350" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B351" s="35" t="s">
+      <c r="B351" s="34" t="s">
         <v>519</v>
       </c>
-      <c r="C351" s="58">
-        <v>1</v>
-      </c>
-      <c r="D351" s="8">
+      <c r="C351" s="56">
+        <v>1</v>
+      </c>
+      <c r="D351" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B352" s="27" t="s">
+      <c r="B352" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="C352" s="58">
-        <v>1</v>
-      </c>
-      <c r="D352" s="8">
+      <c r="C352" s="56">
+        <v>1</v>
+      </c>
+      <c r="D352" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B353" s="27" t="s">
+      <c r="B353" s="26" t="s">
         <v>521</v>
       </c>
-      <c r="C353" s="58">
-        <v>1</v>
-      </c>
-      <c r="D353" s="8">
+      <c r="C353" s="56">
+        <v>1</v>
+      </c>
+      <c r="D353" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B354" s="27"/>
+      <c r="B354" s="26"/>
     </row>
     <row r="355" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A355" s="34" t="s">
+      <c r="A355" s="67" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B356" s="27" t="s">
+      <c r="B356" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="C356" s="8">
+      <c r="C356" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B357" s="27" t="s">
+      <c r="B357" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="C357" s="8">
+      <c r="C357" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B358" s="27" t="s">
+      <c r="B358" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="C358" s="8">
+      <c r="C358" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B359" s="27" t="s">
+      <c r="B359" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C359" s="8">
+      <c r="C359" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B360" s="27" t="s">
+      <c r="B360" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="C360" s="8">
+      <c r="C360" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B361" s="27" t="s">
+      <c r="B361" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="C361" s="8">
+      <c r="C361" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B362" s="27" t="s">
+      <c r="B362" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="C362" s="8">
+      <c r="C362" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B363" s="27"/>
+      <c r="B363" s="26"/>
     </row>
     <row r="364" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A364" s="28" t="s">
+      <c r="A364" s="27" t="s">
         <v>331</v>
       </c>
-      <c r="B364" s="27" t="s">
+      <c r="B364" s="26" t="s">
         <v>398</v>
       </c>
-      <c r="C364" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D364" s="14">
+      <c r="C364" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D364" s="13">
         <v>1.2</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B365" s="27" t="s">
+      <c r="B365" s="26" t="s">
         <v>399</v>
       </c>
-      <c r="C365" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D365" s="14">
+      <c r="C365" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D365" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A366" s="16"/>
-      <c r="B366" s="27" t="s">
+      <c r="A366" s="15"/>
+      <c r="B366" s="26" t="s">
         <v>400</v>
       </c>
-      <c r="C366" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D366" s="14">
+      <c r="C366" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D366" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A367" s="16"/>
-      <c r="B367" s="27" t="s">
+      <c r="A367" s="15"/>
+      <c r="B367" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="C367" s="14">
+      <c r="C367" s="13">
         <v>2</v>
       </c>
-      <c r="D367" s="14">
+      <c r="D367" s="13">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A368" s="16"/>
-      <c r="B368" s="27" t="s">
+      <c r="A368" s="15"/>
+      <c r="B368" s="26" t="s">
         <v>402</v>
       </c>
-      <c r="C368" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D368" s="14">
+      <c r="C368" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D368" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A369" s="16"/>
-      <c r="B369" s="27" t="s">
+      <c r="A369" s="15"/>
+      <c r="B369" s="26" t="s">
         <v>403</v>
       </c>
-      <c r="C369" s="14">
+      <c r="C369" s="13">
         <v>1.2</v>
       </c>
-      <c r="D369" s="14">
+      <c r="D369" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A370" s="16"/>
-      <c r="B370" s="27" t="s">
+      <c r="A370" s="15"/>
+      <c r="B370" s="26" t="s">
         <v>404</v>
       </c>
-      <c r="C370" s="14">
-        <v>1</v>
-      </c>
-      <c r="D370" s="14">
+      <c r="C370" s="13">
+        <v>1</v>
+      </c>
+      <c r="D370" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A371" s="16"/>
-      <c r="B371" s="27" t="s">
+      <c r="A371" s="15"/>
+      <c r="B371" s="26" t="s">
         <v>405</v>
       </c>
-      <c r="C371" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D371" s="14">
+      <c r="C371" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D371" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A372" s="16"/>
-      <c r="B372" s="27" t="s">
+      <c r="A372" s="15"/>
+      <c r="B372" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="C372" s="14">
+      <c r="C372" s="13">
         <v>2</v>
       </c>
-      <c r="D372" s="14">
+      <c r="D372" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A373" s="16"/>
-      <c r="B373" s="27" t="s">
+      <c r="A373" s="15"/>
+      <c r="B373" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="C373" s="14">
-        <v>1</v>
-      </c>
-      <c r="D373" s="14">
+      <c r="C373" s="13">
+        <v>1</v>
+      </c>
+      <c r="D373" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A374" s="16"/>
-      <c r="B374" s="27" t="s">
+      <c r="A374" s="15"/>
+      <c r="B374" s="26" t="s">
         <v>438</v>
       </c>
-      <c r="C374" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D374" s="14">
+      <c r="C374" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D374" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A375" s="16"/>
-      <c r="B375" s="27" t="s">
+      <c r="A375" s="15"/>
+      <c r="B375" s="26" t="s">
         <v>439</v>
       </c>
-      <c r="C375" s="8">
-        <v>1</v>
-      </c>
-      <c r="D375" s="14">
+      <c r="C375" s="7">
+        <v>1</v>
+      </c>
+      <c r="D375" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A376" s="16"/>
-      <c r="B376" s="27" t="s">
+      <c r="A376" s="15"/>
+      <c r="B376" s="26" t="s">
         <v>440</v>
       </c>
-      <c r="C376" s="8">
-        <v>1</v>
-      </c>
-      <c r="D376" s="8">
+      <c r="C376" s="7">
+        <v>1</v>
+      </c>
+      <c r="D376" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A377" s="16"/>
-      <c r="B377" s="27"/>
+      <c r="A377" s="15"/>
+      <c r="B377" s="26"/>
     </row>
     <row r="378" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A378" s="34" t="s">
+      <c r="A378" s="53" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B379" s="27" t="s">
+      <c r="B379" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="C379" s="8">
+      <c r="C379" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B380" s="27" t="s">
+      <c r="B380" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="C380" s="8">
+      <c r="C380" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B381" s="27" t="s">
+      <c r="B381" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C381" s="8">
+      <c r="C381" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B382" s="27" t="s">
+      <c r="B382" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="C382" s="8">
+      <c r="C382" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B383" s="27" t="s">
+      <c r="B383" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="C383" s="8">
+      <c r="C383" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B384" s="27" t="s">
+      <c r="B384" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="C384" s="8">
+      <c r="C384" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B385" s="27" t="s">
+      <c r="B385" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="C385" s="8">
+      <c r="C385" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B386" s="27" t="s">
+      <c r="B386" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C386" s="8">
+      <c r="C386" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B387" s="27" t="s">
+      <c r="B387" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="C387" s="8">
+      <c r="C387" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B388" s="27"/>
+      <c r="B388" s="26"/>
     </row>
     <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A389" s="34" t="s">
+      <c r="A389" s="33" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B390" s="27" t="s">
+      <c r="B390" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="C390" s="8">
+      <c r="C390" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B391" s="27" t="s">
+      <c r="B391" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C391" s="8">
+      <c r="C391" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B392" s="27" t="s">
+      <c r="B392" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C392" s="8">
+      <c r="C392" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B393" s="27" t="s">
+      <c r="B393" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="C393" s="8">
+      <c r="C393" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B394" s="27" t="s">
+      <c r="B394" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C394" s="8">
+      <c r="C394" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B395" s="27" t="s">
+      <c r="B395" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="C395" s="8">
+      <c r="C395" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B396" s="27" t="s">
+      <c r="B396" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="C396" s="8">
+      <c r="C396" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B397" s="27"/>
+      <c r="B397" s="26"/>
     </row>
     <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A398" s="34" t="s">
+      <c r="A398" s="33" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B399" s="27" t="s">
+      <c r="B399" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="C399" s="8">
+      <c r="C399" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B400" s="27" t="s">
+      <c r="B400" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="C400" s="8">
+      <c r="C400" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B401" s="27" t="s">
+      <c r="B401" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C401" s="8">
+      <c r="C401" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B402" s="27" t="s">
+      <c r="B402" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="C402" s="8">
+      <c r="C402" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B403" s="27" t="s">
+      <c r="B403" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="C403" s="8">
+      <c r="C403" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B404" s="27" t="s">
+      <c r="B404" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="C404" s="8">
+      <c r="C404" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B405" s="27" t="s">
+      <c r="B405" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C405" s="8">
+      <c r="C405" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B406" s="27"/>
+      <c r="B406" s="26"/>
     </row>
     <row r="407" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A407" s="34" t="s">
+      <c r="A407" s="33" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B408" s="27" t="s">
+      <c r="B408" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="C408" s="8">
+      <c r="C408" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B409" s="27" t="s">
+      <c r="B409" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="C409" s="8">
+      <c r="C409" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B410" s="27" t="s">
+      <c r="B410" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="C410" s="8">
+      <c r="C410" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B411" s="27" t="s">
+      <c r="B411" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="C411" s="8">
+      <c r="C411" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B412" s="27" t="s">
+      <c r="B412" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="C412" s="8">
+      <c r="C412" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B413" s="27" t="s">
+      <c r="B413" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="C413" s="8">
+      <c r="C413" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B414" s="27" t="s">
+      <c r="B414" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C414" s="8">
+      <c r="C414" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B415" s="27"/>
+      <c r="B415" s="26"/>
     </row>
     <row r="416" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A416" s="34" t="s">
+      <c r="A416" s="33" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B417" s="27" t="s">
+      <c r="B417" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="C417" s="8">
+      <c r="C417" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B418" s="27" t="s">
+      <c r="B418" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="C418" s="8">
+      <c r="C418" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B419" s="27" t="s">
+      <c r="B419" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="C419" s="8">
+      <c r="C419" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B420" s="27" t="s">
+      <c r="B420" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="C420" s="8">
+      <c r="C420" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B421" s="27" t="s">
+      <c r="B421" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="C421" s="8">
+      <c r="C421" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B422" s="27" t="s">
+      <c r="B422" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="C422" s="8">
+      <c r="C422" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B423" s="27"/>
+      <c r="B423" s="26"/>
     </row>
     <row r="424" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A424" s="34" t="s">
+      <c r="A424" s="33" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B425" s="27" t="s">
+      <c r="B425" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="C425" s="8">
+      <c r="C425" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B426" s="27" t="s">
+      <c r="B426" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="C426" s="8">
+      <c r="C426" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B427" s="27" t="s">
+      <c r="B427" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="C427" s="8">
+      <c r="C427" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B428" s="27" t="s">
+      <c r="B428" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="C428" s="8">
+      <c r="C428" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B429" s="27" t="s">
+      <c r="B429" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="C429" s="8">
+      <c r="C429" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B430" s="27" t="s">
+      <c r="B430" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="C430" s="8">
+      <c r="C430" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B431" s="27" t="s">
+      <c r="B431" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="C431" s="8">
+      <c r="C431" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B432" s="27"/>
+      <c r="B432" s="26"/>
     </row>
     <row r="433" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A433" s="34" t="s">
+      <c r="A433" s="33" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B434" s="27" t="s">
+      <c r="B434" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="C434" s="8">
+      <c r="C434" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B435" s="27" t="s">
+      <c r="B435" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="C435" s="8">
+      <c r="C435" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B436" s="27" t="s">
+      <c r="B436" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="C436" s="8">
+      <c r="C436" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B437" s="27" t="s">
+      <c r="B437" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="C437" s="8">
+      <c r="C437" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B438" s="27" t="s">
+      <c r="B438" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="C438" s="8">
+      <c r="C438" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B439" s="27" t="s">
+      <c r="B439" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="C439" s="8">
+      <c r="C439" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B440" s="27" t="s">
+      <c r="B440" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="C440" s="8">
+      <c r="C440" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B441" s="27"/>
+      <c r="B441" s="26"/>
     </row>
     <row r="442" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A442" s="34" t="s">
+      <c r="A442" s="33" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B443" s="27" t="s">
+      <c r="B443" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="C443" s="8">
+      <c r="C443" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B444" s="27" t="s">
+      <c r="B444" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="C444" s="8">
+      <c r="C444" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B445" s="27" t="s">
+      <c r="B445" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="C445" s="8">
+      <c r="C445" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B446" s="27" t="s">
+      <c r="B446" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="C446" s="8">
+      <c r="C446" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B447" s="27" t="s">
+      <c r="B447" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="C447" s="8">
+      <c r="C447" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B448" s="27"/>
-      <c r="D448" s="14"/>
+      <c r="B448" s="26"/>
+      <c r="D448" s="13"/>
     </row>
     <row r="449" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A449" s="28" t="s">
+      <c r="A449" s="27" t="s">
         <v>421</v>
       </c>
-      <c r="B449" s="30" t="s">
+      <c r="B449" s="29" t="s">
         <v>445</v>
       </c>
-      <c r="C449" s="14">
+      <c r="C449" s="13">
         <v>1.2</v>
       </c>
-      <c r="D449" s="14">
+      <c r="D449" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A450" s="16"/>
-      <c r="B450" s="30" t="s">
+      <c r="A450" s="15"/>
+      <c r="B450" s="29" t="s">
         <v>411</v>
       </c>
-      <c r="C450" s="14">
+      <c r="C450" s="13">
         <v>1.2</v>
       </c>
-      <c r="D450" s="14">
+      <c r="D450" s="13">
         <v>0.8</v>
       </c>
     </row>
     <row r="451" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A451" s="16"/>
-      <c r="B451" s="30" t="s">
+      <c r="A451" s="15"/>
+      <c r="B451" s="29" t="s">
         <v>412</v>
       </c>
-      <c r="C451" s="14">
+      <c r="C451" s="13">
         <v>0.8</v>
       </c>
-      <c r="D451" s="14">
+      <c r="D451" s="13">
         <v>0.5</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A452" s="16"/>
-      <c r="B452" s="30" t="s">
+      <c r="A452" s="15"/>
+      <c r="B452" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="C452" s="14">
-        <v>1</v>
-      </c>
-      <c r="D452" s="14">
+      <c r="C452" s="13">
+        <v>1</v>
+      </c>
+      <c r="D452" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="453" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A453" s="16"/>
-      <c r="B453" s="30" t="s">
+      <c r="A453" s="15"/>
+      <c r="B453" s="29" t="s">
         <v>414</v>
       </c>
-      <c r="C453" s="14">
+      <c r="C453" s="13">
         <v>2</v>
       </c>
-      <c r="D453" s="14">
+      <c r="D453" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="454" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A454" s="16"/>
-      <c r="B454" s="30" t="s">
+      <c r="A454" s="15"/>
+      <c r="B454" s="29" t="s">
         <v>446</v>
       </c>
-      <c r="C454" s="14">
+      <c r="C454" s="13">
         <v>1.2</v>
       </c>
-      <c r="D454" s="14">
+      <c r="D454" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="455" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A455" s="16"/>
-      <c r="B455" s="30" t="s">
+      <c r="A455" s="15"/>
+      <c r="B455" s="29" t="s">
         <v>415</v>
       </c>
-      <c r="C455" s="14">
-        <v>1</v>
-      </c>
-      <c r="D455" s="14">
+      <c r="C455" s="13">
+        <v>1</v>
+      </c>
+      <c r="D455" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="456" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A456" s="16"/>
-      <c r="B456" s="30" t="s">
+      <c r="A456" s="15"/>
+      <c r="B456" s="29" t="s">
         <v>416</v>
       </c>
-      <c r="C456" s="14">
+      <c r="C456" s="13">
         <v>2</v>
       </c>
-      <c r="D456" s="14">
+      <c r="D456" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="457" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A457" s="16"/>
-      <c r="B457" s="30" t="s">
+      <c r="A457" s="15"/>
+      <c r="B457" s="29" t="s">
         <v>417</v>
       </c>
-      <c r="C457" s="14">
+      <c r="C457" s="13">
         <v>2</v>
       </c>
-      <c r="D457" s="14">
+      <c r="D457" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="458" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A458" s="16"/>
-      <c r="B458" s="30" t="s">
+      <c r="A458" s="15"/>
+      <c r="B458" s="29" t="s">
         <v>418</v>
       </c>
-      <c r="C458" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="D458" s="14">
+      <c r="C458" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D458" s="13">
         <v>1.8</v>
       </c>
     </row>
     <row r="459" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A459" s="16"/>
-      <c r="B459" s="30" t="s">
+      <c r="A459" s="15"/>
+      <c r="B459" s="29" t="s">
         <v>419</v>
       </c>
-      <c r="C459" s="14">
+      <c r="C459" s="13">
         <v>2.5</v>
       </c>
-      <c r="D459" s="14">
+      <c r="D459" s="13">
         <v>2.5</v>
       </c>
     </row>
     <row r="460" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A460" s="16"/>
-      <c r="B460" s="35" t="s">
+      <c r="A460" s="15"/>
+      <c r="B460" s="34" t="s">
         <v>420</v>
       </c>
-      <c r="C460" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D460" s="14">
+      <c r="C460" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D460" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="461" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A461" s="16"/>
-      <c r="B461" s="8" t="s">
+      <c r="A461" s="15"/>
+      <c r="B461" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="C461" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D461" s="14">
+      <c r="C461" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D461" s="13">
         <v>1.5</v>
       </c>
     </row>
     <row r="462" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A462" s="16"/>
-      <c r="B462" s="8" t="s">
+      <c r="A462" s="15"/>
+      <c r="B462" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="C462" s="8">
-        <v>1</v>
-      </c>
-      <c r="D462" s="8">
+      <c r="C462" s="7">
+        <v>1</v>
+      </c>
+      <c r="D462" s="7">
         <v>0.8</v>
       </c>
     </row>
     <row r="463" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B463" s="8" t="s">
+      <c r="B463" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="C463" s="8">
-        <v>1</v>
-      </c>
-      <c r="D463" s="8">
+      <c r="C463" s="7">
+        <v>1</v>
+      </c>
+      <c r="D463" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="464" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A464" s="34" t="s">
+      <c r="A464" s="52" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="465" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B465" s="27" t="s">
+      <c r="B465" s="26" t="s">
         <v>553</v>
       </c>
-      <c r="C465" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D465" s="8">
+      <c r="C465" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D465" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="466" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B466" s="27" t="s">
+      <c r="B466" s="26" t="s">
         <v>554</v>
       </c>
-      <c r="C466" s="8">
+      <c r="C466" s="7">
         <v>2</v>
       </c>
-      <c r="D466" s="8">
+      <c r="D466" s="7">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="467" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A467" s="25" t="s">
+      <c r="A467" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="B467" s="27" t="s">
+      <c r="B467" s="26" t="s">
         <v>555</v>
       </c>
-      <c r="C467" s="8">
+      <c r="C467" s="7">
         <v>2</v>
       </c>
-      <c r="D467" s="8">
+      <c r="D467" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="468" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B468" s="27" t="s">
+      <c r="B468" s="26" t="s">
         <v>556</v>
       </c>
       <c r="C468">
         <v>2.5</v>
       </c>
-      <c r="D468" s="8">
+      <c r="D468" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="469" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B469" s="27" t="s">
+      <c r="B469" s="26" t="s">
         <v>557</v>
       </c>
       <c r="C469">
         <v>2</v>
       </c>
-      <c r="D469" s="8">
+      <c r="D469" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="470" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B470" s="27" t="s">
+      <c r="B470" s="26" t="s">
         <v>558</v>
       </c>
       <c r="C470">
         <v>1.8</v>
       </c>
-      <c r="D470" s="8">
+      <c r="D470" s="7">
         <v>2</v>
       </c>
     </row>
@@ -8358,134 +8362,134 @@
       <c r="C471">
         <v>2</v>
       </c>
-      <c r="D471" s="8">
+      <c r="D471" s="7">
         <v>2.5</v>
       </c>
     </row>
     <row r="472" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B472" s="27" t="s">
+      <c r="B472" s="26" t="s">
         <v>560</v>
       </c>
-      <c r="C472" s="8">
+      <c r="C472" s="7">
         <v>2</v>
       </c>
-      <c r="D472" s="8">
+      <c r="D472" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="473" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B473" s="27" t="s">
+      <c r="B473" s="26" t="s">
         <v>561</v>
       </c>
-      <c r="C473" s="8">
+      <c r="C473" s="7">
         <v>1.8</v>
       </c>
-      <c r="D473" s="8">
+      <c r="D473" s="7">
         <v>1.8</v>
       </c>
     </row>
     <row r="474" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B474" s="27" t="s">
+      <c r="B474" s="26" t="s">
         <v>562</v>
       </c>
-      <c r="C474" s="8">
+      <c r="C474" s="7">
         <v>2.5</v>
       </c>
-      <c r="D474" s="8">
+      <c r="D474" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="475" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B475" s="27" t="s">
+      <c r="B475" s="26" t="s">
         <v>563</v>
       </c>
-      <c r="C475" s="8">
+      <c r="C475" s="7">
         <v>2</v>
       </c>
-      <c r="D475" s="8">
+      <c r="D475" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="476" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B476" s="27" t="s">
+      <c r="B476" s="26" t="s">
         <v>564</v>
       </c>
-      <c r="C476" s="8">
+      <c r="C476" s="7">
         <v>2.5</v>
       </c>
-      <c r="D476" s="8">
+      <c r="D476" s="7">
         <v>2.5</v>
       </c>
     </row>
     <row r="477" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B477" s="27" t="s">
+      <c r="B477" s="26" t="s">
         <v>565</v>
       </c>
-      <c r="C477" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D477" s="8">
+      <c r="C477" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D477" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="479" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A479" s="34" t="s">
+      <c r="A479" s="67" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="480" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B480" s="27" t="s">
+      <c r="B480" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="C480" s="8">
+      <c r="C480" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="481" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B481" s="27" t="s">
+      <c r="B481" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="C481" s="8">
+      <c r="C481" s="7">
         <v>1.2</v>
       </c>
     </row>
     <row r="482" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B482" s="27" t="s">
+      <c r="B482" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="C482" s="8">
+      <c r="C482" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="483" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B483" s="27" t="s">
+      <c r="B483" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="C483" s="8">
+      <c r="C483" s="7">
         <v>2.5</v>
       </c>
     </row>
     <row r="484" spans="2:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B484" s="27" t="s">
+      <c r="B484" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="C484" s="8">
+      <c r="C484" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="485" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B485" s="27" t="s">
+      <c r="B485" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="C485" s="8">
+      <c r="C485" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="486" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B486" s="27" t="s">
+      <c r="B486" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="C486" s="8">
+      <c r="C486" s="7">
         <v>1</v>
       </c>
     </row>

--- a/project/requisitos_backlog.xlsx
+++ b/project/requisitos_backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciasorniscaletti/Desktop/UNI/TFG/erp-fraud-data-TFG/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901B28D4-37C9-5042-BFD4-F4A1658DC090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CD84A1-ACEB-6543-BF08-AAC2243150F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>Fecha compromiso</t>
   </si>
   <si>
-    <t>Segunda fecha</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
@@ -1752,12 +1749,15 @@
   <si>
     <t>Realizado No explicitamente</t>
   </si>
+  <si>
+    <t>Tiempo Real</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1834,6 +1834,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2051,9 +2057,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2135,21 +2138,14 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2476,7 +2472,7 @@
     <col min="4" max="4" width="15.5" style="7" customWidth="1"/>
     <col min="5" max="5" width="11.83203125" style="7" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="7" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" style="39" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" style="7" customWidth="1"/>
     <col min="9" max="9" width="3.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="7"/>
@@ -2499,355 +2495,390 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>293</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>294</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2" s="38"/>
       <c r="L2" s="7"/>
     </row>
     <row r="3" spans="1:12" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>296</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>297</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="38"/>
       <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="D4" s="5">
         <v>8</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="G4" s="36">
         <v>46094</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5">
+        <f>SUM(PLANNING!D18:D35)</f>
+        <v>10.75</v>
+      </c>
       <c r="I4" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>15</v>
       </c>
       <c r="D5" s="5">
         <v>5</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="36">
         <v>46094</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="5">
+        <f>SUM(PLANNING!D38:D48)</f>
+        <v>5.5</v>
+      </c>
       <c r="I5" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="D6" s="5">
         <v>5</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="36">
         <v>46094</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5">
+        <f>SUM(PLANNING!D51:D62)</f>
+        <v>9.3000000000000007</v>
+      </c>
       <c r="I6" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="D7" s="5">
         <v>5</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" s="36">
         <v>46094</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="5">
+        <f>SUM(PLANNING!D65:D76)</f>
+        <v>9.1999999999999993</v>
+      </c>
       <c r="I7" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="D8" s="5">
         <v>8</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="G8" s="36">
         <v>46094</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="5">
+        <f>SUM(PLANNING!D79:D88)</f>
+        <v>8.3999999999999986</v>
+      </c>
       <c r="I8" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="G9" s="36">
         <v>46094</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="5">
+        <f>SUM(PLANNING!D91:D99)</f>
+        <v>8</v>
+      </c>
       <c r="I9" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="D10" s="5">
         <v>8</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="G10" s="36">
         <v>46094</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5">
+        <f>SUM(PLANNING!D102:D111)</f>
+        <v>10.100000000000001</v>
+      </c>
       <c r="I10" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="D11" s="5">
         <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="36">
         <v>46094</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="5">
+        <f>SUM(PLANNING!D114:D121)</f>
+        <v>8.8000000000000007</v>
+      </c>
       <c r="I11" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="D12" s="5">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="36">
         <v>46094</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="5">
+        <f>SUM(PLANNING!D124:D133)</f>
+        <v>9.1999999999999993</v>
+      </c>
       <c r="I12" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="C13" s="41" t="s">
         <v>39</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>40</v>
       </c>
       <c r="D13" s="5">
         <v>8</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="36"/>
-      <c r="H13" s="5"/>
+      <c r="G13" s="36">
+        <v>46129</v>
+      </c>
+      <c r="H13" s="5">
+        <f>SUM(PLANNING!D136:D145)</f>
+        <v>13</v>
+      </c>
       <c r="I13" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="38" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>42</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="D14" s="5">
         <v>5</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" s="36">
         <v>46094</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="5">
+        <f>SUM(PLANNING!D148:D155)</f>
+        <v>8.1</v>
+      </c>
       <c r="I14" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.2">
@@ -2862,48 +2893,53 @@
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:12" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="41" t="s">
-        <v>468</v>
-      </c>
-      <c r="B16" s="42" t="s">
+      <c r="A16" s="40" t="s">
+        <v>467</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="C16" s="41" t="s">
         <v>471</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>472</v>
       </c>
       <c r="D16" s="5">
         <v>21</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="36">
+        <v>46129</v>
+      </c>
+      <c r="H16" s="5">
+        <f>SUM(PLANNING!D158:D173)</f>
+        <v>32.800000000000004</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="36"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="46" t="s">
+      <c r="B17" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>469</v>
+      <c r="C17" s="46" t="s">
+        <v>468</v>
       </c>
       <c r="D17" s="5">
         <v>8</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" s="36"/>
       <c r="H17" s="5"/>
@@ -2911,338 +2947,378 @@
     </row>
     <row r="18" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>49</v>
-      </c>
       <c r="C18" s="20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D18" s="5">
         <v>13</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="36">
         <v>46121</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="5">
+        <f>SUM(PLANNING!D186:D200)</f>
+        <v>17.599999999999998</v>
+      </c>
       <c r="I18" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="C19" s="22" t="s">
         <v>313</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>314</v>
       </c>
       <c r="D19" s="13">
         <v>10</v>
       </c>
       <c r="E19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>12</v>
       </c>
       <c r="G19" s="36">
         <v>46121</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5">
+        <f>SUM(PLANNING!D202:D219)</f>
+        <v>31</v>
+      </c>
       <c r="I19" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>315</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="C20" s="22" t="s">
         <v>316</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>317</v>
       </c>
       <c r="D20" s="13">
         <v>8</v>
       </c>
       <c r="E20" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>12</v>
       </c>
       <c r="G20" s="36">
         <v>46121</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5">
+        <f>SUM(PLANNING!D223:D241)</f>
+        <v>25.099999999999998</v>
+      </c>
       <c r="I20" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="43" t="s">
-        <v>318</v>
-      </c>
-      <c r="B21" s="44" t="s">
+      <c r="A21" s="42" t="s">
+        <v>317</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>547</v>
+      </c>
+      <c r="C21" s="44" t="s">
         <v>548</v>
-      </c>
-      <c r="C21" s="45" t="s">
-        <v>549</v>
       </c>
       <c r="D21" s="13">
         <v>18</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="39"/>
-      <c r="H21" s="13"/>
+        <v>11</v>
+      </c>
+      <c r="G21" s="36">
+        <v>46129</v>
+      </c>
+      <c r="H21" s="13">
+        <f>SUM(PLANNING!D243:D269)</f>
+        <v>36.700000000000003</v>
+      </c>
       <c r="I21" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="C22" s="22" t="s">
         <v>320</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>321</v>
       </c>
       <c r="D22" s="13">
         <v>8</v>
       </c>
       <c r="E22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>12</v>
       </c>
       <c r="G22" s="36">
         <v>46121</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="5">
+        <f>SUM(PLANNING!D271:D281)</f>
+        <v>14.8</v>
+      </c>
       <c r="I22" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>322</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="C23" s="22" t="s">
         <v>323</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>324</v>
       </c>
       <c r="D23" s="13">
         <v>8</v>
       </c>
       <c r="E23" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>12</v>
       </c>
       <c r="G23" s="36">
         <v>46121</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="5">
+        <f>SUM(PLANNING!D283:D294)</f>
+        <v>15</v>
+      </c>
       <c r="I23" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="C24" s="23" t="s">
         <v>326</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>327</v>
       </c>
       <c r="D24" s="13">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>12</v>
       </c>
       <c r="G24" s="36">
         <v>46121</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="5">
+        <f>SUM(PLANNING!D297:D314)</f>
+        <v>38.799999999999997</v>
+      </c>
       <c r="I24" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="C25" s="22" t="s">
         <v>329</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>330</v>
       </c>
       <c r="D25" s="13">
         <v>10</v>
       </c>
       <c r="E25" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>12</v>
       </c>
       <c r="G25" s="36">
         <v>46121</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="5">
+        <f>SUM(PLANNING!D316:D328)</f>
+        <v>19.700000000000003</v>
+      </c>
       <c r="I25" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="85" x14ac:dyDescent="0.2">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="40" t="s">
+        <v>493</v>
+      </c>
+      <c r="B26" s="41" t="s">
         <v>494</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="C26" s="41" t="s">
         <v>495</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>496</v>
       </c>
       <c r="D26" s="5">
         <v>10</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="36"/>
-      <c r="H26" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="G26" s="36">
+        <v>46129</v>
+      </c>
+      <c r="H26" s="5">
+        <f>SUM(PLANNING!D330:D339)</f>
+        <v>12.500000000000002</v>
+      </c>
       <c r="I26" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="85" x14ac:dyDescent="0.2">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="40" t="s">
+        <v>506</v>
+      </c>
+      <c r="B27" s="41" t="s">
         <v>507</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="C27" s="41" t="s">
         <v>508</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>509</v>
       </c>
       <c r="D27" s="5">
         <v>12</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="36"/>
-      <c r="H27" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="G27" s="36">
+        <v>46129</v>
+      </c>
+      <c r="H27" s="5">
+        <f>SUM(PLANNING!D342:D353)</f>
+        <v>16.8</v>
+      </c>
       <c r="I27" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="A28" s="62" t="s">
+      <c r="A28" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="60" t="s">
+      <c r="C28" s="62" t="s">
         <v>52</v>
-      </c>
-      <c r="C28" s="63" t="s">
-        <v>53</v>
       </c>
       <c r="D28" s="5">
         <v>5</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="36"/>
-      <c r="H28" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="G28" s="36">
+        <v>46121</v>
+      </c>
       <c r="I28" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="C29" s="22" t="s">
         <v>332</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>333</v>
       </c>
       <c r="D29" s="13">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>11</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>12</v>
       </c>
       <c r="G29" s="36">
         <v>46121</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="5">
+        <f>SUM(PLANNING!D364:D376)</f>
+        <v>18.3</v>
+      </c>
       <c r="I29" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="A30" s="46" t="s">
+      <c r="A30" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="65" t="s">
+      <c r="C30" s="64" t="s">
         <v>55</v>
-      </c>
-      <c r="C30" s="65" t="s">
-        <v>56</v>
       </c>
       <c r="D30" s="5">
         <v>8</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G30" s="36"/>
       <c r="H30" s="5"/>
@@ -3250,22 +3326,22 @@
     </row>
     <row r="31" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="D31" s="5">
         <v>5</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="G31" s="36"/>
       <c r="H31" s="5"/>
@@ -3273,22 +3349,22 @@
     </row>
     <row r="32" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="D32" s="5">
         <v>5</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="G32" s="36"/>
       <c r="H32" s="5"/>
@@ -3296,22 +3372,22 @@
     </row>
     <row r="33" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="C33" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="D33" s="5">
         <v>5</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="G33" s="36"/>
       <c r="H33" s="5"/>
@@ -3319,22 +3395,22 @@
     </row>
     <row r="34" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="C34" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="D34" s="5">
         <v>3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G34" s="36"/>
       <c r="H34" s="5"/>
@@ -3342,22 +3418,22 @@
     </row>
     <row r="35" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="D35" s="5">
         <v>3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G35" s="36"/>
       <c r="H35" s="5"/>
@@ -3365,22 +3441,22 @@
     </row>
     <row r="36" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="C36" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="D36" s="5">
         <v>3</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G36" s="36"/>
       <c r="H36" s="5"/>
@@ -3388,22 +3464,22 @@
     </row>
     <row r="37" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="D37" s="5">
         <v>3</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G37" s="36"/>
       <c r="H37" s="5"/>
@@ -3411,72 +3487,80 @@
     </row>
     <row r="38" spans="1:9" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="27" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B38" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="C38" s="23" t="s">
         <v>422</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>423</v>
       </c>
       <c r="D38" s="13">
         <v>5</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G38" s="36">
         <v>46121</v>
       </c>
-      <c r="H38" s="5"/>
+      <c r="H38" s="5">
+        <f>SUM(PLANNING!D449:D463)</f>
+        <v>20.000000000000004</v>
+      </c>
       <c r="I38" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="68" x14ac:dyDescent="0.2">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="56" t="s">
+        <v>549</v>
+      </c>
+      <c r="B39" s="57" t="s">
         <v>550</v>
       </c>
-      <c r="B39" s="58" t="s">
+      <c r="C39" s="57" t="s">
         <v>551</v>
-      </c>
-      <c r="C39" s="58" t="s">
-        <v>552</v>
       </c>
       <c r="D39" s="5">
         <v>13</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G39" s="36"/>
-      <c r="H39" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="G39" s="36">
+        <v>46129</v>
+      </c>
+      <c r="H39" s="5">
+        <f>SUM(PLANNING!D465:D477)</f>
+        <v>28.5</v>
+      </c>
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="60" t="s">
+      <c r="C40" s="60" t="s">
         <v>82</v>
-      </c>
-      <c r="C40" s="61" t="s">
-        <v>83</v>
       </c>
       <c r="D40" s="5">
         <v>5</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G40" s="36"/>
       <c r="H40" s="5"/>
@@ -3490,36 +3574,36 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>472</v>
+      </c>
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" s="47" t="s">
         <v>473</v>
       </c>
-      <c r="B43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="48" t="s">
+      <c r="B44" s="8"/>
+    </row>
+    <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A45" s="48" t="s">
         <v>474</v>
       </c>
-      <c r="B44" s="8"/>
-    </row>
-    <row r="45" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="49" t="s">
+    </row>
+    <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A46" s="49" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="50" t="s">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="50" t="s">
         <v>476</v>
       </c>
-      <c r="B46" s="2"/>
-    </row>
-    <row r="47" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="51" t="s">
-        <v>477</v>
-      </c>
       <c r="B47" s="2"/>
     </row>
     <row r="48" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="64" t="s">
-        <v>566</v>
+      <c r="A48" s="63" t="s">
+        <v>565</v>
       </c>
       <c r="B48" s="2"/>
     </row>
@@ -3534,33 +3618,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H18:I20">
-    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H18)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I25 I26:I27">
-    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="Sí">
+  <conditionalFormatting sqref="H22:I25">
+    <cfRule type="containsText" dxfId="6" priority="14" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:I29">
-    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:I38">
-    <cfRule type="containsText" dxfId="5" priority="12" operator="containsText" text="Sí">
+    <cfRule type="containsText" dxfId="4" priority="12" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",H38)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I12 I39:I1048576 I14:I15 I17">
-    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="Sí">
+  <conditionalFormatting sqref="I1:I17">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Sí">
       <formula>NOT(ISERROR(SEARCH("Sí",I1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I28">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Sí">
-      <formula>NOT(ISERROR(SEARCH("Sí",I28)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
@@ -3568,14 +3647,14 @@
       <formula>NOT(ISERROR(SEARCH("Sí",I21)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Sí">
-      <formula>NOT(ISERROR(SEARCH("Sí",I13)))</formula>
+  <conditionalFormatting sqref="I26:I28">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",I26)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Sí">
-      <formula>NOT(ISERROR(SEARCH("Sí",I16)))</formula>
+  <conditionalFormatting sqref="I39:I1048576">
+    <cfRule type="containsText" dxfId="0" priority="18" operator="containsText" text="Sí">
+      <formula>NOT(ISERROR(SEARCH("Sí",I39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3687,7 +3766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:D486"/>
+  <dimension ref="A2:H486"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.33203125" style="24" bestFit="1" customWidth="1"/>
@@ -3697,162 +3776,144 @@
     <col min="5" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="C2" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="D2" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="G2" s="7">
+        <f>SUM(C:C)</f>
+        <v>431.99999999999989</v>
+      </c>
+      <c r="H2" s="7">
+        <f>SUM(D:D)</f>
+        <v>427.95000000000016</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="C3" s="13">
-        <v>0.6</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="13"/>
     </row>
-    <row r="4" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="13">
-        <v>0.8</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C4" s="13"/>
       <c r="D4" s="13"/>
     </row>
-    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="15"/>
       <c r="B5" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="C5" s="13">
-        <v>0.8</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C5" s="13"/>
       <c r="D5" s="13"/>
     </row>
-    <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="15"/>
       <c r="B6" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="C6" s="13">
-        <v>0.8</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C6" s="13"/>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="29" t="s">
-        <v>302</v>
-      </c>
-      <c r="C7" s="13">
-        <v>0.5</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C7" s="13"/>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="29" t="s">
-        <v>303</v>
-      </c>
-      <c r="C8" s="13">
-        <v>0.5</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C8" s="13"/>
       <c r="D8" s="13"/>
     </row>
-    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="13">
-        <v>1</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="C9" s="13"/>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="C10" s="13">
-        <v>1</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C10" s="13"/>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
       <c r="B11" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C11" s="13"/>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="15"/>
       <c r="B12" s="29" t="s">
-        <v>306</v>
-      </c>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="C12" s="13"/>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="C13" s="13">
-        <v>1</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C13" s="13"/>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="C14" s="13">
-        <v>1.2</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="C14" s="13"/>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="C15" s="13">
-        <v>0.6</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="C15" s="13"/>
       <c r="D15" s="13"/>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="54" t="s">
-        <v>8</v>
+      <c r="A17" s="53" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B18" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="7">
         <v>0.5</v>
@@ -3863,7 +3924,7 @@
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B19" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19" s="7">
         <v>0.5</v>
@@ -3874,7 +3935,7 @@
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B20" s="26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="7">
         <v>1</v>
@@ -3885,7 +3946,7 @@
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -3896,7 +3957,7 @@
     </row>
     <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B22" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" s="7">
         <v>1.5</v>
@@ -3907,7 +3968,7 @@
     </row>
     <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B23" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="7">
         <v>2</v>
@@ -3918,7 +3979,7 @@
     </row>
     <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B24" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" s="7">
         <v>1</v>
@@ -3929,7 +3990,7 @@
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" s="7">
         <v>0.7</v>
@@ -3940,7 +4001,7 @@
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B26" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" s="7">
         <v>1.2</v>
@@ -3951,7 +4012,7 @@
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B27" s="26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="7">
         <v>0.8</v>
@@ -3962,7 +4023,7 @@
     </row>
     <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B28" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="7">
         <v>1.5</v>
@@ -3973,7 +4034,7 @@
     </row>
     <row r="29" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" s="7">
         <v>1.5</v>
@@ -3984,7 +4045,7 @@
     </row>
     <row r="30" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="7">
         <v>1.2</v>
@@ -3995,7 +4056,7 @@
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B31" s="26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" s="7">
         <v>1.2</v>
@@ -4006,7 +4067,7 @@
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B32" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" s="7">
         <v>1.2</v>
@@ -4017,7 +4078,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B33" s="35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33" s="7">
         <v>1.5</v>
@@ -4028,7 +4089,7 @@
     </row>
     <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B34" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C34" s="7">
         <v>1</v>
@@ -4039,7 +4100,7 @@
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B35" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -4052,13 +4113,13 @@
       <c r="B36" s="26"/>
     </row>
     <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="54" t="s">
-        <v>13</v>
+      <c r="A37" s="53" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B38" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" s="7">
         <v>0.8</v>
@@ -4069,7 +4130,7 @@
     </row>
     <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B39" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -4080,7 +4141,7 @@
     </row>
     <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B40" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" s="7">
         <v>1</v>
@@ -4091,7 +4152,7 @@
     </row>
     <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B41" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C41" s="7">
         <v>0.7</v>
@@ -4102,7 +4163,7 @@
     </row>
     <row r="42" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B42" s="26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C42" s="7">
         <v>1</v>
@@ -4113,7 +4174,7 @@
     </row>
     <row r="43" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B43" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" s="7">
         <v>1.2</v>
@@ -4124,7 +4185,7 @@
     </row>
     <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C44" s="7">
         <v>0.8</v>
@@ -4135,7 +4196,7 @@
     </row>
     <row r="45" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B45" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C45" s="7">
         <v>1.5</v>
@@ -4146,7 +4207,7 @@
     </row>
     <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B46" s="26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C46" s="7">
         <v>1.5</v>
@@ -4157,7 +4218,7 @@
     </row>
     <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B47" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4168,7 +4229,7 @@
     </row>
     <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B48" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C48" s="7">
         <v>1</v>
@@ -4181,13 +4242,13 @@
       <c r="B49" s="26"/>
     </row>
     <row r="50" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="54" t="s">
-        <v>17</v>
+      <c r="A50" s="53" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B51" s="26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C51" s="7">
         <v>0.8</v>
@@ -4198,7 +4259,7 @@
     </row>
     <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B52" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C52" s="7">
         <v>0.8</v>
@@ -4209,7 +4270,7 @@
     </row>
     <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B53" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C53" s="7">
         <v>0.8</v>
@@ -4220,7 +4281,7 @@
     </row>
     <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B54" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C54" s="7">
         <v>1.2</v>
@@ -4231,7 +4292,7 @@
     </row>
     <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B55" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -4242,7 +4303,7 @@
     </row>
     <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C56" s="7">
         <v>1</v>
@@ -4253,7 +4314,7 @@
     </row>
     <row r="57" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B57" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -4264,7 +4325,7 @@
     </row>
     <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B58" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C58" s="7">
         <v>1.2</v>
@@ -4275,7 +4336,7 @@
     </row>
     <row r="59" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B59" s="26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C59" s="7">
         <v>0.7</v>
@@ -4286,7 +4347,7 @@
     </row>
     <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B60" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C60" s="7">
         <v>1.5</v>
@@ -4297,7 +4358,7 @@
     </row>
     <row r="61" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B61" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -4308,7 +4369,7 @@
     </row>
     <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B62" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C62" s="7">
         <v>1</v>
@@ -4321,13 +4382,13 @@
       <c r="B63" s="26"/>
     </row>
     <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="54" t="s">
-        <v>20</v>
+      <c r="A64" s="53" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B65" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -4338,7 +4399,7 @@
     </row>
     <row r="66" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B66" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C66" s="7">
         <v>0.8</v>
@@ -4349,7 +4410,7 @@
     </row>
     <row r="67" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B67" s="26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C67" s="7">
         <v>1.2</v>
@@ -4360,7 +4421,7 @@
     </row>
     <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B68" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C68" s="7">
         <v>1</v>
@@ -4371,7 +4432,7 @@
     </row>
     <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B69" s="26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C69" s="7">
         <v>2</v>
@@ -4382,7 +4443,7 @@
     </row>
     <row r="70" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B70" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
@@ -4393,7 +4454,7 @@
     </row>
     <row r="71" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B71" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C71" s="7">
         <v>0.8</v>
@@ -4404,7 +4465,7 @@
     </row>
     <row r="72" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B72" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C72" s="7">
         <v>0.8</v>
@@ -4415,7 +4476,7 @@
     </row>
     <row r="73" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B73" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C73" s="7">
         <v>1.5</v>
@@ -4426,7 +4487,7 @@
     </row>
     <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B74" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C74" s="7">
         <v>1</v>
@@ -4437,7 +4498,7 @@
     </row>
     <row r="75" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B75" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
@@ -4449,7 +4510,7 @@
     <row r="76" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A76" s="7"/>
       <c r="B76" s="25" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C76" s="7">
         <v>0.8</v>
@@ -4462,13 +4523,13 @@
       <c r="B77" s="26"/>
     </row>
     <row r="78" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A78" s="54" t="s">
-        <v>23</v>
+      <c r="A78" s="53" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B79" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C79" s="7">
         <v>1.2</v>
@@ -4479,7 +4540,7 @@
     </row>
     <row r="80" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B80" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C80" s="7">
         <v>0.8</v>
@@ -4490,7 +4551,7 @@
     </row>
     <row r="81" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B81" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C81" s="7">
         <v>0.8</v>
@@ -4501,7 +4562,7 @@
     </row>
     <row r="82" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B82" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C82" s="7">
         <v>1</v>
@@ -4512,7 +4573,7 @@
     </row>
     <row r="83" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B83" s="26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C83" s="7">
         <v>1.5</v>
@@ -4523,7 +4584,7 @@
     </row>
     <row r="84" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B84" s="26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C84" s="7">
         <v>1</v>
@@ -4534,7 +4595,7 @@
     </row>
     <row r="85" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B85" s="26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C85" s="7">
         <v>0.8</v>
@@ -4545,7 +4606,7 @@
     </row>
     <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B86" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C86" s="7">
         <v>1.5</v>
@@ -4556,7 +4617,7 @@
     </row>
     <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B87" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C87" s="7">
         <v>1</v>
@@ -4567,7 +4628,7 @@
     </row>
     <row r="88" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B88" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C88" s="7">
         <v>1</v>
@@ -4580,13 +4641,13 @@
       <c r="B89" s="26"/>
     </row>
     <row r="90" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="54" t="s">
-        <v>26</v>
+      <c r="A90" s="53" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B91" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C91" s="7">
         <v>1</v>
@@ -4597,7 +4658,7 @@
     </row>
     <row r="92" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B92" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C92" s="7">
         <v>1.2</v>
@@ -4608,7 +4669,7 @@
     </row>
     <row r="93" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B93" s="26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C93" s="7">
         <v>0.8</v>
@@ -4619,7 +4680,7 @@
     </row>
     <row r="94" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B94" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C94" s="7">
         <v>1</v>
@@ -4630,7 +4691,7 @@
     </row>
     <row r="95" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B95" s="26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C95" s="7">
         <v>1</v>
@@ -4641,7 +4702,7 @@
     </row>
     <row r="96" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B96" s="26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C96" s="7">
         <v>0.8</v>
@@ -4652,7 +4713,7 @@
     </row>
     <row r="97" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B97" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C97" s="7">
         <v>1.5</v>
@@ -4663,7 +4724,7 @@
     </row>
     <row r="98" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B98" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C98" s="7">
         <v>1</v>
@@ -4674,7 +4735,7 @@
     </row>
     <row r="99" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B99" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
@@ -4687,13 +4748,13 @@
       <c r="B100" s="26"/>
     </row>
     <row r="101" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="54" t="s">
-        <v>29</v>
+      <c r="A101" s="53" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B102" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C102" s="7">
         <v>1</v>
@@ -4704,7 +4765,7 @@
     </row>
     <row r="103" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B103" s="26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C103" s="7">
         <v>1.2</v>
@@ -4715,7 +4776,7 @@
     </row>
     <row r="104" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B104" s="26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C104" s="7">
         <v>1.5</v>
@@ -4726,7 +4787,7 @@
     </row>
     <row r="105" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B105" s="26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C105" s="7">
         <v>0.8</v>
@@ -4737,7 +4798,7 @@
     </row>
     <row r="106" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B106" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C106" s="7">
         <v>1.2</v>
@@ -4748,7 +4809,7 @@
     </row>
     <row r="107" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B107" s="26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C107" s="7">
         <v>0.7</v>
@@ -4759,7 +4820,7 @@
     </row>
     <row r="108" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B108" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C108" s="7">
         <v>1.5</v>
@@ -4770,7 +4831,7 @@
     </row>
     <row r="109" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B109" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C109" s="7">
         <v>1.5</v>
@@ -4781,7 +4842,7 @@
     </row>
     <row r="110" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B110" s="26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C110" s="7">
         <v>1</v>
@@ -4792,7 +4853,7 @@
     </row>
     <row r="111" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B111" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C111" s="7">
         <v>1</v>
@@ -4805,13 +4866,13 @@
       <c r="B112" s="26"/>
     </row>
     <row r="113" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A113" s="54" t="s">
-        <v>32</v>
+      <c r="A113" s="53" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B114" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C114" s="7">
         <v>0.8</v>
@@ -4822,7 +4883,7 @@
     </row>
     <row r="115" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B115" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C115" s="7">
         <v>1.2</v>
@@ -4833,7 +4894,7 @@
     </row>
     <row r="116" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B116" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C116" s="7">
         <v>1.2</v>
@@ -4844,29 +4905,29 @@
     </row>
     <row r="117" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B117" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C117" s="7">
         <v>1</v>
       </c>
       <c r="D117" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B118" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C118" s="7">
         <v>0.6</v>
       </c>
       <c r="D118" s="7">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B119" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C119" s="7">
         <v>1.2</v>
@@ -4877,7 +4938,7 @@
     </row>
     <row r="120" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B120" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C120" s="7">
         <v>1</v>
@@ -4888,7 +4949,7 @@
     </row>
     <row r="121" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B121" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C121" s="7">
         <v>1</v>
@@ -4901,13 +4962,13 @@
       <c r="B122" s="26"/>
     </row>
     <row r="123" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A123" s="54" t="s">
-        <v>35</v>
+      <c r="A123" s="53" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B124" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C124" s="7">
         <v>1</v>
@@ -4918,29 +4979,29 @@
     </row>
     <row r="125" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B125" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C125" s="7">
         <v>1.2</v>
       </c>
       <c r="D125" s="7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B126" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C126" s="7">
         <v>1.2</v>
       </c>
       <c r="D126" s="7">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B127" s="26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C127" s="7">
         <v>1</v>
@@ -4951,7 +5012,7 @@
     </row>
     <row r="128" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B128" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C128" s="7">
         <v>0.8</v>
@@ -4962,7 +5023,7 @@
     </row>
     <row r="129" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B129" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C129" s="7">
         <v>0.8</v>
@@ -4973,7 +5034,7 @@
     </row>
     <row r="130" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B130" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C130" s="7">
         <v>0.8</v>
@@ -4984,7 +5045,7 @@
     </row>
     <row r="131" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B131" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C131" s="7">
         <v>1.5</v>
@@ -4995,7 +5056,7 @@
     </row>
     <row r="132" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B132" s="26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C132" s="7">
         <v>1</v>
@@ -5006,7 +5067,7 @@
     </row>
     <row r="133" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B133" s="26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C133" s="7">
         <v>1</v>
@@ -5019,87 +5080,117 @@
       <c r="B134" s="26"/>
     </row>
     <row r="135" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A135" s="52" t="s">
-        <v>38</v>
+      <c r="A135" s="51" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B136" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C136" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D136" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B137" s="26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C137" s="7">
         <v>0.8</v>
       </c>
+      <c r="D137" s="7">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="138" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B138" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C138" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D138" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B139" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C139" s="7">
         <v>1.2</v>
       </c>
+      <c r="D139" s="7">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="140" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B140" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C140" s="7">
         <v>2</v>
       </c>
+      <c r="D140" s="7">
+        <v>2</v>
+      </c>
     </row>
     <row r="141" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B141" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C141" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D141" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B142" s="26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C142" s="7">
+        <v>1</v>
+      </c>
+      <c r="D142" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B143" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C143" s="7">
+        <v>1</v>
+      </c>
+      <c r="D143" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C144" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D144" s="7">
         <v>1.5</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B145" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C145" s="7">
+        <v>1</v>
+      </c>
+      <c r="D145" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5107,13 +5198,13 @@
       <c r="B146" s="26"/>
     </row>
     <row r="147" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A147" s="54" t="s">
-        <v>41</v>
+      <c r="A147" s="53" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B148" s="26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C148" s="7">
         <v>2</v>
@@ -5124,7 +5215,7 @@
     </row>
     <row r="149" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B149" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C149" s="7">
         <v>1.2</v>
@@ -5135,7 +5226,7 @@
     </row>
     <row r="150" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B150" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C150" s="7">
         <v>1</v>
@@ -5146,7 +5237,7 @@
     </row>
     <row r="151" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B151" s="26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C151" s="7">
         <v>1.5</v>
@@ -5157,7 +5248,7 @@
     </row>
     <row r="152" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B152" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C152" s="7">
         <v>0.8</v>
@@ -5168,7 +5259,7 @@
     </row>
     <row r="153" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B153" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C153" s="7">
         <v>1.5</v>
@@ -5179,7 +5270,7 @@
     </row>
     <row r="154" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B154" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C154" s="7">
         <v>1</v>
@@ -5190,7 +5281,7 @@
     </row>
     <row r="155" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B155" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C155" s="7">
         <v>1</v>
@@ -5203,13 +5294,13 @@
       <c r="B156" s="26"/>
     </row>
     <row r="157" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A157" s="52" t="s">
-        <v>44</v>
+      <c r="A157" s="51" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B158" s="26" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C158" s="7">
         <v>1</v>
@@ -5220,7 +5311,7 @@
     </row>
     <row r="159" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B159" s="26" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C159" s="7">
         <v>1.5</v>
@@ -5231,7 +5322,7 @@
     </row>
     <row r="160" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B160" s="26" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C160" s="7">
         <v>2</v>
@@ -5242,7 +5333,7 @@
     </row>
     <row r="161" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B161" s="26" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C161" s="7">
         <v>1.2</v>
@@ -5253,7 +5344,7 @@
     </row>
     <row r="162" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B162" s="26" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C162" s="7">
         <v>3</v>
@@ -5264,7 +5355,7 @@
     </row>
     <row r="163" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B163" s="26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C163" s="7">
         <v>2</v>
@@ -5275,7 +5366,7 @@
     </row>
     <row r="164" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B164" s="26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C164" s="7">
         <v>1.2</v>
@@ -5286,7 +5377,7 @@
     </row>
     <row r="165" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B165" s="26" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C165" s="7">
         <v>2</v>
@@ -5297,7 +5388,7 @@
     </row>
     <row r="166" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B166" s="26" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C166" s="7">
         <v>1.8</v>
@@ -5308,7 +5399,7 @@
     </row>
     <row r="167" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B167" s="26" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C167" s="7">
         <v>1.5</v>
@@ -5319,7 +5410,7 @@
     </row>
     <row r="168" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B168" s="26" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C168" s="7">
         <v>1.5</v>
@@ -5330,7 +5421,7 @@
     </row>
     <row r="169" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B169" s="26" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C169" s="7">
         <v>1</v>
@@ -5341,7 +5432,7 @@
     </row>
     <row r="170" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B170" s="26" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C170" s="7">
         <v>2.5</v>
@@ -5352,7 +5443,7 @@
     </row>
     <row r="171" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B171" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C171" s="7">
         <v>1.5</v>
@@ -5363,7 +5454,7 @@
     </row>
     <row r="172" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B172" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C172" s="7">
         <v>1.5</v>
@@ -5374,7 +5465,7 @@
     </row>
     <row r="173" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B173" s="34" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C173" s="7">
         <v>1.5</v>
@@ -5387,61 +5478,61 @@
       <c r="B174" s="26"/>
     </row>
     <row r="175" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A175" s="53" t="s">
-        <v>46</v>
+      <c r="A175" s="52" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B176" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B177" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B178" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B179" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B180" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B181" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B182" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B183" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B184" s="26"/>
     </row>
     <row r="185" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A185" s="66" t="s">
-        <v>48</v>
+      <c r="A185" s="65" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B186" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C186" s="7">
         <v>1.5</v>
@@ -5452,7 +5543,7 @@
     </row>
     <row r="187" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B187" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C187" s="7">
         <v>0.6</v>
@@ -5463,7 +5554,7 @@
     </row>
     <row r="188" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B188" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C188" s="7">
         <v>1.2</v>
@@ -5474,7 +5565,7 @@
     </row>
     <row r="189" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B189" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C189" s="7">
         <v>0.6</v>
@@ -5485,7 +5576,7 @@
     </row>
     <row r="190" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B190" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C190" s="7">
         <v>1.2</v>
@@ -5496,7 +5587,7 @@
     </row>
     <row r="191" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B191" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C191" s="7">
         <v>2</v>
@@ -5507,15 +5598,18 @@
     </row>
     <row r="192" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B192" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C192" s="7">
         <v>1.5</v>
+      </c>
+      <c r="D192" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B193" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C193" s="7">
         <v>1</v>
@@ -5526,7 +5620,7 @@
     </row>
     <row r="194" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B194" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C194" s="7">
         <v>1</v>
@@ -5538,31 +5632,31 @@
     <row r="195" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A195" s="13"/>
       <c r="B195" s="26" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C195" s="13">
         <v>1</v>
       </c>
       <c r="D195" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A196" s="13"/>
       <c r="B196" s="26" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C196" s="13">
         <v>1</v>
       </c>
       <c r="D196" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A197" s="13"/>
       <c r="B197" s="26" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C197" s="13">
         <v>1.2</v>
@@ -5574,7 +5668,7 @@
     <row r="198" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A198" s="13"/>
       <c r="B198" s="26" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C198" s="13">
         <v>1.2</v>
@@ -5586,7 +5680,7 @@
     <row r="199" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A199" s="13"/>
       <c r="B199" s="26" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C199" s="13">
         <v>1</v>
@@ -5598,7 +5692,7 @@
     <row r="200" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A200" s="13"/>
       <c r="B200" s="26" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C200" s="13">
         <v>0.5</v>
@@ -5615,10 +5709,10 @@
     </row>
     <row r="202" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A202" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B202" s="26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C202" s="13">
         <v>1.5</v>
@@ -5630,7 +5724,7 @@
     <row r="203" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="15"/>
       <c r="B203" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C203" s="13">
         <v>1</v>
@@ -5642,7 +5736,7 @@
     <row r="204" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="15"/>
       <c r="B204" s="26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C204" s="13">
         <v>1</v>
@@ -5654,7 +5748,7 @@
     <row r="205" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A205" s="18"/>
       <c r="B205" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C205" s="13">
         <v>1.5</v>
@@ -5666,7 +5760,7 @@
     <row r="206" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="15"/>
       <c r="B206" s="26" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C206" s="13">
         <v>2</v>
@@ -5677,10 +5771,10 @@
     </row>
     <row r="207" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B207" s="26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C207" s="13">
         <v>1.5</v>
@@ -5692,7 +5786,7 @@
     <row r="208" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="15"/>
       <c r="B208" s="26" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C208" s="13">
         <v>1.5</v>
@@ -5704,7 +5798,7 @@
     <row r="209" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="15"/>
       <c r="B209" s="26" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C209" s="13">
         <v>1.5</v>
@@ -5716,7 +5810,7 @@
     <row r="210" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="15"/>
       <c r="B210" s="26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C210" s="13">
         <v>1.5</v>
@@ -5728,7 +5822,7 @@
     <row r="211" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="15"/>
       <c r="B211" s="26" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C211" s="13">
         <v>1</v>
@@ -5740,7 +5834,7 @@
     <row r="212" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="15"/>
       <c r="B212" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C212" s="13">
         <v>2</v>
@@ -5752,7 +5846,7 @@
     <row r="213" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="15"/>
       <c r="B213" s="26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C213" s="13">
         <v>1</v>
@@ -5764,7 +5858,7 @@
     <row r="214" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="15"/>
       <c r="B214" s="26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C214" s="13">
         <v>2.5</v>
@@ -5776,7 +5870,7 @@
     <row r="215" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="18"/>
       <c r="B215" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C215" s="13">
         <v>1.2</v>
@@ -5788,7 +5882,7 @@
     <row r="216" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="18"/>
       <c r="B216" s="26" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C216" s="13">
         <v>0.5</v>
@@ -5800,7 +5894,7 @@
     <row r="217" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="18"/>
       <c r="B217" s="26" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C217" s="13">
         <v>0.5</v>
@@ -5812,7 +5906,7 @@
     <row r="218" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="18"/>
       <c r="B218" s="26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C218" s="13">
         <v>0.5</v>
@@ -5824,7 +5918,7 @@
     <row r="219" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="18"/>
       <c r="B219" s="26" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C219" s="13">
         <v>0.5</v>
@@ -5841,7 +5935,7 @@
     </row>
     <row r="221" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B221" s="26"/>
       <c r="C221" s="13"/>
@@ -5850,7 +5944,7 @@
     <row r="222" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="15"/>
       <c r="B222" s="26" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C222" s="13"/>
       <c r="D222" s="13"/>
@@ -5858,7 +5952,7 @@
     <row r="223" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="15"/>
       <c r="B223" s="26" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C223" s="13">
         <v>1.2</v>
@@ -5870,7 +5964,7 @@
     <row r="224" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="15"/>
       <c r="B224" s="26" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C224" s="13">
         <v>1.2</v>
@@ -5882,7 +5976,7 @@
     <row r="225" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="15"/>
       <c r="B225" s="26" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C225" s="13">
         <v>1</v>
@@ -5894,7 +5988,7 @@
     <row r="226" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="15"/>
       <c r="B226" s="26" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C226" s="13">
         <v>1</v>
@@ -5906,7 +6000,7 @@
     <row r="227" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="15"/>
       <c r="B227" s="26" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C227" s="13">
         <v>0.8</v>
@@ -5918,7 +6012,7 @@
     <row r="228" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="15"/>
       <c r="B228" s="26" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C228" s="13">
         <v>0.5</v>
@@ -5930,7 +6024,7 @@
     <row r="229" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A229" s="7"/>
       <c r="B229" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C229" s="13">
         <v>0.8</v>
@@ -5942,7 +6036,7 @@
     <row r="230" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="15"/>
       <c r="B230" s="26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C230" s="13">
         <v>1.2</v>
@@ -5954,7 +6048,7 @@
     <row r="231" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="15"/>
       <c r="B231" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C231" s="13">
         <v>1</v>
@@ -5966,7 +6060,7 @@
     <row r="232" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="15"/>
       <c r="B232" s="26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C232" s="13">
         <v>0.8</v>
@@ -5978,7 +6072,7 @@
     <row r="233" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="15"/>
       <c r="B233" s="26" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C233" s="13">
         <v>2.5</v>
@@ -5990,7 +6084,7 @@
     <row r="234" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="15"/>
       <c r="B234" s="26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C234" s="13">
         <v>1.5</v>
@@ -6002,7 +6096,7 @@
     <row r="235" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="15"/>
       <c r="B235" s="26" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C235" s="13">
         <v>1.5</v>
@@ -6014,7 +6108,7 @@
     <row r="236" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="18"/>
       <c r="B236" s="29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C236" s="13">
         <v>2</v>
@@ -6026,7 +6120,7 @@
     <row r="237" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="15"/>
       <c r="B237" s="26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C237" s="13">
         <v>1.2</v>
@@ -6038,7 +6132,7 @@
     <row r="238" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="15"/>
       <c r="B238" s="26" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C238" s="13">
         <v>1</v>
@@ -6050,7 +6144,7 @@
     <row r="239" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A239" s="15"/>
       <c r="B239" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C239" s="13">
         <v>2</v>
@@ -6062,7 +6156,7 @@
     <row r="240" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A240" s="15"/>
       <c r="B240" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C240" s="13">
         <v>1</v>
@@ -6074,7 +6168,7 @@
     <row r="241" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A241" s="15"/>
       <c r="B241" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C241" s="13">
         <v>1</v>
@@ -6090,11 +6184,11 @@
       <c r="D242" s="13"/>
     </row>
     <row r="243" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A243" s="55" t="s">
-        <v>318</v>
+      <c r="A243" s="54" t="s">
+        <v>317</v>
       </c>
       <c r="B243" s="26" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C243" s="13">
         <v>1.5</v>
@@ -6106,7 +6200,7 @@
     <row r="244" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A244" s="15"/>
       <c r="B244" s="26" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C244" s="13">
         <v>0.8</v>
@@ -6118,7 +6212,7 @@
     <row r="245" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A245" s="15"/>
       <c r="B245" s="26" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C245" s="13">
         <v>0.6</v>
@@ -6130,7 +6224,7 @@
     <row r="246" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A246" s="15"/>
       <c r="B246" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C246" s="13">
         <v>0.8</v>
@@ -6142,7 +6236,7 @@
     <row r="247" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A247" s="15"/>
       <c r="B247" s="26" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C247" s="13">
         <v>0.8</v>
@@ -6154,7 +6248,7 @@
     <row r="248" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A248" s="15"/>
       <c r="B248" s="26" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C248" s="13">
         <v>1.3</v>
@@ -6166,7 +6260,7 @@
     <row r="249" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A249" s="18"/>
       <c r="B249" s="26" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C249" s="13">
         <v>1</v>
@@ -6178,7 +6272,7 @@
     <row r="250" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="15"/>
       <c r="B250" s="29" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C250" s="13">
         <v>2</v>
@@ -6190,7 +6284,7 @@
     <row r="251" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A251" s="15"/>
       <c r="B251" s="26" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C251" s="13">
         <v>1.4</v>
@@ -6202,7 +6296,7 @@
     <row r="252" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="15"/>
       <c r="B252" s="26" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C252" s="13">
         <v>1.2</v>
@@ -6214,7 +6308,7 @@
     <row r="253" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="15"/>
       <c r="B253" s="26" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C253" s="13">
         <v>2.2000000000000002</v>
@@ -6226,7 +6320,7 @@
     <row r="254" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="15"/>
       <c r="B254" s="26" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C254" s="13">
         <v>0.9</v>
@@ -6238,7 +6332,7 @@
     <row r="255" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A255" s="15"/>
       <c r="B255" s="26" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C255" s="13">
         <v>1.8</v>
@@ -6250,7 +6344,7 @@
     <row r="256" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="15"/>
       <c r="B256" s="26" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C256" s="13">
         <v>1.5</v>
@@ -6262,7 +6356,7 @@
     <row r="257" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="15"/>
       <c r="B257" s="26" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C257" s="13">
         <v>0.8</v>
@@ -6274,7 +6368,7 @@
     <row r="258" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="15"/>
       <c r="B258" s="26" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C258" s="13">
         <v>1.2</v>
@@ -6286,7 +6380,7 @@
     <row r="259" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="15"/>
       <c r="B259" s="26" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C259" s="13">
         <v>2.2000000000000002</v>
@@ -6298,7 +6392,7 @@
     <row r="260" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="15"/>
       <c r="B260" s="26" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C260" s="13">
         <v>1.3</v>
@@ -6310,7 +6404,7 @@
     <row r="261" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A261" s="15"/>
       <c r="B261" s="26" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C261" s="13">
         <v>2.2000000000000002</v>
@@ -6321,10 +6415,10 @@
     </row>
     <row r="262" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A262" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B262" s="26" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C262" s="13">
         <v>0.9</v>
@@ -6336,7 +6430,7 @@
     <row r="263" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A263" s="15"/>
       <c r="B263" s="26" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C263" s="13">
         <v>1</v>
@@ -6348,7 +6442,7 @@
     <row r="264" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A264" s="15"/>
       <c r="B264" s="26" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C264" s="13">
         <v>1.2</v>
@@ -6360,7 +6454,7 @@
     <row r="265" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A265" s="15"/>
       <c r="B265" s="26" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C265" s="13">
         <v>2</v>
@@ -6372,7 +6466,7 @@
     <row r="266" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="15"/>
       <c r="B266" s="26" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C266" s="13">
         <v>2.2000000000000002</v>
@@ -6384,7 +6478,7 @@
     <row r="267" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="15"/>
       <c r="B267" s="26" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C267" s="13">
         <v>1.2</v>
@@ -6396,7 +6490,7 @@
     <row r="268" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A268" s="15"/>
       <c r="B268" s="26" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C268" s="13">
         <v>1</v>
@@ -6408,7 +6502,7 @@
     <row r="269" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="15"/>
       <c r="B269" s="26" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C269" s="13">
         <v>2</v>
@@ -6425,10 +6519,10 @@
     </row>
     <row r="271" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A271" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B271" s="29" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C271" s="13">
         <v>1.5</v>
@@ -6440,7 +6534,7 @@
     <row r="272" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A272" s="15"/>
       <c r="B272" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C272" s="13">
         <v>1.5</v>
@@ -6452,7 +6546,7 @@
     <row r="273" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="15"/>
       <c r="B273" s="26" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C273" s="13">
         <v>2</v>
@@ -6464,7 +6558,7 @@
     <row r="274" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="15"/>
       <c r="B274" s="26" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C274" s="13">
         <v>2</v>
@@ -6476,7 +6570,7 @@
     <row r="275" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="15"/>
       <c r="B275" s="26" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C275" s="13">
         <v>1.5</v>
@@ -6488,7 +6582,7 @@
     <row r="276" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="15"/>
       <c r="B276" s="26" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C276" s="13">
         <v>1</v>
@@ -6500,7 +6594,7 @@
     <row r="277" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="15"/>
       <c r="B277" s="26" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C277" s="13">
         <v>2</v>
@@ -6512,7 +6606,7 @@
     <row r="278" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="15"/>
       <c r="B278" s="26" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C278" s="13">
         <v>1.5</v>
@@ -6523,10 +6617,10 @@
     </row>
     <row r="279" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B279" s="26" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C279" s="13">
         <v>1</v>
@@ -6538,7 +6632,7 @@
     <row r="280" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="15"/>
       <c r="B280" s="26" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C280" s="13">
         <v>1</v>
@@ -6550,7 +6644,7 @@
     <row r="281" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="15"/>
       <c r="B281" s="26" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C281" s="13">
         <v>1.5</v>
@@ -6567,10 +6661,10 @@
     </row>
     <row r="283" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A283" s="27" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B283" s="26" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C283" s="13">
         <v>1.5</v>
@@ -6582,7 +6676,7 @@
     <row r="284" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="15"/>
       <c r="B284" s="26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C284" s="13">
         <v>1</v>
@@ -6594,7 +6688,7 @@
     <row r="285" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="18"/>
       <c r="B285" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C285" s="13">
         <v>1.5</v>
@@ -6606,7 +6700,7 @@
     <row r="286" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="15"/>
       <c r="B286" s="26" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C286" s="13">
         <v>2</v>
@@ -6618,7 +6712,7 @@
     <row r="287" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="15"/>
       <c r="B287" s="26" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C287" s="13">
         <v>1.5</v>
@@ -6630,7 +6724,7 @@
     <row r="288" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="15"/>
       <c r="B288" s="26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C288" s="13">
         <v>2.5</v>
@@ -6642,7 +6736,7 @@
     <row r="289" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="15"/>
       <c r="B289" s="26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C289" s="13">
         <v>2</v>
@@ -6654,7 +6748,7 @@
     <row r="290" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="15"/>
       <c r="B290" s="26" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C290" s="13">
         <v>1</v>
@@ -6666,7 +6760,7 @@
     <row r="291" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="15"/>
       <c r="B291" s="26" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C291" s="13">
         <v>1.2</v>
@@ -6678,7 +6772,7 @@
     <row r="292" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="15"/>
       <c r="B292" s="26" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C292" s="13">
         <v>1</v>
@@ -6690,7 +6784,7 @@
     <row r="293" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="15"/>
       <c r="B293" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C293" s="13">
         <v>0.8</v>
@@ -6702,7 +6796,7 @@
     <row r="294" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="15"/>
       <c r="B294" s="26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C294" s="13">
         <v>0.5</v>
@@ -6719,7 +6813,7 @@
     </row>
     <row r="296" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B296" s="26"/>
       <c r="C296" s="13"/>
@@ -6727,10 +6821,10 @@
     </row>
     <row r="297" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A297" s="27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B297" s="26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C297" s="13">
         <v>2</v>
@@ -6742,7 +6836,7 @@
     <row r="298" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A298" s="18"/>
       <c r="B298" s="29" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C298" s="13">
         <v>2</v>
@@ -6754,7 +6848,7 @@
     <row r="299" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A299" s="15"/>
       <c r="B299" s="26" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C299" s="13">
         <v>2.5</v>
@@ -6766,7 +6860,7 @@
     <row r="300" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A300" s="15"/>
       <c r="B300" s="26" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C300" s="13">
         <v>1.5</v>
@@ -6778,7 +6872,7 @@
     <row r="301" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="15"/>
       <c r="B301" s="26" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C301" s="13">
         <v>2</v>
@@ -6790,7 +6884,7 @@
     <row r="302" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A302" s="15"/>
       <c r="B302" s="26" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C302" s="13">
         <v>1.5</v>
@@ -6802,7 +6896,7 @@
     <row r="303" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="15"/>
       <c r="B303" s="26" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C303" s="13">
         <v>2</v>
@@ -6814,7 +6908,7 @@
     <row r="304" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A304" s="15"/>
       <c r="B304" s="26" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C304" s="13">
         <v>2</v>
@@ -6826,7 +6920,7 @@
     <row r="305" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="15"/>
       <c r="B305" s="26" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C305" s="13">
         <v>2</v>
@@ -6838,7 +6932,7 @@
     <row r="306" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="15"/>
       <c r="B306" s="26" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C306" s="13">
         <v>2</v>
@@ -6850,7 +6944,7 @@
     <row r="307" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="18"/>
       <c r="B307" s="29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C307" s="13">
         <v>1.5</v>
@@ -6862,7 +6956,7 @@
     <row r="308" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="15"/>
       <c r="B308" s="26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C308" s="13">
         <v>1</v>
@@ -6874,7 +6968,7 @@
     <row r="309" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="15"/>
       <c r="B309" s="26" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C309" s="13">
         <v>3</v>
@@ -6886,7 +6980,7 @@
     <row r="310" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="15"/>
       <c r="B310" s="26" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C310" s="13">
         <v>1.5</v>
@@ -6898,7 +6992,7 @@
     <row r="311" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="15"/>
       <c r="B311" s="26" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C311" s="13">
         <v>1.5</v>
@@ -6910,7 +7004,7 @@
     <row r="312" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="15"/>
       <c r="B312" s="26" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C312" s="7">
         <v>2</v>
@@ -6922,7 +7016,7 @@
     <row r="313" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="15"/>
       <c r="B313" s="26" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C313" s="7">
         <v>1</v>
@@ -6934,7 +7028,7 @@
     <row r="314" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="15"/>
       <c r="B314" s="26" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C314" s="7">
         <v>1</v>
@@ -6945,7 +7039,7 @@
     </row>
     <row r="315" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B315" s="26"/>
       <c r="C315" s="13"/>
@@ -6953,10 +7047,10 @@
     </row>
     <row r="316" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A316" s="27" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B316" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C316" s="13">
         <v>0.8</v>
@@ -6968,7 +7062,7 @@
     <row r="317" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="15"/>
       <c r="B317" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C317" s="13">
         <v>2</v>
@@ -6980,7 +7074,7 @@
     <row r="318" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="15"/>
       <c r="B318" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C318" s="13">
         <v>1.2</v>
@@ -6992,7 +7086,7 @@
     <row r="319" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="18"/>
       <c r="B319" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C319" s="13">
         <v>1.5</v>
@@ -7004,7 +7098,7 @@
     <row r="320" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="15"/>
       <c r="B320" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C320" s="13">
         <v>2.5</v>
@@ -7016,7 +7110,7 @@
     <row r="321" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="15"/>
       <c r="B321" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C321" s="13">
         <v>2</v>
@@ -7028,7 +7122,7 @@
     <row r="322" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="15"/>
       <c r="B322" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C322" s="13">
         <v>1.5</v>
@@ -7040,7 +7134,7 @@
     <row r="323" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="15"/>
       <c r="B323" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C323" s="13">
         <v>3</v>
@@ -7052,7 +7146,7 @@
     <row r="324" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="15"/>
       <c r="B324" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C324" s="13">
         <v>1.2</v>
@@ -7064,7 +7158,7 @@
     <row r="325" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="15"/>
       <c r="B325" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C325" s="13">
         <v>1.2</v>
@@ -7076,7 +7170,7 @@
     <row r="326" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="15"/>
       <c r="B326" s="17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C326" s="13">
         <v>1.5</v>
@@ -7088,7 +7182,7 @@
     <row r="327" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A327" s="15"/>
       <c r="B327" s="17" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C327" s="13">
         <v>1</v>
@@ -7099,7 +7193,7 @@
     </row>
     <row r="328" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B328" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C328" s="13">
         <v>1</v>
@@ -7109,24 +7203,24 @@
       </c>
     </row>
     <row r="329" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A329" s="52" t="s">
-        <v>50</v>
+      <c r="A329" s="51" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B330" s="26" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C330" s="7">
         <v>1.2</v>
       </c>
       <c r="D330" s="7">
-        <v>15</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B331" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C331" s="7">
         <v>2</v>
@@ -7137,7 +7231,7 @@
     </row>
     <row r="332" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B332" s="26" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C332" s="7">
         <v>1</v>
@@ -7148,7 +7242,7 @@
     </row>
     <row r="333" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B333" s="26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C333" s="7">
         <v>1.2</v>
@@ -7159,7 +7253,7 @@
     </row>
     <row r="334" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B334" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C334" s="7">
         <v>1</v>
@@ -7170,7 +7264,7 @@
     </row>
     <row r="335" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B335" s="26" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C335" s="7">
         <v>0.8</v>
@@ -7181,7 +7275,7 @@
     </row>
     <row r="336" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B336" s="26" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C336" s="7">
         <v>1.5</v>
@@ -7192,7 +7286,7 @@
     </row>
     <row r="337" spans="1:4" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B337" s="26" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C337" s="7">
         <v>1</v>
@@ -7203,9 +7297,9 @@
     </row>
     <row r="338" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B338" s="34" t="s">
-        <v>503</v>
-      </c>
-      <c r="C338" s="56">
+        <v>502</v>
+      </c>
+      <c r="C338" s="55">
         <v>0.8</v>
       </c>
       <c r="D338" s="7">
@@ -7214,9 +7308,9 @@
     </row>
     <row r="339" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B339" s="34" t="s">
-        <v>504</v>
-      </c>
-      <c r="C339" s="56">
+        <v>503</v>
+      </c>
+      <c r="C339" s="55">
         <v>1</v>
       </c>
       <c r="D339" s="7">
@@ -7224,19 +7318,19 @@
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C340" s="56"/>
-    </row>
-    <row r="341" spans="1:4" ht="19" x14ac:dyDescent="0.2">
-      <c r="A341" s="41" t="s">
-        <v>507</v>
-      </c>
-      <c r="C341" s="56"/>
+      <c r="C340" s="55"/>
+    </row>
+    <row r="341" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A341" s="67" t="s">
+        <v>506</v>
+      </c>
+      <c r="C341" s="55"/>
     </row>
     <row r="342" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B342" s="34" t="s">
-        <v>510</v>
-      </c>
-      <c r="C342" s="56">
+        <v>509</v>
+      </c>
+      <c r="C342" s="55">
         <v>1</v>
       </c>
       <c r="D342" s="7">
@@ -7245,9 +7339,9 @@
     </row>
     <row r="343" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B343" s="34" t="s">
-        <v>511</v>
-      </c>
-      <c r="C343" s="56">
+        <v>510</v>
+      </c>
+      <c r="C343" s="55">
         <v>2.5</v>
       </c>
       <c r="D343" s="7">
@@ -7256,9 +7350,9 @@
     </row>
     <row r="344" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B344" s="34" t="s">
-        <v>512</v>
-      </c>
-      <c r="C344" s="56">
+        <v>511</v>
+      </c>
+      <c r="C344" s="55">
         <v>0.8</v>
       </c>
       <c r="D344" s="7">
@@ -7267,9 +7361,9 @@
     </row>
     <row r="345" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B345" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="C345" s="56">
+        <v>512</v>
+      </c>
+      <c r="C345" s="55">
         <v>0.8</v>
       </c>
       <c r="D345" s="7">
@@ -7278,9 +7372,9 @@
     </row>
     <row r="346" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B346" s="34" t="s">
-        <v>514</v>
-      </c>
-      <c r="C346" s="56">
+        <v>513</v>
+      </c>
+      <c r="C346" s="55">
         <v>1</v>
       </c>
       <c r="D346" s="7">
@@ -7289,12 +7383,12 @@
     </row>
     <row r="347" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A347" s="24" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B347" s="34" t="s">
-        <v>515</v>
-      </c>
-      <c r="C347" s="56">
+        <v>514</v>
+      </c>
+      <c r="C347" s="55">
         <v>0.8</v>
       </c>
       <c r="D347" s="7">
@@ -7303,9 +7397,9 @@
     </row>
     <row r="348" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B348" s="34" t="s">
-        <v>516</v>
-      </c>
-      <c r="C348" s="56">
+        <v>515</v>
+      </c>
+      <c r="C348" s="55">
         <v>0.8</v>
       </c>
       <c r="D348" s="7">
@@ -7314,9 +7408,9 @@
     </row>
     <row r="349" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B349" s="34" t="s">
-        <v>517</v>
-      </c>
-      <c r="C349" s="56">
+        <v>516</v>
+      </c>
+      <c r="C349" s="55">
         <v>0.5</v>
       </c>
       <c r="D349" s="7">
@@ -7325,9 +7419,9 @@
     </row>
     <row r="350" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B350" s="34" t="s">
-        <v>518</v>
-      </c>
-      <c r="C350" s="56">
+        <v>517</v>
+      </c>
+      <c r="C350" s="55">
         <v>1.8</v>
       </c>
       <c r="D350" s="7">
@@ -7336,9 +7430,9 @@
     </row>
     <row r="351" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B351" s="34" t="s">
-        <v>519</v>
-      </c>
-      <c r="C351" s="56">
+        <v>518</v>
+      </c>
+      <c r="C351" s="55">
         <v>1</v>
       </c>
       <c r="D351" s="7">
@@ -7347,9 +7441,9 @@
     </row>
     <row r="352" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B352" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="C352" s="56">
+        <v>519</v>
+      </c>
+      <c r="C352" s="55">
         <v>1</v>
       </c>
       <c r="D352" s="7">
@@ -7358,9 +7452,9 @@
     </row>
     <row r="353" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B353" s="26" t="s">
-        <v>521</v>
-      </c>
-      <c r="C353" s="56">
+        <v>520</v>
+      </c>
+      <c r="C353" s="55">
         <v>1</v>
       </c>
       <c r="D353" s="7">
@@ -7371,64 +7465,43 @@
       <c r="B354" s="26"/>
     </row>
     <row r="355" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A355" s="67" t="s">
-        <v>51</v>
+      <c r="A355" s="66" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B356" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="C356" s="7">
-        <v>1.2</v>
+        <v>221</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B357" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="C357" s="7">
-        <v>1</v>
+        <v>222</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B358" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="C358" s="7">
-        <v>1.2</v>
+        <v>223</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B359" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="C359" s="7">
-        <v>1.5</v>
+        <v>224</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B360" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C360" s="7">
-        <v>1.5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B361" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="C361" s="7">
-        <v>1</v>
+        <v>226</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B362" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="C362" s="7">
-        <v>1</v>
+        <v>227</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
@@ -7436,10 +7509,10 @@
     </row>
     <row r="364" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="27" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B364" s="26" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C364" s="13">
         <v>1.5</v>
@@ -7450,7 +7523,7 @@
     </row>
     <row r="365" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B365" s="26" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C365" s="13">
         <v>1.5</v>
@@ -7462,7 +7535,7 @@
     <row r="366" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="15"/>
       <c r="B366" s="26" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C366" s="13">
         <v>1.5</v>
@@ -7474,7 +7547,7 @@
     <row r="367" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="15"/>
       <c r="B367" s="26" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C367" s="13">
         <v>2</v>
@@ -7486,7 +7559,7 @@
     <row r="368" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="15"/>
       <c r="B368" s="26" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C368" s="13">
         <v>1.5</v>
@@ -7498,7 +7571,7 @@
     <row r="369" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="15"/>
       <c r="B369" s="26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C369" s="13">
         <v>1.2</v>
@@ -7510,7 +7583,7 @@
     <row r="370" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="15"/>
       <c r="B370" s="26" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C370" s="13">
         <v>1</v>
@@ -7522,7 +7595,7 @@
     <row r="371" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A371" s="15"/>
       <c r="B371" s="26" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C371" s="13">
         <v>1.5</v>
@@ -7534,7 +7607,7 @@
     <row r="372" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="15"/>
       <c r="B372" s="26" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C372" s="13">
         <v>2</v>
@@ -7546,7 +7619,7 @@
     <row r="373" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="15"/>
       <c r="B373" s="26" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C373" s="13">
         <v>1</v>
@@ -7558,7 +7631,7 @@
     <row r="374" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="15"/>
       <c r="B374" s="26" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C374" s="7">
         <v>1.5</v>
@@ -7570,7 +7643,7 @@
     <row r="375" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="15"/>
       <c r="B375" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C375" s="7">
         <v>1</v>
@@ -7582,7 +7655,7 @@
     <row r="376" spans="1:4" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="15"/>
       <c r="B376" s="26" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C376" s="7">
         <v>1</v>
@@ -7596,456 +7669,306 @@
       <c r="B377" s="26"/>
     </row>
     <row r="378" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A378" s="53" t="s">
-        <v>54</v>
+      <c r="A378" s="52" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B379" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="C379" s="7">
-        <v>1</v>
+        <v>228</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B380" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="C380" s="7">
-        <v>1.5</v>
+        <v>229</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B381" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="C381" s="7">
-        <v>1.5</v>
+        <v>230</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B382" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="C382" s="7">
-        <v>2</v>
+        <v>231</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B383" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="C383" s="7">
-        <v>1.5</v>
+        <v>232</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B384" s="26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B385" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="C384" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="385" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B385" s="26" t="s">
+    </row>
+    <row r="386" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B386" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="C385" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B386" s="26" t="s">
+    </row>
+    <row r="387" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B387" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C386" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B387" s="26" t="s">
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B388" s="26"/>
+    </row>
+    <row r="389" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A389" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B390" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="C387" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B388" s="26"/>
-    </row>
-    <row r="389" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A389" s="33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B390" s="26" t="s">
+    </row>
+    <row r="391" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B391" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="C390" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B391" s="26" t="s">
+    </row>
+    <row r="392" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B392" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C391" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B392" s="26" t="s">
+    </row>
+    <row r="393" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B393" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C392" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B393" s="26" t="s">
+    </row>
+    <row r="394" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B394" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="C393" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B394" s="26" t="s">
+    </row>
+    <row r="395" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B395" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C394" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B395" s="26" t="s">
+    </row>
+    <row r="396" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B396" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="C395" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B396" s="26" t="s">
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B397" s="26"/>
+    </row>
+    <row r="398" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A398" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B399" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="C396" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B397" s="26"/>
-    </row>
-    <row r="398" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A398" s="33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B399" s="26" t="s">
+    </row>
+    <row r="400" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B400" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="C399" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B400" s="26" t="s">
+    </row>
+    <row r="401" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B401" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="C400" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B401" s="26" t="s">
+    </row>
+    <row r="402" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B402" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C401" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B402" s="26" t="s">
+    </row>
+    <row r="403" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B403" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="C402" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B403" s="26" t="s">
+    </row>
+    <row r="404" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B404" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="C403" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B404" s="26" t="s">
+    </row>
+    <row r="405" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B405" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="C404" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B405" s="26" t="s">
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B406" s="26"/>
+    </row>
+    <row r="407" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A407" s="33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B408" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C405" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B406" s="26"/>
-    </row>
-    <row r="407" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A407" s="33" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B408" s="26" t="s">
+    </row>
+    <row r="409" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B409" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="C408" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B409" s="26" t="s">
+    </row>
+    <row r="410" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B410" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="C409" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B410" s="26" t="s">
+    </row>
+    <row r="411" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B411" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="C410" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B411" s="26" t="s">
+    </row>
+    <row r="412" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B412" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="C411" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B412" s="26" t="s">
+    </row>
+    <row r="413" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B413" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="C412" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B413" s="26" t="s">
+    </row>
+    <row r="414" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B414" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="C413" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B414" s="26" t="s">
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B415" s="26"/>
+    </row>
+    <row r="416" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A416" s="33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B417" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C414" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B415" s="26"/>
-    </row>
-    <row r="416" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A416" s="33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B417" s="26" t="s">
+    </row>
+    <row r="418" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B418" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="C417" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B418" s="26" t="s">
+    </row>
+    <row r="419" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B419" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="C418" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B419" s="26" t="s">
+    </row>
+    <row r="420" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B420" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="C419" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B420" s="26" t="s">
+    </row>
+    <row r="421" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B421" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="C420" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B421" s="26" t="s">
+    </row>
+    <row r="422" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B422" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="C421" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B422" s="26" t="s">
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B423" s="26"/>
+    </row>
+    <row r="424" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A424" s="33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B425" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="C422" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B423" s="26"/>
-    </row>
-    <row r="424" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A424" s="33" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B425" s="26" t="s">
+    </row>
+    <row r="426" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B426" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="C425" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B426" s="26" t="s">
+    </row>
+    <row r="427" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B427" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="C426" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B427" s="26" t="s">
+    </row>
+    <row r="428" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B428" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="C427" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B428" s="26" t="s">
+    </row>
+    <row r="429" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B429" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="C428" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B429" s="26" t="s">
+    </row>
+    <row r="430" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B430" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="C429" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B430" s="26" t="s">
+    </row>
+    <row r="431" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B431" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="C430" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B431" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="C431" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B432" s="26"/>
     </row>
     <row r="433" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A433" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B434" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="C434" s="7">
-        <v>1.2</v>
+        <v>271</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B435" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="C435" s="7">
-        <v>1</v>
+        <v>272</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B436" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="C436" s="7">
-        <v>1</v>
+        <v>273</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B437" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="C437" s="7">
-        <v>1.2</v>
+        <v>274</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B438" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="C438" s="7">
-        <v>1.5</v>
+        <v>275</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B439" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="C439" s="7">
-        <v>1</v>
+        <v>276</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B440" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="C440" s="7">
-        <v>1</v>
+        <v>277</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.2">
@@ -8053,47 +7976,32 @@
     </row>
     <row r="442" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A442" s="33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B443" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="C443" s="7">
-        <v>1.2</v>
+        <v>278</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B444" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="C444" s="7">
-        <v>1.2</v>
+        <v>279</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B445" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="C445" s="7">
-        <v>1.5</v>
+        <v>280</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B446" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="C446" s="7">
-        <v>0.8</v>
+        <v>281</v>
       </c>
     </row>
     <row r="447" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B447" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="C447" s="7">
-        <v>1</v>
+        <v>282</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.2">
@@ -8102,10 +8010,10 @@
     </row>
     <row r="449" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A449" s="27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B449" s="29" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C449" s="13">
         <v>1.2</v>
@@ -8117,7 +8025,7 @@
     <row r="450" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A450" s="15"/>
       <c r="B450" s="29" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C450" s="13">
         <v>1.2</v>
@@ -8129,7 +8037,7 @@
     <row r="451" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A451" s="15"/>
       <c r="B451" s="29" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C451" s="13">
         <v>0.8</v>
@@ -8141,7 +8049,7 @@
     <row r="452" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A452" s="15"/>
       <c r="B452" s="29" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C452" s="13">
         <v>1</v>
@@ -8153,7 +8061,7 @@
     <row r="453" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A453" s="15"/>
       <c r="B453" s="29" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C453" s="13">
         <v>2</v>
@@ -8165,7 +8073,7 @@
     <row r="454" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A454" s="15"/>
       <c r="B454" s="29" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C454" s="13">
         <v>1.2</v>
@@ -8177,7 +8085,7 @@
     <row r="455" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A455" s="15"/>
       <c r="B455" s="29" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C455" s="13">
         <v>1</v>
@@ -8189,7 +8097,7 @@
     <row r="456" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A456" s="15"/>
       <c r="B456" s="29" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C456" s="13">
         <v>2</v>
@@ -8201,7 +8109,7 @@
     <row r="457" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A457" s="15"/>
       <c r="B457" s="29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C457" s="13">
         <v>2</v>
@@ -8213,7 +8121,7 @@
     <row r="458" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A458" s="15"/>
       <c r="B458" s="29" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C458" s="13">
         <v>1.5</v>
@@ -8225,7 +8133,7 @@
     <row r="459" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A459" s="15"/>
       <c r="B459" s="29" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C459" s="13">
         <v>2.5</v>
@@ -8237,7 +8145,7 @@
     <row r="460" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A460" s="15"/>
       <c r="B460" s="34" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C460" s="7">
         <v>1.5</v>
@@ -8249,7 +8157,7 @@
     <row r="461" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A461" s="15"/>
       <c r="B461" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C461" s="7">
         <v>1.5</v>
@@ -8261,7 +8169,7 @@
     <row r="462" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A462" s="15"/>
       <c r="B462" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C462" s="7">
         <v>1</v>
@@ -8272,7 +8180,7 @@
     </row>
     <row r="463" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B463" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C463" s="7">
         <v>1</v>
@@ -8282,13 +8190,13 @@
       </c>
     </row>
     <row r="464" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A464" s="52" t="s">
-        <v>79</v>
+      <c r="A464" s="51" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="465" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B465" s="26" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C465" s="7">
         <v>1.5</v>
@@ -8299,7 +8207,7 @@
     </row>
     <row r="466" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B466" s="26" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C466" s="7">
         <v>2</v>
@@ -8310,10 +8218,10 @@
     </row>
     <row r="467" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A467" s="24" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B467" s="26" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C467" s="7">
         <v>2</v>
@@ -8324,7 +8232,7 @@
     </row>
     <row r="468" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B468" s="26" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C468">
         <v>2.5</v>
@@ -8335,7 +8243,7 @@
     </row>
     <row r="469" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B469" s="26" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C469">
         <v>2</v>
@@ -8346,7 +8254,7 @@
     </row>
     <row r="470" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B470" s="26" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C470">
         <v>1.8</v>
@@ -8357,7 +8265,7 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B471" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C471">
         <v>2</v>
@@ -8368,7 +8276,7 @@
     </row>
     <row r="472" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B472" s="26" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C472" s="7">
         <v>2</v>
@@ -8379,7 +8287,7 @@
     </row>
     <row r="473" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B473" s="26" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C473" s="7">
         <v>1.8</v>
@@ -8390,7 +8298,7 @@
     </row>
     <row r="474" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B474" s="26" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C474" s="7">
         <v>2.5</v>
@@ -8401,7 +8309,7 @@
     </row>
     <row r="475" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B475" s="26" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C475" s="7">
         <v>2</v>
@@ -8412,7 +8320,7 @@
     </row>
     <row r="476" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B476" s="26" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C476" s="7">
         <v>2.5</v>
@@ -8423,7 +8331,7 @@
     </row>
     <row r="477" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B477" s="26" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C477" s="7">
         <v>1.5</v>
@@ -8433,64 +8341,43 @@
       </c>
     </row>
     <row r="479" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A479" s="67" t="s">
-        <v>81</v>
+      <c r="A479" s="66" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="480" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B480" s="26" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="481" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B481" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="C480" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="481" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B481" s="26" t="s">
+    </row>
+    <row r="482" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B482" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="C481" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="482" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B482" s="26" t="s">
+    </row>
+    <row r="483" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B483" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="C482" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="483" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B483" s="26" t="s">
+    </row>
+    <row r="484" spans="2:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B484" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="C483" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="484" spans="2:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B484" s="26" t="s">
+    </row>
+    <row r="485" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B485" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="C484" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="485" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B485" s="26" t="s">
+    </row>
+    <row r="486" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B486" s="26" t="s">
         <v>289</v>
-      </c>
-      <c r="C485" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="486" spans="2:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="B486" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="C486" s="7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
